--- a/Financial Analysis/CHGG.xlsx
+++ b/Financial Analysis/CHGG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1DFEB5-C821-4DC3-918C-DE310DB8037A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BBB3A0-CD4A-43EE-9FC0-7EE89DCA8577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
-    <comment ref="P9" authorId="0" shapeId="0" xr:uid="{94656086-D00F-4C13-943D-0312225931CA}">
+    <comment ref="P10" authorId="0" shapeId="0" xr:uid="{94656086-D00F-4C13-943D-0312225931CA}">
       <text>
         <r>
           <rPr>
@@ -55,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q9" authorId="0" shapeId="0" xr:uid="{6D8908CC-E2E9-49FD-90B4-3B619850FED4}">
+    <comment ref="Q10" authorId="0" shapeId="0" xr:uid="{6D8908CC-E2E9-49FD-90B4-3B619850FED4}">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P14" authorId="0" shapeId="0" xr:uid="{401EA79A-C515-4B57-A3D0-FCC5282EF222}">
+    <comment ref="P15" authorId="0" shapeId="0" xr:uid="{401EA79A-C515-4B57-A3D0-FCC5282EF222}">
       <text>
         <r>
           <rPr>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
   <si>
     <t>CHGG</t>
   </si>
@@ -383,7 +383,7 @@
     <t>Language learning</t>
   </si>
   <si>
-    <t>Slightly undervalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -504,7 +504,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -554,7 +554,7 @@
     <xdr:to>
       <xdr:col>30</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>62</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -919,17 +919,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>0.56620000000000004</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E3" s="5">
-        <v>45751</v>
+        <v>45799</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45799</v>
       </c>
       <c r="G3" s="5">
-        <v>45802</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -937,11 +937,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>105.1</f>
-        <v>105.1</v>
+        <v>106.6</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -950,7 +949,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>59.507620000000003</v>
+        <v>104.47865999999999</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -958,11 +957,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>161.5+154.2+212.7</f>
-        <v>528.4</v>
+        <f>44.1+44.2+38.1</f>
+        <v>126.4</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -970,11 +969,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>127.3</f>
-        <v>127.3</v>
+        <f>62.5</f>
+        <v>62.5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="J7" t="s">
         <v>87</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>401.09999999999997</v>
+        <v>63.900000000000006</v>
       </c>
       <c r="J8" t="s">
         <v>89</v>
@@ -1004,7 +1003,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>-341.59237999999993</v>
+        <v>40.578659999999985</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB0C3E2D-253D-46B0-9AD3-C7A573AF3AFF}">
-  <dimension ref="B1:ET63"/>
+  <dimension ref="B1:ET64"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -1196,19 +1195,19 @@
         <v>143.5</v>
       </c>
       <c r="S3" s="8">
-        <v>115</v>
+        <v>121.4</v>
       </c>
       <c r="T3" s="8">
-        <f>P3*0.75</f>
-        <v>122.32499999999999</v>
+        <f>P3*0.8</f>
+        <v>130.47999999999999</v>
       </c>
       <c r="U3" s="8">
         <f t="shared" ref="U3" si="0">Q3*0.75</f>
         <v>102.44999999999999</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*0.85</f>
-        <v>121.97499999999999</v>
+        <f>R3*0.95</f>
+        <v>136.32499999999999</v>
       </c>
       <c r="X3" s="8">
         <v>321.10000000000002</v>
@@ -1237,47 +1236,47 @@
       </c>
       <c r="AE3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>461.75</v>
+        <v>490.65499999999997</v>
       </c>
       <c r="AF3" s="8">
         <f>AE3*0.98</f>
-        <v>452.51499999999999</v>
+        <v>480.84189999999995</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.1</f>
-        <v>497.76650000000001</v>
+        <v>528.92609000000004</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.07</f>
-        <v>532.61015500000008</v>
+        <v>565.95091630000013</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.05</f>
-        <v>559.24066275000007</v>
+        <v>594.24846211500017</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.04</f>
-        <v>581.61028926000006</v>
+        <v>618.01840059960023</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.03</f>
-        <v>599.05859793780007</v>
+        <v>636.55895261758826</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" ref="AL3:AO3" si="1">AK3*1.03</f>
-        <v>617.03035587593411</v>
+        <v>655.65572119611591</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="1"/>
-        <v>635.54126655221216</v>
+        <v>675.32539283199935</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="1"/>
-        <v>654.60750454877859</v>
+        <v>695.58515461695936</v>
       </c>
       <c r="AO3" s="8">
         <f t="shared" si="1"/>
-        <v>674.24572968524194</v>
+        <v>716.45270925546811</v>
       </c>
     </row>
     <row r="4" spans="2:145" x14ac:dyDescent="0.3">
@@ -1333,12 +1332,11 @@
         <v>45.6</v>
       </c>
       <c r="S4" s="2">
-        <f>S3-S5</f>
-        <v>37.949999999999989</v>
+        <v>54</v>
       </c>
       <c r="T4" s="2">
         <f t="shared" ref="T4:V4" si="2">T3-T5</f>
-        <v>39.143999999999991</v>
+        <v>41.753599999999992</v>
       </c>
       <c r="U4" s="2">
         <f t="shared" si="2"/>
@@ -1346,7 +1344,7 @@
       </c>
       <c r="V4" s="2">
         <f t="shared" si="2"/>
-        <v>39.031999999999996</v>
+        <v>43.623999999999995</v>
       </c>
       <c r="X4" s="2">
         <v>80</v>
@@ -1375,47 +1373,47 @@
       </c>
       <c r="AE4" s="2">
         <f>SUM(S4:V4)</f>
-        <v>148.90999999999997</v>
+        <v>172.16159999999999</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" ref="AF4:AO4" si="3">AF3-AF5</f>
-        <v>140.27965</v>
+        <v>149.06098900000001</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="3"/>
-        <v>149.32995</v>
+        <v>158.67782700000004</v>
       </c>
       <c r="AH4" s="2">
         <f t="shared" si="3"/>
-        <v>159.78304650000007</v>
+        <v>169.78527489000004</v>
       </c>
       <c r="AI4" s="2">
         <f t="shared" si="3"/>
-        <v>167.77219882500003</v>
+        <v>178.27453863450006</v>
       </c>
       <c r="AJ4" s="2">
         <f t="shared" si="3"/>
-        <v>174.48308677800003</v>
+        <v>185.40552017988011</v>
       </c>
       <c r="AK4" s="2">
         <f t="shared" si="3"/>
-        <v>179.71757938134004</v>
+        <v>190.9676857852765</v>
       </c>
       <c r="AL4" s="2">
         <f t="shared" si="3"/>
-        <v>185.10910676278024</v>
+        <v>196.69671635883481</v>
       </c>
       <c r="AM4" s="2">
         <f t="shared" si="3"/>
-        <v>190.66237996566366</v>
+        <v>202.59761784959983</v>
       </c>
       <c r="AN4" s="2">
         <f t="shared" si="3"/>
-        <v>196.38225136463359</v>
+        <v>208.67554638508784</v>
       </c>
       <c r="AO4" s="2">
         <f t="shared" si="3"/>
-        <v>202.27371890557259</v>
+        <v>214.93581277664049</v>
       </c>
     </row>
     <row r="5" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1423,7 +1421,7 @@
         <v>14</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:R5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:S5" si="4">C3-C4</f>
         <v>127</v>
       </c>
       <c r="D5" s="8">
@@ -1487,12 +1485,12 @@
         <v>97.9</v>
       </c>
       <c r="S5" s="8">
-        <f>S3*0.67</f>
-        <v>77.050000000000011</v>
+        <f t="shared" si="4"/>
+        <v>67.400000000000006</v>
       </c>
       <c r="T5" s="8">
         <f>T3*0.68</f>
-        <v>83.180999999999997</v>
+        <v>88.726399999999998</v>
       </c>
       <c r="U5" s="8">
         <f>U3*0.68</f>
@@ -1500,7 +1498,7 @@
       </c>
       <c r="V5" s="8">
         <f>V3*0.68</f>
-        <v>82.942999999999998</v>
+        <v>92.700999999999993</v>
       </c>
       <c r="X5" s="8">
         <f t="shared" ref="X5:AE5" si="5">X3-X4</f>
@@ -1532,47 +1530,47 @@
       </c>
       <c r="AE5" s="8">
         <f t="shared" si="5"/>
-        <v>312.84000000000003</v>
+        <v>318.49339999999995</v>
       </c>
       <c r="AF5" s="8">
         <f>AF3*0.69</f>
-        <v>312.23534999999998</v>
+        <v>331.78091099999995</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" ref="AG5:AO5" si="6">AG3*0.7</f>
-        <v>348.43655000000001</v>
+        <v>370.24826300000001</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="6"/>
-        <v>372.82710850000001</v>
+        <v>396.16564141000009</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="6"/>
-        <v>391.46846392500004</v>
+        <v>415.9739234805001</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="6"/>
-        <v>407.12720248200003</v>
+        <v>432.61288041972011</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="6"/>
-        <v>419.34101855646003</v>
+        <v>445.59126683231176</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="6"/>
-        <v>431.92124911315386</v>
+        <v>458.9590048372811</v>
       </c>
       <c r="AM5" s="8">
         <f t="shared" si="6"/>
-        <v>444.8788865865485</v>
+        <v>472.72777498239952</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" si="6"/>
-        <v>458.225253184145</v>
+        <v>486.90960823187152</v>
       </c>
       <c r="AO5" s="8">
         <f t="shared" si="6"/>
-        <v>471.97201077966935</v>
+        <v>501.51689647882762</v>
       </c>
     </row>
     <row r="6" spans="2:145" x14ac:dyDescent="0.3">
@@ -1628,8 +1626,7 @@
         <v>41</v>
       </c>
       <c r="S6" s="2">
-        <f>O6*0.9</f>
-        <v>39.96</v>
+        <v>29.4</v>
       </c>
       <c r="T6" s="2">
         <f t="shared" ref="T6:V6" si="7">P6*0.9</f>
@@ -1670,47 +1667,47 @@
       </c>
       <c r="AE6" s="2">
         <f>SUM(S6:V6)</f>
-        <v>153.36000000000001</v>
+        <v>142.80000000000001</v>
       </c>
       <c r="AF6" s="2">
         <f>AE6*1.02</f>
-        <v>156.42720000000003</v>
+        <v>145.65600000000001</v>
       </c>
       <c r="AG6" s="2">
         <f t="shared" ref="AG6:AJ6" si="8">AF6*1.02</f>
-        <v>159.55574400000003</v>
+        <v>148.56912</v>
       </c>
       <c r="AH6" s="2">
         <f t="shared" si="8"/>
-        <v>162.74685888000005</v>
+        <v>151.54050240000001</v>
       </c>
       <c r="AI6" s="2">
         <f t="shared" si="8"/>
-        <v>166.00179605760005</v>
+        <v>154.57131244800001</v>
       </c>
       <c r="AJ6" s="2">
         <f t="shared" si="8"/>
-        <v>169.32183197875204</v>
+        <v>157.66273869696002</v>
       </c>
       <c r="AK6" s="2">
         <f>AJ6*1.01</f>
-        <v>171.01505029853956</v>
+        <v>159.23936608392961</v>
       </c>
       <c r="AL6" s="2">
         <f t="shared" ref="AL6:AO6" si="9">AK6*1.01</f>
-        <v>172.72520080152495</v>
+        <v>160.8317597447689</v>
       </c>
       <c r="AM6" s="2">
         <f t="shared" si="9"/>
-        <v>174.4524528095402</v>
+        <v>162.4400773422166</v>
       </c>
       <c r="AN6" s="2">
         <f t="shared" si="9"/>
-        <v>176.19697733763562</v>
+        <v>164.06447811563876</v>
       </c>
       <c r="AO6" s="2">
         <f t="shared" si="9"/>
-        <v>177.95894711101198</v>
+        <v>165.70512289679516</v>
       </c>
     </row>
     <row r="7" spans="2:145" x14ac:dyDescent="0.3">
@@ -1766,12 +1763,11 @@
         <v>27.9</v>
       </c>
       <c r="S7" s="2">
-        <f>S3*0.17</f>
-        <v>19.55</v>
+        <v>25.6</v>
       </c>
       <c r="T7" s="2">
         <f t="shared" ref="T7" si="10">T3*0.17</f>
-        <v>20.795249999999999</v>
+        <v>22.1816</v>
       </c>
       <c r="U7" s="2">
         <f>U3*0.2</f>
@@ -1779,7 +1775,7 @@
       </c>
       <c r="V7" s="2">
         <f>V3*0.2</f>
-        <v>24.395</v>
+        <v>27.265000000000001</v>
       </c>
       <c r="X7" s="2">
         <v>54.7</v>
@@ -1808,47 +1804,47 @@
       </c>
       <c r="AE7" s="2">
         <f>SUM(S7:V7)</f>
-        <v>85.230249999999998</v>
+        <v>95.536599999999993</v>
       </c>
       <c r="AF7" s="2">
         <f>AF3*0.17</f>
-        <v>76.927549999999997</v>
+        <v>81.743122999999997</v>
       </c>
       <c r="AG7" s="2">
         <f>AG3*0.16</f>
-        <v>79.64264</v>
+        <v>84.628174400000006</v>
       </c>
       <c r="AH7" s="2">
         <f t="shared" ref="AH7:AO7" si="11">AH3*0.15</f>
-        <v>79.891523250000006</v>
+        <v>84.89263744500002</v>
       </c>
       <c r="AI7" s="2">
         <f t="shared" si="11"/>
-        <v>83.886099412500002</v>
+        <v>89.137269317250016</v>
       </c>
       <c r="AJ7" s="2">
         <f t="shared" si="11"/>
-        <v>87.241543389</v>
+        <v>92.702760089940028</v>
       </c>
       <c r="AK7" s="2">
         <f t="shared" si="11"/>
-        <v>89.858789690670008</v>
+        <v>95.483842892638236</v>
       </c>
       <c r="AL7" s="2">
         <f t="shared" si="11"/>
-        <v>92.554553381390107</v>
+        <v>98.348358179417389</v>
       </c>
       <c r="AM7" s="2">
         <f t="shared" si="11"/>
-        <v>95.331189982831816</v>
+        <v>101.2988089247999</v>
       </c>
       <c r="AN7" s="2">
         <f t="shared" si="11"/>
-        <v>98.19112568231678</v>
+        <v>104.33777319254391</v>
       </c>
       <c r="AO7" s="2">
         <f t="shared" si="11"/>
-        <v>101.13685945278628</v>
+        <v>107.46790638832022</v>
       </c>
     </row>
     <row r="8" spans="2:145" x14ac:dyDescent="0.3">
@@ -1904,8 +1900,7 @@
         <v>56.3</v>
       </c>
       <c r="S8" s="2">
-        <f>O8*1.02</f>
-        <v>56.61</v>
+        <v>39.4</v>
       </c>
       <c r="T8" s="2">
         <f t="shared" ref="T8:V8" si="12">P8*1.02</f>
@@ -1946,3284 +1941,3284 @@
       </c>
       <c r="AE8" s="2">
         <f>SUM(S8:V8)</f>
-        <v>222.05399999999997</v>
+        <v>204.84399999999999</v>
       </c>
       <c r="AF8" s="2">
         <f>AE8*1.02</f>
-        <v>226.49507999999997</v>
+        <v>208.94087999999999</v>
       </c>
       <c r="AG8" s="2">
         <f t="shared" ref="AG8:AO8" si="13">AF8*1.02</f>
-        <v>231.02498159999999</v>
+        <v>213.11969759999999</v>
       </c>
       <c r="AH8" s="2">
         <f t="shared" si="13"/>
-        <v>235.64548123199998</v>
+        <v>217.38209155199999</v>
       </c>
       <c r="AI8" s="2">
         <f t="shared" si="13"/>
-        <v>240.35839085663997</v>
+        <v>221.72973338303999</v>
       </c>
       <c r="AJ8" s="2">
         <f t="shared" si="13"/>
-        <v>245.16555867377278</v>
+        <v>226.16432805070079</v>
       </c>
       <c r="AK8" s="2">
         <f t="shared" si="13"/>
-        <v>250.06886984724824</v>
+        <v>230.68761461171482</v>
       </c>
       <c r="AL8" s="2">
         <f t="shared" si="13"/>
-        <v>255.07024724419321</v>
+        <v>235.30136690394912</v>
       </c>
       <c r="AM8" s="2">
         <f t="shared" si="13"/>
-        <v>260.17165218907707</v>
+        <v>240.00739424202811</v>
       </c>
       <c r="AN8" s="2">
         <f t="shared" si="13"/>
-        <v>265.37508523285862</v>
+        <v>244.80754212686867</v>
       </c>
       <c r="AO8" s="2">
         <f t="shared" si="13"/>
-        <v>270.68258693751579</v>
+        <v>249.70369296940603</v>
       </c>
     </row>
     <row r="9" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2">
+        <v>2</v>
+      </c>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2">
+        <f>SUM(S9:V9)</f>
+        <v>2</v>
+      </c>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+      <c r="AH9" s="2"/>
+      <c r="AI9" s="2"/>
+      <c r="AJ9" s="2"/>
+      <c r="AK9" s="2"/>
+      <c r="AL9" s="2"/>
+      <c r="AM9" s="2"/>
+      <c r="AN9" s="2"/>
+      <c r="AO9" s="2"/>
+    </row>
+    <row r="10" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="2">
-        <f t="shared" ref="C9:P9" si="14">SUM(C6:C8)</f>
+      <c r="C10" s="2">
+        <f t="shared" ref="C10:P10" si="14">SUM(C6:C8)</f>
         <v>110.19999999999999</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D10" s="2">
         <f t="shared" si="14"/>
         <v>103</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E10" s="2">
         <f t="shared" si="14"/>
         <v>104.5</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F10" s="2">
         <f t="shared" si="14"/>
         <v>125.6</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G10" s="2">
         <f t="shared" si="14"/>
         <v>141.80000000000001</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H10" s="2">
         <f t="shared" si="14"/>
         <v>141.69999999999999</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I10" s="2">
         <f t="shared" si="14"/>
         <v>130.9</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J10" s="2">
         <f t="shared" si="14"/>
         <v>146.10000000000002</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K10" s="2">
         <f t="shared" si="14"/>
         <v>142.9</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L10" s="2">
         <f t="shared" si="14"/>
         <v>154.19999999999999</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M10" s="2">
         <f t="shared" si="14"/>
         <v>132.19999999999999</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N10" s="2">
         <f t="shared" si="14"/>
         <v>128.80000000000001</v>
       </c>
-      <c r="O9" s="2">
+      <c r="O10" s="2">
         <f t="shared" si="14"/>
         <v>130.30000000000001</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P10" s="2">
         <f t="shared" si="14"/>
         <v>121.2</v>
       </c>
-      <c r="Q9" s="2">
-        <f t="shared" ref="Q9:R9" si="15">SUM(Q6:Q8)</f>
+      <c r="Q10" s="2">
+        <f t="shared" ref="Q10:R10" si="15">SUM(Q6:Q8)</f>
         <v>119.69999999999999</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R10" s="2">
         <f t="shared" si="15"/>
         <v>125.2</v>
       </c>
-      <c r="S9" s="2">
-        <f t="shared" ref="S9:V9" si="16">SUM(S6:S8)</f>
-        <v>116.12</v>
-      </c>
-      <c r="T9" s="2">
-        <f t="shared" si="16"/>
-        <v>115.20525000000001</v>
-      </c>
-      <c r="U9" s="2">
+      <c r="S10" s="2">
+        <f>SUM(S6:S9)</f>
+        <v>96.4</v>
+      </c>
+      <c r="T10" s="2">
+        <f t="shared" ref="T10:V10" si="16">SUM(T6:T9)</f>
+        <v>116.5916</v>
+      </c>
+      <c r="U10" s="2">
         <f t="shared" si="16"/>
         <v>110.598</v>
       </c>
-      <c r="V9" s="2">
+      <c r="V10" s="2">
         <f t="shared" si="16"/>
-        <v>118.721</v>
-      </c>
-      <c r="X9" s="2">
-        <f t="shared" ref="X9:AD9" si="17">SUM(X6:X8)</f>
+        <v>121.59099999999998</v>
+      </c>
+      <c r="X10" s="2">
+        <f t="shared" ref="X10:AD10" si="17">SUM(X6:X8)</f>
         <v>246.7</v>
       </c>
-      <c r="Y9" s="2">
+      <c r="Y10" s="2">
         <f t="shared" si="17"/>
         <v>300.89999999999998</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Z10" s="2">
         <f t="shared" si="17"/>
         <v>382.1</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA10" s="2">
         <f t="shared" si="17"/>
         <v>443.29999999999995</v>
       </c>
-      <c r="AB9" s="2">
+      <c r="AB10" s="2">
         <f t="shared" si="17"/>
         <v>560.5</v>
       </c>
-      <c r="AC9" s="2">
+      <c r="AC10" s="2">
         <f t="shared" si="17"/>
         <v>558.1</v>
       </c>
-      <c r="AD9" s="2">
+      <c r="AD10" s="2">
         <f t="shared" si="17"/>
         <v>496.4</v>
       </c>
-      <c r="AE9" s="2">
-        <f t="shared" ref="AE9:AO9" si="18">SUM(AE6:AE8)</f>
-        <v>460.64425</v>
-      </c>
-      <c r="AF9" s="2">
+      <c r="AE10" s="2">
+        <f>SUM(AE6:AE9)</f>
+        <v>445.18060000000003</v>
+      </c>
+      <c r="AF10" s="2">
+        <f t="shared" ref="AF10:AO10" si="18">SUM(AF6:AF9)</f>
+        <v>436.34000300000002</v>
+      </c>
+      <c r="AG10" s="2">
         <f t="shared" si="18"/>
-        <v>459.84983</v>
-      </c>
-      <c r="AG9" s="2">
+        <v>446.31699200000003</v>
+      </c>
+      <c r="AH10" s="2">
         <f t="shared" si="18"/>
-        <v>470.22336560000002</v>
-      </c>
-      <c r="AH9" s="2">
+        <v>453.81523139700005</v>
+      </c>
+      <c r="AI10" s="2">
         <f t="shared" si="18"/>
-        <v>478.28386336200003</v>
-      </c>
-      <c r="AI9" s="2">
+        <v>465.43831514829003</v>
+      </c>
+      <c r="AJ10" s="2">
         <f t="shared" si="18"/>
-        <v>490.24628632674001</v>
-      </c>
-      <c r="AJ9" s="2">
+        <v>476.52982683760081</v>
+      </c>
+      <c r="AK10" s="2">
         <f t="shared" si="18"/>
-        <v>501.72893404152478</v>
-      </c>
-      <c r="AK9" s="2">
+        <v>485.41082358828265</v>
+      </c>
+      <c r="AL10" s="2">
         <f t="shared" si="18"/>
-        <v>510.94270983645777</v>
-      </c>
-      <c r="AL9" s="2">
+        <v>494.48148482813542</v>
+      </c>
+      <c r="AM10" s="2">
         <f t="shared" si="18"/>
-        <v>520.35000142710828</v>
-      </c>
-      <c r="AM9" s="2">
+        <v>503.7462805090446</v>
+      </c>
+      <c r="AN10" s="2">
         <f t="shared" si="18"/>
-        <v>529.95529498144901</v>
-      </c>
-      <c r="AN9" s="2">
+        <v>513.20979343505132</v>
+      </c>
+      <c r="AO10" s="2">
         <f t="shared" si="18"/>
-        <v>539.76318825281101</v>
-      </c>
-      <c r="AO9" s="2">
-        <f t="shared" si="18"/>
-        <v>549.77839350131399</v>
+        <v>522.87672225452138</v>
       </c>
     </row>
-    <row r="10" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="1" t="s">
+    <row r="11" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="8">
-        <f t="shared" ref="C10:P10" si="19">C5-C9</f>
+      <c r="C11" s="8">
+        <f t="shared" ref="C11:P11" si="19">C5-C10</f>
         <v>16.800000000000011</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D11" s="8">
         <f t="shared" si="19"/>
         <v>34.800000000000011</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E11" s="8">
         <f t="shared" si="19"/>
         <v>0.30000000000001137</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F11" s="8">
         <f t="shared" si="19"/>
         <v>26.200000000000017</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G11" s="8">
         <f t="shared" si="19"/>
         <v>5.2999999999999829</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H11" s="8">
         <f t="shared" si="19"/>
         <v>7.3000000000000114</v>
       </c>
-      <c r="I10" s="8">
+      <c r="I11" s="8">
         <f t="shared" si="19"/>
         <v>-11.40000000000002</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J11" s="8">
         <f t="shared" si="19"/>
         <v>7.6999999999999602</v>
       </c>
-      <c r="K10" s="8">
+      <c r="K11" s="8">
         <f t="shared" si="19"/>
         <v>-4.5000000000000284</v>
       </c>
-      <c r="L10" s="8">
+      <c r="L11" s="8">
         <f t="shared" si="19"/>
         <v>-18.699999999999989</v>
       </c>
-      <c r="M10" s="8">
+      <c r="M11" s="8">
         <f t="shared" si="19"/>
         <v>-57.899999999999977</v>
       </c>
-      <c r="N10" s="8">
+      <c r="N11" s="8">
         <f t="shared" si="19"/>
         <v>13.399999999999977</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O11" s="8">
         <f t="shared" si="19"/>
         <v>-2.4000000000000057</v>
       </c>
-      <c r="P10" s="8">
+      <c r="P11" s="8">
         <f t="shared" si="19"/>
         <v>-3.5000000000000142</v>
       </c>
-      <c r="Q10" s="8">
-        <f t="shared" ref="Q10:R10" si="20">Q5-Q9</f>
+      <c r="Q11" s="8">
+        <f t="shared" ref="Q11:R11" si="20">Q5-Q10</f>
         <v>-26.5</v>
       </c>
-      <c r="R10" s="8">
+      <c r="R11" s="8">
         <f t="shared" si="20"/>
         <v>-27.299999999999997</v>
       </c>
-      <c r="S10" s="8">
-        <f t="shared" ref="S10:V10" si="21">S5-S9</f>
-        <v>-39.069999999999993</v>
-      </c>
-      <c r="T10" s="8">
+      <c r="S11" s="8">
+        <f t="shared" ref="S11:V11" si="21">S5-S10</f>
+        <v>-29</v>
+      </c>
+      <c r="T11" s="8">
         <f t="shared" si="21"/>
-        <v>-32.024250000000009</v>
-      </c>
-      <c r="U10" s="8">
+        <v>-27.865200000000002</v>
+      </c>
+      <c r="U11" s="8">
         <f t="shared" si="21"/>
         <v>-40.932000000000002</v>
       </c>
-      <c r="V10" s="8">
+      <c r="V11" s="8">
         <f t="shared" si="21"/>
-        <v>-35.778000000000006</v>
-      </c>
-      <c r="X10" s="8">
-        <f t="shared" ref="X10:AD10" si="22">X5-X9</f>
+        <v>-28.889999999999986</v>
+      </c>
+      <c r="X11" s="8">
+        <f t="shared" ref="X11:AD11" si="22">X5-X10</f>
         <v>-5.5999999999999659</v>
       </c>
-      <c r="Y10" s="8">
+      <c r="Y11" s="8">
         <f t="shared" si="22"/>
         <v>17.800000000000011</v>
       </c>
-      <c r="Z10" s="8">
+      <c r="Z11" s="8">
         <f t="shared" si="22"/>
         <v>56.799999999999955</v>
       </c>
-      <c r="AA10" s="8">
+      <c r="AA11" s="8">
         <f t="shared" si="22"/>
         <v>78.099999999999909</v>
       </c>
-      <c r="AB10" s="8">
+      <c r="AB11" s="8">
         <f t="shared" si="22"/>
         <v>8.8999999999999773</v>
       </c>
-      <c r="AC10" s="8">
+      <c r="AC11" s="8">
         <f t="shared" si="22"/>
         <v>-67.700000000000045</v>
       </c>
-      <c r="AD10" s="8">
+      <c r="AD11" s="8">
         <f t="shared" si="22"/>
         <v>-59.699999999999932</v>
       </c>
-      <c r="AE10" s="8">
-        <f t="shared" ref="AE10:AO10" si="23">AE5-AE9</f>
-        <v>-147.80424999999997</v>
-      </c>
-      <c r="AF10" s="8">
+      <c r="AE11" s="8">
+        <f t="shared" ref="AE11:AO11" si="23">AE5-AE10</f>
+        <v>-126.68720000000008</v>
+      </c>
+      <c r="AF11" s="8">
         <f t="shared" si="23"/>
-        <v>-147.61448000000001</v>
-      </c>
-      <c r="AG10" s="8">
+        <v>-104.55909200000008</v>
+      </c>
+      <c r="AG11" s="8">
         <f t="shared" si="23"/>
-        <v>-121.78681560000001</v>
-      </c>
-      <c r="AH10" s="8">
+        <v>-76.068729000000019</v>
+      </c>
+      <c r="AH11" s="8">
         <f t="shared" si="23"/>
-        <v>-105.45675486200003</v>
-      </c>
-      <c r="AI10" s="8">
+        <v>-57.649589986999956</v>
+      </c>
+      <c r="AI11" s="8">
         <f t="shared" si="23"/>
-        <v>-98.777822401739968</v>
-      </c>
-      <c r="AJ10" s="8">
+        <v>-49.464391667789926</v>
+      </c>
+      <c r="AJ11" s="8">
         <f t="shared" si="23"/>
-        <v>-94.601731559524751</v>
-      </c>
-      <c r="AK10" s="8">
+        <v>-43.916946417880695</v>
+      </c>
+      <c r="AK11" s="8">
         <f t="shared" si="23"/>
-        <v>-91.601691279997738</v>
-      </c>
-      <c r="AL10" s="8">
+        <v>-39.819556755970893</v>
+      </c>
+      <c r="AL11" s="8">
         <f t="shared" si="23"/>
-        <v>-88.428752313954419</v>
-      </c>
-      <c r="AM10" s="8">
+        <v>-35.522479990854322</v>
+      </c>
+      <c r="AM11" s="8">
         <f t="shared" si="23"/>
-        <v>-85.076408394900511</v>
-      </c>
-      <c r="AN10" s="8">
+        <v>-31.018505526645072</v>
+      </c>
+      <c r="AN11" s="8">
         <f t="shared" si="23"/>
-        <v>-81.537935068666002</v>
-      </c>
-      <c r="AO10" s="8">
+        <v>-26.300185203179808</v>
+      </c>
+      <c r="AO11" s="8">
         <f t="shared" si="23"/>
-        <v>-77.806382721644638</v>
-      </c>
-    </row>
-    <row r="11" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1.9</v>
-      </c>
-      <c r="D11" s="2">
-        <v>1.7</v>
-      </c>
-      <c r="E11" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="F11" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="G11" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="H11" s="2">
-        <v>1.6</v>
-      </c>
-      <c r="I11" s="2">
-        <v>1.5</v>
-      </c>
-      <c r="J11" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="K11" s="2">
-        <v>1.3</v>
-      </c>
-      <c r="L11" s="2">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="M11" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="N11" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="O11" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="P11" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="R11" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="S11" s="2">
-        <v>1</v>
-      </c>
-      <c r="T11" s="2">
-        <v>1</v>
-      </c>
-      <c r="U11" s="2">
-        <v>1</v>
-      </c>
-      <c r="V11" s="2">
-        <v>1</v>
-      </c>
-      <c r="X11" s="2">
-        <v>11.2</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>44.9</v>
-      </c>
-      <c r="Z11" s="2">
-        <v>66.3</v>
-      </c>
-      <c r="AA11" s="2">
-        <f>SUM(C11:F11)</f>
-        <v>6.7999999999999989</v>
-      </c>
-      <c r="AB11" s="2">
-        <f>SUM(G11:J11)</f>
-        <v>6</v>
-      </c>
-      <c r="AC11" s="2">
-        <f>SUM(K11:N11)</f>
-        <v>3.8000000000000007</v>
-      </c>
-      <c r="AD11" s="2">
-        <f>SUM(O11:R11)</f>
-        <v>2.6999999999999997</v>
-      </c>
-      <c r="AE11" s="2">
-        <f>SUM(S11:V11)</f>
-        <v>4</v>
-      </c>
-      <c r="AF11" s="2">
-        <f t="shared" ref="AF11:AO11" si="24">AE11*1.03</f>
-        <v>4.12</v>
-      </c>
-      <c r="AG11" s="2">
-        <f t="shared" si="24"/>
-        <v>4.2435999999999998</v>
-      </c>
-      <c r="AH11" s="2">
-        <f t="shared" si="24"/>
-        <v>4.370908</v>
-      </c>
-      <c r="AI11" s="2">
-        <f t="shared" si="24"/>
-        <v>4.5020352400000005</v>
-      </c>
-      <c r="AJ11" s="2">
-        <f t="shared" si="24"/>
-        <v>4.6370962972000003</v>
-      </c>
-      <c r="AK11" s="2">
-        <f t="shared" si="24"/>
-        <v>4.7762091861160005</v>
-      </c>
-      <c r="AL11" s="2">
-        <f t="shared" si="24"/>
-        <v>4.9194954616994808</v>
-      </c>
-      <c r="AM11" s="2">
-        <f t="shared" si="24"/>
-        <v>5.0670803255504655</v>
-      </c>
-      <c r="AN11" s="2">
-        <f t="shared" si="24"/>
-        <v>5.2190927353169796</v>
-      </c>
-      <c r="AO11" s="2">
-        <f t="shared" si="24"/>
-        <v>5.3756655173764889</v>
+        <v>-21.359825775693764</v>
       </c>
     </row>
     <row r="12" spans="2:145" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="H12" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J12" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="K12" s="2">
+        <v>1.3</v>
+      </c>
+      <c r="L12" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="N12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="O12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="P12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="S12" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T12" s="2">
+        <v>1</v>
+      </c>
+      <c r="U12" s="2">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2">
+        <v>1</v>
+      </c>
+      <c r="X12" s="2">
+        <v>11.2</v>
+      </c>
+      <c r="Y12" s="2">
+        <v>44.9</v>
+      </c>
+      <c r="Z12" s="2">
+        <v>66.3</v>
+      </c>
+      <c r="AA12" s="2">
+        <f>SUM(C12:F12)</f>
+        <v>6.7999999999999989</v>
+      </c>
+      <c r="AB12" s="2">
+        <f>SUM(G12:J12)</f>
+        <v>6</v>
+      </c>
+      <c r="AC12" s="2">
+        <f>SUM(K12:N12)</f>
+        <v>3.8000000000000007</v>
+      </c>
+      <c r="AD12" s="2">
+        <f>SUM(O12:R12)</f>
+        <v>2.6999999999999997</v>
+      </c>
+      <c r="AE12" s="2">
+        <f>SUM(S12:V12)</f>
+        <v>3.5</v>
+      </c>
+      <c r="AF12" s="2">
+        <f t="shared" ref="AF12:AO12" si="24">AE12*1.03</f>
+        <v>3.605</v>
+      </c>
+      <c r="AG12" s="2">
+        <f t="shared" si="24"/>
+        <v>3.7131500000000002</v>
+      </c>
+      <c r="AH12" s="2">
+        <f t="shared" si="24"/>
+        <v>3.8245445000000005</v>
+      </c>
+      <c r="AI12" s="2">
+        <f t="shared" si="24"/>
+        <v>3.9392808350000004</v>
+      </c>
+      <c r="AJ12" s="2">
+        <f t="shared" si="24"/>
+        <v>4.0574592600500008</v>
+      </c>
+      <c r="AK12" s="2">
+        <f t="shared" si="24"/>
+        <v>4.1791830378515007</v>
+      </c>
+      <c r="AL12" s="2">
+        <f t="shared" si="24"/>
+        <v>4.3045585289870454</v>
+      </c>
+      <c r="AM12" s="2">
+        <f t="shared" si="24"/>
+        <v>4.4336952848566566</v>
+      </c>
+      <c r="AN12" s="2">
+        <f t="shared" si="24"/>
+        <v>4.5667061434023566</v>
+      </c>
+      <c r="AO12" s="2">
+        <f t="shared" si="24"/>
+        <v>4.7037073277044277</v>
+      </c>
+    </row>
+    <row r="13" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C13" s="2">
         <v>77.2</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D13" s="2">
         <v>-1.9</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E13" s="2">
         <v>-8.6999999999999993</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F13" s="2">
         <v>-1.1000000000000001</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G13" s="2">
         <v>-6.2</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H13" s="2">
         <v>-1.8</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I13" s="2">
         <v>-97.3</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J13" s="2">
         <v>4.2</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K13" s="2">
         <v>-12.1</v>
       </c>
-      <c r="L12" s="2">
+      <c r="L13" s="2">
         <v>-64.099999999999994</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M13" s="2">
         <v>-40.5</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N13" s="2">
         <v>-5.0999999999999996</v>
       </c>
-      <c r="O12" s="2">
+      <c r="O13" s="2">
         <v>-10.8</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P13" s="2">
         <v>-7.1</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q13" s="2">
         <v>-7.6</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R13" s="2">
         <v>-25.8</v>
       </c>
-      <c r="S12" s="2">
-        <f>O12*1.02</f>
-        <v>-11.016000000000002</v>
-      </c>
-      <c r="T12" s="2">
-        <f t="shared" ref="T12:V12" si="25">P12*1.02</f>
+      <c r="S13" s="2">
+        <v>-13</v>
+      </c>
+      <c r="T13" s="2">
+        <f t="shared" ref="T13:V13" si="25">P13*1.02</f>
         <v>-7.242</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U13" s="2">
         <f t="shared" si="25"/>
         <v>-7.7519999999999998</v>
       </c>
-      <c r="V12" s="2">
+      <c r="V13" s="2">
         <f t="shared" si="25"/>
         <v>-26.316000000000003</v>
       </c>
-      <c r="X12" s="2">
+      <c r="X13" s="2">
         <v>-4</v>
       </c>
-      <c r="Y12" s="2">
+      <c r="Y13" s="2">
         <v>-20.100000000000001</v>
       </c>
-      <c r="Z12" s="2">
+      <c r="Z13" s="2">
         <v>-8.6999999999999993</v>
       </c>
-      <c r="AA12" s="2">
-        <f>SUM(C12:F12)</f>
+      <c r="AA13" s="2">
+        <f>SUM(C13:F13)</f>
         <v>65.5</v>
       </c>
-      <c r="AB12" s="2">
-        <f>SUM(G12:J12)</f>
+      <c r="AB13" s="2">
+        <f>SUM(G13:J13)</f>
         <v>-101.1</v>
       </c>
-      <c r="AC12" s="2">
-        <f>SUM(K12:N12)</f>
+      <c r="AC13" s="2">
+        <f>SUM(K13:N13)</f>
         <v>-121.79999999999998</v>
       </c>
-      <c r="AD12" s="2">
-        <f>SUM(O12:R12)</f>
+      <c r="AD13" s="2">
+        <f>SUM(O13:R13)</f>
         <v>-51.3</v>
       </c>
-      <c r="AE12" s="2">
-        <f>SUM(S12:V12)</f>
-        <v>-52.326000000000008</v>
-      </c>
-      <c r="AF12" s="2">
-        <f t="shared" ref="AF12:AO12" si="26">AE12*1.03</f>
-        <v>-53.895780000000009</v>
-      </c>
-      <c r="AG12" s="2">
+      <c r="AE13" s="2">
+        <f>SUM(S13:V13)</f>
+        <v>-54.31</v>
+      </c>
+      <c r="AF13" s="2">
+        <f t="shared" ref="AF13:AO13" si="26">AE13*1.03</f>
+        <v>-55.939300000000003</v>
+      </c>
+      <c r="AG13" s="2">
         <f t="shared" si="26"/>
-        <v>-55.512653400000012</v>
-      </c>
-      <c r="AH12" s="2">
+        <v>-57.617479000000003</v>
+      </c>
+      <c r="AH13" s="2">
         <f t="shared" si="26"/>
-        <v>-57.178033002000014</v>
-      </c>
-      <c r="AI12" s="2">
+        <v>-59.346003370000005</v>
+      </c>
+      <c r="AI13" s="2">
         <f t="shared" si="26"/>
-        <v>-58.893373992060013</v>
-      </c>
-      <c r="AJ12" s="2">
+        <v>-61.126383471100006</v>
+      </c>
+      <c r="AJ13" s="2">
         <f t="shared" si="26"/>
-        <v>-60.660175211821816</v>
-      </c>
-      <c r="AK12" s="2">
+        <v>-62.960174975233009</v>
+      </c>
+      <c r="AK13" s="2">
         <f t="shared" si="26"/>
-        <v>-62.479980468176471</v>
-      </c>
-      <c r="AL12" s="2">
+        <v>-64.848980224490006</v>
+      </c>
+      <c r="AL13" s="2">
         <f t="shared" si="26"/>
-        <v>-64.354379882221764</v>
-      </c>
-      <c r="AM12" s="2">
+        <v>-66.794449631224708</v>
+      </c>
+      <c r="AM13" s="2">
         <f t="shared" si="26"/>
-        <v>-66.285011278688415</v>
-      </c>
-      <c r="AN12" s="2">
+        <v>-68.798283120161457</v>
+      </c>
+      <c r="AN13" s="2">
         <f t="shared" si="26"/>
-        <v>-68.273561617049069</v>
-      </c>
-      <c r="AO12" s="2">
+        <v>-70.862231613766298</v>
+      </c>
+      <c r="AO13" s="2">
         <f t="shared" si="26"/>
-        <v>-70.321768465560538</v>
+        <v>-72.988098562179289</v>
       </c>
     </row>
-    <row r="13" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="1" t="s">
+    <row r="14" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="8">
-        <f t="shared" ref="C13:P13" si="27">C10-C11-C12</f>
+      <c r="C14" s="8">
+        <f t="shared" ref="C14:P14" si="27">C11-C12-C13</f>
         <v>-62.29999999999999</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D14" s="8">
         <f t="shared" si="27"/>
         <v>35.000000000000007</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E14" s="8">
         <f t="shared" si="27"/>
         <v>7.400000000000011</v>
       </c>
-      <c r="F13" s="8">
+      <c r="F14" s="8">
         <f t="shared" si="27"/>
         <v>25.700000000000017</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G14" s="8">
         <f t="shared" si="27"/>
         <v>9.8999999999999826</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H14" s="8">
         <f t="shared" si="27"/>
         <v>7.5000000000000115</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I14" s="8">
         <f t="shared" si="27"/>
         <v>84.399999999999977</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J14" s="8">
         <f t="shared" si="27"/>
         <v>2.1999999999999602</v>
       </c>
-      <c r="K13" s="8">
+      <c r="K14" s="8">
         <f t="shared" si="27"/>
         <v>6.2999999999999714</v>
       </c>
-      <c r="L13" s="8">
+      <c r="L14" s="8">
         <f t="shared" si="27"/>
         <v>44.300000000000004</v>
       </c>
-      <c r="M13" s="8">
+      <c r="M14" s="8">
         <f t="shared" si="27"/>
         <v>-18.09999999999998</v>
       </c>
-      <c r="N13" s="8">
+      <c r="N14" s="8">
         <f t="shared" si="27"/>
         <v>17.799999999999976</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O14" s="8">
         <f t="shared" si="27"/>
         <v>7.6999999999999948</v>
       </c>
-      <c r="P13" s="8">
+      <c r="P14" s="8">
         <f t="shared" si="27"/>
         <v>2.8999999999999853</v>
       </c>
-      <c r="Q13" s="8">
-        <f t="shared" ref="Q13:V13" si="28">Q10-Q11-Q12</f>
+      <c r="Q14" s="8">
+        <f t="shared" ref="Q14:V14" si="28">Q11-Q12-Q13</f>
         <v>-19.600000000000001</v>
       </c>
-      <c r="R13" s="8">
+      <c r="R14" s="8">
         <f t="shared" si="28"/>
         <v>-2.0999999999999979</v>
       </c>
-      <c r="S13" s="8">
+      <c r="S14" s="8">
         <f t="shared" si="28"/>
-        <v>-29.053999999999991</v>
-      </c>
-      <c r="T13" s="8">
+        <v>-16.5</v>
+      </c>
+      <c r="T14" s="8">
         <f t="shared" si="28"/>
-        <v>-25.782250000000008</v>
-      </c>
-      <c r="U13" s="8">
+        <v>-21.623200000000001</v>
+      </c>
+      <c r="U14" s="8">
         <f t="shared" si="28"/>
         <v>-34.18</v>
       </c>
-      <c r="V13" s="8">
+      <c r="V14" s="8">
         <f t="shared" si="28"/>
-        <v>-10.462000000000003</v>
-      </c>
-      <c r="X13" s="8">
-        <f t="shared" ref="X13:AD13" si="29">X10-X11-X12</f>
+        <v>-3.5739999999999839</v>
+      </c>
+      <c r="X14" s="8">
+        <f t="shared" ref="X14:AD14" si="29">X11-X12-X13</f>
         <v>-12.799999999999965</v>
       </c>
-      <c r="Y13" s="8">
+      <c r="Y14" s="8">
         <f t="shared" si="29"/>
         <v>-6.9999999999999858</v>
       </c>
-      <c r="Z13" s="8">
+      <c r="Z14" s="8">
         <f t="shared" si="29"/>
         <v>-0.80000000000004334</v>
       </c>
-      <c r="AA13" s="8">
+      <c r="AA14" s="8">
         <f t="shared" si="29"/>
         <v>5.7999999999999119</v>
       </c>
-      <c r="AB13" s="8">
+      <c r="AB14" s="8">
         <f t="shared" si="29"/>
         <v>103.99999999999997</v>
       </c>
-      <c r="AC13" s="8">
+      <c r="AC14" s="8">
         <f t="shared" si="29"/>
         <v>50.29999999999994</v>
       </c>
-      <c r="AD13" s="8">
+      <c r="AD14" s="8">
         <f t="shared" si="29"/>
         <v>-11.099999999999937</v>
       </c>
-      <c r="AE13" s="8">
-        <f t="shared" ref="AE13:AO13" si="30">AE10-AE11-AE12</f>
-        <v>-99.47824999999996</v>
-      </c>
-      <c r="AF13" s="8">
+      <c r="AE14" s="8">
+        <f t="shared" ref="AE14:AO14" si="30">AE11-AE12-AE13</f>
+        <v>-75.877200000000073</v>
+      </c>
+      <c r="AF14" s="8">
         <f t="shared" si="30"/>
-        <v>-97.838700000000017</v>
-      </c>
-      <c r="AG13" s="8">
+        <v>-52.224792000000079</v>
+      </c>
+      <c r="AG14" s="8">
         <f t="shared" si="30"/>
-        <v>-70.517762199999993</v>
-      </c>
-      <c r="AH13" s="8">
+        <v>-22.164400000000015</v>
+      </c>
+      <c r="AH14" s="8">
         <f t="shared" si="30"/>
-        <v>-52.649629860000012</v>
-      </c>
-      <c r="AI13" s="8">
+        <v>-2.1281311169999526</v>
+      </c>
+      <c r="AI14" s="8">
         <f t="shared" si="30"/>
-        <v>-44.386483649679953</v>
-      </c>
-      <c r="AJ13" s="8">
+        <v>7.7227109683100821</v>
+      </c>
+      <c r="AJ14" s="8">
         <f t="shared" si="30"/>
-        <v>-38.578652644902938</v>
-      </c>
-      <c r="AK13" s="8">
+        <v>14.985769297302312</v>
+      </c>
+      <c r="AK14" s="8">
         <f t="shared" si="30"/>
-        <v>-33.897919997937272</v>
-      </c>
-      <c r="AL13" s="8">
+        <v>20.850240430667611</v>
+      </c>
+      <c r="AL14" s="8">
         <f t="shared" si="30"/>
-        <v>-28.993867893432139</v>
-      </c>
-      <c r="AM13" s="8">
+        <v>26.967411111383342</v>
+      </c>
+      <c r="AM14" s="8">
         <f t="shared" si="30"/>
-        <v>-23.85847744176256</v>
-      </c>
-      <c r="AN13" s="8">
+        <v>33.346082308659732</v>
+      </c>
+      <c r="AN14" s="8">
         <f t="shared" si="30"/>
-        <v>-18.48346618693391</v>
-      </c>
-      <c r="AO13" s="8">
+        <v>39.995340267184133</v>
+      </c>
+      <c r="AO14" s="8">
         <f t="shared" si="30"/>
-        <v>-12.86027977346059</v>
+        <v>46.924565458781096</v>
       </c>
     </row>
-    <row r="14" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+    <row r="15" spans="2:145" x14ac:dyDescent="0.3">
+      <c r="B15" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C15" s="2">
         <v>2.8</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D15" s="2">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E15" s="2">
         <v>0.7</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F15" s="2">
         <v>1.4</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G15" s="2">
         <v>4.2</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H15" s="2">
         <v>0.1</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I15" s="2">
         <v>-167.3</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J15" s="2">
         <v>0.3</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K15" s="2">
         <v>4.2</v>
       </c>
-      <c r="L14" s="2">
+      <c r="L15" s="2">
         <v>19.7</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M15" s="2">
         <v>0.2</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N15" s="2">
         <v>8.1</v>
       </c>
-      <c r="O14" s="2">
+      <c r="O15" s="2">
         <v>9.1</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P15" s="2">
         <f>138.3-129.9</f>
         <v>8.4000000000000057</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="Q15" s="2">
         <v>-2.7</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R15" s="2">
         <v>4</v>
       </c>
-      <c r="S14" s="2">
-        <v>0</v>
-      </c>
-      <c r="T14" s="2">
-        <v>0</v>
-      </c>
-      <c r="U14" s="2">
-        <v>0</v>
-      </c>
-      <c r="V14" s="2">
-        <v>0</v>
-      </c>
-      <c r="X14" s="2">
+      <c r="S15" s="2">
+        <v>1</v>
+      </c>
+      <c r="T15" s="2">
+        <v>0</v>
+      </c>
+      <c r="U15" s="2">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2">
+        <v>0</v>
+      </c>
+      <c r="X15" s="2">
         <v>1.4</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y15" s="2">
         <v>2.6</v>
       </c>
-      <c r="Z14" s="2">
+      <c r="Z15" s="2">
         <v>5.4</v>
       </c>
-      <c r="AA14" s="2">
-        <f>SUM(C14:F14)</f>
+      <c r="AA15" s="2">
+        <f>SUM(C15:F15)</f>
         <v>7.1</v>
       </c>
-      <c r="AB14" s="2">
-        <f>SUM(G14:J14)</f>
+      <c r="AB15" s="2">
+        <f>SUM(G15:J15)</f>
         <v>-162.69999999999999</v>
       </c>
-      <c r="AC14" s="2">
-        <f>SUM(K14:N14)</f>
+      <c r="AC15" s="2">
+        <f>SUM(K15:N15)</f>
         <v>32.199999999999996</v>
       </c>
-      <c r="AD14" s="2">
-        <f>SUM(O14:R14)</f>
+      <c r="AD15" s="2">
+        <f>SUM(O15:R15)</f>
         <v>18.800000000000008</v>
       </c>
-      <c r="AE14" s="2">
-        <f>SUM(S14:V14)</f>
-        <v>0</v>
-      </c>
-      <c r="AF14" s="2">
-        <f>AF13*0.15</f>
-        <v>-14.675805000000002</v>
-      </c>
-      <c r="AG14" s="2">
-        <f t="shared" ref="AG14:AO14" si="31">AG13*0.15</f>
-        <v>-10.577664329999999</v>
-      </c>
-      <c r="AH14" s="2">
+      <c r="AE15" s="2">
+        <f>SUM(S15:V15)</f>
+        <v>1</v>
+      </c>
+      <c r="AF15" s="2">
+        <f>AF14*0.15</f>
+        <v>-7.8337188000000113</v>
+      </c>
+      <c r="AG15" s="2">
+        <f t="shared" ref="AG15:AO15" si="31">AG14*0.15</f>
+        <v>-3.3246600000000019</v>
+      </c>
+      <c r="AH15" s="2">
         <f t="shared" si="31"/>
-        <v>-7.8974444790000016</v>
-      </c>
-      <c r="AI14" s="2">
+        <v>-0.31921966754999287</v>
+      </c>
+      <c r="AI15" s="2">
         <f t="shared" si="31"/>
-        <v>-6.6579725474519931</v>
-      </c>
-      <c r="AJ14" s="2">
+        <v>1.1584066452465123</v>
+      </c>
+      <c r="AJ15" s="2">
         <f t="shared" si="31"/>
-        <v>-5.7867978967354405</v>
-      </c>
-      <c r="AK14" s="2">
+        <v>2.2478653945953466</v>
+      </c>
+      <c r="AK15" s="2">
         <f t="shared" si="31"/>
-        <v>-5.0846879996905905</v>
-      </c>
-      <c r="AL14" s="2">
+        <v>3.1275360646001418</v>
+      </c>
+      <c r="AL15" s="2">
         <f t="shared" si="31"/>
-        <v>-4.349080184014821</v>
-      </c>
-      <c r="AM14" s="2">
+        <v>4.0451116667075011</v>
+      </c>
+      <c r="AM15" s="2">
         <f t="shared" si="31"/>
-        <v>-3.5787716162643837</v>
-      </c>
-      <c r="AN14" s="2">
+        <v>5.0019123462989592</v>
+      </c>
+      <c r="AN15" s="2">
         <f t="shared" si="31"/>
-        <v>-2.7725199280400865</v>
-      </c>
-      <c r="AO14" s="2">
+        <v>5.9993010400776194</v>
+      </c>
+      <c r="AO15" s="2">
         <f t="shared" si="31"/>
-        <v>-1.9290419660190885</v>
+        <v>7.0386848188171642</v>
       </c>
     </row>
-    <row r="15" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="1" t="s">
+    <row r="16" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="8">
-        <f t="shared" ref="C15:P15" si="32">C13-C14</f>
+      <c r="C16" s="8">
+        <f t="shared" ref="C16:P16" si="32">C14-C15</f>
         <v>-65.099999999999994</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D16" s="8">
         <f t="shared" si="32"/>
         <v>32.800000000000004</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E16" s="8">
         <f t="shared" si="32"/>
         <v>6.7000000000000108</v>
       </c>
-      <c r="F15" s="8">
+      <c r="F16" s="8">
         <f t="shared" si="32"/>
         <v>24.300000000000018</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G16" s="8">
         <f t="shared" si="32"/>
         <v>5.6999999999999824</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H16" s="8">
         <f t="shared" si="32"/>
         <v>7.4000000000000119</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I16" s="8">
         <f t="shared" si="32"/>
         <v>251.7</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J16" s="8">
         <f t="shared" si="32"/>
         <v>1.8999999999999602</v>
       </c>
-      <c r="K15" s="8">
+      <c r="K16" s="8">
         <f t="shared" si="32"/>
         <v>2.0999999999999712</v>
       </c>
-      <c r="L15" s="8">
+      <c r="L16" s="8">
         <f t="shared" si="32"/>
         <v>24.600000000000005</v>
       </c>
-      <c r="M15" s="8">
+      <c r="M16" s="8">
         <f t="shared" si="32"/>
         <v>-18.299999999999979</v>
       </c>
-      <c r="N15" s="8">
+      <c r="N16" s="8">
         <f t="shared" si="32"/>
         <v>9.6999999999999762</v>
       </c>
-      <c r="O15" s="8">
+      <c r="O16" s="8">
         <f t="shared" si="32"/>
         <v>-1.4000000000000048</v>
       </c>
-      <c r="P15" s="8">
+      <c r="P16" s="8">
         <f t="shared" si="32"/>
         <v>-5.5000000000000204</v>
       </c>
-      <c r="Q15" s="8">
-        <f t="shared" ref="Q15:R15" si="33">Q13-Q14</f>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16:R16" si="33">Q14-Q15</f>
         <v>-16.900000000000002</v>
       </c>
-      <c r="R15" s="8">
+      <c r="R16" s="8">
         <f t="shared" si="33"/>
         <v>-6.0999999999999979</v>
       </c>
-      <c r="S15" s="8">
-        <f t="shared" ref="S15:V15" si="34">S13-S14</f>
-        <v>-29.053999999999991</v>
-      </c>
-      <c r="T15" s="8">
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:V16" si="34">S14-S15</f>
+        <v>-17.5</v>
+      </c>
+      <c r="T16" s="8">
         <f t="shared" si="34"/>
-        <v>-25.782250000000008</v>
-      </c>
-      <c r="U15" s="8">
+        <v>-21.623200000000001</v>
+      </c>
+      <c r="U16" s="8">
         <f t="shared" si="34"/>
         <v>-34.18</v>
       </c>
-      <c r="V15" s="8">
+      <c r="V16" s="8">
         <f t="shared" si="34"/>
-        <v>-10.462000000000003</v>
-      </c>
-      <c r="X15" s="8">
-        <f t="shared" ref="X15:AD15" si="35">X13-X14</f>
+        <v>-3.5739999999999839</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" ref="X16:AD16" si="35">X14-X15</f>
         <v>-14.199999999999966</v>
       </c>
-      <c r="Y15" s="8">
+      <c r="Y16" s="8">
         <f t="shared" si="35"/>
         <v>-9.5999999999999854</v>
       </c>
-      <c r="Z15" s="8">
+      <c r="Z16" s="8">
         <f t="shared" si="35"/>
         <v>-6.2000000000000437</v>
       </c>
-      <c r="AA15" s="8">
+      <c r="AA16" s="8">
         <f t="shared" si="35"/>
         <v>-1.3000000000000878</v>
       </c>
-      <c r="AB15" s="8">
+      <c r="AB16" s="8">
         <f t="shared" si="35"/>
         <v>266.69999999999993</v>
       </c>
-      <c r="AC15" s="8">
+      <c r="AC16" s="8">
         <f t="shared" si="35"/>
         <v>18.099999999999945</v>
       </c>
-      <c r="AD15" s="8">
+      <c r="AD16" s="8">
         <f t="shared" si="35"/>
         <v>-29.899999999999945</v>
       </c>
-      <c r="AE15" s="8">
-        <f t="shared" ref="AE15:AO15" si="36">AE13-AE14</f>
-        <v>-99.47824999999996</v>
-      </c>
-      <c r="AF15" s="8">
+      <c r="AE16" s="8">
+        <f t="shared" ref="AE16:AO16" si="36">AE14-AE15</f>
+        <v>-76.877200000000073</v>
+      </c>
+      <c r="AF16" s="8">
         <f t="shared" si="36"/>
-        <v>-83.16289500000002</v>
-      </c>
-      <c r="AG15" s="8">
+        <v>-44.391073200000065</v>
+      </c>
+      <c r="AG16" s="8">
         <f t="shared" si="36"/>
-        <v>-59.940097869999995</v>
-      </c>
-      <c r="AH15" s="8">
+        <v>-18.839740000000013</v>
+      </c>
+      <c r="AH16" s="8">
         <f t="shared" si="36"/>
-        <v>-44.752185381000011</v>
-      </c>
-      <c r="AI15" s="8">
+        <v>-1.8089114494499596</v>
+      </c>
+      <c r="AI16" s="8">
         <f t="shared" si="36"/>
-        <v>-37.728511102227962</v>
-      </c>
-      <c r="AJ15" s="8">
+        <v>6.5643043230635696</v>
+      </c>
+      <c r="AJ16" s="8">
         <f t="shared" si="36"/>
-        <v>-32.791854748167495</v>
-      </c>
-      <c r="AK15" s="8">
+        <v>12.737903902706964</v>
+      </c>
+      <c r="AK16" s="8">
         <f t="shared" si="36"/>
-        <v>-28.813231998246682</v>
-      </c>
-      <c r="AL15" s="8">
+        <v>17.722704366067468</v>
+      </c>
+      <c r="AL16" s="8">
         <f t="shared" si="36"/>
-        <v>-24.644787709417319</v>
-      </c>
-      <c r="AM15" s="8">
+        <v>22.92229944467584</v>
+      </c>
+      <c r="AM16" s="8">
         <f t="shared" si="36"/>
-        <v>-20.279705825498176</v>
-      </c>
-      <c r="AN15" s="8">
+        <v>28.344169962360773</v>
+      </c>
+      <c r="AN16" s="8">
         <f t="shared" si="36"/>
-        <v>-15.710946258893824</v>
-      </c>
-      <c r="AO15" s="8">
+        <v>33.996039227106515</v>
+      </c>
+      <c r="AO16" s="8">
         <f t="shared" si="36"/>
-        <v>-10.931237807441502</v>
-      </c>
-      <c r="AP15" s="1">
-        <f>AO15*(1+$AS$20)</f>
-        <v>-10.821925429367086</v>
-      </c>
-      <c r="AQ15" s="1">
-        <f t="shared" ref="AQ15:DB15" si="37">AP15*(1+$AS$20)</f>
-        <v>-10.713706175073415</v>
-      </c>
-      <c r="AR15" s="1">
+        <v>39.885880639963929</v>
+      </c>
+      <c r="AP16" s="1">
+        <f>AO16*(1+$AS$21)</f>
+        <v>39.487021833564292</v>
+      </c>
+      <c r="AQ16" s="1">
+        <f t="shared" ref="AQ16:DB16" si="37">AP16*(1+$AS$21)</f>
+        <v>39.092151615228651</v>
+      </c>
+      <c r="AR16" s="1">
         <f t="shared" si="37"/>
-        <v>-10.606569113322681</v>
-      </c>
-      <c r="AS15" s="1">
+        <v>38.701230099076362</v>
+      </c>
+      <c r="AS16" s="1">
         <f t="shared" si="37"/>
-        <v>-10.500503422189455</v>
-      </c>
-      <c r="AT15" s="1">
+        <v>38.3142177980856</v>
+      </c>
+      <c r="AT16" s="1">
         <f t="shared" si="37"/>
-        <v>-10.39549838796756</v>
-      </c>
-      <c r="AU15" s="1">
+        <v>37.931075620104743</v>
+      </c>
+      <c r="AU16" s="1">
         <f t="shared" si="37"/>
-        <v>-10.291543404087884</v>
-      </c>
-      <c r="AV15" s="1">
+        <v>37.551764863903692</v>
+      </c>
+      <c r="AV16" s="1">
         <f t="shared" si="37"/>
-        <v>-10.188627970047005</v>
-      </c>
-      <c r="AW15" s="1">
+        <v>37.176247215264652</v>
+      </c>
+      <c r="AW16" s="1">
         <f t="shared" si="37"/>
-        <v>-10.086741690346535</v>
-      </c>
-      <c r="AX15" s="1">
+        <v>36.804484743112006</v>
+      </c>
+      <c r="AX16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.9858742734430699</v>
-      </c>
-      <c r="AY15" s="1">
+        <v>36.436439895680884</v>
+      </c>
+      <c r="AY16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.8860155307086384</v>
-      </c>
-      <c r="AZ15" s="1">
+        <v>36.072075496724075</v>
+      </c>
+      <c r="AZ16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.7871553754015519</v>
-      </c>
-      <c r="BA15" s="1">
+        <v>35.711354741756836</v>
+      </c>
+      <c r="BA16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.6892838216475354</v>
-      </c>
-      <c r="BB15" s="1">
+        <v>35.354241194339266</v>
+      </c>
+      <c r="BB16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.5923909834310592</v>
-      </c>
-      <c r="BC15" s="1">
+        <v>35.000698782395872</v>
+      </c>
+      <c r="BC16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.4964670735967491</v>
-      </c>
-      <c r="BD15" s="1">
+        <v>34.650691794571912</v>
+      </c>
+      <c r="BD16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.4015024028607819</v>
-      </c>
-      <c r="BE15" s="1">
+        <v>34.304184876626195</v>
+      </c>
+      <c r="BE16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.3074873788321746</v>
-      </c>
-      <c r="BF15" s="1">
+        <v>33.961143027859933</v>
+      </c>
+      <c r="BF16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.2144125050438532</v>
-      </c>
-      <c r="BG15" s="1">
+        <v>33.621531597581331</v>
+      </c>
+      <c r="BG16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.1222683799934146</v>
-      </c>
-      <c r="BH15" s="1">
+        <v>33.285316281605517</v>
+      </c>
+      <c r="BH16" s="1">
         <f t="shared" si="37"/>
-        <v>-9.0310456961934804</v>
-      </c>
-      <c r="BI15" s="1">
+        <v>32.95246311878946</v>
+      </c>
+      <c r="BI16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.9407352392315449</v>
-      </c>
-      <c r="BJ15" s="1">
+        <v>32.622938487601566</v>
+      </c>
+      <c r="BJ16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.8513278868392291</v>
-      </c>
-      <c r="BK15" s="1">
+        <v>32.296709102725551</v>
+      </c>
+      <c r="BK16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.7628146079708369</v>
-      </c>
-      <c r="BL15" s="1">
+        <v>31.973742011698295</v>
+      </c>
+      <c r="BL16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.6751864618911281</v>
-      </c>
-      <c r="BM15" s="1">
+        <v>31.654004591581312</v>
+      </c>
+      <c r="BM16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.5884345972722169</v>
-      </c>
-      <c r="BN15" s="1">
+        <v>31.337464545665497</v>
+      </c>
+      <c r="BN16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.5025502512994944</v>
-      </c>
-      <c r="BO15" s="1">
+        <v>31.024089900208843</v>
+      </c>
+      <c r="BO16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.4175247487864997</v>
-      </c>
-      <c r="BP15" s="1">
+        <v>30.713849001206754</v>
+      </c>
+      <c r="BP16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.3333495012986347</v>
-      </c>
-      <c r="BQ15" s="1">
+        <v>30.406710511194685</v>
+      </c>
+      <c r="BQ16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.250016006285648</v>
-      </c>
-      <c r="BR15" s="1">
+        <v>30.102643406082738</v>
+      </c>
+      <c r="BR16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.1675158462227913</v>
-      </c>
-      <c r="BS15" s="1">
+        <v>29.801616972021911</v>
+      </c>
+      <c r="BS16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.0858406877605624</v>
-      </c>
-      <c r="BT15" s="1">
+        <v>29.50360080230169</v>
+      </c>
+      <c r="BT16" s="1">
         <f t="shared" si="37"/>
-        <v>-8.004982280882956</v>
-      </c>
-      <c r="BU15" s="1">
+        <v>29.208564794278672</v>
+      </c>
+      <c r="BU16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.9249324580741263</v>
-      </c>
-      <c r="BV15" s="1">
+        <v>28.916479146335885</v>
+      </c>
+      <c r="BV16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.8456831334933845</v>
-      </c>
-      <c r="BW15" s="1">
+        <v>28.627314354872524</v>
+      </c>
+      <c r="BW16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.7672263021584502</v>
-      </c>
-      <c r="BX15" s="1">
+        <v>28.341041211323798</v>
+      </c>
+      <c r="BX16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.6895540391368655</v>
-      </c>
-      <c r="BY15" s="1">
+        <v>28.05763079921056</v>
+      </c>
+      <c r="BY16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.612658498745497</v>
-      </c>
-      <c r="BZ15" s="1">
+        <v>27.777054491218454</v>
+      </c>
+      <c r="BZ16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.5365319137580418</v>
-      </c>
-      <c r="CA15" s="1">
+        <v>27.499283946306271</v>
+      </c>
+      <c r="CA16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.4611665946204617</v>
-      </c>
-      <c r="CB15" s="1">
+        <v>27.224291106843207</v>
+      </c>
+      <c r="CB16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.3865549286742569</v>
-      </c>
-      <c r="CC15" s="1">
+        <v>26.952048195774776</v>
+      </c>
+      <c r="CC16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.3126893793875141</v>
-      </c>
-      <c r="CD15" s="1">
+        <v>26.682527713817027</v>
+      </c>
+      <c r="CD16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.2395624855936385</v>
-      </c>
-      <c r="CE15" s="1">
+        <v>26.415702436678856</v>
+      </c>
+      <c r="CE16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.1671668607377024</v>
-      </c>
-      <c r="CF15" s="1">
+        <v>26.151545412312068</v>
+      </c>
+      <c r="CF16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.0954951921303255</v>
-      </c>
-      <c r="CG15" s="1">
+        <v>25.890029958188947</v>
+      </c>
+      <c r="CG16" s="1">
         <f t="shared" si="37"/>
-        <v>-7.0245402402090225</v>
-      </c>
-      <c r="CH15" s="1">
+        <v>25.631129658607058</v>
+      </c>
+      <c r="CH16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.9542948378069323</v>
-      </c>
-      <c r="CI15" s="1">
+        <v>25.374818362020989</v>
+      </c>
+      <c r="CI16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.8847518894288626</v>
-      </c>
-      <c r="CJ15" s="1">
+        <v>25.121070178400778</v>
+      </c>
+      <c r="CJ16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.8159043705345743</v>
-      </c>
-      <c r="CK15" s="1">
+        <v>24.869859476616771</v>
+      </c>
+      <c r="CK16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.7477453268292287</v>
-      </c>
-      <c r="CL15" s="1">
+        <v>24.621160881850603</v>
+      </c>
+      <c r="CL16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.6802678735609362</v>
-      </c>
-      <c r="CM15" s="1">
+        <v>24.374949273032097</v>
+      </c>
+      <c r="CM16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.6134651948253271</v>
-      </c>
-      <c r="CN15" s="1">
+        <v>24.131199780301777</v>
+      </c>
+      <c r="CN16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.5473305428770736</v>
-      </c>
-      <c r="CO15" s="1">
+        <v>23.889887782498761</v>
+      </c>
+      <c r="CO16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.4818572374483026</v>
-      </c>
-      <c r="CP15" s="1">
+        <v>23.650988904673774</v>
+      </c>
+      <c r="CP16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.4170386650738198</v>
-      </c>
-      <c r="CQ15" s="1">
+        <v>23.414479015627037</v>
+      </c>
+      <c r="CQ16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.3528682784230819</v>
-      </c>
-      <c r="CR15" s="1">
+        <v>23.180334225470766</v>
+      </c>
+      <c r="CR16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.2893395956388511</v>
-      </c>
-      <c r="CS15" s="1">
+        <v>22.948530883216058</v>
+      </c>
+      <c r="CS16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.2264461996824627</v>
-      </c>
-      <c r="CT15" s="1">
+        <v>22.719045574383898</v>
+      </c>
+      <c r="CT16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.164181737685638</v>
-      </c>
-      <c r="CU15" s="1">
+        <v>22.491855118640061</v>
+      </c>
+      <c r="CU16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.1025399203087813</v>
-      </c>
-      <c r="CV15" s="1">
+        <v>22.266936567453659</v>
+      </c>
+      <c r="CV16" s="1">
         <f t="shared" si="37"/>
-        <v>-6.0415145211056931</v>
-      </c>
-      <c r="CW15" s="1">
+        <v>22.044267201779121</v>
+      </c>
+      <c r="CW16" s="1">
         <f t="shared" si="37"/>
-        <v>-5.9810993758946358</v>
-      </c>
-      <c r="CX15" s="1">
+        <v>21.823824529761328</v>
+      </c>
+      <c r="CX16" s="1">
         <f t="shared" si="37"/>
-        <v>-5.921288382135689</v>
-      </c>
-      <c r="CY15" s="1">
+        <v>21.605586284463715</v>
+      </c>
+      <c r="CY16" s="1">
         <f t="shared" si="37"/>
-        <v>-5.8620754983143319</v>
-      </c>
-      <c r="CZ15" s="1">
+        <v>21.389530421619078</v>
+      </c>
+      <c r="CZ16" s="1">
         <f t="shared" si="37"/>
-        <v>-5.8034547433311889</v>
-      </c>
-      <c r="DA15" s="1">
+        <v>21.175635117402887</v>
+      </c>
+      <c r="DA16" s="1">
         <f t="shared" si="37"/>
-        <v>-5.7454201958978768</v>
-      </c>
-      <c r="DB15" s="1">
+        <v>20.963878766228859</v>
+      </c>
+      <c r="DB16" s="1">
         <f t="shared" si="37"/>
-        <v>-5.6879659939388976</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" ref="DC15:EO15" si="38">DB15*(1+$AS$20)</f>
-        <v>-5.6310863339995088</v>
-      </c>
-      <c r="DD15" s="1">
+        <v>20.75423997856657</v>
+      </c>
+      <c r="DC16" s="1">
+        <f t="shared" ref="DC16:EO16" si="38">DB16*(1+$AS$21)</f>
+        <v>20.546697578780904</v>
+      </c>
+      <c r="DD16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.5747754706595138</v>
-      </c>
-      <c r="DE15" s="1">
+        <v>20.341230602993093</v>
+      </c>
+      <c r="DE16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.5190277159529186</v>
-      </c>
-      <c r="DF15" s="1">
+        <v>20.137818296963161</v>
+      </c>
+      <c r="DF16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.463837438793389</v>
-      </c>
-      <c r="DG15" s="1">
+        <v>19.93644011399353</v>
+      </c>
+      <c r="DG16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.4091990644054553</v>
-      </c>
-      <c r="DH15" s="1">
+        <v>19.737075712853596</v>
+      </c>
+      <c r="DH16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.3551070737614008</v>
-      </c>
-      <c r="DI15" s="1">
+        <v>19.53970495572506</v>
+      </c>
+      <c r="DI16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.3015560030237872</v>
-      </c>
-      <c r="DJ15" s="1">
+        <v>19.34430790616781</v>
+      </c>
+      <c r="DJ16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.2485404429935496</v>
-      </c>
-      <c r="DK15" s="1">
+        <v>19.150864827106133</v>
+      </c>
+      <c r="DK16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.1960550385636139</v>
-      </c>
-      <c r="DL15" s="1">
+        <v>18.959356178835073</v>
+      </c>
+      <c r="DL16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.144094488177978</v>
-      </c>
-      <c r="DM15" s="1">
+        <v>18.769762617046723</v>
+      </c>
+      <c r="DM16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.0926535432961986</v>
-      </c>
-      <c r="DN15" s="1">
+        <v>18.582064990876255</v>
+      </c>
+      <c r="DN16" s="1">
         <f t="shared" si="38"/>
-        <v>-5.0417270078632361</v>
-      </c>
-      <c r="DO15" s="1">
+        <v>18.396244340967492</v>
+      </c>
+      <c r="DO16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.9913097377846034</v>
-      </c>
-      <c r="DP15" s="1">
+        <v>18.212281897557816</v>
+      </c>
+      <c r="DP16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.9413966404067571</v>
-      </c>
-      <c r="DQ15" s="1">
+        <v>18.030159078582237</v>
+      </c>
+      <c r="DQ16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.8919826740026897</v>
-      </c>
-      <c r="DR15" s="1">
+        <v>17.849857487796413</v>
+      </c>
+      <c r="DR16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.8430628472626625</v>
-      </c>
-      <c r="DS15" s="1">
+        <v>17.67135891291845</v>
+      </c>
+      <c r="DS16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.7946322187900359</v>
-      </c>
-      <c r="DT15" s="1">
+        <v>17.494645323789264</v>
+      </c>
+      <c r="DT16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.7466858966021359</v>
-      </c>
-      <c r="DU15" s="1">
+        <v>17.31969887055137</v>
+      </c>
+      <c r="DU16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.6992190376361149</v>
-      </c>
-      <c r="DV15" s="1">
+        <v>17.146501881845857</v>
+      </c>
+      <c r="DV16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.6522268472597537</v>
-      </c>
-      <c r="DW15" s="1">
+        <v>16.975036863027398</v>
+      </c>
+      <c r="DW16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.6057045787871562</v>
-      </c>
-      <c r="DX15" s="1">
+        <v>16.805286494397123</v>
+      </c>
+      <c r="DX16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.5596475329992847</v>
-      </c>
-      <c r="DY15" s="1">
+        <v>16.637233629453153</v>
+      </c>
+      <c r="DY16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.5140510576692918</v>
-      </c>
-      <c r="DZ15" s="1">
+        <v>16.47086129315862</v>
+      </c>
+      <c r="DZ16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.4689105470925989</v>
-      </c>
-      <c r="EA15" s="1">
+        <v>16.306152680227033</v>
+      </c>
+      <c r="EA16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.4242214416216727</v>
-      </c>
-      <c r="EB15" s="1">
+        <v>16.143091153424763</v>
+      </c>
+      <c r="EB16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.3799792272054558</v>
-      </c>
-      <c r="EC15" s="1">
+        <v>15.981660241890514</v>
+      </c>
+      <c r="EC16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.3361794349334009</v>
-      </c>
-      <c r="ED15" s="1">
+        <v>15.821843639471609</v>
+      </c>
+      <c r="ED16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.292817640584067</v>
-      </c>
-      <c r="EE15" s="1">
+        <v>15.663625203076894</v>
+      </c>
+      <c r="EE16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.2498894641782261</v>
-      </c>
-      <c r="EF15" s="1">
+        <v>15.506988951046125</v>
+      </c>
+      <c r="EF16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.207390569536444</v>
-      </c>
-      <c r="EG15" s="1">
+        <v>15.351919061535664</v>
+      </c>
+      <c r="EG16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.1653166638410797</v>
-      </c>
-      <c r="EH15" s="1">
+        <v>15.198399870920307</v>
+      </c>
+      <c r="EH16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.1236634972026689</v>
-      </c>
-      <c r="EI15" s="1">
+        <v>15.046415872211103</v>
+      </c>
+      <c r="EI16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.0824268622306423</v>
-      </c>
-      <c r="EJ15" s="1">
+        <v>14.895951713488992</v>
+      </c>
+      <c r="EJ16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.041602593608336</v>
-      </c>
-      <c r="EK15" s="1">
+        <v>14.746992196354103</v>
+      </c>
+      <c r="EK16" s="1">
         <f t="shared" si="38"/>
-        <v>-4.0011865676722529</v>
-      </c>
-      <c r="EL15" s="1">
+        <v>14.599522274390562</v>
+      </c>
+      <c r="EL16" s="1">
         <f t="shared" si="38"/>
-        <v>-3.9611747019955303</v>
-      </c>
-      <c r="EM15" s="1">
+        <v>14.453527051646656</v>
+      </c>
+      <c r="EM16" s="1">
         <f t="shared" si="38"/>
-        <v>-3.9215629549755748</v>
-      </c>
-      <c r="EN15" s="1">
+        <v>14.308991781130189</v>
+      </c>
+      <c r="EN16" s="1">
         <f t="shared" si="38"/>
-        <v>-3.882347325425819</v>
-      </c>
-      <c r="EO15" s="1">
+        <v>14.165901863318886</v>
+      </c>
+      <c r="EO16" s="1">
         <f t="shared" si="38"/>
-        <v>-3.8435238521715607</v>
-      </c>
-    </row>
-    <row r="16" spans="2:145" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="D16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="E16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="F16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="G16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="H16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="I16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="J16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="K16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="L16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="M16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="N16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="O16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="P16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>104.3</v>
-      </c>
-      <c r="R16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="S16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="T16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="U16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="V16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="X16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="Y16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="Z16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="AA16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="AB16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="AC16" s="2">
-        <v>103.7</v>
-      </c>
-      <c r="AD16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AE16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AF16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AG16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AH16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AI16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AJ16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AK16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AL16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AM16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AN16" s="2">
-        <v>105.1</v>
-      </c>
-      <c r="AO16" s="2">
-        <v>105.1</v>
+        <v>14.024242844685697</v>
       </c>
     </row>
     <row r="17" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="D17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="E17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="F17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="G17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="H17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="I17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="J17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="K17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="L17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="M17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="N17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="O17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="P17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="Q17" s="2">
+        <v>104.3</v>
+      </c>
+      <c r="R17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="S17" s="2">
+        <v>106.6</v>
+      </c>
+      <c r="T17" s="2">
+        <v>106.6</v>
+      </c>
+      <c r="U17" s="2">
+        <v>106.6</v>
+      </c>
+      <c r="V17" s="2">
+        <v>106.6</v>
+      </c>
+      <c r="X17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="Y17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="AA17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="AB17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>103.7</v>
+      </c>
+      <c r="AD17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AE17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AF17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AG17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AH17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AI17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AJ17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AK17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AL17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AM17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AN17" s="2">
+        <v>105.1</v>
+      </c>
+      <c r="AO17" s="2">
+        <v>105.1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="7">
-        <f t="shared" ref="C17:P17" si="39">C15/C16</f>
+      <c r="C18" s="7">
+        <f t="shared" ref="C18:P18" si="39">C16/C17</f>
         <v>-0.62777242044358716</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D18" s="7">
         <f t="shared" si="39"/>
         <v>0.31629701060752174</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E18" s="7">
         <f t="shared" si="39"/>
         <v>6.4609450337512156E-2</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F18" s="7">
         <f t="shared" si="39"/>
         <v>0.23432979749276778</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G18" s="7">
         <f t="shared" si="39"/>
         <v>5.4966248794599638E-2</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H18" s="7">
         <f t="shared" si="39"/>
         <v>7.1359691417550733E-2</v>
       </c>
-      <c r="I17" s="7">
+      <c r="I18" s="7">
         <f t="shared" si="39"/>
         <v>2.4271938283510122</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J18" s="7">
         <f t="shared" si="39"/>
         <v>1.8322082931532886E-2</v>
       </c>
-      <c r="K17" s="7">
+      <c r="K18" s="7">
         <f t="shared" si="39"/>
         <v>2.025072324011544E-2</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L18" s="7">
         <f t="shared" si="39"/>
         <v>0.23722275795564132</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M18" s="7">
         <f t="shared" si="39"/>
         <v>-0.17647058823529391</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N18" s="7">
         <f t="shared" si="39"/>
         <v>9.3539054966248564E-2</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O18" s="7">
         <f t="shared" si="39"/>
         <v>-1.3500482160077192E-2</v>
       </c>
-      <c r="P17" s="7">
+      <c r="P18" s="7">
         <f t="shared" si="39"/>
         <v>-5.3037608486017553E-2</v>
       </c>
-      <c r="Q17" s="7">
-        <f t="shared" ref="Q17:R17" si="40">Q15/Q16</f>
+      <c r="Q18" s="7">
+        <f t="shared" ref="Q18:R18" si="40">Q16/Q17</f>
         <v>-0.16203259827420904</v>
       </c>
-      <c r="R17" s="7">
+      <c r="R18" s="7">
         <f t="shared" si="40"/>
         <v>-5.8039961941008543E-2</v>
       </c>
-      <c r="S17" s="7">
-        <f t="shared" ref="S17:V17" si="41">S15/S16</f>
-        <v>-0.27644148430066595</v>
-      </c>
-      <c r="T17" s="7">
+      <c r="S18" s="7">
+        <f t="shared" ref="S18:V18" si="41">S16/S17</f>
+        <v>-0.16416510318949346</v>
+      </c>
+      <c r="T18" s="7">
         <f t="shared" si="41"/>
-        <v>-0.2453116079923883</v>
-      </c>
-      <c r="U17" s="7">
+        <v>-0.20284427767354599</v>
+      </c>
+      <c r="U18" s="7">
         <f t="shared" si="41"/>
-        <v>-0.32521408182683159</v>
-      </c>
-      <c r="V17" s="7">
+        <v>-0.32063789868667919</v>
+      </c>
+      <c r="V18" s="7">
         <f t="shared" si="41"/>
-        <v>-9.954329210275932E-2</v>
-      </c>
-      <c r="X17" s="7">
-        <f t="shared" ref="X17:AD17" si="42">X15/X16</f>
+        <v>-3.3527204502814108E-2</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" ref="X18:AD18" si="42">X16/X17</f>
         <v>-0.13693346190935357</v>
       </c>
-      <c r="Y17" s="7">
+      <c r="Y18" s="7">
         <f t="shared" si="42"/>
         <v>-9.2574734811957424E-2</v>
       </c>
-      <c r="Z17" s="7">
+      <c r="Z18" s="7">
         <f t="shared" si="42"/>
         <v>-5.9787849566056352E-2</v>
       </c>
-      <c r="AA17" s="7">
+      <c r="AA18" s="7">
         <f t="shared" si="42"/>
         <v>-1.2536162005786767E-2</v>
       </c>
-      <c r="AB17" s="7">
+      <c r="AB18" s="7">
         <f t="shared" si="42"/>
         <v>2.5718418514946957</v>
       </c>
-      <c r="AC17" s="7">
+      <c r="AC18" s="7">
         <f t="shared" si="42"/>
         <v>0.17454194792671113</v>
       </c>
-      <c r="AD17" s="7">
+      <c r="AD18" s="7">
         <f t="shared" si="42"/>
         <v>-0.28449096098953325</v>
       </c>
-      <c r="AE17" s="7">
-        <f t="shared" ref="AE17:AO17" si="43">AE15/AE16</f>
-        <v>-0.94651046622264479</v>
-      </c>
-      <c r="AF17" s="7">
+      <c r="AE18" s="7">
+        <f t="shared" ref="AE18:AO18" si="43">AE16/AE17</f>
+        <v>-0.7314671741198866</v>
+      </c>
+      <c r="AF18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.79127397716460535</v>
-      </c>
-      <c r="AG17" s="7">
+        <v>-0.42236986869648019</v>
+      </c>
+      <c r="AG18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.57031491788772593</v>
-      </c>
-      <c r="AH17" s="7">
+        <v>-0.17925537583254059</v>
+      </c>
+      <c r="AH18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.42580576004757387</v>
-      </c>
-      <c r="AI17" s="7">
+        <v>-1.7211336341103327E-2</v>
+      </c>
+      <c r="AI18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.35897727024003773</v>
-      </c>
-      <c r="AJ17" s="7">
+        <v>6.2457700504886492E-2</v>
+      </c>
+      <c r="AJ18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.312006229763725</v>
-      </c>
-      <c r="AK17" s="7">
+        <v>0.12119794388874372</v>
+      </c>
+      <c r="AK18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.27415063747142421</v>
-      </c>
-      <c r="AL17" s="7">
+        <v>0.16862706342595118</v>
+      </c>
+      <c r="AL18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.2344889410981667</v>
-      </c>
-      <c r="AM17" s="7">
+        <v>0.21809989956875206</v>
+      </c>
+      <c r="AM18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.19295628758799407</v>
-      </c>
-      <c r="AN17" s="7">
+        <v>0.26968763046965533</v>
+      </c>
+      <c r="AN18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.14948569228252925</v>
-      </c>
-      <c r="AO17" s="7">
+        <v>0.32346374145676993</v>
+      </c>
+      <c r="AO18" s="7">
         <f t="shared" si="43"/>
-        <v>-0.10400797152656044</v>
+        <v>0.37950409743067487</v>
       </c>
     </row>
-    <row r="19" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="1" t="s">
+    <row r="20" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10">
-        <f t="shared" ref="G19:P19" si="44">G3/C3-1</f>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10">
+        <f t="shared" ref="G20:P20" si="44">G3/C3-1</f>
         <v>1.9153225806451513E-2</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H20" s="10">
         <f t="shared" si="44"/>
         <v>-1.9143576826196496E-2</v>
       </c>
-      <c r="I19" s="10">
+      <c r="I20" s="10">
         <f t="shared" si="44"/>
         <v>-4.1884816753926746E-2</v>
       </c>
-      <c r="J19" s="10">
+      <c r="J20" s="10">
         <f t="shared" si="44"/>
         <v>-1.1084337349397622E-2</v>
       </c>
-      <c r="K19" s="10">
+      <c r="K20" s="10">
         <f t="shared" si="44"/>
         <v>-7.2205736894164207E-2</v>
       </c>
-      <c r="L19" s="10">
+      <c r="L20" s="10">
         <f t="shared" si="44"/>
         <v>-6.0606060606060552E-2</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M20" s="10">
         <f t="shared" si="44"/>
         <v>-4.1287188828172283E-2</v>
       </c>
-      <c r="N19" s="10">
+      <c r="N20" s="10">
         <f t="shared" si="44"/>
         <v>-8.3820662768031129E-2</v>
       </c>
-      <c r="O19" s="10">
+      <c r="O20" s="10">
         <f t="shared" si="44"/>
         <v>-7.0362473347547971E-2</v>
       </c>
-      <c r="P19" s="10">
+      <c r="P20" s="10">
         <f t="shared" si="44"/>
         <v>-0.10825587752870425</v>
       </c>
-      <c r="Q19" s="10">
-        <f t="shared" ref="Q19" si="45">Q3/M3-1</f>
+      <c r="Q20" s="10">
+        <f t="shared" ref="Q20" si="45">Q3/M3-1</f>
         <v>-0.13489550348321733</v>
       </c>
-      <c r="R19" s="10">
-        <f t="shared" ref="R19" si="46">R3/N3-1</f>
+      <c r="R20" s="10">
+        <f t="shared" ref="R20" si="46">R3/N3-1</f>
         <v>-0.23670212765957444</v>
       </c>
-      <c r="S19" s="10">
-        <f t="shared" ref="S19" si="47">S3/O3-1</f>
-        <v>-0.3405963302752294</v>
-      </c>
-      <c r="T19" s="10">
-        <f t="shared" ref="T19" si="48">T3/P3-1</f>
+      <c r="S20" s="10">
+        <f t="shared" ref="S20" si="47">S3/O3-1</f>
+        <v>-0.30389908256880738</v>
+      </c>
+      <c r="T20" s="10">
+        <f t="shared" ref="T20" si="48">T3/P3-1</f>
+        <v>-0.20000000000000007</v>
+      </c>
+      <c r="U20" s="10">
+        <f t="shared" ref="U20" si="49">U3/Q3-1</f>
         <v>-0.25</v>
       </c>
-      <c r="U19" s="10">
-        <f t="shared" ref="U19" si="49">U3/Q3-1</f>
-        <v>-0.25</v>
-      </c>
-      <c r="V19" s="10">
-        <f t="shared" ref="V19" si="50">V3/R3-1</f>
-        <v>-0.15000000000000002</v>
-      </c>
-      <c r="X19" s="10"/>
-      <c r="Y19" s="10">
+      <c r="V20" s="10">
+        <f t="shared" ref="V20" si="50">V3/R3-1</f>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="X20" s="10"/>
+      <c r="Y20" s="10">
         <f>Y3/X3-1</f>
         <v>0.27966365618187461</v>
       </c>
-      <c r="Z19" s="10">
-        <f t="shared" ref="Z19:AO19" si="51">Z3/Y3-1</f>
+      <c r="Z20" s="10">
+        <f t="shared" ref="Z20:AO20" si="51">Z3/Y3-1</f>
         <v>0.56802141640301773</v>
       </c>
-      <c r="AA19" s="10">
+      <c r="AA20" s="10">
         <f t="shared" si="51"/>
         <v>0.20487350613068456</v>
       </c>
-      <c r="AB19" s="10">
+      <c r="AB20" s="10">
         <f t="shared" si="51"/>
         <v>-1.223753703465158E-2</v>
       </c>
-      <c r="AC19" s="10">
+      <c r="AC20" s="10">
         <f t="shared" si="51"/>
         <v>-6.5727699530516381E-2</v>
       </c>
-      <c r="AD19" s="10">
+      <c r="AD20" s="10">
         <f t="shared" si="51"/>
         <v>-0.13791178112786151</v>
       </c>
-      <c r="AE19" s="10">
+      <c r="AE20" s="10">
         <f t="shared" si="51"/>
-        <v>-0.2523477979274612</v>
-      </c>
-      <c r="AF19" s="10">
+        <v>-0.20554566062176172</v>
+      </c>
+      <c r="AF20" s="10">
         <f t="shared" si="51"/>
         <v>-2.0000000000000018E-2</v>
       </c>
-      <c r="AG19" s="10">
+      <c r="AG20" s="10">
         <f t="shared" si="51"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AH19" s="10">
+        <v>0.10000000000000031</v>
+      </c>
+      <c r="AH20" s="10">
         <f t="shared" si="51"/>
         <v>7.0000000000000062E-2</v>
       </c>
-      <c r="AI19" s="10">
+      <c r="AI20" s="10">
         <f t="shared" si="51"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AJ19" s="10">
+      <c r="AJ20" s="10">
         <f t="shared" si="51"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AK19" s="10">
+      <c r="AK20" s="10">
         <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AL19" s="10">
+      <c r="AL20" s="10">
         <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AM19" s="10">
+      <c r="AM20" s="10">
         <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AN19" s="10">
+      <c r="AN20" s="10">
         <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="AO19" s="10">
+      <c r="AO20" s="10">
         <f t="shared" si="51"/>
         <v>3.0000000000000027E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="9">
-        <f t="shared" ref="C20:J20" si="52">C5/C3</f>
-        <v>0.6401209677419355</v>
-      </c>
-      <c r="D20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.69420654911838797</v>
-      </c>
-      <c r="E20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.60965677719604427</v>
-      </c>
-      <c r="F20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.73156626506024103</v>
-      </c>
-      <c r="G20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.72749752720079131</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.76527991782229077</v>
-      </c>
-      <c r="I20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.72556162720097139</v>
-      </c>
-      <c r="J20" s="9">
-        <f t="shared" si="52"/>
-        <v>0.74951267056530213</v>
-      </c>
-      <c r="K20" s="9">
-        <f t="shared" ref="K20:P20" si="53">K5/K3</f>
-        <v>0.73773987206823022</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="53"/>
-        <v>0.74084199015855656</v>
-      </c>
-      <c r="M20" s="9">
-        <f t="shared" si="53"/>
-        <v>0.4705509816339456</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="53"/>
-        <v>0.75638297872340421</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" si="53"/>
-        <v>0.73337155963302758</v>
-      </c>
-      <c r="P20" s="9">
-        <f t="shared" si="53"/>
-        <v>0.72164316370324955</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" ref="Q20:R20" si="54">Q5/Q3</f>
-        <v>0.68228404099560758</v>
-      </c>
-      <c r="R20" s="9">
-        <f t="shared" si="54"/>
-        <v>0.68222996515679446</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" ref="S20:V20" si="55">S5/S3</f>
-        <v>0.67000000000000015</v>
-      </c>
-      <c r="T20" s="9">
-        <f t="shared" si="55"/>
-        <v>0.68</v>
-      </c>
-      <c r="U20" s="9">
-        <f t="shared" si="55"/>
-        <v>0.68</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="55"/>
-        <v>0.68</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" ref="X20:AO20" si="56">X5/X3</f>
-        <v>0.7508564310183744</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.77561450474568028</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.68120440788452585</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.67164755893340189</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.74256651017214403</v>
-      </c>
-      <c r="AC20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.68453378001116694</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.70709196891191717</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.677509474824039</v>
-      </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.69</v>
-      </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AI20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AJ20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AN20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AO20" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AR20" t="s">
-        <v>49</v>
-      </c>
-      <c r="AS20" s="9">
-        <v>-0.01</v>
       </c>
     </row>
     <row r="21" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
+        <v>43</v>
+      </c>
+      <c r="C21" s="9">
+        <f t="shared" ref="C21:J21" si="52">C5/C3</f>
+        <v>0.6401209677419355</v>
+      </c>
+      <c r="D21" s="9">
+        <f t="shared" si="52"/>
+        <v>0.69420654911838797</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" si="52"/>
+        <v>0.60965677719604427</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="52"/>
+        <v>0.73156626506024103</v>
+      </c>
       <c r="G21" s="9">
-        <f t="shared" ref="G21" si="57">G6/C6-1</f>
-        <v>0.1366594360086768</v>
+        <f t="shared" si="52"/>
+        <v>0.72749752720079131</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21" si="58">H6/D6-1</f>
-        <v>0.26201923076923062</v>
+        <f t="shared" si="52"/>
+        <v>0.76527991782229077</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" ref="I21" si="59">I6/E6-1</f>
-        <v>4.8498845265589008E-2</v>
+        <f t="shared" si="52"/>
+        <v>0.72556162720097139</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" ref="J21" si="60">J6/F6-1</f>
-        <v>-3.1380753138075312E-2</v>
+        <f t="shared" si="52"/>
+        <v>0.74951267056530213</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" ref="K21:P21" si="61">K6/G6-1</f>
-        <v>-0.10496183206106868</v>
+        <f t="shared" ref="K21:P21" si="53">K5/K3</f>
+        <v>0.73773987206823022</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="61"/>
-        <v>7.6190476190476364E-3</v>
+        <f t="shared" si="53"/>
+        <v>0.74084199015855656</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="61"/>
-        <v>1.7621145374449476E-2</v>
+        <f t="shared" si="53"/>
+        <v>0.4705509816339456</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="61"/>
-        <v>-1.2958963282937219E-2</v>
+        <f t="shared" si="53"/>
+        <v>0.75638297872340421</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="61"/>
-        <v>-5.3304904051172719E-2</v>
+        <f t="shared" si="53"/>
+        <v>0.73337155963302758</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="61"/>
-        <v>-0.17391304347826075</v>
+        <f t="shared" si="53"/>
+        <v>0.72164316370324955</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" ref="Q21" si="62">Q6/M6-1</f>
-        <v>-0.10606060606060619</v>
+        <f t="shared" ref="Q21:R21" si="54">Q5/Q3</f>
+        <v>0.68228404099560758</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" ref="R21" si="63">R6/N6-1</f>
-        <v>-0.10284463894967177</v>
+        <f t="shared" si="54"/>
+        <v>0.68222996515679446</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21" si="64">S6/O6-1</f>
-        <v>-9.9999999999999978E-2</v>
+        <f t="shared" ref="S21:V21" si="55">S5/S3</f>
+        <v>0.55518945634266892</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21" si="65">T6/P6-1</f>
-        <v>-9.9999999999999978E-2</v>
+        <f t="shared" si="55"/>
+        <v>0.68</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" ref="U21" si="66">U6/Q6-1</f>
-        <v>-9.9999999999999867E-2</v>
+        <f t="shared" si="55"/>
+        <v>0.68</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" ref="V21" si="67">V6/R6-1</f>
-        <v>-0.10000000000000009</v>
-      </c>
-      <c r="X21" s="9"/>
+        <f t="shared" si="55"/>
+        <v>0.68</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" ref="X21:AO21" si="56">X5/X3</f>
+        <v>0.7508564310183744</v>
+      </c>
       <c r="Y21" s="9">
-        <f>Y6/X6-1</f>
-        <v>0.22309711286089251</v>
+        <f t="shared" si="56"/>
+        <v>0.77561450474568028</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:AO21" si="68">Z6/Y6-1</f>
-        <v>0.22246065808297555</v>
+        <f t="shared" si="56"/>
+        <v>0.68120440788452585</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="68"/>
-        <v>4.6225863077823393E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.67164755893340189</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="68"/>
-        <v>9.9552572706935072E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.74256651017214403</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" si="68"/>
-        <v>-2.4923702950152782E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.68453378001116694</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" si="68"/>
-        <v>-0.11111111111111116</v>
+        <f t="shared" si="56"/>
+        <v>0.70709196891191717</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="68"/>
-        <v>-9.9999999999999756E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.64911883095046408</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="68"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.69</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="68"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="68"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="68"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="68"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="68"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="68"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="68"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="68"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AO21" s="9">
-        <f t="shared" si="68"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="56"/>
+        <v>0.7</v>
       </c>
       <c r="AR21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AS21" s="9">
-        <v>0.12</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="22" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="9">
-        <f t="shared" ref="C22:J22" si="69">C7/C3</f>
-        <v>0.13205645161290322</v>
-      </c>
-      <c r="D22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.1093198992443325</v>
-      </c>
-      <c r="E22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.15823152995927864</v>
-      </c>
-      <c r="F22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.14602409638554217</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.21018793273986153</v>
+        <f t="shared" ref="G22" si="57">G6/C6-1</f>
+        <v>0.1366594360086768</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.18130457113507961</v>
+        <f t="shared" ref="H22" si="58">H6/D6-1</f>
+        <v>0.26201923076923062</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.19307832422586524</v>
+        <f t="shared" ref="I22" si="59">I6/E6-1</f>
+        <v>4.8498845265589008E-2</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="69"/>
-        <v>0.18567251461988304</v>
+        <f t="shared" ref="J22" si="60">J6/F6-1</f>
+        <v>-3.1380753138075312E-2</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22:P22" si="70">K7/K3</f>
-        <v>0.19722814498933902</v>
+        <f t="shared" ref="K22:P22" si="61">K6/G6-1</f>
+        <v>-0.10496183206106868</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="70"/>
-        <v>0.16949152542372881</v>
+        <f t="shared" si="61"/>
+        <v>7.6190476190476364E-3</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="70"/>
-        <v>0.1830272324255858</v>
+        <f t="shared" si="61"/>
+        <v>1.7621145374449476E-2</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="70"/>
-        <v>0.15797872340425531</v>
+        <f t="shared" si="61"/>
+        <v>-1.2958963282937219E-2</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="70"/>
-        <v>0.17431192660550457</v>
+        <f t="shared" si="61"/>
+        <v>-5.3304904051172719E-2</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="70"/>
-        <v>0.14408338442673208</v>
+        <f t="shared" si="61"/>
+        <v>-0.17391304347826075</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22:R22" si="71">Q7/Q3</f>
-        <v>0.19399707174231334</v>
+        <f t="shared" ref="Q22" si="62">Q6/M6-1</f>
+        <v>-0.10606060606060619</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" si="71"/>
-        <v>0.19442508710801393</v>
+        <f t="shared" ref="R22" si="63">R6/N6-1</f>
+        <v>-0.10284463894967177</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:V22" si="72">S7/S3</f>
-        <v>0.17</v>
+        <f t="shared" ref="S22" si="64">S6/O6-1</f>
+        <v>-0.33783783783783783</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="72"/>
-        <v>0.17</v>
+        <f t="shared" ref="T22" si="65">T6/P6-1</f>
+        <v>-9.9999999999999978E-2</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="72"/>
-        <v>0.2</v>
+        <f t="shared" ref="U22" si="66">U6/Q6-1</f>
+        <v>-9.9999999999999867E-2</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="72"/>
-        <v>0.2</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" ref="X22:AO22" si="73">X7/X3</f>
-        <v>0.17035191529118654</v>
-      </c>
+        <f t="shared" ref="V22" si="67">V6/R6-1</f>
+        <v>-0.10000000000000009</v>
+      </c>
+      <c r="X22" s="9"/>
       <c r="Y22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15478218544658068</v>
+        <f>Y6/X6-1</f>
+        <v>0.22309711286089251</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.12711469812199289</v>
+        <f t="shared" ref="Z22:AO22" si="68">Z6/Y6-1</f>
+        <v>0.22246065808297555</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.13577225299497617</v>
+        <f t="shared" si="68"/>
+        <v>4.6225863077823393E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.1926186750130412</v>
+        <f t="shared" si="68"/>
+        <v>9.9552572706935072E-2</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.17671691792294808</v>
+        <f t="shared" si="68"/>
+        <v>-2.4923702950152782E-2</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.17535621761658032</v>
+        <f t="shared" si="68"/>
+        <v>-0.11111111111111116</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.18458094206821873</v>
+        <f t="shared" si="68"/>
+        <v>-0.16197183098591528</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.16999999999999998</v>
+        <f t="shared" si="68"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.16</v>
+        <f t="shared" si="68"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="73"/>
-        <v>0.15</v>
+        <f t="shared" si="68"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AS22" s="2">
-        <f>NPV(AS21,AE15:EO15)</f>
-        <v>-326.67571140036154</v>
+        <v>50</v>
+      </c>
+      <c r="AS22" s="9">
+        <v>0.12</v>
       </c>
     </row>
     <row r="23" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
+        <v>45</v>
+      </c>
+      <c r="C23" s="9">
+        <f t="shared" ref="C23:J23" si="69">C7/C3</f>
+        <v>0.13205645161290322</v>
+      </c>
+      <c r="D23" s="9">
+        <f t="shared" si="69"/>
+        <v>0.1093198992443325</v>
+      </c>
+      <c r="E23" s="9">
+        <f t="shared" si="69"/>
+        <v>0.15823152995927864</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="69"/>
+        <v>0.14602409638554217</v>
+      </c>
       <c r="G23" s="9">
-        <f t="shared" ref="G23" si="74">G8/C8-1</f>
-        <v>0.23746701846965701</v>
+        <f t="shared" si="69"/>
+        <v>0.21018793273986153</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23" si="75">H8/D8-1</f>
-        <v>0.35768261964735504</v>
+        <f t="shared" si="69"/>
+        <v>0.18130457113507961</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" ref="I23" si="76">I8/E8-1</f>
-        <v>0.57941176470588251</v>
+        <f t="shared" si="69"/>
+        <v>0.19307832422586524</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" ref="J23" si="77">J8/F8-1</f>
-        <v>0.29894736842105263</v>
+        <f t="shared" si="69"/>
+        <v>0.18567251461988304</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" ref="K23:P23" si="78">K8/G8-1</f>
-        <v>0.25799573560767586</v>
+        <f t="shared" ref="K23:P23" si="70">K7/K3</f>
+        <v>0.19722814498933902</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="78"/>
-        <v>0.30426716141001853</v>
+        <f t="shared" si="70"/>
+        <v>0.16949152542372881</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="78"/>
-        <v>6.3314711359404141E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.1830272324255858</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="78"/>
-        <v>-0.1345218800648299</v>
+        <f t="shared" si="70"/>
+        <v>0.15797872340425531</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="78"/>
-        <v>-5.9322033898305038E-2</v>
+        <f t="shared" si="70"/>
+        <v>0.17431192660550457</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="78"/>
-        <v>-0.2318634423897582</v>
+        <f t="shared" si="70"/>
+        <v>0.14408338442673208</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" ref="Q23" si="79">Q8/M8-1</f>
-        <v>-9.1068301225919468E-2</v>
+        <f t="shared" ref="Q23:R23" si="71">Q7/Q3</f>
+        <v>0.19399707174231334</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" ref="R23" si="80">R8/N8-1</f>
-        <v>5.4307116104868935E-2</v>
+        <f t="shared" si="71"/>
+        <v>0.19442508710801393</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23" si="81">S8/O8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="S23:V23" si="72">S7/S3</f>
+        <v>0.21087314662273476</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23" si="82">T8/P8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="72"/>
+        <v>0.17</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" ref="U23" si="83">U8/Q8-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23" si="84">V8/R8-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="X23" s="9"/>
+        <f t="shared" si="72"/>
+        <v>0.2</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" ref="X23:AO23" si="73">X7/X3</f>
+        <v>0.17035191529118654</v>
+      </c>
       <c r="Y23" s="9">
-        <f>Y8/X8-1</f>
-        <v>0.25482625482625476</v>
+        <f t="shared" si="73"/>
+        <v>0.15478218544658068</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23:AO23" si="85">Z8/Y8-1</f>
-        <v>0.32615384615384624</v>
+        <f t="shared" si="73"/>
+        <v>0.12711469812199289</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="85"/>
-        <v>0.23047177107501926</v>
+        <f t="shared" si="73"/>
+        <v>0.13577225299497617</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="85"/>
-        <v>0.35889377749842866</v>
+        <f t="shared" si="73"/>
+        <v>0.1926186750130412</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="85"/>
-        <v>0.10915818686401502</v>
+        <f t="shared" si="73"/>
+        <v>0.17671691792294808</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="85"/>
-        <v>-9.2160133444537218E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.17535621761658032</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.19471237427520355</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.17</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.16</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="73"/>
+        <v>0.15</v>
       </c>
       <c r="AR23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AS23" s="2">
-        <f>Main!D8</f>
-        <v>401.09999999999997</v>
+        <f>NPV(AS22,AE16:EO16)</f>
+        <v>28.817784958557201</v>
       </c>
     </row>
     <row r="24" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
-        <v>47</v>
-      </c>
-      <c r="C24" s="9">
-        <f t="shared" ref="C24:J24" si="86">C10/C3</f>
-        <v>8.4677419354838759E-2</v>
-      </c>
-      <c r="D24" s="9">
-        <f t="shared" si="86"/>
-        <v>0.17531486146095723</v>
-      </c>
-      <c r="E24" s="9">
-        <f t="shared" si="86"/>
-        <v>1.7452006980803454E-3</v>
-      </c>
-      <c r="F24" s="9">
-        <f t="shared" si="86"/>
-        <v>0.12626506024096393</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" si="86"/>
-        <v>2.6211671612265001E-2</v>
+        <f t="shared" ref="G24" si="74">G8/C8-1</f>
+        <v>0.23746701846965701</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="86"/>
-        <v>3.7493579866461284E-2</v>
+        <f t="shared" ref="H24" si="75">H8/D8-1</f>
+        <v>0.35768261964735504</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="86"/>
-        <v>-6.9216757741348028E-2</v>
+        <f t="shared" ref="I24" si="76">I8/E8-1</f>
+        <v>0.57941176470588251</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="86"/>
-        <v>3.7524366471734703E-2</v>
+        <f t="shared" ref="J24" si="77">J8/F8-1</f>
+        <v>0.29894736842105263</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" ref="K24:P24" si="87">K10/K3</f>
-        <v>-2.3987206823027872E-2</v>
+        <f t="shared" ref="K24:P24" si="78">K8/G8-1</f>
+        <v>0.25799573560767586</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.1022416621104428</v>
+        <f t="shared" si="78"/>
+        <v>0.30426716141001853</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="87"/>
-        <v>-0.36668777707409739</v>
+        <f t="shared" si="78"/>
+        <v>6.3314711359404141E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="87"/>
-        <v>7.1276595744680732E-2</v>
+        <f t="shared" si="78"/>
+        <v>-0.1345218800648299</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="87"/>
-        <v>-1.3761467889908289E-2</v>
+        <f t="shared" si="78"/>
+        <v>-5.9322033898305038E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="87"/>
-        <v>-2.1459227467811245E-2</v>
+        <f t="shared" si="78"/>
+        <v>-0.2318634423897582</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24:R24" si="88">Q10/Q3</f>
-        <v>-0.19399707174231334</v>
+        <f t="shared" ref="Q24" si="79">Q8/M8-1</f>
+        <v>-9.1068301225919468E-2</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" si="88"/>
-        <v>-0.19024390243902436</v>
+        <f t="shared" ref="R24" si="80">R8/N8-1</f>
+        <v>5.4307116104868935E-2</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="89">S10/S3</f>
-        <v>-0.33973913043478254</v>
+        <f t="shared" ref="S24" si="81">S8/O8-1</f>
+        <v>-0.29009009009009012</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="89"/>
-        <v>-0.26179644389944828</v>
+        <f t="shared" ref="T24" si="82">T8/P8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="89"/>
-        <v>-0.39953147877013184</v>
+        <f t="shared" ref="U24" si="83">U8/Q8-1</f>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="89"/>
-        <v>-0.29332240213158439</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" ref="X24:AO24" si="90">X10/X3</f>
-        <v>-1.7440049828713691E-2</v>
-      </c>
+        <f t="shared" ref="V24" si="84">V8/R8-1</f>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="X24" s="9"/>
       <c r="Y24" s="9">
-        <f t="shared" si="90"/>
-        <v>4.3319542467753741E-2</v>
+        <f>Y8/X8-1</f>
+        <v>0.25482625482625476</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" si="90"/>
-        <v>8.8157690516839915E-2</v>
+        <f t="shared" ref="Z24:AO24" si="85">Z8/Y8-1</f>
+        <v>0.32615384615384624</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="90"/>
-        <v>0.10060543604276687</v>
+        <f t="shared" si="85"/>
+        <v>0.23047177107501926</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="90"/>
-        <v>1.1606677099634817E-2</v>
+        <f t="shared" si="85"/>
+        <v>0.35889377749842866</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="90"/>
-        <v>-9.4500279173646076E-2</v>
+        <f t="shared" si="85"/>
+        <v>0.10915818686401502</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="90"/>
-        <v>-9.6664507772020611E-2</v>
+        <f t="shared" si="85"/>
+        <v>-9.2160133444537218E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.32009583107742279</v>
+        <f t="shared" si="85"/>
+        <v>-5.9053743683968762E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.32620903174480409</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.24466655670881832</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.19799989518036887</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.17662846960378678</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.16265484518832934</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.15290940084213381</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.143313455281177</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.13386449137510278</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.12456003712464335</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.11539766482164741</v>
+        <f t="shared" si="85"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AR24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AS24" s="2">
-        <f>AS22+AS23</f>
-        <v>74.42428859963843</v>
+        <f>Main!D8</f>
+        <v>63.900000000000006</v>
       </c>
     </row>
     <row r="25" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:J25" si="91">C14/C13</f>
-        <v>-4.4943820224719107E-2</v>
+        <f t="shared" ref="C25:J25" si="86">C11/C3</f>
+        <v>8.4677419354838759E-2</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="91"/>
-        <v>6.2857142857142848E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.17531486146095723</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="91"/>
-        <v>9.4594594594594447E-2</v>
+        <f t="shared" si="86"/>
+        <v>1.7452006980803454E-3</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="91"/>
-        <v>5.4474708171206185E-2</v>
+        <f t="shared" si="86"/>
+        <v>0.12626506024096393</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="91"/>
-        <v>0.42424242424242503</v>
+        <f t="shared" si="86"/>
+        <v>2.6211671612265001E-2</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="91"/>
-        <v>1.3333333333333313E-2</v>
+        <f t="shared" si="86"/>
+        <v>3.7493579866461284E-2</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="91"/>
-        <v>-1.9822274881516595</v>
+        <f t="shared" si="86"/>
+        <v>-6.9216757741348028E-2</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="91"/>
-        <v>0.13636363636363882</v>
+        <f t="shared" si="86"/>
+        <v>3.7524366471734703E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" ref="K25:P25" si="92">K14/K13</f>
-        <v>0.66666666666666974</v>
+        <f t="shared" ref="K25:P25" si="87">K11/K3</f>
+        <v>-2.3987206823027872E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="92"/>
-        <v>0.44469525959367939</v>
+        <f t="shared" si="87"/>
+        <v>-0.1022416621104428</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="92"/>
-        <v>-1.1049723756906091E-2</v>
+        <f t="shared" si="87"/>
+        <v>-0.36668777707409739</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="92"/>
-        <v>0.45505617977528151</v>
+        <f t="shared" si="87"/>
+        <v>7.1276595744680732E-2</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="92"/>
-        <v>1.1818181818181825</v>
+        <f t="shared" si="87"/>
+        <v>-1.3761467889908289E-2</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="92"/>
-        <v>2.8965517241379479</v>
+        <f t="shared" si="87"/>
+        <v>-2.1459227467811245E-2</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="93">Q14/Q13</f>
-        <v>0.13775510204081631</v>
+        <f t="shared" ref="Q25:R25" si="88">Q11/Q3</f>
+        <v>-0.19399707174231334</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="93"/>
-        <v>-1.9047619047619067</v>
+        <f t="shared" si="88"/>
+        <v>-0.19024390243902436</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="94">S14/S13</f>
-        <v>0</v>
+        <f t="shared" ref="S25:V25" si="89">S11/S3</f>
+        <v>-0.23887973640856672</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="94"/>
-        <v>0</v>
+        <f t="shared" si="89"/>
+        <v>-0.2135591661557327</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="94"/>
-        <v>0</v>
+        <f t="shared" si="89"/>
+        <v>-0.39953147877013184</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="94"/>
-        <v>0</v>
+        <f t="shared" si="89"/>
+        <v>-0.21192004401247011</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" ref="X25:AO25" si="95">X14/X13</f>
-        <v>-0.10937500000000029</v>
+        <f t="shared" ref="X25:AO25" si="90">X11/X3</f>
+        <v>-1.7440049828713691E-2</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="95"/>
-        <v>-0.37142857142857222</v>
+        <f t="shared" si="90"/>
+        <v>4.3319542467753741E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="95"/>
-        <v>-6.749999999999635</v>
+        <f t="shared" si="90"/>
+        <v>8.8157690516839915E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="95"/>
-        <v>1.2241379310345013</v>
+        <f t="shared" si="90"/>
+        <v>0.10060543604276687</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="95"/>
-        <v>-1.5644230769230771</v>
+        <f t="shared" si="90"/>
+        <v>1.1606677099634817E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.64015904572564675</v>
+        <f t="shared" si="90"/>
+        <v>-9.4500279173646076E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="95"/>
-        <v>-1.6936936936937039</v>
+        <f t="shared" si="90"/>
+        <v>-9.6664507772020611E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="95"/>
-        <v>0</v>
+        <f t="shared" si="90"/>
+        <v>-0.2582001610092633</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-0.21745004335104759</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-0.14381731292551669</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-0.10186323288226813</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-8.3238569085631861E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-7.1060904295523503E-2</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-6.2554389648011799E-2</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-5.4178555669506689E-2</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-4.5931199768111698E-2</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-3.7810158869279832E-2</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="95"/>
-        <v>0.15</v>
+        <f t="shared" si="90"/>
+        <v>-2.9813308680053319E-2</v>
       </c>
       <c r="AR25" t="s">
-        <v>54</v>
-      </c>
-      <c r="AS25" s="3">
-        <f>AS24/AO16</f>
-        <v>0.70812834062453311</v>
+        <v>53</v>
+      </c>
+      <c r="AS25" s="2">
+        <f>AS23+AS24</f>
+        <v>92.717784958557203</v>
       </c>
     </row>
     <row r="26" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="9">
+        <f t="shared" ref="C26:J26" si="91">C15/C14</f>
+        <v>-4.4943820224719107E-2</v>
+      </c>
+      <c r="D26" s="9">
+        <f t="shared" si="91"/>
+        <v>6.2857142857142848E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="91"/>
+        <v>9.4594594594594447E-2</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="91"/>
+        <v>5.4474708171206185E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="91"/>
+        <v>0.42424242424242503</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="91"/>
+        <v>1.3333333333333313E-2</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="91"/>
+        <v>-1.9822274881516595</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="91"/>
+        <v>0.13636363636363882</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" ref="K26:P26" si="92">K15/K14</f>
+        <v>0.66666666666666974</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="92"/>
+        <v>0.44469525959367939</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="92"/>
+        <v>-1.1049723756906091E-2</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="92"/>
+        <v>0.45505617977528151</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" si="92"/>
+        <v>1.1818181818181825</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="92"/>
+        <v>2.8965517241379479</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" ref="Q26:R26" si="93">Q15/Q14</f>
+        <v>0.13775510204081631</v>
+      </c>
+      <c r="R26" s="9">
+        <f t="shared" si="93"/>
+        <v>-1.9047619047619067</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26:V26" si="94">S15/S14</f>
+        <v>-6.0606060606060608E-2</v>
+      </c>
+      <c r="T26" s="9">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="U26" s="9">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="V26" s="9">
+        <f t="shared" si="94"/>
+        <v>0</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" ref="X26:AO26" si="95">X15/X14</f>
+        <v>-0.10937500000000029</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" si="95"/>
+        <v>-0.37142857142857222</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" si="95"/>
+        <v>-6.749999999999635</v>
+      </c>
+      <c r="AA26" s="9">
+        <f t="shared" si="95"/>
+        <v>1.2241379310345013</v>
+      </c>
+      <c r="AB26" s="9">
+        <f t="shared" si="95"/>
+        <v>-1.5644230769230771</v>
+      </c>
+      <c r="AC26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.64015904572564675</v>
+      </c>
+      <c r="AD26" s="9">
+        <f t="shared" si="95"/>
+        <v>-1.6936936936937039</v>
+      </c>
+      <c r="AE26" s="9">
+        <f t="shared" si="95"/>
+        <v>-1.3179189532560493E-2</v>
+      </c>
+      <c r="AF26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AG26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AH26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AI26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AJ26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AK26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AL26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AM26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AN26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AO26" s="9">
+        <f t="shared" si="95"/>
+        <v>0.15</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS26" s="3">
+        <f>AS25/AO17</f>
+        <v>0.88218634594250434</v>
+      </c>
+    </row>
+    <row r="27" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="9">
-        <f t="shared" ref="C26:J26" si="96">C15/C3</f>
+      <c r="C27" s="9">
+        <f t="shared" ref="C27:J27" si="96">C16/C3</f>
         <v>-0.32812499999999994</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D27" s="9">
         <f t="shared" si="96"/>
         <v>0.16523929471032747</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E27" s="9">
         <f t="shared" si="96"/>
         <v>3.8976148923792968E-2</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F27" s="9">
         <f t="shared" si="96"/>
         <v>0.11710843373493984</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G27" s="9">
         <f t="shared" si="96"/>
         <v>2.8189910979228402E-2</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H27" s="9">
         <f t="shared" si="96"/>
         <v>3.8007190549563495E-2</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I27" s="9">
         <f t="shared" si="96"/>
         <v>1.5282331511839709</v>
       </c>
-      <c r="J26" s="9">
+      <c r="J27" s="9">
         <f t="shared" si="96"/>
         <v>9.2592592592590662E-3</v>
       </c>
-      <c r="K26" s="9">
-        <f t="shared" ref="K26:P26" si="97">K15/K3</f>
+      <c r="K27" s="9">
+        <f t="shared" ref="K27:P27" si="97">K16/K3</f>
         <v>1.1194029850746115E-2</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L27" s="9">
         <f t="shared" si="97"/>
         <v>0.13449972662657192</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M27" s="9">
         <f t="shared" si="97"/>
         <v>-0.11589613679544002</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N27" s="9">
         <f t="shared" si="97"/>
         <v>5.1595744680850937E-2</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O27" s="9">
         <f t="shared" si="97"/>
         <v>-8.027522935779843E-3</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P27" s="9">
         <f t="shared" si="97"/>
         <v>-3.3721643163703373E-2</v>
       </c>
-      <c r="Q26" s="9">
-        <f t="shared" ref="Q26:R26" si="98">Q15/Q3</f>
+      <c r="Q27" s="9">
+        <f t="shared" ref="Q27:R27" si="98">Q16/Q3</f>
         <v>-0.12371888726207908</v>
       </c>
-      <c r="R26" s="9">
+      <c r="R27" s="9">
         <f t="shared" si="98"/>
         <v>-4.2508710801393713E-2</v>
       </c>
-      <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="99">S15/S3</f>
-        <v>-0.25264347826086947</v>
-      </c>
-      <c r="T26" s="9">
+      <c r="S27" s="9">
+        <f t="shared" ref="S27:V27" si="99">S16/S3</f>
+        <v>-0.1441515650741351</v>
+      </c>
+      <c r="T27" s="9">
         <f t="shared" si="99"/>
-        <v>-0.21076844471694267</v>
-      </c>
-      <c r="U26" s="9">
+        <v>-0.16572041692213368</v>
+      </c>
+      <c r="U27" s="9">
         <f t="shared" si="99"/>
         <v>-0.333626159102001</v>
       </c>
-      <c r="V26" s="9">
+      <c r="V27" s="9">
         <f t="shared" si="99"/>
-        <v>-8.5771674523467956E-2</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" ref="X26:AO26" si="100">X15/X3</f>
+        <v>-2.6216761415734341E-2</v>
+      </c>
+      <c r="X27" s="9">
+        <f t="shared" ref="X27:AO27" si="100">X16/X3</f>
         <v>-4.4222983494238442E-2</v>
       </c>
-      <c r="Y26" s="9">
+      <c r="Y27" s="9">
         <f t="shared" si="100"/>
         <v>-2.3363348746653651E-2</v>
       </c>
-      <c r="Z26" s="9">
+      <c r="Z27" s="9">
         <f t="shared" si="100"/>
         <v>-9.6228465000776729E-3</v>
       </c>
-      <c r="AA26" s="9">
+      <c r="AA27" s="9">
         <f t="shared" si="100"/>
         <v>-1.674610331057694E-3</v>
       </c>
-      <c r="AB26" s="9">
+      <c r="AB27" s="9">
         <f t="shared" si="100"/>
         <v>0.34780907668231603</v>
       </c>
-      <c r="AC26" s="9">
+      <c r="AC27" s="9">
         <f t="shared" si="100"/>
         <v>2.5265214963707351E-2</v>
       </c>
-      <c r="AD26" s="9">
+      <c r="AD27" s="9">
         <f t="shared" si="100"/>
         <v>-4.8413212435233069E-2</v>
       </c>
-      <c r="AE26" s="9">
+      <c r="AE27" s="9">
         <f t="shared" si="100"/>
-        <v>-0.21543746616134263</v>
-      </c>
-      <c r="AF26" s="9">
+        <v>-0.15668280156117859</v>
+      </c>
+      <c r="AF27" s="9">
         <f t="shared" si="100"/>
-        <v>-0.18377931118305477</v>
-      </c>
-      <c r="AG26" s="9">
+        <v>-9.231947798226417E-2</v>
+      </c>
+      <c r="AG27" s="9">
         <f t="shared" si="100"/>
-        <v>-0.12041810340792318</v>
-      </c>
-      <c r="AH26" s="9">
+        <v>-3.5618851775680062E-2</v>
+      </c>
+      <c r="AH27" s="9">
         <f t="shared" si="100"/>
-        <v>-8.4024281101061624E-2</v>
-      </c>
-      <c r="AI26" s="9">
+        <v>-3.1962338028817486E-3</v>
+      </c>
+      <c r="AI27" s="9">
         <f t="shared" si="100"/>
-        <v>-6.7463819452438331E-2</v>
-      </c>
-      <c r="AJ26" s="9">
+        <v>1.1046396821458214E-2</v>
+      </c>
+      <c r="AJ27" s="9">
         <f t="shared" si="100"/>
-        <v>-5.6381146196518531E-2</v>
-      </c>
-      <c r="AK26" s="9">
+        <v>2.0610881310894103E-2</v>
+      </c>
+      <c r="AK27" s="9">
         <f t="shared" si="100"/>
-        <v>-4.8097518502252336E-2</v>
-      </c>
-      <c r="AL26" s="9">
+        <v>2.7841418761279057E-2</v>
+      </c>
+      <c r="AL27" s="9">
         <f t="shared" si="100"/>
-        <v>-3.994096477543907E-2</v>
-      </c>
-      <c r="AM26" s="9">
+        <v>3.4960877643008405E-2</v>
+      </c>
+      <c r="AM27" s="9">
         <f t="shared" si="100"/>
-        <v>-3.1909345455275989E-2</v>
-      </c>
-      <c r="AN26" s="9">
+        <v>4.197113015919416E-2</v>
+      </c>
+      <c r="AN27" s="9">
         <f t="shared" si="100"/>
-        <v>-2.4000559342385465E-2</v>
-      </c>
-      <c r="AO26" s="9">
+        <v>4.8874014923201245E-2</v>
+      </c>
+      <c r="AO27" s="9">
         <f t="shared" si="100"/>
-        <v>-1.6212542884838931E-2</v>
-      </c>
-      <c r="AR26" t="s">
+        <v>5.5671337584043773E-2</v>
+      </c>
+      <c r="AR27" t="s">
         <v>55</v>
       </c>
-      <c r="AS26" s="3">
+      <c r="AS27" s="3">
         <f>Main!D3</f>
-        <v>0.56620000000000004</v>
-      </c>
-    </row>
-    <row r="27" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR27" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AS27" s="10">
-        <f>AS25/AS26-1</f>
-        <v>0.25066821021641306</v>
+        <v>0.98009999999999997</v>
       </c>
     </row>
     <row r="28" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="AR28" t="s">
+      <c r="AR28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="AS28" s="10">
+        <f>AS26/AS27-1</f>
+        <v>-9.9901697844603232E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:45" x14ac:dyDescent="0.3">
+      <c r="AR29" t="s">
         <v>57</v>
       </c>
-      <c r="AS28" s="6" t="s">
+      <c r="AS29" s="6" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="1" t="s">
+    <row r="30" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B30" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="AB29" s="8">
-        <f>AB15</f>
+      <c r="AB30" s="8">
+        <f>AB16</f>
         <v>266.69999999999993</v>
       </c>
-      <c r="AC29" s="8">
-        <f>AC15</f>
+      <c r="AC30" s="8">
+        <f>AC16</f>
         <v>18.099999999999945</v>
       </c>
-      <c r="AD29" s="8">
+      <c r="AD30" s="8">
         <v>-837.1</v>
       </c>
-      <c r="AE29" s="8">
-        <f>AE15</f>
-        <v>-99.47824999999996</v>
-      </c>
-      <c r="AF29" s="8">
-        <f t="shared" ref="AF29:AO29" si="101">AF15</f>
-        <v>-83.16289500000002</v>
-      </c>
-      <c r="AG29" s="8">
+      <c r="AE30" s="8">
+        <f>AE16</f>
+        <v>-76.877200000000073</v>
+      </c>
+      <c r="AF30" s="8">
+        <f t="shared" ref="AF30:AO30" si="101">AF16</f>
+        <v>-44.391073200000065</v>
+      </c>
+      <c r="AG30" s="8">
         <f t="shared" si="101"/>
-        <v>-59.940097869999995</v>
-      </c>
-      <c r="AH29" s="8">
+        <v>-18.839740000000013</v>
+      </c>
+      <c r="AH30" s="8">
         <f t="shared" si="101"/>
-        <v>-44.752185381000011</v>
-      </c>
-      <c r="AI29" s="8">
+        <v>-1.8089114494499596</v>
+      </c>
+      <c r="AI30" s="8">
         <f t="shared" si="101"/>
-        <v>-37.728511102227962</v>
-      </c>
-      <c r="AJ29" s="8">
+        <v>6.5643043230635696</v>
+      </c>
+      <c r="AJ30" s="8">
         <f t="shared" si="101"/>
-        <v>-32.791854748167495</v>
-      </c>
-      <c r="AK29" s="8">
+        <v>12.737903902706964</v>
+      </c>
+      <c r="AK30" s="8">
         <f t="shared" si="101"/>
-        <v>-28.813231998246682</v>
-      </c>
-      <c r="AL29" s="8">
+        <v>17.722704366067468</v>
+      </c>
+      <c r="AL30" s="8">
         <f t="shared" si="101"/>
-        <v>-24.644787709417319</v>
-      </c>
-      <c r="AM29" s="8">
+        <v>22.92229944467584</v>
+      </c>
+      <c r="AM30" s="8">
         <f t="shared" si="101"/>
-        <v>-20.279705825498176</v>
-      </c>
-      <c r="AN29" s="8">
+        <v>28.344169962360773</v>
+      </c>
+      <c r="AN30" s="8">
         <f t="shared" si="101"/>
-        <v>-15.710946258893824</v>
-      </c>
-      <c r="AO29" s="8">
+        <v>33.996039227106515</v>
+      </c>
+      <c r="AO30" s="8">
         <f t="shared" si="101"/>
-        <v>-10.931237807441502</v>
-      </c>
-    </row>
-    <row r="30" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="B30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AB30" s="2">
-        <v>133.5</v>
-      </c>
-      <c r="AC30" s="2">
-        <v>133.5</v>
-      </c>
-      <c r="AD30" s="2">
-        <v>84.6</v>
-      </c>
-      <c r="AE30" s="2">
-        <v>60</v>
-      </c>
-      <c r="AF30" s="2">
-        <f>AE30*0.8</f>
-        <v>48</v>
-      </c>
-      <c r="AG30" s="2">
-        <f t="shared" ref="AG30:AO30" si="102">AF30*0.8</f>
-        <v>38.400000000000006</v>
-      </c>
-      <c r="AH30" s="2">
-        <f t="shared" si="102"/>
-        <v>30.720000000000006</v>
-      </c>
-      <c r="AI30" s="2">
-        <f t="shared" si="102"/>
-        <v>24.576000000000008</v>
-      </c>
-      <c r="AJ30" s="2">
-        <f t="shared" si="102"/>
-        <v>19.660800000000009</v>
-      </c>
-      <c r="AK30" s="2">
-        <f t="shared" si="102"/>
-        <v>15.728640000000008</v>
-      </c>
-      <c r="AL30" s="2">
-        <f t="shared" si="102"/>
-        <v>12.582912000000007</v>
-      </c>
-      <c r="AM30" s="2">
-        <f t="shared" si="102"/>
-        <v>10.066329600000007</v>
-      </c>
-      <c r="AN30" s="2">
-        <f t="shared" si="102"/>
-        <v>8.0530636800000064</v>
-      </c>
-      <c r="AO30" s="2">
-        <f t="shared" si="102"/>
-        <v>6.4424509440000053</v>
+        <v>39.885880639963929</v>
       </c>
     </row>
     <row r="31" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AB31" s="2">
-        <v>90</v>
+        <v>133.5</v>
       </c>
       <c r="AC31" s="2">
-        <v>129.69999999999999</v>
+        <v>133.5</v>
       </c>
       <c r="AD31" s="2">
-        <v>78.3</v>
+        <v>84.6</v>
       </c>
       <c r="AE31" s="2">
         <v>60</v>
       </c>
       <c r="AF31" s="2">
-        <f>AE31*0.97</f>
-        <v>58.199999999999996</v>
+        <f>AE31*0.8</f>
+        <v>48</v>
       </c>
       <c r="AG31" s="2">
-        <f t="shared" ref="AG31:AO31" si="103">AF31*0.97</f>
-        <v>56.453999999999994</v>
+        <f t="shared" ref="AG31:AO31" si="102">AF31*0.8</f>
+        <v>38.400000000000006</v>
       </c>
       <c r="AH31" s="2">
-        <f t="shared" si="103"/>
-        <v>54.760379999999991</v>
+        <f t="shared" si="102"/>
+        <v>30.720000000000006</v>
       </c>
       <c r="AI31" s="2">
-        <f t="shared" si="103"/>
-        <v>53.117568599999991</v>
+        <f t="shared" si="102"/>
+        <v>24.576000000000008</v>
       </c>
       <c r="AJ31" s="2">
-        <f t="shared" si="103"/>
-        <v>51.524041541999992</v>
+        <f t="shared" si="102"/>
+        <v>19.660800000000009</v>
       </c>
       <c r="AK31" s="2">
-        <f t="shared" si="103"/>
-        <v>49.978320295739991</v>
+        <f t="shared" si="102"/>
+        <v>15.728640000000008</v>
       </c>
       <c r="AL31" s="2">
-        <f t="shared" si="103"/>
-        <v>48.47897068686779</v>
+        <f t="shared" si="102"/>
+        <v>12.582912000000007</v>
       </c>
       <c r="AM31" s="2">
-        <f t="shared" si="103"/>
-        <v>47.024601566261758</v>
+        <f t="shared" si="102"/>
+        <v>10.066329600000007</v>
       </c>
       <c r="AN31" s="2">
-        <f t="shared" si="103"/>
-        <v>45.613863519273906</v>
+        <f t="shared" si="102"/>
+        <v>8.0530636800000064</v>
       </c>
       <c r="AO31" s="2">
-        <f t="shared" si="103"/>
-        <v>44.245447613695688</v>
+        <f t="shared" si="102"/>
+        <v>6.4424509440000053</v>
       </c>
     </row>
     <row r="32" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AB32" s="2">
-        <v>-168.9</v>
+        <v>90</v>
       </c>
       <c r="AC32" s="2">
-        <v>26.6</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="AD32" s="2">
-        <v>143.30000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="AE32" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF32" s="2">
-        <v>0</v>
+        <f>AE32*0.97</f>
+        <v>58.199999999999996</v>
       </c>
       <c r="AG32" s="2">
-        <v>0</v>
+        <f t="shared" ref="AG32:AO32" si="103">AF32*0.97</f>
+        <v>56.453999999999994</v>
       </c>
       <c r="AH32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>54.760379999999991</v>
       </c>
       <c r="AI32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>53.117568599999991</v>
       </c>
       <c r="AJ32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>51.524041541999992</v>
       </c>
       <c r="AK32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>49.978320295739991</v>
       </c>
       <c r="AL32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>48.47897068686779</v>
       </c>
       <c r="AM32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>47.024601566261758</v>
       </c>
       <c r="AN32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>45.613863519273906</v>
       </c>
       <c r="AO32" s="2">
-        <v>0</v>
+        <f t="shared" si="103"/>
+        <v>44.245447613695688</v>
       </c>
     </row>
     <row r="33" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AB33" s="2">
-        <v>-93.5</v>
+        <v>-168.9</v>
       </c>
       <c r="AC33" s="2">
-        <v>-85.9</v>
+        <v>26.6</v>
       </c>
       <c r="AD33" s="2">
-        <v>-19.5</v>
+        <v>143.30000000000001</v>
       </c>
       <c r="AE33" s="2">
         <v>0</v>
@@ -5261,16 +5256,16 @@
     </row>
     <row r="34" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AB34" s="2">
-        <v>0</v>
+        <v>-93.5</v>
       </c>
       <c r="AC34" s="2">
-        <v>7</v>
+        <v>-85.9</v>
       </c>
       <c r="AD34" s="2">
-        <v>0</v>
+        <v>-19.5</v>
       </c>
       <c r="AE34" s="2">
         <v>0</v>
@@ -5308,16 +5303,16 @@
     </row>
     <row r="35" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AB35" s="2">
         <v>0</v>
       </c>
       <c r="AC35" s="2">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="AD35" s="2">
-        <v>677.2</v>
+        <v>0</v>
       </c>
       <c r="AE35" s="2">
         <v>0</v>
@@ -5355,201 +5350,201 @@
     </row>
     <row r="36" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AB36" s="2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC36" s="2">
-        <v>4.0999999999999996</v>
+        <v>3.6</v>
       </c>
       <c r="AD36" s="2">
-        <v>5.8</v>
+        <v>677.2</v>
       </c>
       <c r="AE36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AF36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AG36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AH36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AI36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AK36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AL36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AM36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AN36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AO36" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AB37" s="2">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="AC37" s="2">
-        <v>3.2</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="AD37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AE37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AF37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AG37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AH37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AI37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AJ37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AK37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AL37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AM37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AN37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
       <c r="AO37" s="2">
-        <v>2.1</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="38" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AB38" s="2">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="AC38" s="2">
-        <v>6.1</v>
+        <v>3.2</v>
       </c>
       <c r="AD38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AE38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AF38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AG38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AH38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AI38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AJ38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AK38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AL38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AM38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AN38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
       <c r="AO38" s="2">
-        <v>5.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="39" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AB39" s="2">
-        <v>9.6999999999999993</v>
+        <v>6.3</v>
       </c>
       <c r="AC39" s="2">
-        <v>2.1</v>
+        <v>6.1</v>
       </c>
       <c r="AD39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AE39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AF39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AG39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AH39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AI39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AJ39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AK39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AL39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AM39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AN39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO39" s="2">
-        <v>0</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="40" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AB40" s="2">
-        <v>-5</v>
+        <v>9.6999999999999993</v>
       </c>
       <c r="AC40" s="2">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD40" s="2">
         <v>0</v>
@@ -5590,10 +5585,10 @@
     </row>
     <row r="41" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AB41" s="2">
-        <v>1.6</v>
+        <v>-5</v>
       </c>
       <c r="AC41" s="2">
         <v>0</v>
@@ -5637,10 +5632,10 @@
     </row>
     <row r="42" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="AB42" s="2">
-        <v>-4.5999999999999996</v>
+        <v>1.6</v>
       </c>
       <c r="AC42" s="2">
         <v>0</v>
@@ -5684,16 +5679,16 @@
     </row>
     <row r="43" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="AB43" s="2">
-        <v>5.2</v>
+        <v>-4.5999999999999996</v>
       </c>
       <c r="AC43" s="2">
         <v>0</v>
       </c>
       <c r="AD43" s="2">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AE43" s="2">
         <v>0</v>
@@ -5731,16 +5726,16 @@
     </row>
     <row r="44" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="AB44" s="2">
-        <v>0.4</v>
+        <v>5.2</v>
       </c>
       <c r="AC44" s="2">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="AD44" s="2">
-        <v>0.7</v>
+        <v>5.6</v>
       </c>
       <c r="AE44" s="2">
         <v>0</v>
@@ -5778,16 +5773,16 @@
     </row>
     <row r="45" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB45" s="2">
-        <v>-3.8</v>
+        <v>0.4</v>
       </c>
       <c r="AC45" s="2">
-        <v>-7.8</v>
+        <v>-1.2</v>
       </c>
       <c r="AD45" s="2">
-        <v>7.8</v>
+        <v>0.7</v>
       </c>
       <c r="AE45" s="2">
         <v>0</v>
@@ -5825,16 +5820,16 @@
     </row>
     <row r="46" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AB46" s="2">
-        <v>17.2</v>
+        <v>-3.8</v>
       </c>
       <c r="AC46" s="2">
-        <v>3.5</v>
+        <v>-7.8</v>
       </c>
       <c r="AD46" s="2">
-        <v>-41.7</v>
+        <v>7.8</v>
       </c>
       <c r="AE46" s="2">
         <v>0</v>
@@ -5872,16 +5867,16 @@
     </row>
     <row r="47" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AB47" s="2">
-        <v>14.6</v>
+        <v>17.2</v>
       </c>
       <c r="AC47" s="2">
-        <v>10.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD47" s="2">
-        <v>1.1000000000000001</v>
+        <v>-41.7</v>
       </c>
       <c r="AE47" s="2">
         <v>0</v>
@@ -5919,16 +5914,16 @@
     </row>
     <row r="48" spans="2:41" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AB48" s="2">
-        <v>-4.0999999999999996</v>
+        <v>14.6</v>
       </c>
       <c r="AC48" s="2">
-        <v>13.1</v>
+        <v>10.8</v>
       </c>
       <c r="AD48" s="2">
-        <v>-12.4</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="AE48" s="2">
         <v>0</v>
@@ -5966,16 +5961,16 @@
     </row>
     <row r="49" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AB49" s="2">
-        <v>7.5</v>
+        <v>-4.0999999999999996</v>
       </c>
       <c r="AC49" s="2">
-        <v>-1.6</v>
+        <v>13.1</v>
       </c>
       <c r="AD49" s="2">
-        <v>-15.9</v>
+        <v>-12.4</v>
       </c>
       <c r="AE49" s="2">
         <v>0</v>
@@ -6013,16 +6008,16 @@
     </row>
     <row r="50" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AB50" s="2">
-        <v>-20.100000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="AC50" s="2">
-        <v>-7.3</v>
+        <v>-1.6</v>
       </c>
       <c r="AD50" s="2">
-        <v>47.1</v>
+        <v>-15.9</v>
       </c>
       <c r="AE50" s="2">
         <v>0</v>
@@ -6060,718 +6055,765 @@
     </row>
     <row r="51" spans="2:150" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
+        <v>82</v>
+      </c>
+      <c r="AB51" s="2">
+        <v>-20.100000000000001</v>
+      </c>
+      <c r="AC51" s="2">
+        <v>-7.3</v>
+      </c>
+      <c r="AD51" s="2">
+        <v>47.1</v>
+      </c>
+      <c r="AE51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN51" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:150" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
         <v>83</v>
       </c>
-      <c r="AB51" s="2">
+      <c r="AB52" s="2">
         <v>-5.8</v>
       </c>
-      <c r="AC51" s="2">
+      <c r="AC52" s="2">
         <v>-11.3</v>
       </c>
-      <c r="AD51" s="2">
+      <c r="AD52" s="2">
         <v>-7.8</v>
       </c>
-      <c r="AE51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AK51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AL51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AM51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AN51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AO51" s="2">
+      <c r="AE52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="2">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="1" t="s">
+    <row r="53" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B53" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="AB52" s="8">
-        <f>AB29+SUM(AB30:AB51)</f>
+      <c r="AB53" s="8">
+        <f>AB30+SUM(AB31:AB52)</f>
         <v>255.59999999999991</v>
       </c>
-      <c r="AC52" s="8">
-        <f>AC29+SUM(AC30:AC51)</f>
+      <c r="AC53" s="8">
+        <f>AC30+SUM(AC31:AC52)</f>
         <v>246.2999999999999</v>
       </c>
-      <c r="AD52" s="8">
-        <f>AD29+SUM(AD30:AD51)</f>
+      <c r="AD53" s="8">
+        <f>AD30+SUM(AD31:AD52)</f>
         <v>125.10000000000014</v>
       </c>
-      <c r="AE52" s="8">
-        <f>AE29+SUM(AE30:AE51)</f>
-        <v>34.321750000000023</v>
-      </c>
-      <c r="AF52" s="8">
-        <f t="shared" ref="AF52:AO52" si="104">AF29+SUM(AF30:AF51)</f>
-        <v>36.837104999999966</v>
-      </c>
-      <c r="AG52" s="8">
+      <c r="AE53" s="8">
+        <f>AE30+SUM(AE31:AE52)</f>
+        <v>56.92279999999991</v>
+      </c>
+      <c r="AF53" s="8">
+        <f t="shared" ref="AF53:AO53" si="104">AF30+SUM(AF31:AF52)</f>
+        <v>75.608926799999921</v>
+      </c>
+      <c r="AG53" s="8">
         <f t="shared" si="104"/>
-        <v>48.713902130000001</v>
-      </c>
-      <c r="AH52" s="8">
+        <v>89.81425999999999</v>
+      </c>
+      <c r="AH53" s="8">
         <f t="shared" si="104"/>
-        <v>54.528194618999983</v>
-      </c>
-      <c r="AI52" s="8">
+        <v>97.471468550550028</v>
+      </c>
+      <c r="AI53" s="8">
         <f t="shared" si="104"/>
-        <v>53.765057497772027</v>
-      </c>
-      <c r="AJ52" s="8">
+        <v>98.057872923063556</v>
+      </c>
+      <c r="AJ53" s="8">
         <f t="shared" si="104"/>
-        <v>52.192986793832503</v>
-      </c>
-      <c r="AK52" s="8">
+        <v>97.722745444706959</v>
+      </c>
+      <c r="AK53" s="8">
         <f t="shared" si="104"/>
-        <v>50.693728297493323</v>
-      </c>
-      <c r="AL52" s="8">
+        <v>97.229664661807476</v>
+      </c>
+      <c r="AL53" s="8">
         <f t="shared" si="104"/>
-        <v>50.217094977450486</v>
-      </c>
-      <c r="AM52" s="8">
+        <v>97.784182131543645</v>
+      </c>
+      <c r="AM53" s="8">
         <f t="shared" si="104"/>
-        <v>50.611225340763589</v>
-      </c>
-      <c r="AN52" s="8">
+        <v>99.235101128622546</v>
+      </c>
+      <c r="AN53" s="8">
         <f t="shared" si="104"/>
-        <v>51.755980940380084</v>
-      </c>
-      <c r="AO52" s="8">
+        <v>101.46296642638043</v>
+      </c>
+      <c r="AO53" s="8">
         <f t="shared" si="104"/>
-        <v>53.556660750254196</v>
+        <v>104.37377919765963</v>
       </c>
     </row>
-    <row r="53" spans="2:150" x14ac:dyDescent="0.3">
-      <c r="B53" t="s">
+    <row r="54" spans="2:150" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
         <v>69</v>
       </c>
-      <c r="AB53" s="2">
+      <c r="AB54" s="2">
         <v>103.1</v>
       </c>
-      <c r="AC53" s="2">
+      <c r="AC54" s="2">
         <v>83.1</v>
       </c>
-      <c r="AD53" s="2">
+      <c r="AD54" s="2">
         <v>75</v>
       </c>
-      <c r="AE53" s="2">
+      <c r="AE54" s="2">
         <v>65</v>
       </c>
-      <c r="AF53" s="2">
-        <f>AE53*0.99</f>
+      <c r="AF54" s="2">
+        <f>AE54*0.99</f>
         <v>64.349999999999994</v>
       </c>
-      <c r="AG53" s="2">
-        <f t="shared" ref="AG53:AO53" si="105">AF53*0.99</f>
+      <c r="AG54" s="2">
+        <f t="shared" ref="AG54:AO54" si="105">AF54*0.99</f>
         <v>63.706499999999991</v>
       </c>
-      <c r="AH53" s="2">
+      <c r="AH54" s="2">
         <f t="shared" si="105"/>
         <v>63.069434999999991</v>
       </c>
-      <c r="AI53" s="2">
+      <c r="AI54" s="2">
         <f t="shared" si="105"/>
         <v>62.438740649999993</v>
       </c>
-      <c r="AJ53" s="2">
+      <c r="AJ54" s="2">
         <f t="shared" si="105"/>
         <v>61.814353243499994</v>
       </c>
-      <c r="AK53" s="2">
+      <c r="AK54" s="2">
         <f t="shared" si="105"/>
         <v>61.196209711064995</v>
       </c>
-      <c r="AL53" s="2">
+      <c r="AL54" s="2">
         <f t="shared" si="105"/>
         <v>60.584247613954346</v>
       </c>
-      <c r="AM53" s="2">
+      <c r="AM54" s="2">
         <f t="shared" si="105"/>
         <v>59.978405137814804</v>
       </c>
-      <c r="AN53" s="2">
+      <c r="AN54" s="2">
         <f t="shared" si="105"/>
         <v>59.378621086436652</v>
       </c>
-      <c r="AO53" s="2">
+      <c r="AO54" s="2">
         <f t="shared" si="105"/>
         <v>58.784834875572287</v>
       </c>
     </row>
-    <row r="54" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="1" t="s">
+    <row r="55" spans="2:150" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B55" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="AB54" s="8">
-        <f>AB52-AB53</f>
+      <c r="AB55" s="8">
+        <f>AB53-AB54</f>
         <v>152.49999999999991</v>
       </c>
-      <c r="AC54" s="8">
-        <f>AC52-AC53</f>
+      <c r="AC55" s="8">
+        <f>AC53-AC54</f>
         <v>163.1999999999999</v>
       </c>
-      <c r="AD54" s="8">
-        <f>AD52-AD53</f>
+      <c r="AD55" s="8">
+        <f>AD53-AD54</f>
         <v>50.100000000000136</v>
       </c>
-      <c r="AE54" s="8">
-        <f>AE52-AE53</f>
-        <v>-30.678249999999977</v>
-      </c>
-      <c r="AF54" s="8">
-        <f t="shared" ref="AF54:AO54" si="106">AF52-AF53</f>
-        <v>-27.512895000000029</v>
-      </c>
-      <c r="AG54" s="8">
+      <c r="AE55" s="8">
+        <f>AE53-AE54</f>
+        <v>-8.0772000000000901</v>
+      </c>
+      <c r="AF55" s="8">
+        <f t="shared" ref="AF55:AO55" si="106">AF53-AF54</f>
+        <v>11.258926799999927</v>
+      </c>
+      <c r="AG55" s="8">
         <f t="shared" si="106"/>
-        <v>-14.99259786999999</v>
-      </c>
-      <c r="AH54" s="8">
+        <v>26.107759999999999</v>
+      </c>
+      <c r="AH55" s="8">
         <f t="shared" si="106"/>
-        <v>-8.5412403810000086</v>
-      </c>
-      <c r="AI54" s="8">
+        <v>34.402033550550037</v>
+      </c>
+      <c r="AI55" s="8">
         <f t="shared" si="106"/>
-        <v>-8.6736831522279658</v>
-      </c>
-      <c r="AJ54" s="8">
+        <v>35.619132273063563</v>
+      </c>
+      <c r="AJ55" s="8">
         <f t="shared" si="106"/>
-        <v>-9.6213664496674909</v>
-      </c>
-      <c r="AK54" s="8">
+        <v>35.908392201206965</v>
+      </c>
+      <c r="AK55" s="8">
         <f t="shared" si="106"/>
-        <v>-10.502481413571672</v>
-      </c>
-      <c r="AL54" s="8">
+        <v>36.033454950742481</v>
+      </c>
+      <c r="AL55" s="8">
         <f t="shared" si="106"/>
-        <v>-10.36715263650386</v>
-      </c>
-      <c r="AM54" s="8">
+        <v>37.199934517589298</v>
+      </c>
+      <c r="AM55" s="8">
         <f t="shared" si="106"/>
-        <v>-9.3671797970512145</v>
-      </c>
-      <c r="AN54" s="8">
+        <v>39.256695990807742</v>
+      </c>
+      <c r="AN55" s="8">
         <f t="shared" si="106"/>
-        <v>-7.6226401460565683</v>
-      </c>
-      <c r="AO54" s="8">
+        <v>42.084345339943781</v>
+      </c>
+      <c r="AO55" s="8">
         <f t="shared" si="106"/>
-        <v>-5.2281741253180911</v>
-      </c>
-      <c r="AP54" s="1">
-        <f>AO54*(1+$AS$20)</f>
-        <v>-5.1758923840649098</v>
-      </c>
-      <c r="AQ54" s="1">
-        <f t="shared" ref="AQ54:DB54" si="107">AP54*(1+$AS$20)</f>
-        <v>-5.124133460224261</v>
-      </c>
-      <c r="AR54" s="1">
+        <v>45.588944322087343</v>
+      </c>
+      <c r="AP55" s="1">
+        <f>AO55*(1+$AS$21)</f>
+        <v>45.133054878866467</v>
+      </c>
+      <c r="AQ55" s="1">
+        <f t="shared" ref="AQ55:DB55" si="107">AP55*(1+$AS$21)</f>
+        <v>44.681724330077799</v>
+      </c>
+      <c r="AR55" s="1">
         <f t="shared" si="107"/>
-        <v>-5.0728921256220181</v>
-      </c>
-      <c r="AS54" s="1">
+        <v>44.234907086777021</v>
+      </c>
+      <c r="AS55" s="1">
         <f t="shared" si="107"/>
-        <v>-5.022163204365798</v>
-      </c>
-      <c r="AT54" s="1">
+        <v>43.79255801590925</v>
+      </c>
+      <c r="AT55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.9719415723221401</v>
-      </c>
-      <c r="AU54" s="1">
+        <v>43.354632435750155</v>
+      </c>
+      <c r="AU55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.9222221565989184</v>
-      </c>
-      <c r="AV54" s="1">
+        <v>42.921086111392654</v>
+      </c>
+      <c r="AV55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.8729999350329294</v>
-      </c>
-      <c r="AW54" s="1">
+        <v>42.491875250278724</v>
+      </c>
+      <c r="AW55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.8242699356826</v>
-      </c>
-      <c r="AX54" s="1">
+        <v>42.066956497775934</v>
+      </c>
+      <c r="AX55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.7760272363257741</v>
-      </c>
-      <c r="AY54" s="1">
+        <v>41.646286932798176</v>
+      </c>
+      <c r="AY55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.7282669639625166</v>
-      </c>
-      <c r="AZ54" s="1">
+        <v>41.229824063470197</v>
+      </c>
+      <c r="AZ55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.680984294322891</v>
-      </c>
-      <c r="BA54" s="1">
+        <v>40.817525822835492</v>
+      </c>
+      <c r="BA55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.6341744513796623</v>
-      </c>
-      <c r="BB54" s="1">
+        <v>40.409350564607138</v>
+      </c>
+      <c r="BB55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.587832706865866</v>
-      </c>
-      <c r="BC54" s="1">
+        <v>40.005257058961064</v>
+      </c>
+      <c r="BC55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.5419543797972075</v>
-      </c>
-      <c r="BD54" s="1">
+        <v>39.605204488371456</v>
+      </c>
+      <c r="BD55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.4965348359992356</v>
-      </c>
-      <c r="BE54" s="1">
+        <v>39.209152443487739</v>
+      </c>
+      <c r="BE55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.4515694876392429</v>
-      </c>
-      <c r="BF54" s="1">
+        <v>38.817060919052864</v>
+      </c>
+      <c r="BF55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.4070537927628504</v>
-      </c>
-      <c r="BG54" s="1">
+        <v>38.428890309862332</v>
+      </c>
+      <c r="BG55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.3629832548352221</v>
-      </c>
-      <c r="BH54" s="1">
+        <v>38.044601406763711</v>
+      </c>
+      <c r="BH55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.3193534222868699</v>
-      </c>
-      <c r="BI54" s="1">
+        <v>37.664155392696074</v>
+      </c>
+      <c r="BI55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.2761598880640008</v>
-      </c>
-      <c r="BJ54" s="1">
+        <v>37.287513838769115</v>
+      </c>
+      <c r="BJ55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.233398289183361</v>
-      </c>
-      <c r="BK54" s="1">
+        <v>36.914638700381424</v>
+      </c>
+      <c r="BK55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.1910643062915272</v>
-      </c>
-      <c r="BL54" s="1">
+        <v>36.545492313377608</v>
+      </c>
+      <c r="BL55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.1491536632286117</v>
-      </c>
-      <c r="BM54" s="1">
+        <v>36.180037390243832</v>
+      </c>
+      <c r="BM55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.1076621265963258</v>
-      </c>
-      <c r="BN54" s="1">
+        <v>35.818237016341392</v>
+      </c>
+      <c r="BN55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.0665855053303623</v>
-      </c>
-      <c r="BO54" s="1">
+        <v>35.46005464617798</v>
+      </c>
+      <c r="BO55" s="1">
         <f t="shared" si="107"/>
-        <v>-4.0259196502770589</v>
-      </c>
-      <c r="BP54" s="1">
+        <v>35.105454099716198</v>
+      </c>
+      <c r="BP55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.9856604537742881</v>
-      </c>
-      <c r="BQ54" s="1">
+        <v>34.754399558719037</v>
+      </c>
+      <c r="BQ55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.9458038492365453</v>
-      </c>
-      <c r="BR54" s="1">
+        <v>34.406855563131849</v>
+      </c>
+      <c r="BR55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.9063458107441797</v>
-      </c>
-      <c r="BS54" s="1">
+        <v>34.062787007500532</v>
+      </c>
+      <c r="BS55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.8672823526367379</v>
-      </c>
-      <c r="BT54" s="1">
+        <v>33.722159137425528</v>
+      </c>
+      <c r="BT55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.8286095291103703</v>
-      </c>
-      <c r="BU54" s="1">
+        <v>33.384937546051276</v>
+      </c>
+      <c r="BU55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.7903234338192666</v>
-      </c>
-      <c r="BV54" s="1">
+        <v>33.051088170590766</v>
+      </c>
+      <c r="BV55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.7524201994810737</v>
-      </c>
-      <c r="BW54" s="1">
+        <v>32.720577288884861</v>
+      </c>
+      <c r="BW55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.7148959974862628</v>
-      </c>
-      <c r="BX54" s="1">
+        <v>32.393371515996016</v>
+      </c>
+      <c r="BX55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.6777470375114003</v>
-      </c>
-      <c r="BY54" s="1">
+        <v>32.069437800836056</v>
+      </c>
+      <c r="BY55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.6409695671362861</v>
-      </c>
-      <c r="BZ54" s="1">
+        <v>31.748743422827694</v>
+      </c>
+      <c r="BZ55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.604559871464923</v>
-      </c>
-      <c r="CA54" s="1">
+        <v>31.431255988599418</v>
+      </c>
+      <c r="CA55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.5685142727502739</v>
-      </c>
-      <c r="CB54" s="1">
+        <v>31.116943428713423</v>
+      </c>
+      <c r="CB55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.5328291300227712</v>
-      </c>
-      <c r="CC54" s="1">
+        <v>30.805773994426289</v>
+      </c>
+      <c r="CC55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.4975008387225435</v>
-      </c>
-      <c r="CD54" s="1">
+        <v>30.497716254482025</v>
+      </c>
+      <c r="CD55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.4625258303353181</v>
-      </c>
-      <c r="CE54" s="1">
+        <v>30.192739091937206</v>
+      </c>
+      <c r="CE55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.4279005720319651</v>
-      </c>
-      <c r="CF54" s="1">
+        <v>29.890811701017835</v>
+      </c>
+      <c r="CF55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.3936215663116456</v>
-      </c>
-      <c r="CG54" s="1">
+        <v>29.591903584007657</v>
+      </c>
+      <c r="CG55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.3596853506485291</v>
-      </c>
-      <c r="CH54" s="1">
+        <v>29.295984548167581</v>
+      </c>
+      <c r="CH55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.3260884971420439</v>
-      </c>
-      <c r="CI54" s="1">
+        <v>29.003024702685906</v>
+      </c>
+      <c r="CI55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.2928276121706235</v>
-      </c>
-      <c r="CJ54" s="1">
+        <v>28.712994455659047</v>
+      </c>
+      <c r="CJ55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.259899336048917</v>
-      </c>
-      <c r="CK54" s="1">
+        <v>28.425864511102457</v>
+      </c>
+      <c r="CK55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.2273003426884279</v>
-      </c>
-      <c r="CL54" s="1">
+        <v>28.141605865991433</v>
+      </c>
+      <c r="CL55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.1950273392615438</v>
-      </c>
-      <c r="CM54" s="1">
+        <v>27.860189807331519</v>
+      </c>
+      <c r="CM55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.1630770658689285</v>
-      </c>
-      <c r="CN54" s="1">
+        <v>27.581587909258204</v>
+      </c>
+      <c r="CN55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.1314462952102393</v>
-      </c>
-      <c r="CO54" s="1">
+        <v>27.30577203016562</v>
+      </c>
+      <c r="CO55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.1001318322581368</v>
-      </c>
-      <c r="CP54" s="1">
+        <v>27.032714309863962</v>
+      </c>
+      <c r="CP55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.0691305139355554</v>
-      </c>
-      <c r="CQ54" s="1">
+        <v>26.762387166765322</v>
+      </c>
+      <c r="CQ55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.0384392087961998</v>
-      </c>
-      <c r="CR54" s="1">
+        <v>26.49476329509767</v>
+      </c>
+      <c r="CR55" s="1">
         <f t="shared" si="107"/>
-        <v>-3.0080548167082379</v>
-      </c>
-      <c r="CS54" s="1">
+        <v>26.229815662146692</v>
+      </c>
+      <c r="CS55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.9779742685411557</v>
-      </c>
-      <c r="CT54" s="1">
+        <v>25.967517505525226</v>
+      </c>
+      <c r="CT55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.9481945258557443</v>
-      </c>
-      <c r="CU54" s="1">
+        <v>25.707842330469973</v>
+      </c>
+      <c r="CU55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.918712580597187</v>
-      </c>
-      <c r="CV54" s="1">
+        <v>25.450763907165271</v>
+      </c>
+      <c r="CV55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.8895254547912153</v>
-      </c>
-      <c r="CW54" s="1">
+        <v>25.196256268093617</v>
+      </c>
+      <c r="CW55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.8606302002433033</v>
-      </c>
-      <c r="CX54" s="1">
+        <v>24.944293705412679</v>
+      </c>
+      <c r="CX55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.8320238982408701</v>
-      </c>
-      <c r="CY54" s="1">
+        <v>24.694850768358553</v>
+      </c>
+      <c r="CY55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.8037036592584612</v>
-      </c>
-      <c r="CZ54" s="1">
+        <v>24.447902260674965</v>
+      </c>
+      <c r="CZ55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.7756666226658764</v>
-      </c>
-      <c r="DA54" s="1">
+        <v>24.203423238068215</v>
+      </c>
+      <c r="DA55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.7479099564392175</v>
-      </c>
-      <c r="DB54" s="1">
+        <v>23.961389005687533</v>
+      </c>
+      <c r="DB55" s="1">
         <f t="shared" si="107"/>
-        <v>-2.7204308568748252</v>
-      </c>
-      <c r="DC54" s="1">
-        <f t="shared" ref="DC54:ET54" si="108">DB54*(1+$AS$20)</f>
-        <v>-2.6932265483060771</v>
-      </c>
-      <c r="DD54" s="1">
+        <v>23.721775115630656</v>
+      </c>
+      <c r="DC55" s="1">
+        <f t="shared" ref="DC55:ET55" si="108">DB55*(1+$AS$21)</f>
+        <v>23.484557364474348</v>
+      </c>
+      <c r="DD55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.6662942828230163</v>
-      </c>
-      <c r="DE54" s="1">
+        <v>23.249711790829604</v>
+      </c>
+      <c r="DE55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.6396313399947862</v>
-      </c>
-      <c r="DF54" s="1">
+        <v>23.017214672921309</v>
+      </c>
+      <c r="DF55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.6132350265948383</v>
-      </c>
-      <c r="DG54" s="1">
+        <v>22.787042526192096</v>
+      </c>
+      <c r="DG55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.58710267632889</v>
-      </c>
-      <c r="DH54" s="1">
+        <v>22.559172100930173</v>
+      </c>
+      <c r="DH55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.5612316495656011</v>
-      </c>
-      <c r="DI54" s="1">
+        <v>22.333580379920871</v>
+      </c>
+      <c r="DI55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.535619333069945</v>
-      </c>
-      <c r="DJ54" s="1">
+        <v>22.110244576121662</v>
+      </c>
+      <c r="DJ55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.5102631397392456</v>
-      </c>
-      <c r="DK54" s="1">
+        <v>21.889142130360444</v>
+      </c>
+      <c r="DK55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.4851605083418531</v>
-      </c>
-      <c r="DL54" s="1">
+        <v>21.670250709056837</v>
+      </c>
+      <c r="DL55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.4603089032584347</v>
-      </c>
-      <c r="DM54" s="1">
+        <v>21.453548201966267</v>
+      </c>
+      <c r="DM55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.4357058142258503</v>
-      </c>
-      <c r="DN54" s="1">
+        <v>21.239012719946604</v>
+      </c>
+      <c r="DN55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.411348756083592</v>
-      </c>
-      <c r="DO54" s="1">
+        <v>21.026622592747138</v>
+      </c>
+      <c r="DO55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.387235268522756</v>
-      </c>
-      <c r="DP54" s="1">
+        <v>20.816356366819665</v>
+      </c>
+      <c r="DP55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.3633629158375284</v>
-      </c>
-      <c r="DQ54" s="1">
+        <v>20.608192803151468</v>
+      </c>
+      <c r="DQ55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.339729286679153</v>
-      </c>
-      <c r="DR54" s="1">
+        <v>20.402110875119952</v>
+      </c>
+      <c r="DR55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.3163319938123617</v>
-      </c>
-      <c r="DS54" s="1">
+        <v>20.198089766368753</v>
+      </c>
+      <c r="DS55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.2931686738742378</v>
-      </c>
-      <c r="DT54" s="1">
+        <v>19.996108868705065</v>
+      </c>
+      <c r="DT55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.2702369871354953</v>
-      </c>
-      <c r="DU54" s="1">
+        <v>19.796147780018014</v>
+      </c>
+      <c r="DU55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.2475346172641402</v>
-      </c>
-      <c r="DV54" s="1">
+        <v>19.598186302217833</v>
+      </c>
+      <c r="DV55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.2250592710914989</v>
-      </c>
-      <c r="DW54" s="1">
+        <v>19.402204439195653</v>
+      </c>
+      <c r="DW55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.2028086783805838</v>
-      </c>
-      <c r="DX54" s="1">
+        <v>19.208182394803696</v>
+      </c>
+      <c r="DX55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.1807805915967777</v>
-      </c>
-      <c r="DY54" s="1">
+        <v>19.016100570855659</v>
+      </c>
+      <c r="DY55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.1589727856808101</v>
-      </c>
-      <c r="DZ54" s="1">
+        <v>18.825939565147102</v>
+      </c>
+      <c r="DZ55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.1373830578240018</v>
-      </c>
-      <c r="EA54" s="1">
+        <v>18.637680169495631</v>
+      </c>
+      <c r="EA55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.1160092272457618</v>
-      </c>
-      <c r="EB54" s="1">
+        <v>18.451303367800676</v>
+      </c>
+      <c r="EB55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.0948491349733041</v>
-      </c>
-      <c r="EC54" s="1">
+        <v>18.266790334122671</v>
+      </c>
+      <c r="EC55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.073900643623571</v>
-      </c>
-      <c r="ED54" s="1">
+        <v>18.084122430781445</v>
+      </c>
+      <c r="ED55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.0531616371873351</v>
-      </c>
-      <c r="EE54" s="1">
+        <v>17.903281206473629</v>
+      </c>
+      <c r="EE55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.032630020815462</v>
-      </c>
-      <c r="EF54" s="1">
+        <v>17.724248394408892</v>
+      </c>
+      <c r="EF55" s="1">
         <f t="shared" si="108"/>
-        <v>-2.0123037206073073</v>
-      </c>
-      <c r="EG54" s="1">
+        <v>17.547005910464804</v>
+      </c>
+      <c r="EG55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.9921806834012343</v>
-      </c>
-      <c r="EH54" s="1">
+        <v>17.371535851360157</v>
+      </c>
+      <c r="EH55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.972258876567222</v>
-      </c>
-      <c r="EI54" s="1">
+        <v>17.197820492846557</v>
+      </c>
+      <c r="EI55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.9525362878015498</v>
-      </c>
-      <c r="EJ54" s="1">
+        <v>17.025842287918092</v>
+      </c>
+      <c r="EJ55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.9330109249235343</v>
-      </c>
-      <c r="EK54" s="1">
+        <v>16.855583865038909</v>
+      </c>
+      <c r="EK55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.913680815674299</v>
-      </c>
-      <c r="EL54" s="1">
+        <v>16.687028026388521</v>
+      </c>
+      <c r="EL55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.8945440075175561</v>
-      </c>
-      <c r="EM54" s="1">
+        <v>16.520157746124635</v>
+      </c>
+      <c r="EM55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.8755985674423805</v>
-      </c>
-      <c r="EN54" s="1">
+        <v>16.354956168663389</v>
+      </c>
+      <c r="EN55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.8568425817679568</v>
-      </c>
-      <c r="EO54" s="1">
+        <v>16.191406606976756</v>
+      </c>
+      <c r="EO55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.8382741559502773</v>
-      </c>
-      <c r="EP54" s="1">
+        <v>16.02949254090699</v>
+      </c>
+      <c r="EP55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.8198914143907745</v>
-      </c>
-      <c r="EQ54" s="1">
+        <v>15.869197615497919</v>
+      </c>
+      <c r="EQ55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.8016925002468667</v>
-      </c>
-      <c r="ER54" s="1">
+        <v>15.710505639342939</v>
+      </c>
+      <c r="ER55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.783675575244398</v>
-      </c>
-      <c r="ES54" s="1">
+        <v>15.553400582949509</v>
+      </c>
+      <c r="ES55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.7658388194919541</v>
-      </c>
-      <c r="ET54" s="1">
+        <v>15.397866577120014</v>
+      </c>
+      <c r="ET55" s="1">
         <f t="shared" si="108"/>
-        <v>-1.7481804312970346</v>
-      </c>
-    </row>
-    <row r="58" spans="2:150" x14ac:dyDescent="0.3">
-      <c r="AR58" t="s">
-        <v>86</v>
-      </c>
-      <c r="AS58" s="2">
-        <f>NPV(AS21,AE54:ET54)</f>
-        <v>-102.93890386082246</v>
+        <v>15.243887911348814</v>
       </c>
     </row>
     <row r="59" spans="2:150" x14ac:dyDescent="0.3">
       <c r="AR59" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="AS59" s="2">
-        <f>Main!D8</f>
-        <v>401.09999999999997</v>
+        <f>NPV(AS22,AE55:ET55)</f>
+        <v>252.55472952584131</v>
       </c>
     </row>
     <row r="60" spans="2:150" x14ac:dyDescent="0.3">
       <c r="AR60" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AS60" s="2">
-        <f>AS58+AS59</f>
-        <v>298.16109613917752</v>
+        <f>Main!D8</f>
+        <v>63.900000000000006</v>
       </c>
     </row>
     <row r="61" spans="2:150" x14ac:dyDescent="0.3">
       <c r="AR61" t="s">
-        <v>54</v>
-      </c>
-      <c r="AS61" s="3">
-        <f>AS60/Model!AO16</f>
-        <v>2.8369276511815178</v>
+        <v>53</v>
+      </c>
+      <c r="AS61" s="2">
+        <f>AS59+AS60</f>
+        <v>316.45472952584134</v>
       </c>
     </row>
     <row r="62" spans="2:150" x14ac:dyDescent="0.3">
       <c r="AR62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AS62" s="3">
-        <f>Main!D3</f>
-        <v>0.56620000000000004</v>
+        <f>AS61/Model!AO17</f>
+        <v>3.0109869602839332</v>
       </c>
     </row>
     <row r="63" spans="2:150" x14ac:dyDescent="0.3">
-      <c r="AR63" s="1" t="s">
+      <c r="AR63" t="s">
+        <v>55</v>
+      </c>
+      <c r="AS63" s="3">
+        <f>Main!D3</f>
+        <v>0.98009999999999997</v>
+      </c>
+    </row>
+    <row r="64" spans="2:150" x14ac:dyDescent="0.3">
+      <c r="AR64" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AS63" s="10">
-        <f>AS61/AS62-1</f>
-        <v>4.0104691825883387</v>
+      <c r="AS64" s="10">
+        <f>AS62/AS63-1</f>
+        <v>2.0721221919027988</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CHGG.xlsx
+++ b/Financial Analysis/CHGG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BBB3A0-CD4A-43EE-9FC0-7EE89DCA8577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A011C9D0-079E-42B2-997D-21BC4FD798F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
   </bookViews>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="94">
   <si>
     <t>CHGG</t>
   </si>
@@ -383,7 +383,13 @@
     <t>Language learning</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Q225 8K</t>
+  </si>
+  <si>
+    <t>Roughly 10% of revenue ("We remain confident that Busuu will achieve approximately $48 million of revenue in 2025")</t>
+  </si>
+  <si>
+    <t>Undervalued</t>
   </si>
 </sst>
 </file>
@@ -496,14 +502,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>91440</xdr:rowOff>
     </xdr:to>
@@ -520,8 +526,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11864340" y="0"/>
-          <a:ext cx="0" cy="6126480"/>
+          <a:off x="13098780" y="0"/>
+          <a:ext cx="0" cy="6309360"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -894,7 +900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D8F67F3-1170-4F04-975E-778BC84293D4}">
-  <dimension ref="B2:K9"/>
+  <dimension ref="B2:K11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="7" width="13.44140625" style="4" customWidth="1"/>
@@ -919,17 +925,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>0.98009999999999997</v>
+        <v>1.68</v>
       </c>
       <c r="E3" s="5">
-        <v>45799</v>
+        <v>45905</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45799</v>
+        <v>45905</v>
       </c>
       <c r="G3" s="5">
-        <v>45880</v>
+        <v>45964</v>
       </c>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
@@ -937,10 +943,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>106.6</v>
+        <v>106.9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -949,7 +955,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>104.47865999999999</v>
+        <v>179.59200000000001</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -957,11 +963,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>44.1+44.2+38.1</f>
-        <v>126.4</v>
+        <f>36.8+48.8+28.5</f>
+        <v>114.1</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -973,7 +979,7 @@
         <v>62.5</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J7" t="s">
         <v>87</v>
@@ -988,13 +994,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>63.900000000000006</v>
-      </c>
-      <c r="J8" t="s">
-        <v>89</v>
-      </c>
-      <c r="K8" t="s">
-        <v>90</v>
+        <v>51.599999999999994</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
@@ -1003,8 +1003,22 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>40.578659999999985</v>
-      </c>
+        <v>127.99200000000002</v>
+      </c>
+      <c r="J9" t="s">
+        <v>89</v>
+      </c>
+      <c r="K9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="K11" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1198,16 +1212,14 @@
         <v>121.4</v>
       </c>
       <c r="T3" s="8">
-        <f>P3*0.8</f>
-        <v>130.47999999999999</v>
+        <v>105.1</v>
       </c>
       <c r="U3" s="8">
-        <f t="shared" ref="U3" si="0">Q3*0.75</f>
-        <v>102.44999999999999</v>
+        <v>76</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*0.95</f>
-        <v>136.32499999999999</v>
+        <f>R3*0.65</f>
+        <v>93.275000000000006</v>
       </c>
       <c r="X3" s="8">
         <v>321.10000000000002</v>
@@ -1236,47 +1248,47 @@
       </c>
       <c r="AE3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>490.65499999999997</v>
+        <v>395.77499999999998</v>
       </c>
       <c r="AF3" s="8">
-        <f>AE3*0.98</f>
-        <v>480.84189999999995</v>
+        <f>AE3*1.15</f>
+        <v>455.14124999999996</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.1</f>
-        <v>528.92609000000004</v>
+        <v>500.65537499999999</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.07</f>
-        <v>565.95091630000013</v>
+        <v>535.70125125000004</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.05</f>
-        <v>594.24846211500017</v>
+        <v>562.48631381250004</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.04</f>
-        <v>618.01840059960023</v>
+        <v>584.98576636500002</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.03</f>
-        <v>636.55895261758826</v>
+        <v>602.53533935594999</v>
       </c>
       <c r="AL3" s="8">
-        <f t="shared" ref="AL3:AO3" si="1">AK3*1.03</f>
-        <v>655.65572119611591</v>
+        <f t="shared" ref="AL3:AO3" si="0">AK3*1.03</f>
+        <v>620.61139953662848</v>
       </c>
       <c r="AM3" s="8">
-        <f t="shared" si="1"/>
-        <v>675.32539283199935</v>
+        <f t="shared" si="0"/>
+        <v>639.22974152272741</v>
       </c>
       <c r="AN3" s="8">
-        <f t="shared" si="1"/>
-        <v>695.58515461695936</v>
+        <f t="shared" si="0"/>
+        <v>658.40663376840928</v>
       </c>
       <c r="AO3" s="8">
-        <f t="shared" si="1"/>
-        <v>716.45270925546811</v>
+        <f t="shared" si="0"/>
+        <v>678.15883278146157</v>
       </c>
     </row>
     <row r="4" spans="2:145" x14ac:dyDescent="0.3">
@@ -1335,16 +1347,15 @@
         <v>54</v>
       </c>
       <c r="T4" s="2">
-        <f t="shared" ref="T4:V4" si="2">T3-T5</f>
-        <v>41.753599999999992</v>
+        <v>35.5</v>
       </c>
       <c r="U4" s="2">
-        <f t="shared" si="2"/>
-        <v>32.783999999999992</v>
+        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
+        <v>33.44</v>
       </c>
       <c r="V4" s="2">
-        <f t="shared" si="2"/>
-        <v>43.623999999999995</v>
+        <f t="shared" si="1"/>
+        <v>30.780749999999998</v>
       </c>
       <c r="X4" s="2">
         <v>80</v>
@@ -1373,47 +1384,47 @@
       </c>
       <c r="AE4" s="2">
         <f>SUM(S4:V4)</f>
-        <v>172.16159999999999</v>
+        <v>153.72075000000001</v>
       </c>
       <c r="AF4" s="2">
-        <f t="shared" ref="AF4:AO4" si="3">AF3-AF5</f>
-        <v>149.06098900000001</v>
+        <f t="shared" ref="AF4:AO4" si="2">AF3-AF5</f>
+        <v>159.29943749999995</v>
       </c>
       <c r="AG4" s="2">
-        <f t="shared" si="3"/>
-        <v>158.67782700000004</v>
+        <f t="shared" si="2"/>
+        <v>160.20971999999995</v>
       </c>
       <c r="AH4" s="2">
-        <f t="shared" si="3"/>
-        <v>169.78527489000004</v>
+        <f t="shared" si="2"/>
+        <v>166.06738788750005</v>
       </c>
       <c r="AI4" s="2">
-        <f t="shared" si="3"/>
-        <v>178.27453863450006</v>
+        <f t="shared" si="2"/>
+        <v>168.74589414375004</v>
       </c>
       <c r="AJ4" s="2">
-        <f t="shared" si="3"/>
-        <v>185.40552017988011</v>
+        <f t="shared" si="2"/>
+        <v>175.49572990950003</v>
       </c>
       <c r="AK4" s="2">
-        <f t="shared" si="3"/>
-        <v>190.9676857852765</v>
+        <f t="shared" si="2"/>
+        <v>180.76060180678502</v>
       </c>
       <c r="AL4" s="2">
-        <f t="shared" si="3"/>
-        <v>196.69671635883481</v>
+        <f t="shared" si="2"/>
+        <v>186.18341986098858</v>
       </c>
       <c r="AM4" s="2">
-        <f t="shared" si="3"/>
-        <v>202.59761784959983</v>
+        <f t="shared" si="2"/>
+        <v>191.76892245681825</v>
       </c>
       <c r="AN4" s="2">
-        <f t="shared" si="3"/>
-        <v>208.67554638508784</v>
+        <f t="shared" si="2"/>
+        <v>197.52199013052279</v>
       </c>
       <c r="AO4" s="2">
-        <f t="shared" si="3"/>
-        <v>214.93581277664049</v>
+        <f t="shared" si="2"/>
+        <v>203.44764983443849</v>
       </c>
     </row>
     <row r="5" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1421,156 +1432,156 @@
         <v>14</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:S5" si="4">C3-C4</f>
+        <f t="shared" ref="C5:T5" si="3">C3-C4</f>
         <v>127</v>
       </c>
       <c r="D5" s="8">
+        <f t="shared" si="3"/>
+        <v>137.80000000000001</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" si="3"/>
+        <v>104.80000000000001</v>
+      </c>
+      <c r="F5" s="8">
+        <f t="shared" si="3"/>
+        <v>151.80000000000001</v>
+      </c>
+      <c r="G5" s="8">
+        <f t="shared" si="3"/>
+        <v>147.1</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="3"/>
+        <v>149</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="3"/>
+        <v>119.49999999999999</v>
+      </c>
+      <c r="J5" s="8">
+        <f t="shared" si="3"/>
+        <v>153.79999999999998</v>
+      </c>
+      <c r="K5" s="8">
+        <f t="shared" si="3"/>
+        <v>138.39999999999998</v>
+      </c>
+      <c r="L5" s="8">
+        <f t="shared" si="3"/>
+        <v>135.5</v>
+      </c>
+      <c r="M5" s="8">
+        <f t="shared" si="3"/>
+        <v>74.300000000000011</v>
+      </c>
+      <c r="N5" s="8">
+        <f t="shared" si="3"/>
+        <v>142.19999999999999</v>
+      </c>
+      <c r="O5" s="8">
+        <f t="shared" si="3"/>
+        <v>127.9</v>
+      </c>
+      <c r="P5" s="8">
+        <f t="shared" si="3"/>
+        <v>117.69999999999999</v>
+      </c>
+      <c r="Q5" s="8">
+        <f t="shared" si="3"/>
+        <v>93.199999999999989</v>
+      </c>
+      <c r="R5" s="8">
+        <f t="shared" si="3"/>
+        <v>97.9</v>
+      </c>
+      <c r="S5" s="8">
+        <f t="shared" si="3"/>
+        <v>67.400000000000006</v>
+      </c>
+      <c r="T5" s="8">
+        <f t="shared" si="3"/>
+        <v>69.599999999999994</v>
+      </c>
+      <c r="U5" s="8">
+        <f>U3*0.56</f>
+        <v>42.56</v>
+      </c>
+      <c r="V5" s="8">
+        <f>V3*0.67</f>
+        <v>62.494250000000008</v>
+      </c>
+      <c r="X5" s="8">
+        <f t="shared" ref="X5:AE5" si="4">X3-X4</f>
+        <v>241.10000000000002</v>
+      </c>
+      <c r="Y5" s="8">
         <f t="shared" si="4"/>
-        <v>137.80000000000001</v>
-      </c>
-      <c r="E5" s="8">
+        <v>318.7</v>
+      </c>
+      <c r="Z5" s="8">
         <f t="shared" si="4"/>
-        <v>104.80000000000001</v>
-      </c>
-      <c r="F5" s="8">
+        <v>438.9</v>
+      </c>
+      <c r="AA5" s="8">
         <f t="shared" si="4"/>
-        <v>151.80000000000001</v>
-      </c>
-      <c r="G5" s="8">
+        <v>521.39999999999986</v>
+      </c>
+      <c r="AB5" s="8">
         <f t="shared" si="4"/>
-        <v>147.1</v>
-      </c>
-      <c r="H5" s="8">
+        <v>569.4</v>
+      </c>
+      <c r="AC5" s="8">
         <f t="shared" si="4"/>
-        <v>149</v>
-      </c>
-      <c r="I5" s="8">
+        <v>490.4</v>
+      </c>
+      <c r="AD5" s="8">
         <f t="shared" si="4"/>
-        <v>119.49999999999999</v>
-      </c>
-      <c r="J5" s="8">
+        <v>436.70000000000005</v>
+      </c>
+      <c r="AE5" s="8">
         <f t="shared" si="4"/>
-        <v>153.79999999999998</v>
-      </c>
-      <c r="K5" s="8">
-        <f t="shared" si="4"/>
-        <v>138.39999999999998</v>
-      </c>
-      <c r="L5" s="8">
-        <f t="shared" si="4"/>
-        <v>135.5</v>
-      </c>
-      <c r="M5" s="8">
-        <f t="shared" si="4"/>
-        <v>74.300000000000011</v>
-      </c>
-      <c r="N5" s="8">
-        <f t="shared" si="4"/>
-        <v>142.19999999999999</v>
-      </c>
-      <c r="O5" s="8">
-        <f t="shared" si="4"/>
-        <v>127.9</v>
-      </c>
-      <c r="P5" s="8">
-        <f t="shared" si="4"/>
-        <v>117.69999999999999</v>
-      </c>
-      <c r="Q5" s="8">
-        <f t="shared" si="4"/>
-        <v>93.199999999999989</v>
-      </c>
-      <c r="R5" s="8">
-        <f t="shared" si="4"/>
-        <v>97.9</v>
-      </c>
-      <c r="S5" s="8">
-        <f t="shared" si="4"/>
-        <v>67.400000000000006</v>
-      </c>
-      <c r="T5" s="8">
-        <f>T3*0.68</f>
-        <v>88.726399999999998</v>
-      </c>
-      <c r="U5" s="8">
-        <f>U3*0.68</f>
-        <v>69.665999999999997</v>
-      </c>
-      <c r="V5" s="8">
-        <f>V3*0.68</f>
-        <v>92.700999999999993</v>
-      </c>
-      <c r="X5" s="8">
-        <f t="shared" ref="X5:AE5" si="5">X3-X4</f>
-        <v>241.10000000000002</v>
-      </c>
-      <c r="Y5" s="8">
+        <v>242.05424999999997</v>
+      </c>
+      <c r="AF5" s="8">
+        <f>AF3*0.65</f>
+        <v>295.8418125</v>
+      </c>
+      <c r="AG5" s="8">
+        <f>AG3*0.68</f>
+        <v>340.44565500000004</v>
+      </c>
+      <c r="AH5" s="8">
+        <f>AH3*0.69</f>
+        <v>369.63386336249999</v>
+      </c>
+      <c r="AI5" s="8">
+        <f t="shared" ref="AI5:AO5" si="5">AI3*0.7</f>
+        <v>393.74041966875001</v>
+      </c>
+      <c r="AJ5" s="8">
         <f t="shared" si="5"/>
-        <v>318.7</v>
-      </c>
-      <c r="Z5" s="8">
+        <v>409.49003645549999</v>
+      </c>
+      <c r="AK5" s="8">
         <f t="shared" si="5"/>
-        <v>438.9</v>
-      </c>
-      <c r="AA5" s="8">
+        <v>421.77473754916497</v>
+      </c>
+      <c r="AL5" s="8">
         <f t="shared" si="5"/>
-        <v>521.39999999999986</v>
-      </c>
-      <c r="AB5" s="8">
+        <v>434.4279796756399</v>
+      </c>
+      <c r="AM5" s="8">
         <f t="shared" si="5"/>
-        <v>569.4</v>
-      </c>
-      <c r="AC5" s="8">
+        <v>447.46081906590916</v>
+      </c>
+      <c r="AN5" s="8">
         <f t="shared" si="5"/>
-        <v>490.4</v>
-      </c>
-      <c r="AD5" s="8">
+        <v>460.88464363788648</v>
+      </c>
+      <c r="AO5" s="8">
         <f t="shared" si="5"/>
-        <v>436.70000000000005</v>
-      </c>
-      <c r="AE5" s="8">
-        <f t="shared" si="5"/>
-        <v>318.49339999999995</v>
-      </c>
-      <c r="AF5" s="8">
-        <f>AF3*0.69</f>
-        <v>331.78091099999995</v>
-      </c>
-      <c r="AG5" s="8">
-        <f t="shared" ref="AG5:AO5" si="6">AG3*0.7</f>
-        <v>370.24826300000001</v>
-      </c>
-      <c r="AH5" s="8">
-        <f t="shared" si="6"/>
-        <v>396.16564141000009</v>
-      </c>
-      <c r="AI5" s="8">
-        <f t="shared" si="6"/>
-        <v>415.9739234805001</v>
-      </c>
-      <c r="AJ5" s="8">
-        <f t="shared" si="6"/>
-        <v>432.61288041972011</v>
-      </c>
-      <c r="AK5" s="8">
-        <f t="shared" si="6"/>
-        <v>445.59126683231176</v>
-      </c>
-      <c r="AL5" s="8">
-        <f t="shared" si="6"/>
-        <v>458.9590048372811</v>
-      </c>
-      <c r="AM5" s="8">
-        <f t="shared" si="6"/>
-        <v>472.72777498239952</v>
-      </c>
-      <c r="AN5" s="8">
-        <f t="shared" si="6"/>
-        <v>486.90960823187152</v>
-      </c>
-      <c r="AO5" s="8">
-        <f t="shared" si="6"/>
-        <v>501.51689647882762</v>
+        <v>474.71118294702308</v>
       </c>
     </row>
     <row r="6" spans="2:145" x14ac:dyDescent="0.3">
@@ -1629,16 +1640,15 @@
         <v>29.4</v>
       </c>
       <c r="T6" s="2">
-        <f t="shared" ref="T6:V6" si="7">P6*0.9</f>
-        <v>39.330000000000005</v>
+        <v>28.7</v>
       </c>
       <c r="U6" s="2">
-        <f t="shared" si="7"/>
-        <v>37.17</v>
+        <f>Q6*0.8</f>
+        <v>33.04</v>
       </c>
       <c r="V6" s="2">
-        <f t="shared" si="7"/>
-        <v>36.9</v>
+        <f>R6*0.85</f>
+        <v>34.85</v>
       </c>
       <c r="X6" s="2">
         <v>114.3</v>
@@ -1667,47 +1677,47 @@
       </c>
       <c r="AE6" s="2">
         <f>SUM(S6:V6)</f>
-        <v>142.80000000000001</v>
+        <v>125.98999999999998</v>
       </c>
       <c r="AF6" s="2">
-        <f>AE6*1.02</f>
-        <v>145.65600000000001</v>
+        <f>AE6*0.95</f>
+        <v>119.69049999999997</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" ref="AG6:AJ6" si="8">AF6*1.02</f>
-        <v>148.56912</v>
+        <f t="shared" ref="AG6:AJ6" si="6">AF6*1.02</f>
+        <v>122.08430999999997</v>
       </c>
       <c r="AH6" s="2">
-        <f t="shared" si="8"/>
-        <v>151.54050240000001</v>
+        <f t="shared" si="6"/>
+        <v>124.52599619999998</v>
       </c>
       <c r="AI6" s="2">
-        <f t="shared" si="8"/>
-        <v>154.57131244800001</v>
+        <f t="shared" si="6"/>
+        <v>127.01651612399998</v>
       </c>
       <c r="AJ6" s="2">
-        <f t="shared" si="8"/>
-        <v>157.66273869696002</v>
+        <f t="shared" si="6"/>
+        <v>129.55684644647997</v>
       </c>
       <c r="AK6" s="2">
         <f>AJ6*1.01</f>
-        <v>159.23936608392961</v>
+        <v>130.85241491094476</v>
       </c>
       <c r="AL6" s="2">
-        <f t="shared" ref="AL6:AO6" si="9">AK6*1.01</f>
-        <v>160.8317597447689</v>
+        <f t="shared" ref="AL6:AO6" si="7">AK6*1.01</f>
+        <v>132.1609390600542</v>
       </c>
       <c r="AM6" s="2">
-        <f t="shared" si="9"/>
-        <v>162.4400773422166</v>
+        <f t="shared" si="7"/>
+        <v>133.48254845065475</v>
       </c>
       <c r="AN6" s="2">
-        <f t="shared" si="9"/>
-        <v>164.06447811563876</v>
+        <f t="shared" si="7"/>
+        <v>134.8173739351613</v>
       </c>
       <c r="AO6" s="2">
-        <f t="shared" si="9"/>
-        <v>165.70512289679516</v>
+        <f t="shared" si="7"/>
+        <v>136.16554767451291</v>
       </c>
     </row>
     <row r="7" spans="2:145" x14ac:dyDescent="0.3">
@@ -1766,16 +1776,15 @@
         <v>25.6</v>
       </c>
       <c r="T7" s="2">
-        <f t="shared" ref="T7" si="10">T3*0.17</f>
-        <v>22.1816</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="U7" s="2">
-        <f>U3*0.2</f>
-        <v>20.49</v>
+        <f>U3*0.19</f>
+        <v>14.44</v>
       </c>
       <c r="V7" s="2">
-        <f>V3*0.2</f>
-        <v>27.265000000000001</v>
+        <f>V3*0.19</f>
+        <v>17.722250000000003</v>
       </c>
       <c r="X7" s="2">
         <v>54.7</v>
@@ -1804,47 +1813,47 @@
       </c>
       <c r="AE7" s="2">
         <f>SUM(S7:V7)</f>
-        <v>95.536599999999993</v>
+        <v>75.16225</v>
       </c>
       <c r="AF7" s="2">
-        <f>AF3*0.17</f>
-        <v>81.743122999999997</v>
+        <f>AF3*0.15</f>
+        <v>68.271187499999996</v>
       </c>
       <c r="AG7" s="2">
-        <f>AG3*0.16</f>
-        <v>84.628174400000006</v>
+        <f>AG3*0.15</f>
+        <v>75.098306249999993</v>
       </c>
       <c r="AH7" s="2">
-        <f t="shared" ref="AH7:AO7" si="11">AH3*0.15</f>
-        <v>84.89263744500002</v>
+        <f t="shared" ref="AH7:AO7" si="8">AH3*0.15</f>
+        <v>80.355187687500006</v>
       </c>
       <c r="AI7" s="2">
-        <f t="shared" si="11"/>
-        <v>89.137269317250016</v>
+        <f t="shared" si="8"/>
+        <v>84.372947071875004</v>
       </c>
       <c r="AJ7" s="2">
-        <f t="shared" si="11"/>
-        <v>92.702760089940028</v>
+        <f t="shared" si="8"/>
+        <v>87.74786495475</v>
       </c>
       <c r="AK7" s="2">
-        <f t="shared" si="11"/>
-        <v>95.483842892638236</v>
+        <f t="shared" si="8"/>
+        <v>90.380300903392495</v>
       </c>
       <c r="AL7" s="2">
-        <f t="shared" si="11"/>
-        <v>98.348358179417389</v>
+        <f t="shared" si="8"/>
+        <v>93.091709930494275</v>
       </c>
       <c r="AM7" s="2">
-        <f t="shared" si="11"/>
-        <v>101.2988089247999</v>
+        <f t="shared" si="8"/>
+        <v>95.884461228409108</v>
       </c>
       <c r="AN7" s="2">
-        <f t="shared" si="11"/>
-        <v>104.33777319254391</v>
+        <f t="shared" si="8"/>
+        <v>98.760995065261383</v>
       </c>
       <c r="AO7" s="2">
-        <f t="shared" si="11"/>
-        <v>107.46790638832022</v>
+        <f t="shared" si="8"/>
+        <v>101.72382491721923</v>
       </c>
     </row>
     <row r="8" spans="2:145" x14ac:dyDescent="0.3">
@@ -1903,15 +1912,14 @@
         <v>39.4</v>
       </c>
       <c r="T8" s="2">
-        <f t="shared" ref="T8:V8" si="12">P8*1.02</f>
-        <v>55.08</v>
+        <v>60</v>
       </c>
       <c r="U8" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="U8:V8" si="9">Q8*1.02</f>
         <v>52.938000000000002</v>
       </c>
       <c r="V8" s="2">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>57.425999999999995</v>
       </c>
       <c r="X8" s="2">
@@ -1941,47 +1949,47 @@
       </c>
       <c r="AE8" s="2">
         <f>SUM(S8:V8)</f>
-        <v>204.84399999999999</v>
+        <v>209.76400000000001</v>
       </c>
       <c r="AF8" s="2">
-        <f>AE8*1.02</f>
-        <v>208.94087999999999</v>
+        <f>AE8*0.9</f>
+        <v>188.78760000000003</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" ref="AG8:AO8" si="13">AF8*1.02</f>
-        <v>213.11969759999999</v>
+        <f>AF8*1.03</f>
+        <v>194.45122800000004</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" si="13"/>
-        <v>217.38209155199999</v>
+        <f t="shared" ref="AH8:AJ8" si="10">AG8*1.02</f>
+        <v>198.34025256000004</v>
       </c>
       <c r="AI8" s="2">
-        <f t="shared" si="13"/>
-        <v>221.72973338303999</v>
+        <f t="shared" si="10"/>
+        <v>202.30705761120004</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" si="13"/>
-        <v>226.16432805070079</v>
+        <f t="shared" si="10"/>
+        <v>206.35319876342405</v>
       </c>
       <c r="AK8" s="2">
-        <f t="shared" si="13"/>
-        <v>230.68761461171482</v>
+        <f>AJ8*1.01</f>
+        <v>208.41673075105828</v>
       </c>
       <c r="AL8" s="2">
-        <f t="shared" si="13"/>
-        <v>235.30136690394912</v>
+        <f t="shared" ref="AL8:AO8" si="11">AK8*1.01</f>
+        <v>210.50089805856888</v>
       </c>
       <c r="AM8" s="2">
-        <f t="shared" si="13"/>
-        <v>240.00739424202811</v>
+        <f t="shared" si="11"/>
+        <v>212.60590703915457</v>
       </c>
       <c r="AN8" s="2">
-        <f t="shared" si="13"/>
-        <v>244.80754212686867</v>
+        <f t="shared" si="11"/>
+        <v>214.73196610954611</v>
       </c>
       <c r="AO8" s="2">
-        <f t="shared" si="13"/>
-        <v>249.70369296940603</v>
+        <f t="shared" si="11"/>
+        <v>216.87928577064156</v>
       </c>
     </row>
     <row r="9" spans="2:145" x14ac:dyDescent="0.3">
@@ -2037,67 +2045,67 @@
         <v>33</v>
       </c>
       <c r="C10" s="2">
-        <f t="shared" ref="C10:P10" si="14">SUM(C6:C8)</f>
+        <f t="shared" ref="C10:P10" si="12">SUM(C6:C8)</f>
         <v>110.19999999999999</v>
       </c>
       <c r="D10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>103</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>104.5</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>125.6</v>
       </c>
       <c r="G10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>141.80000000000001</v>
       </c>
       <c r="H10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>141.69999999999999</v>
       </c>
       <c r="I10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>130.9</v>
       </c>
       <c r="J10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>146.10000000000002</v>
       </c>
       <c r="K10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>142.9</v>
       </c>
       <c r="L10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>154.19999999999999</v>
       </c>
       <c r="M10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>132.19999999999999</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>128.80000000000001</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>130.30000000000001</v>
       </c>
       <c r="P10" s="2">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v>121.2</v>
       </c>
       <c r="Q10" s="2">
-        <f t="shared" ref="Q10:R10" si="15">SUM(Q6:Q8)</f>
+        <f t="shared" ref="Q10:R10" si="13">SUM(Q6:Q8)</f>
         <v>119.69999999999999</v>
       </c>
       <c r="R10" s="2">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v>125.2</v>
       </c>
       <c r="S10" s="2">
@@ -2105,88 +2113,88 @@
         <v>96.4</v>
       </c>
       <c r="T10" s="2">
-        <f t="shared" ref="T10:V10" si="16">SUM(T6:T9)</f>
-        <v>116.5916</v>
+        <f t="shared" ref="T10:V10" si="14">SUM(T6:T9)</f>
+        <v>106.1</v>
       </c>
       <c r="U10" s="2">
-        <f t="shared" si="16"/>
-        <v>110.598</v>
+        <f t="shared" si="14"/>
+        <v>100.41800000000001</v>
       </c>
       <c r="V10" s="2">
-        <f t="shared" si="16"/>
-        <v>121.59099999999998</v>
+        <f t="shared" si="14"/>
+        <v>109.99825</v>
       </c>
       <c r="X10" s="2">
-        <f t="shared" ref="X10:AD10" si="17">SUM(X6:X8)</f>
+        <f t="shared" ref="X10:AD10" si="15">SUM(X6:X8)</f>
         <v>246.7</v>
       </c>
       <c r="Y10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>300.89999999999998</v>
       </c>
       <c r="Z10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>382.1</v>
       </c>
       <c r="AA10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>443.29999999999995</v>
       </c>
       <c r="AB10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>560.5</v>
       </c>
       <c r="AC10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>558.1</v>
       </c>
       <c r="AD10" s="2">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>496.4</v>
       </c>
       <c r="AE10" s="2">
         <f>SUM(AE6:AE9)</f>
-        <v>445.18060000000003</v>
+        <v>412.91624999999999</v>
       </c>
       <c r="AF10" s="2">
-        <f t="shared" ref="AF10:AO10" si="18">SUM(AF6:AF9)</f>
-        <v>436.34000300000002</v>
+        <f t="shared" ref="AF10:AO10" si="16">SUM(AF6:AF9)</f>
+        <v>376.74928750000004</v>
       </c>
       <c r="AG10" s="2">
-        <f t="shared" si="18"/>
-        <v>446.31699200000003</v>
+        <f t="shared" si="16"/>
+        <v>391.63384425000004</v>
       </c>
       <c r="AH10" s="2">
-        <f t="shared" si="18"/>
-        <v>453.81523139700005</v>
+        <f t="shared" si="16"/>
+        <v>403.22143644750003</v>
       </c>
       <c r="AI10" s="2">
-        <f t="shared" si="18"/>
-        <v>465.43831514829003</v>
+        <f t="shared" si="16"/>
+        <v>413.69652080707499</v>
       </c>
       <c r="AJ10" s="2">
-        <f t="shared" si="18"/>
-        <v>476.52982683760081</v>
+        <f t="shared" si="16"/>
+        <v>423.65791016465403</v>
       </c>
       <c r="AK10" s="2">
-        <f t="shared" si="18"/>
-        <v>485.41082358828265</v>
+        <f t="shared" si="16"/>
+        <v>429.64944656539558</v>
       </c>
       <c r="AL10" s="2">
-        <f t="shared" si="18"/>
-        <v>494.48148482813542</v>
+        <f t="shared" si="16"/>
+        <v>435.7535470491174</v>
       </c>
       <c r="AM10" s="2">
-        <f t="shared" si="18"/>
-        <v>503.7462805090446</v>
+        <f t="shared" si="16"/>
+        <v>441.97291671821847</v>
       </c>
       <c r="AN10" s="2">
-        <f t="shared" si="18"/>
-        <v>513.20979343505132</v>
+        <f t="shared" si="16"/>
+        <v>448.31033510996883</v>
       </c>
       <c r="AO10" s="2">
-        <f t="shared" si="18"/>
-        <v>522.87672225452138</v>
+        <f t="shared" si="16"/>
+        <v>454.76865836237369</v>
       </c>
     </row>
     <row r="11" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2194,156 +2202,156 @@
         <v>34</v>
       </c>
       <c r="C11" s="8">
-        <f t="shared" ref="C11:P11" si="19">C5-C10</f>
+        <f t="shared" ref="C11:P11" si="17">C5-C10</f>
         <v>16.800000000000011</v>
       </c>
       <c r="D11" s="8">
+        <f t="shared" si="17"/>
+        <v>34.800000000000011</v>
+      </c>
+      <c r="E11" s="8">
+        <f t="shared" si="17"/>
+        <v>0.30000000000001137</v>
+      </c>
+      <c r="F11" s="8">
+        <f t="shared" si="17"/>
+        <v>26.200000000000017</v>
+      </c>
+      <c r="G11" s="8">
+        <f t="shared" si="17"/>
+        <v>5.2999999999999829</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="17"/>
+        <v>7.3000000000000114</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="17"/>
+        <v>-11.40000000000002</v>
+      </c>
+      <c r="J11" s="8">
+        <f t="shared" si="17"/>
+        <v>7.6999999999999602</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" si="17"/>
+        <v>-4.5000000000000284</v>
+      </c>
+      <c r="L11" s="8">
+        <f t="shared" si="17"/>
+        <v>-18.699999999999989</v>
+      </c>
+      <c r="M11" s="8">
+        <f t="shared" si="17"/>
+        <v>-57.899999999999977</v>
+      </c>
+      <c r="N11" s="8">
+        <f t="shared" si="17"/>
+        <v>13.399999999999977</v>
+      </c>
+      <c r="O11" s="8">
+        <f t="shared" si="17"/>
+        <v>-2.4000000000000057</v>
+      </c>
+      <c r="P11" s="8">
+        <f t="shared" si="17"/>
+        <v>-3.5000000000000142</v>
+      </c>
+      <c r="Q11" s="8">
+        <f t="shared" ref="Q11:R11" si="18">Q5-Q10</f>
+        <v>-26.5</v>
+      </c>
+      <c r="R11" s="8">
+        <f t="shared" si="18"/>
+        <v>-27.299999999999997</v>
+      </c>
+      <c r="S11" s="8">
+        <f t="shared" ref="S11:V11" si="19">S5-S10</f>
+        <v>-29</v>
+      </c>
+      <c r="T11" s="8">
         <f t="shared" si="19"/>
-        <v>34.800000000000011</v>
-      </c>
-      <c r="E11" s="8">
+        <v>-36.5</v>
+      </c>
+      <c r="U11" s="8">
         <f t="shared" si="19"/>
-        <v>0.30000000000001137</v>
-      </c>
-      <c r="F11" s="8">
+        <v>-57.858000000000004</v>
+      </c>
+      <c r="V11" s="8">
         <f t="shared" si="19"/>
-        <v>26.200000000000017</v>
-      </c>
-      <c r="G11" s="8">
-        <f t="shared" si="19"/>
-        <v>5.2999999999999829</v>
-      </c>
-      <c r="H11" s="8">
-        <f t="shared" si="19"/>
-        <v>7.3000000000000114</v>
-      </c>
-      <c r="I11" s="8">
-        <f t="shared" si="19"/>
-        <v>-11.40000000000002</v>
-      </c>
-      <c r="J11" s="8">
-        <f t="shared" si="19"/>
-        <v>7.6999999999999602</v>
-      </c>
-      <c r="K11" s="8">
-        <f t="shared" si="19"/>
-        <v>-4.5000000000000284</v>
-      </c>
-      <c r="L11" s="8">
-        <f t="shared" si="19"/>
-        <v>-18.699999999999989</v>
-      </c>
-      <c r="M11" s="8">
-        <f t="shared" si="19"/>
-        <v>-57.899999999999977</v>
-      </c>
-      <c r="N11" s="8">
-        <f t="shared" si="19"/>
-        <v>13.399999999999977</v>
-      </c>
-      <c r="O11" s="8">
-        <f t="shared" si="19"/>
-        <v>-2.4000000000000057</v>
-      </c>
-      <c r="P11" s="8">
-        <f t="shared" si="19"/>
-        <v>-3.5000000000000142</v>
-      </c>
-      <c r="Q11" s="8">
-        <f t="shared" ref="Q11:R11" si="20">Q5-Q10</f>
-        <v>-26.5</v>
-      </c>
-      <c r="R11" s="8">
+        <v>-47.503999999999991</v>
+      </c>
+      <c r="X11" s="8">
+        <f t="shared" ref="X11:AD11" si="20">X5-X10</f>
+        <v>-5.5999999999999659</v>
+      </c>
+      <c r="Y11" s="8">
         <f t="shared" si="20"/>
-        <v>-27.299999999999997</v>
-      </c>
-      <c r="S11" s="8">
-        <f t="shared" ref="S11:V11" si="21">S5-S10</f>
-        <v>-29</v>
-      </c>
-      <c r="T11" s="8">
+        <v>17.800000000000011</v>
+      </c>
+      <c r="Z11" s="8">
+        <f t="shared" si="20"/>
+        <v>56.799999999999955</v>
+      </c>
+      <c r="AA11" s="8">
+        <f t="shared" si="20"/>
+        <v>78.099999999999909</v>
+      </c>
+      <c r="AB11" s="8">
+        <f t="shared" si="20"/>
+        <v>8.8999999999999773</v>
+      </c>
+      <c r="AC11" s="8">
+        <f t="shared" si="20"/>
+        <v>-67.700000000000045</v>
+      </c>
+      <c r="AD11" s="8">
+        <f t="shared" si="20"/>
+        <v>-59.699999999999932</v>
+      </c>
+      <c r="AE11" s="8">
+        <f t="shared" ref="AE11:AO11" si="21">AE5-AE10</f>
+        <v>-170.86200000000002</v>
+      </c>
+      <c r="AF11" s="8">
         <f t="shared" si="21"/>
-        <v>-27.865200000000002</v>
-      </c>
-      <c r="U11" s="8">
+        <v>-80.907475000000034</v>
+      </c>
+      <c r="AG11" s="8">
         <f t="shared" si="21"/>
-        <v>-40.932000000000002</v>
-      </c>
-      <c r="V11" s="8">
+        <v>-51.188189249999994</v>
+      </c>
+      <c r="AH11" s="8">
         <f t="shared" si="21"/>
-        <v>-28.889999999999986</v>
-      </c>
-      <c r="X11" s="8">
-        <f t="shared" ref="X11:AD11" si="22">X5-X10</f>
-        <v>-5.5999999999999659</v>
-      </c>
-      <c r="Y11" s="8">
-        <f t="shared" si="22"/>
-        <v>17.800000000000011</v>
-      </c>
-      <c r="Z11" s="8">
-        <f t="shared" si="22"/>
-        <v>56.799999999999955</v>
-      </c>
-      <c r="AA11" s="8">
-        <f t="shared" si="22"/>
-        <v>78.099999999999909</v>
-      </c>
-      <c r="AB11" s="8">
-        <f t="shared" si="22"/>
-        <v>8.8999999999999773</v>
-      </c>
-      <c r="AC11" s="8">
-        <f t="shared" si="22"/>
-        <v>-67.700000000000045</v>
-      </c>
-      <c r="AD11" s="8">
-        <f t="shared" si="22"/>
-        <v>-59.699999999999932</v>
-      </c>
-      <c r="AE11" s="8">
-        <f t="shared" ref="AE11:AO11" si="23">AE5-AE10</f>
-        <v>-126.68720000000008</v>
-      </c>
-      <c r="AF11" s="8">
-        <f t="shared" si="23"/>
-        <v>-104.55909200000008</v>
-      </c>
-      <c r="AG11" s="8">
-        <f t="shared" si="23"/>
-        <v>-76.068729000000019</v>
-      </c>
-      <c r="AH11" s="8">
-        <f t="shared" si="23"/>
-        <v>-57.649589986999956</v>
+        <v>-33.587573085000031</v>
       </c>
       <c r="AI11" s="8">
-        <f t="shared" si="23"/>
-        <v>-49.464391667789926</v>
+        <f t="shared" si="21"/>
+        <v>-19.956101138324982</v>
       </c>
       <c r="AJ11" s="8">
-        <f t="shared" si="23"/>
-        <v>-43.916946417880695</v>
+        <f t="shared" si="21"/>
+        <v>-14.167873709154037</v>
       </c>
       <c r="AK11" s="8">
-        <f t="shared" si="23"/>
-        <v>-39.819556755970893</v>
+        <f t="shared" si="21"/>
+        <v>-7.8747090162306108</v>
       </c>
       <c r="AL11" s="8">
-        <f t="shared" si="23"/>
-        <v>-35.522479990854322</v>
+        <f t="shared" si="21"/>
+        <v>-1.3255673734774973</v>
       </c>
       <c r="AM11" s="8">
-        <f t="shared" si="23"/>
-        <v>-31.018505526645072</v>
+        <f t="shared" si="21"/>
+        <v>5.4879023476906923</v>
       </c>
       <c r="AN11" s="8">
-        <f t="shared" si="23"/>
-        <v>-26.300185203179808</v>
+        <f t="shared" si="21"/>
+        <v>12.574308527917651</v>
       </c>
       <c r="AO11" s="8">
-        <f t="shared" si="23"/>
-        <v>-21.359825775693764</v>
+        <f t="shared" si="21"/>
+        <v>19.942524584649391</v>
       </c>
     </row>
     <row r="12" spans="2:145" x14ac:dyDescent="0.3">
@@ -2402,7 +2410,7 @@
         <v>0.5</v>
       </c>
       <c r="T12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U12" s="2">
         <v>1</v>
@@ -2437,47 +2445,47 @@
       </c>
       <c r="AE12" s="2">
         <f>SUM(S12:V12)</f>
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" s="2">
-        <f t="shared" ref="AF12:AO12" si="24">AE12*1.03</f>
-        <v>3.605</v>
+        <f t="shared" ref="AF12:AO12" si="22">AE12*1.03</f>
+        <v>2.5750000000000002</v>
       </c>
       <c r="AG12" s="2">
-        <f t="shared" si="24"/>
-        <v>3.7131500000000002</v>
+        <f t="shared" si="22"/>
+        <v>2.6522500000000004</v>
       </c>
       <c r="AH12" s="2">
-        <f t="shared" si="24"/>
-        <v>3.8245445000000005</v>
+        <f t="shared" si="22"/>
+        <v>2.7318175000000005</v>
       </c>
       <c r="AI12" s="2">
-        <f t="shared" si="24"/>
-        <v>3.9392808350000004</v>
+        <f t="shared" si="22"/>
+        <v>2.8137720250000005</v>
       </c>
       <c r="AJ12" s="2">
-        <f t="shared" si="24"/>
-        <v>4.0574592600500008</v>
+        <f t="shared" si="22"/>
+        <v>2.8981851857500005</v>
       </c>
       <c r="AK12" s="2">
-        <f t="shared" si="24"/>
-        <v>4.1791830378515007</v>
+        <f t="shared" si="22"/>
+        <v>2.9851307413225006</v>
       </c>
       <c r="AL12" s="2">
-        <f t="shared" si="24"/>
-        <v>4.3045585289870454</v>
+        <f t="shared" si="22"/>
+        <v>3.0746846635621758</v>
       </c>
       <c r="AM12" s="2">
-        <f t="shared" si="24"/>
-        <v>4.4336952848566566</v>
+        <f t="shared" si="22"/>
+        <v>3.1669252034690412</v>
       </c>
       <c r="AN12" s="2">
-        <f t="shared" si="24"/>
-        <v>4.5667061434023566</v>
+        <f t="shared" si="22"/>
+        <v>3.2619329595731124</v>
       </c>
       <c r="AO12" s="2">
-        <f t="shared" si="24"/>
-        <v>4.7037073277044277</v>
+        <f t="shared" si="22"/>
+        <v>3.3597909483603057</v>
       </c>
     </row>
     <row r="13" spans="2:145" x14ac:dyDescent="0.3">
@@ -2536,15 +2544,14 @@
         <v>-13</v>
       </c>
       <c r="T13" s="2">
-        <f t="shared" ref="T13:V13" si="25">P13*1.02</f>
-        <v>-7.242</v>
+        <v>-2.1</v>
       </c>
       <c r="U13" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" ref="U13:V13" si="23">Q13*1.02</f>
         <v>-7.7519999999999998</v>
       </c>
       <c r="V13" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>-26.316000000000003</v>
       </c>
       <c r="X13" s="2">
@@ -2574,47 +2581,47 @@
       </c>
       <c r="AE13" s="2">
         <f>SUM(S13:V13)</f>
-        <v>-54.31</v>
+        <v>-49.168000000000006</v>
       </c>
       <c r="AF13" s="2">
-        <f t="shared" ref="AF13:AO13" si="26">AE13*1.03</f>
-        <v>-55.939300000000003</v>
+        <f t="shared" ref="AF13:AO13" si="24">AE13*1.03</f>
+        <v>-50.643040000000006</v>
       </c>
       <c r="AG13" s="2">
-        <f t="shared" si="26"/>
-        <v>-57.617479000000003</v>
+        <f t="shared" si="24"/>
+        <v>-52.162331200000011</v>
       </c>
       <c r="AH13" s="2">
-        <f t="shared" si="26"/>
-        <v>-59.346003370000005</v>
+        <f t="shared" si="24"/>
+        <v>-53.727201136000012</v>
       </c>
       <c r="AI13" s="2">
-        <f t="shared" si="26"/>
-        <v>-61.126383471100006</v>
+        <f t="shared" si="24"/>
+        <v>-55.339017170080012</v>
       </c>
       <c r="AJ13" s="2">
-        <f t="shared" si="26"/>
-        <v>-62.960174975233009</v>
+        <f t="shared" si="24"/>
+        <v>-56.999187685182413</v>
       </c>
       <c r="AK13" s="2">
-        <f t="shared" si="26"/>
-        <v>-64.848980224490006</v>
+        <f t="shared" si="24"/>
+        <v>-58.709163315737889</v>
       </c>
       <c r="AL13" s="2">
-        <f t="shared" si="26"/>
-        <v>-66.794449631224708</v>
+        <f t="shared" si="24"/>
+        <v>-60.470438215210031</v>
       </c>
       <c r="AM13" s="2">
-        <f t="shared" si="26"/>
-        <v>-68.798283120161457</v>
+        <f t="shared" si="24"/>
+        <v>-62.284551361666331</v>
       </c>
       <c r="AN13" s="2">
-        <f t="shared" si="26"/>
-        <v>-70.862231613766298</v>
+        <f t="shared" si="24"/>
+        <v>-64.153087902516319</v>
       </c>
       <c r="AO13" s="2">
-        <f t="shared" si="26"/>
-        <v>-72.988098562179289</v>
+        <f t="shared" si="24"/>
+        <v>-66.07768053959181</v>
       </c>
     </row>
     <row r="14" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2622,156 +2629,156 @@
         <v>37</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:P14" si="27">C11-C12-C13</f>
+        <f t="shared" ref="C14:P14" si="25">C11-C12-C13</f>
         <v>-62.29999999999999</v>
       </c>
       <c r="D14" s="8">
+        <f t="shared" si="25"/>
+        <v>35.000000000000007</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="25"/>
+        <v>7.400000000000011</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="25"/>
+        <v>25.700000000000017</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="25"/>
+        <v>9.8999999999999826</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="25"/>
+        <v>7.5000000000000115</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="25"/>
+        <v>84.399999999999977</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="25"/>
+        <v>2.1999999999999602</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="25"/>
+        <v>6.2999999999999714</v>
+      </c>
+      <c r="L14" s="8">
+        <f t="shared" si="25"/>
+        <v>44.300000000000004</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" si="25"/>
+        <v>-18.09999999999998</v>
+      </c>
+      <c r="N14" s="8">
+        <f t="shared" si="25"/>
+        <v>17.799999999999976</v>
+      </c>
+      <c r="O14" s="8">
+        <f t="shared" si="25"/>
+        <v>7.6999999999999948</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" si="25"/>
+        <v>2.8999999999999853</v>
+      </c>
+      <c r="Q14" s="8">
+        <f t="shared" ref="Q14:V14" si="26">Q11-Q12-Q13</f>
+        <v>-19.600000000000001</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="26"/>
+        <v>-2.0999999999999979</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" si="26"/>
+        <v>-16.5</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" si="26"/>
+        <v>-34.4</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="26"/>
+        <v>-51.106000000000002</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" si="26"/>
+        <v>-22.187999999999988</v>
+      </c>
+      <c r="X14" s="8">
+        <f t="shared" ref="X14:AD14" si="27">X11-X12-X13</f>
+        <v>-12.799999999999965</v>
+      </c>
+      <c r="Y14" s="8">
         <f t="shared" si="27"/>
-        <v>35.000000000000007</v>
-      </c>
-      <c r="E14" s="8">
+        <v>-6.9999999999999858</v>
+      </c>
+      <c r="Z14" s="8">
         <f t="shared" si="27"/>
-        <v>7.400000000000011</v>
-      </c>
-      <c r="F14" s="8">
+        <v>-0.80000000000004334</v>
+      </c>
+      <c r="AA14" s="8">
         <f t="shared" si="27"/>
-        <v>25.700000000000017</v>
-      </c>
-      <c r="G14" s="8">
+        <v>5.7999999999999119</v>
+      </c>
+      <c r="AB14" s="8">
         <f t="shared" si="27"/>
-        <v>9.8999999999999826</v>
-      </c>
-      <c r="H14" s="8">
+        <v>103.99999999999997</v>
+      </c>
+      <c r="AC14" s="8">
         <f t="shared" si="27"/>
-        <v>7.5000000000000115</v>
-      </c>
-      <c r="I14" s="8">
+        <v>50.29999999999994</v>
+      </c>
+      <c r="AD14" s="8">
         <f t="shared" si="27"/>
-        <v>84.399999999999977</v>
-      </c>
-      <c r="J14" s="8">
-        <f t="shared" si="27"/>
-        <v>2.1999999999999602</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="27"/>
-        <v>6.2999999999999714</v>
-      </c>
-      <c r="L14" s="8">
-        <f t="shared" si="27"/>
-        <v>44.300000000000004</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" si="27"/>
-        <v>-18.09999999999998</v>
-      </c>
-      <c r="N14" s="8">
-        <f t="shared" si="27"/>
-        <v>17.799999999999976</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="27"/>
-        <v>7.6999999999999948</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" si="27"/>
-        <v>2.8999999999999853</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" ref="Q14:V14" si="28">Q11-Q12-Q13</f>
-        <v>-19.600000000000001</v>
-      </c>
-      <c r="R14" s="8">
+        <v>-11.099999999999937</v>
+      </c>
+      <c r="AE14" s="8">
+        <f t="shared" ref="AE14:AO14" si="28">AE11-AE12-AE13</f>
+        <v>-124.19400000000002</v>
+      </c>
+      <c r="AF14" s="8">
         <f t="shared" si="28"/>
-        <v>-2.0999999999999979</v>
-      </c>
-      <c r="S14" s="8">
+        <v>-32.83943500000003</v>
+      </c>
+      <c r="AG14" s="8">
         <f t="shared" si="28"/>
-        <v>-16.5</v>
-      </c>
-      <c r="T14" s="8">
+        <v>-1.6781080499999845</v>
+      </c>
+      <c r="AH14" s="8">
         <f t="shared" si="28"/>
-        <v>-21.623200000000001</v>
-      </c>
-      <c r="U14" s="8">
+        <v>17.407810550999983</v>
+      </c>
+      <c r="AI14" s="8">
         <f t="shared" si="28"/>
-        <v>-34.18</v>
-      </c>
-      <c r="V14" s="8">
+        <v>32.569144006755032</v>
+      </c>
+      <c r="AJ14" s="8">
         <f t="shared" si="28"/>
-        <v>-3.5739999999999839</v>
-      </c>
-      <c r="X14" s="8">
-        <f t="shared" ref="X14:AD14" si="29">X11-X12-X13</f>
-        <v>-12.799999999999965</v>
-      </c>
-      <c r="Y14" s="8">
-        <f t="shared" si="29"/>
-        <v>-6.9999999999999858</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" si="29"/>
-        <v>-0.80000000000004334</v>
-      </c>
-      <c r="AA14" s="8">
-        <f t="shared" si="29"/>
-        <v>5.7999999999999119</v>
-      </c>
-      <c r="AB14" s="8">
-        <f t="shared" si="29"/>
-        <v>103.99999999999997</v>
-      </c>
-      <c r="AC14" s="8">
-        <f t="shared" si="29"/>
-        <v>50.29999999999994</v>
-      </c>
-      <c r="AD14" s="8">
-        <f t="shared" si="29"/>
-        <v>-11.099999999999937</v>
-      </c>
-      <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AO14" si="30">AE11-AE12-AE13</f>
-        <v>-75.877200000000073</v>
-      </c>
-      <c r="AF14" s="8">
-        <f t="shared" si="30"/>
-        <v>-52.224792000000079</v>
-      </c>
-      <c r="AG14" s="8">
-        <f t="shared" si="30"/>
-        <v>-22.164400000000015</v>
-      </c>
-      <c r="AH14" s="8">
-        <f t="shared" si="30"/>
-        <v>-2.1281311169999526</v>
-      </c>
-      <c r="AI14" s="8">
-        <f t="shared" si="30"/>
-        <v>7.7227109683100821</v>
-      </c>
-      <c r="AJ14" s="8">
-        <f t="shared" si="30"/>
-        <v>14.985769297302312</v>
+        <v>39.933128790278374</v>
       </c>
       <c r="AK14" s="8">
-        <f t="shared" si="30"/>
-        <v>20.850240430667611</v>
+        <f t="shared" si="28"/>
+        <v>47.849323558184778</v>
       </c>
       <c r="AL14" s="8">
-        <f t="shared" si="30"/>
-        <v>26.967411111383342</v>
+        <f t="shared" si="28"/>
+        <v>56.07018617817036</v>
       </c>
       <c r="AM14" s="8">
-        <f t="shared" si="30"/>
-        <v>33.346082308659732</v>
+        <f t="shared" si="28"/>
+        <v>64.605528505887989</v>
       </c>
       <c r="AN14" s="8">
-        <f t="shared" si="30"/>
-        <v>39.995340267184133</v>
+        <f t="shared" si="28"/>
+        <v>73.465463470860854</v>
       </c>
       <c r="AO14" s="8">
-        <f t="shared" si="30"/>
-        <v>46.924565458781096</v>
+        <f t="shared" si="28"/>
+        <v>82.660414175880902</v>
       </c>
     </row>
     <row r="15" spans="2:145" x14ac:dyDescent="0.3">
@@ -2831,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U15" s="2">
         <v>0</v>
@@ -2866,47 +2873,47 @@
       </c>
       <c r="AE15" s="2">
         <f>SUM(S15:V15)</f>
-        <v>1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AF15" s="2">
         <f>AF14*0.15</f>
-        <v>-7.8337188000000113</v>
+        <v>-4.9259152500000045</v>
       </c>
       <c r="AG15" s="2">
-        <f t="shared" ref="AG15:AO15" si="31">AG14*0.15</f>
-        <v>-3.3246600000000019</v>
+        <f t="shared" ref="AG15:AO15" si="29">AG14*0.15</f>
+        <v>-0.25171620749999768</v>
       </c>
       <c r="AH15" s="2">
-        <f t="shared" si="31"/>
-        <v>-0.31921966754999287</v>
+        <f t="shared" si="29"/>
+        <v>2.6111715826499973</v>
       </c>
       <c r="AI15" s="2">
-        <f t="shared" si="31"/>
-        <v>1.1584066452465123</v>
+        <f t="shared" si="29"/>
+        <v>4.8853716010132544</v>
       </c>
       <c r="AJ15" s="2">
-        <f t="shared" si="31"/>
-        <v>2.2478653945953466</v>
+        <f t="shared" si="29"/>
+        <v>5.989969318541756</v>
       </c>
       <c r="AK15" s="2">
-        <f t="shared" si="31"/>
-        <v>3.1275360646001418</v>
+        <f t="shared" si="29"/>
+        <v>7.1773985337277164</v>
       </c>
       <c r="AL15" s="2">
-        <f t="shared" si="31"/>
-        <v>4.0451116667075011</v>
+        <f t="shared" si="29"/>
+        <v>8.4105279267255533</v>
       </c>
       <c r="AM15" s="2">
-        <f t="shared" si="31"/>
-        <v>5.0019123462989592</v>
+        <f t="shared" si="29"/>
+        <v>9.690829275883198</v>
       </c>
       <c r="AN15" s="2">
-        <f t="shared" si="31"/>
-        <v>5.9993010400776194</v>
+        <f t="shared" si="29"/>
+        <v>11.019819520629127</v>
       </c>
       <c r="AO15" s="2">
-        <f t="shared" si="31"/>
-        <v>7.0386848188171642</v>
+        <f t="shared" si="29"/>
+        <v>12.399062126382136</v>
       </c>
     </row>
     <row r="16" spans="2:145" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2914,572 +2921,572 @@
         <v>39</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:P16" si="32">C14-C15</f>
+        <f t="shared" ref="C16:P16" si="30">C14-C15</f>
         <v>-65.099999999999994</v>
       </c>
       <c r="D16" s="8">
+        <f t="shared" si="30"/>
+        <v>32.800000000000004</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="30"/>
+        <v>6.7000000000000108</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="30"/>
+        <v>24.300000000000018</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="30"/>
+        <v>5.6999999999999824</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="30"/>
+        <v>7.4000000000000119</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="30"/>
+        <v>251.7</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="30"/>
+        <v>1.8999999999999602</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="30"/>
+        <v>2.0999999999999712</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="30"/>
+        <v>24.600000000000005</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" si="30"/>
+        <v>-18.299999999999979</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="30"/>
+        <v>9.6999999999999762</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="30"/>
+        <v>-1.4000000000000048</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="30"/>
+        <v>-5.5000000000000204</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16:R16" si="31">Q14-Q15</f>
+        <v>-16.900000000000002</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" si="31"/>
+        <v>-6.0999999999999979</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:V16" si="32">S14-S15</f>
+        <v>-17.5</v>
+      </c>
+      <c r="T16" s="8">
         <f t="shared" si="32"/>
-        <v>32.800000000000004</v>
-      </c>
-      <c r="E16" s="8">
+        <v>-35.6</v>
+      </c>
+      <c r="U16" s="8">
         <f t="shared" si="32"/>
-        <v>6.7000000000000108</v>
-      </c>
-      <c r="F16" s="8">
+        <v>-51.106000000000002</v>
+      </c>
+      <c r="V16" s="8">
         <f t="shared" si="32"/>
-        <v>24.300000000000018</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="32"/>
-        <v>5.6999999999999824</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="32"/>
-        <v>7.4000000000000119</v>
-      </c>
-      <c r="I16" s="8">
-        <f t="shared" si="32"/>
-        <v>251.7</v>
-      </c>
-      <c r="J16" s="8">
-        <f t="shared" si="32"/>
-        <v>1.8999999999999602</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="32"/>
-        <v>2.0999999999999712</v>
-      </c>
-      <c r="L16" s="8">
-        <f t="shared" si="32"/>
-        <v>24.600000000000005</v>
-      </c>
-      <c r="M16" s="8">
-        <f t="shared" si="32"/>
-        <v>-18.299999999999979</v>
-      </c>
-      <c r="N16" s="8">
-        <f t="shared" si="32"/>
-        <v>9.6999999999999762</v>
-      </c>
-      <c r="O16" s="8">
-        <f t="shared" si="32"/>
-        <v>-1.4000000000000048</v>
-      </c>
-      <c r="P16" s="8">
-        <f t="shared" si="32"/>
-        <v>-5.5000000000000204</v>
-      </c>
-      <c r="Q16" s="8">
-        <f t="shared" ref="Q16:R16" si="33">Q14-Q15</f>
-        <v>-16.900000000000002</v>
-      </c>
-      <c r="R16" s="8">
+        <v>-22.187999999999988</v>
+      </c>
+      <c r="X16" s="8">
+        <f t="shared" ref="X16:AD16" si="33">X14-X15</f>
+        <v>-14.199999999999966</v>
+      </c>
+      <c r="Y16" s="8">
         <f t="shared" si="33"/>
-        <v>-6.0999999999999979</v>
-      </c>
-      <c r="S16" s="8">
-        <f t="shared" ref="S16:V16" si="34">S14-S15</f>
-        <v>-17.5</v>
-      </c>
-      <c r="T16" s="8">
+        <v>-9.5999999999999854</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" si="33"/>
+        <v>-6.2000000000000437</v>
+      </c>
+      <c r="AA16" s="8">
+        <f t="shared" si="33"/>
+        <v>-1.3000000000000878</v>
+      </c>
+      <c r="AB16" s="8">
+        <f t="shared" si="33"/>
+        <v>266.69999999999993</v>
+      </c>
+      <c r="AC16" s="8">
+        <f t="shared" si="33"/>
+        <v>18.099999999999945</v>
+      </c>
+      <c r="AD16" s="8">
+        <f t="shared" si="33"/>
+        <v>-29.899999999999945</v>
+      </c>
+      <c r="AE16" s="8">
+        <f t="shared" ref="AE16:AO16" si="34">AE14-AE15</f>
+        <v>-126.39400000000002</v>
+      </c>
+      <c r="AF16" s="8">
         <f t="shared" si="34"/>
-        <v>-21.623200000000001</v>
-      </c>
-      <c r="U16" s="8">
+        <v>-27.913519750000027</v>
+      </c>
+      <c r="AG16" s="8">
         <f t="shared" si="34"/>
-        <v>-34.18</v>
-      </c>
-      <c r="V16" s="8">
+        <v>-1.4263918424999869</v>
+      </c>
+      <c r="AH16" s="8">
         <f t="shared" si="34"/>
-        <v>-3.5739999999999839</v>
-      </c>
-      <c r="X16" s="8">
-        <f t="shared" ref="X16:AD16" si="35">X14-X15</f>
-        <v>-14.199999999999966</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" si="35"/>
-        <v>-9.5999999999999854</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" si="35"/>
-        <v>-6.2000000000000437</v>
-      </c>
-      <c r="AA16" s="8">
-        <f t="shared" si="35"/>
-        <v>-1.3000000000000878</v>
-      </c>
-      <c r="AB16" s="8">
-        <f t="shared" si="35"/>
-        <v>266.69999999999993</v>
-      </c>
-      <c r="AC16" s="8">
-        <f t="shared" si="35"/>
-        <v>18.099999999999945</v>
-      </c>
-      <c r="AD16" s="8">
-        <f t="shared" si="35"/>
-        <v>-29.899999999999945</v>
-      </c>
-      <c r="AE16" s="8">
-        <f t="shared" ref="AE16:AO16" si="36">AE14-AE15</f>
-        <v>-76.877200000000073</v>
-      </c>
-      <c r="AF16" s="8">
-        <f t="shared" si="36"/>
-        <v>-44.391073200000065</v>
-      </c>
-      <c r="AG16" s="8">
-        <f t="shared" si="36"/>
-        <v>-18.839740000000013</v>
-      </c>
-      <c r="AH16" s="8">
-        <f t="shared" si="36"/>
-        <v>-1.8089114494499596</v>
+        <v>14.796638968349985</v>
       </c>
       <c r="AI16" s="8">
-        <f t="shared" si="36"/>
-        <v>6.5643043230635696</v>
+        <f t="shared" si="34"/>
+        <v>27.683772405741777</v>
       </c>
       <c r="AJ16" s="8">
-        <f t="shared" si="36"/>
-        <v>12.737903902706964</v>
+        <f t="shared" si="34"/>
+        <v>33.943159471736621</v>
       </c>
       <c r="AK16" s="8">
-        <f t="shared" si="36"/>
-        <v>17.722704366067468</v>
+        <f t="shared" si="34"/>
+        <v>40.67192502445706</v>
       </c>
       <c r="AL16" s="8">
-        <f t="shared" si="36"/>
-        <v>22.92229944467584</v>
+        <f t="shared" si="34"/>
+        <v>47.65965825144481</v>
       </c>
       <c r="AM16" s="8">
-        <f t="shared" si="36"/>
-        <v>28.344169962360773</v>
+        <f t="shared" si="34"/>
+        <v>54.914699230004793</v>
       </c>
       <c r="AN16" s="8">
-        <f t="shared" si="36"/>
-        <v>33.996039227106515</v>
+        <f t="shared" si="34"/>
+        <v>62.445643950231727</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" si="36"/>
-        <v>39.885880639963929</v>
+        <f t="shared" si="34"/>
+        <v>70.261352049498768</v>
       </c>
       <c r="AP16" s="1">
         <f>AO16*(1+$AS$21)</f>
-        <v>39.487021833564292</v>
+        <v>69.558738529003776</v>
       </c>
       <c r="AQ16" s="1">
-        <f t="shared" ref="AQ16:DB16" si="37">AP16*(1+$AS$21)</f>
-        <v>39.092151615228651</v>
+        <f t="shared" ref="AQ16:DB16" si="35">AP16*(1+$AS$21)</f>
+        <v>68.863151143713736</v>
       </c>
       <c r="AR16" s="1">
-        <f t="shared" si="37"/>
-        <v>38.701230099076362</v>
+        <f t="shared" si="35"/>
+        <v>68.174519632276599</v>
       </c>
       <c r="AS16" s="1">
-        <f t="shared" si="37"/>
-        <v>38.3142177980856</v>
+        <f t="shared" si="35"/>
+        <v>67.492774435953834</v>
       </c>
       <c r="AT16" s="1">
-        <f t="shared" si="37"/>
-        <v>37.931075620104743</v>
+        <f t="shared" si="35"/>
+        <v>66.817846691594298</v>
       </c>
       <c r="AU16" s="1">
-        <f t="shared" si="37"/>
-        <v>37.551764863903692</v>
+        <f t="shared" si="35"/>
+        <v>66.149668224678351</v>
       </c>
       <c r="AV16" s="1">
-        <f t="shared" si="37"/>
-        <v>37.176247215264652</v>
+        <f t="shared" si="35"/>
+        <v>65.488171542431573</v>
       </c>
       <c r="AW16" s="1">
-        <f t="shared" si="37"/>
-        <v>36.804484743112006</v>
+        <f t="shared" si="35"/>
+        <v>64.833289827007263</v>
       </c>
       <c r="AX16" s="1">
-        <f t="shared" si="37"/>
-        <v>36.436439895680884</v>
+        <f t="shared" si="35"/>
+        <v>64.184956928737193</v>
       </c>
       <c r="AY16" s="1">
-        <f t="shared" si="37"/>
-        <v>36.072075496724075</v>
+        <f t="shared" si="35"/>
+        <v>63.54310735944982</v>
       </c>
       <c r="AZ16" s="1">
-        <f t="shared" si="37"/>
-        <v>35.711354741756836</v>
+        <f t="shared" si="35"/>
+        <v>62.907676285855324</v>
       </c>
       <c r="BA16" s="1">
-        <f t="shared" si="37"/>
-        <v>35.354241194339266</v>
+        <f t="shared" si="35"/>
+        <v>62.278599522996771</v>
       </c>
       <c r="BB16" s="1">
-        <f t="shared" si="37"/>
-        <v>35.000698782395872</v>
+        <f t="shared" si="35"/>
+        <v>61.655813527766803</v>
       </c>
       <c r="BC16" s="1">
-        <f t="shared" si="37"/>
-        <v>34.650691794571912</v>
+        <f t="shared" si="35"/>
+        <v>61.039255392489132</v>
       </c>
       <c r="BD16" s="1">
-        <f t="shared" si="37"/>
-        <v>34.304184876626195</v>
+        <f t="shared" si="35"/>
+        <v>60.428862838564243</v>
       </c>
       <c r="BE16" s="1">
-        <f t="shared" si="37"/>
-        <v>33.961143027859933</v>
+        <f t="shared" si="35"/>
+        <v>59.824574210178596</v>
       </c>
       <c r="BF16" s="1">
-        <f t="shared" si="37"/>
-        <v>33.621531597581331</v>
+        <f t="shared" si="35"/>
+        <v>59.226328468076808</v>
       </c>
       <c r="BG16" s="1">
-        <f t="shared" si="37"/>
-        <v>33.285316281605517</v>
+        <f t="shared" si="35"/>
+        <v>58.634065183396039</v>
       </c>
       <c r="BH16" s="1">
-        <f t="shared" si="37"/>
-        <v>32.95246311878946</v>
+        <f t="shared" si="35"/>
+        <v>58.047724531562075</v>
       </c>
       <c r="BI16" s="1">
-        <f t="shared" si="37"/>
-        <v>32.622938487601566</v>
+        <f t="shared" si="35"/>
+        <v>57.467247286246455</v>
       </c>
       <c r="BJ16" s="1">
-        <f t="shared" si="37"/>
-        <v>32.296709102725551</v>
+        <f t="shared" si="35"/>
+        <v>56.892574813383987</v>
       </c>
       <c r="BK16" s="1">
-        <f t="shared" si="37"/>
-        <v>31.973742011698295</v>
+        <f t="shared" si="35"/>
+        <v>56.323649065250144</v>
       </c>
       <c r="BL16" s="1">
-        <f t="shared" si="37"/>
-        <v>31.654004591581312</v>
+        <f t="shared" si="35"/>
+        <v>55.760412574597645</v>
       </c>
       <c r="BM16" s="1">
-        <f t="shared" si="37"/>
-        <v>31.337464545665497</v>
+        <f t="shared" si="35"/>
+        <v>55.20280844885167</v>
       </c>
       <c r="BN16" s="1">
-        <f t="shared" si="37"/>
-        <v>31.024089900208843</v>
+        <f t="shared" si="35"/>
+        <v>54.65078036436315</v>
       </c>
       <c r="BO16" s="1">
-        <f t="shared" si="37"/>
-        <v>30.713849001206754</v>
+        <f t="shared" si="35"/>
+        <v>54.104272560719515</v>
       </c>
       <c r="BP16" s="1">
-        <f t="shared" si="37"/>
-        <v>30.406710511194685</v>
+        <f t="shared" si="35"/>
+        <v>53.563229835112317</v>
       </c>
       <c r="BQ16" s="1">
-        <f t="shared" si="37"/>
-        <v>30.102643406082738</v>
+        <f t="shared" si="35"/>
+        <v>53.027597536761192</v>
       </c>
       <c r="BR16" s="1">
-        <f t="shared" si="37"/>
-        <v>29.801616972021911</v>
+        <f t="shared" si="35"/>
+        <v>52.497321561393576</v>
       </c>
       <c r="BS16" s="1">
-        <f t="shared" si="37"/>
-        <v>29.50360080230169</v>
+        <f t="shared" si="35"/>
+        <v>51.972348345779643</v>
       </c>
       <c r="BT16" s="1">
-        <f t="shared" si="37"/>
-        <v>29.208564794278672</v>
+        <f t="shared" si="35"/>
+        <v>51.452624862321848</v>
       </c>
       <c r="BU16" s="1">
-        <f t="shared" si="37"/>
-        <v>28.916479146335885</v>
+        <f t="shared" si="35"/>
+        <v>50.938098613698628</v>
       </c>
       <c r="BV16" s="1">
-        <f t="shared" si="37"/>
-        <v>28.627314354872524</v>
+        <f t="shared" si="35"/>
+        <v>50.428717627561639</v>
       </c>
       <c r="BW16" s="1">
-        <f t="shared" si="37"/>
-        <v>28.341041211323798</v>
+        <f t="shared" si="35"/>
+        <v>49.924430451286021</v>
       </c>
       <c r="BX16" s="1">
-        <f t="shared" si="37"/>
-        <v>28.05763079921056</v>
+        <f t="shared" si="35"/>
+        <v>49.425186146773157</v>
       </c>
       <c r="BY16" s="1">
-        <f t="shared" si="37"/>
-        <v>27.777054491218454</v>
+        <f t="shared" si="35"/>
+        <v>48.930934285305426</v>
       </c>
       <c r="BZ16" s="1">
-        <f t="shared" si="37"/>
-        <v>27.499283946306271</v>
+        <f t="shared" si="35"/>
+        <v>48.441624942452371</v>
       </c>
       <c r="CA16" s="1">
-        <f t="shared" si="37"/>
-        <v>27.224291106843207</v>
+        <f t="shared" si="35"/>
+        <v>47.957208693027845</v>
       </c>
       <c r="CB16" s="1">
-        <f t="shared" si="37"/>
-        <v>26.952048195774776</v>
+        <f t="shared" si="35"/>
+        <v>47.477636606097569</v>
       </c>
       <c r="CC16" s="1">
-        <f t="shared" si="37"/>
-        <v>26.682527713817027</v>
+        <f t="shared" si="35"/>
+        <v>47.00286024003659</v>
       </c>
       <c r="CD16" s="1">
-        <f t="shared" si="37"/>
-        <v>26.415702436678856</v>
+        <f t="shared" si="35"/>
+        <v>46.532831637636221</v>
       </c>
       <c r="CE16" s="1">
-        <f t="shared" si="37"/>
-        <v>26.151545412312068</v>
+        <f t="shared" si="35"/>
+        <v>46.067503321259856</v>
       </c>
       <c r="CF16" s="1">
-        <f t="shared" si="37"/>
-        <v>25.890029958188947</v>
+        <f t="shared" si="35"/>
+        <v>45.606828288047261</v>
       </c>
       <c r="CG16" s="1">
-        <f t="shared" si="37"/>
-        <v>25.631129658607058</v>
+        <f t="shared" si="35"/>
+        <v>45.150760005166788</v>
       </c>
       <c r="CH16" s="1">
-        <f t="shared" si="37"/>
-        <v>25.374818362020989</v>
+        <f t="shared" si="35"/>
+        <v>44.699252405115118</v>
       </c>
       <c r="CI16" s="1">
-        <f t="shared" si="37"/>
-        <v>25.121070178400778</v>
+        <f t="shared" si="35"/>
+        <v>44.252259881063964</v>
       </c>
       <c r="CJ16" s="1">
-        <f t="shared" si="37"/>
-        <v>24.869859476616771</v>
+        <f t="shared" si="35"/>
+        <v>43.809737282253323</v>
       </c>
       <c r="CK16" s="1">
-        <f t="shared" si="37"/>
-        <v>24.621160881850603</v>
+        <f t="shared" si="35"/>
+        <v>43.37163990943079</v>
       </c>
       <c r="CL16" s="1">
-        <f t="shared" si="37"/>
-        <v>24.374949273032097</v>
+        <f t="shared" si="35"/>
+        <v>42.937923510336482</v>
       </c>
       <c r="CM16" s="1">
-        <f t="shared" si="37"/>
-        <v>24.131199780301777</v>
+        <f t="shared" si="35"/>
+        <v>42.508544275233113</v>
       </c>
       <c r="CN16" s="1">
-        <f t="shared" si="37"/>
-        <v>23.889887782498761</v>
+        <f t="shared" si="35"/>
+        <v>42.08345883248078</v>
       </c>
       <c r="CO16" s="1">
-        <f t="shared" si="37"/>
-        <v>23.650988904673774</v>
+        <f t="shared" si="35"/>
+        <v>41.662624244155971</v>
       </c>
       <c r="CP16" s="1">
-        <f t="shared" si="37"/>
-        <v>23.414479015627037</v>
+        <f t="shared" si="35"/>
+        <v>41.245998001714412</v>
       </c>
       <c r="CQ16" s="1">
-        <f t="shared" si="37"/>
-        <v>23.180334225470766</v>
+        <f t="shared" si="35"/>
+        <v>40.833538021697265</v>
       </c>
       <c r="CR16" s="1">
-        <f t="shared" si="37"/>
-        <v>22.948530883216058</v>
+        <f t="shared" si="35"/>
+        <v>40.42520264148029</v>
       </c>
       <c r="CS16" s="1">
-        <f t="shared" si="37"/>
-        <v>22.719045574383898</v>
+        <f t="shared" si="35"/>
+        <v>40.020950615065487</v>
       </c>
       <c r="CT16" s="1">
-        <f t="shared" si="37"/>
-        <v>22.491855118640061</v>
+        <f t="shared" si="35"/>
+        <v>39.620741108914835</v>
       </c>
       <c r="CU16" s="1">
-        <f t="shared" si="37"/>
-        <v>22.266936567453659</v>
+        <f t="shared" si="35"/>
+        <v>39.224533697825684</v>
       </c>
       <c r="CV16" s="1">
-        <f t="shared" si="37"/>
-        <v>22.044267201779121</v>
+        <f t="shared" si="35"/>
+        <v>38.832288360847429</v>
       </c>
       <c r="CW16" s="1">
-        <f t="shared" si="37"/>
-        <v>21.823824529761328</v>
+        <f t="shared" si="35"/>
+        <v>38.443965477238955</v>
       </c>
       <c r="CX16" s="1">
-        <f t="shared" si="37"/>
-        <v>21.605586284463715</v>
+        <f t="shared" si="35"/>
+        <v>38.059525822466561</v>
       </c>
       <c r="CY16" s="1">
-        <f t="shared" si="37"/>
-        <v>21.389530421619078</v>
+        <f t="shared" si="35"/>
+        <v>37.678930564241895</v>
       </c>
       <c r="CZ16" s="1">
-        <f t="shared" si="37"/>
-        <v>21.175635117402887</v>
+        <f t="shared" si="35"/>
+        <v>37.302141258599477</v>
       </c>
       <c r="DA16" s="1">
-        <f t="shared" si="37"/>
-        <v>20.963878766228859</v>
+        <f t="shared" si="35"/>
+        <v>36.929119846013485</v>
       </c>
       <c r="DB16" s="1">
-        <f t="shared" si="37"/>
-        <v>20.75423997856657</v>
+        <f t="shared" si="35"/>
+        <v>36.559828647553353</v>
       </c>
       <c r="DC16" s="1">
-        <f t="shared" ref="DC16:EO16" si="38">DB16*(1+$AS$21)</f>
-        <v>20.546697578780904</v>
+        <f t="shared" ref="DC16:EO16" si="36">DB16*(1+$AS$21)</f>
+        <v>36.194230361077821</v>
       </c>
       <c r="DD16" s="1">
-        <f t="shared" si="38"/>
-        <v>20.341230602993093</v>
+        <f t="shared" si="36"/>
+        <v>35.832288057467039</v>
       </c>
       <c r="DE16" s="1">
-        <f t="shared" si="38"/>
-        <v>20.137818296963161</v>
+        <f t="shared" si="36"/>
+        <v>35.473965176892371</v>
       </c>
       <c r="DF16" s="1">
-        <f t="shared" si="38"/>
-        <v>19.93644011399353</v>
+        <f t="shared" si="36"/>
+        <v>35.119225525123447</v>
       </c>
       <c r="DG16" s="1">
-        <f t="shared" si="38"/>
-        <v>19.737075712853596</v>
+        <f t="shared" si="36"/>
+        <v>34.768033269872213</v>
       </c>
       <c r="DH16" s="1">
-        <f t="shared" si="38"/>
-        <v>19.53970495572506</v>
+        <f t="shared" si="36"/>
+        <v>34.42035293717349</v>
       </c>
       <c r="DI16" s="1">
-        <f t="shared" si="38"/>
-        <v>19.34430790616781</v>
+        <f t="shared" si="36"/>
+        <v>34.076149407801758</v>
       </c>
       <c r="DJ16" s="1">
-        <f t="shared" si="38"/>
-        <v>19.150864827106133</v>
+        <f t="shared" si="36"/>
+        <v>33.735387913723741</v>
       </c>
       <c r="DK16" s="1">
-        <f t="shared" si="38"/>
-        <v>18.959356178835073</v>
+        <f t="shared" si="36"/>
+        <v>33.398034034586502</v>
       </c>
       <c r="DL16" s="1">
-        <f t="shared" si="38"/>
-        <v>18.769762617046723</v>
+        <f t="shared" si="36"/>
+        <v>33.064053694240634</v>
       </c>
       <c r="DM16" s="1">
-        <f t="shared" si="38"/>
-        <v>18.582064990876255</v>
+        <f t="shared" si="36"/>
+        <v>32.73341315729823</v>
       </c>
       <c r="DN16" s="1">
-        <f t="shared" si="38"/>
-        <v>18.396244340967492</v>
+        <f t="shared" si="36"/>
+        <v>32.406079025725248</v>
       </c>
       <c r="DO16" s="1">
-        <f t="shared" si="38"/>
-        <v>18.212281897557816</v>
+        <f t="shared" si="36"/>
+        <v>32.082018235467991</v>
       </c>
       <c r="DP16" s="1">
-        <f t="shared" si="38"/>
-        <v>18.030159078582237</v>
+        <f t="shared" si="36"/>
+        <v>31.761198053113311</v>
       </c>
       <c r="DQ16" s="1">
-        <f t="shared" si="38"/>
-        <v>17.849857487796413</v>
+        <f t="shared" si="36"/>
+        <v>31.443586072582178</v>
       </c>
       <c r="DR16" s="1">
-        <f t="shared" si="38"/>
-        <v>17.67135891291845</v>
+        <f t="shared" si="36"/>
+        <v>31.129150211856356</v>
       </c>
       <c r="DS16" s="1">
-        <f t="shared" si="38"/>
-        <v>17.494645323789264</v>
+        <f t="shared" si="36"/>
+        <v>30.817858709737791</v>
       </c>
       <c r="DT16" s="1">
-        <f t="shared" si="38"/>
-        <v>17.31969887055137</v>
+        <f t="shared" si="36"/>
+        <v>30.509680122640415</v>
       </c>
       <c r="DU16" s="1">
-        <f t="shared" si="38"/>
-        <v>17.146501881845857</v>
+        <f t="shared" si="36"/>
+        <v>30.20458332141401</v>
       </c>
       <c r="DV16" s="1">
-        <f t="shared" si="38"/>
-        <v>16.975036863027398</v>
+        <f t="shared" si="36"/>
+        <v>29.902537488199869</v>
       </c>
       <c r="DW16" s="1">
-        <f t="shared" si="38"/>
-        <v>16.805286494397123</v>
+        <f t="shared" si="36"/>
+        <v>29.603512113317869</v>
       </c>
       <c r="DX16" s="1">
-        <f t="shared" si="38"/>
-        <v>16.637233629453153</v>
+        <f t="shared" si="36"/>
+        <v>29.307476992184689</v>
       </c>
       <c r="DY16" s="1">
-        <f t="shared" si="38"/>
-        <v>16.47086129315862</v>
+        <f t="shared" si="36"/>
+        <v>29.014402222262841</v>
       </c>
       <c r="DZ16" s="1">
-        <f t="shared" si="38"/>
-        <v>16.306152680227033</v>
+        <f t="shared" si="36"/>
+        <v>28.724258200040214</v>
       </c>
       <c r="EA16" s="1">
-        <f t="shared" si="38"/>
-        <v>16.143091153424763</v>
+        <f t="shared" si="36"/>
+        <v>28.437015618039812</v>
       </c>
       <c r="EB16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.981660241890514</v>
+        <f t="shared" si="36"/>
+        <v>28.152645461859414</v>
       </c>
       <c r="EC16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.821843639471609</v>
+        <f t="shared" si="36"/>
+        <v>27.871119007240821</v>
       </c>
       <c r="ED16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.663625203076894</v>
+        <f t="shared" si="36"/>
+        <v>27.592407817168414</v>
       </c>
       <c r="EE16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.506988951046125</v>
+        <f t="shared" si="36"/>
+        <v>27.31648373899673</v>
       </c>
       <c r="EF16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.351919061535664</v>
+        <f t="shared" si="36"/>
+        <v>27.043318901606764</v>
       </c>
       <c r="EG16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.198399870920307</v>
+        <f t="shared" si="36"/>
+        <v>26.772885712590696</v>
       </c>
       <c r="EH16" s="1">
-        <f t="shared" si="38"/>
-        <v>15.046415872211103</v>
+        <f t="shared" si="36"/>
+        <v>26.50515685546479</v>
       </c>
       <c r="EI16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.895951713488992</v>
+        <f t="shared" si="36"/>
+        <v>26.240105286910143</v>
       </c>
       <c r="EJ16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.746992196354103</v>
+        <f t="shared" si="36"/>
+        <v>25.977704234041042</v>
       </c>
       <c r="EK16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.599522274390562</v>
+        <f t="shared" si="36"/>
+        <v>25.717927191700632</v>
       </c>
       <c r="EL16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.453527051646656</v>
+        <f t="shared" si="36"/>
+        <v>25.460747919783625</v>
       </c>
       <c r="EM16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.308991781130189</v>
+        <f t="shared" si="36"/>
+        <v>25.206140440585788</v>
       </c>
       <c r="EN16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.165901863318886</v>
+        <f t="shared" si="36"/>
+        <v>24.95407903617993</v>
       </c>
       <c r="EO16" s="1">
-        <f t="shared" si="38"/>
-        <v>14.024242844685697</v>
+        <f t="shared" si="36"/>
+        <v>24.704538245818132</v>
       </c>
     </row>
     <row r="17" spans="2:45" x14ac:dyDescent="0.3">
@@ -3538,13 +3545,13 @@
         <v>106.6</v>
       </c>
       <c r="T17" s="2">
-        <v>106.6</v>
+        <v>106.9</v>
       </c>
       <c r="U17" s="2">
-        <v>106.6</v>
+        <v>106.9</v>
       </c>
       <c r="V17" s="2">
-        <v>106.6</v>
+        <v>106.9</v>
       </c>
       <c r="X17" s="2">
         <v>103.7</v>
@@ -3568,37 +3575,37 @@
         <v>105.1</v>
       </c>
       <c r="AE17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AF17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AG17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AH17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AI17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AJ17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AK17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AL17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AM17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AN17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
       <c r="AO17" s="2">
-        <v>105.1</v>
+        <v>106.9</v>
       </c>
     </row>
     <row r="18" spans="2:45" x14ac:dyDescent="0.3">
@@ -3606,156 +3613,156 @@
         <v>40</v>
       </c>
       <c r="C18" s="7">
-        <f t="shared" ref="C18:P18" si="39">C16/C17</f>
+        <f t="shared" ref="C18:P18" si="37">C16/C17</f>
         <v>-0.62777242044358716</v>
       </c>
       <c r="D18" s="7">
+        <f t="shared" si="37"/>
+        <v>0.31629701060752174</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="37"/>
+        <v>6.4609450337512156E-2</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="37"/>
+        <v>0.23432979749276778</v>
+      </c>
+      <c r="G18" s="7">
+        <f t="shared" si="37"/>
+        <v>5.4966248794599638E-2</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="37"/>
+        <v>7.1359691417550733E-2</v>
+      </c>
+      <c r="I18" s="7">
+        <f t="shared" si="37"/>
+        <v>2.4271938283510122</v>
+      </c>
+      <c r="J18" s="7">
+        <f t="shared" si="37"/>
+        <v>1.8322082931532886E-2</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="37"/>
+        <v>2.025072324011544E-2</v>
+      </c>
+      <c r="L18" s="7">
+        <f t="shared" si="37"/>
+        <v>0.23722275795564132</v>
+      </c>
+      <c r="M18" s="7">
+        <f t="shared" si="37"/>
+        <v>-0.17647058823529391</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="37"/>
+        <v>9.3539054966248564E-2</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" si="37"/>
+        <v>-1.3500482160077192E-2</v>
+      </c>
+      <c r="P18" s="7">
+        <f t="shared" si="37"/>
+        <v>-5.3037608486017553E-2</v>
+      </c>
+      <c r="Q18" s="7">
+        <f t="shared" ref="Q18:R18" si="38">Q16/Q17</f>
+        <v>-0.16203259827420904</v>
+      </c>
+      <c r="R18" s="7">
+        <f t="shared" si="38"/>
+        <v>-5.8039961941008543E-2</v>
+      </c>
+      <c r="S18" s="7">
+        <f t="shared" ref="S18:V18" si="39">S16/S17</f>
+        <v>-0.16416510318949346</v>
+      </c>
+      <c r="T18" s="7">
         <f t="shared" si="39"/>
-        <v>0.31629701060752174</v>
-      </c>
-      <c r="E18" s="7">
+        <v>-0.33302151543498598</v>
+      </c>
+      <c r="U18" s="7">
         <f t="shared" si="39"/>
-        <v>6.4609450337512156E-2</v>
-      </c>
-      <c r="F18" s="7">
+        <v>-0.47807296538821326</v>
+      </c>
+      <c r="V18" s="7">
         <f t="shared" si="39"/>
-        <v>0.23432979749276778</v>
-      </c>
-      <c r="G18" s="7">
-        <f t="shared" si="39"/>
-        <v>5.4966248794599638E-2</v>
-      </c>
-      <c r="H18" s="7">
-        <f t="shared" si="39"/>
-        <v>7.1359691417550733E-2</v>
-      </c>
-      <c r="I18" s="7">
-        <f t="shared" si="39"/>
-        <v>2.4271938283510122</v>
-      </c>
-      <c r="J18" s="7">
-        <f t="shared" si="39"/>
-        <v>1.8322082931532886E-2</v>
-      </c>
-      <c r="K18" s="7">
-        <f t="shared" si="39"/>
-        <v>2.025072324011544E-2</v>
-      </c>
-      <c r="L18" s="7">
-        <f t="shared" si="39"/>
-        <v>0.23722275795564132</v>
-      </c>
-      <c r="M18" s="7">
-        <f t="shared" si="39"/>
-        <v>-0.17647058823529391</v>
-      </c>
-      <c r="N18" s="7">
-        <f t="shared" si="39"/>
-        <v>9.3539054966248564E-2</v>
-      </c>
-      <c r="O18" s="7">
-        <f t="shared" si="39"/>
-        <v>-1.3500482160077192E-2</v>
-      </c>
-      <c r="P18" s="7">
-        <f t="shared" si="39"/>
-        <v>-5.3037608486017553E-2</v>
-      </c>
-      <c r="Q18" s="7">
-        <f t="shared" ref="Q18:R18" si="40">Q16/Q17</f>
-        <v>-0.16203259827420904</v>
-      </c>
-      <c r="R18" s="7">
+        <v>-0.20755846585594001</v>
+      </c>
+      <c r="X18" s="7">
+        <f t="shared" ref="X18:AD18" si="40">X16/X17</f>
+        <v>-0.13693346190935357</v>
+      </c>
+      <c r="Y18" s="7">
         <f t="shared" si="40"/>
-        <v>-5.8039961941008543E-2</v>
-      </c>
-      <c r="S18" s="7">
-        <f t="shared" ref="S18:V18" si="41">S16/S17</f>
-        <v>-0.16416510318949346</v>
-      </c>
-      <c r="T18" s="7">
+        <v>-9.2574734811957424E-2</v>
+      </c>
+      <c r="Z18" s="7">
+        <f t="shared" si="40"/>
+        <v>-5.9787849566056352E-2</v>
+      </c>
+      <c r="AA18" s="7">
+        <f t="shared" si="40"/>
+        <v>-1.2536162005786767E-2</v>
+      </c>
+      <c r="AB18" s="7">
+        <f t="shared" si="40"/>
+        <v>2.5718418514946957</v>
+      </c>
+      <c r="AC18" s="7">
+        <f t="shared" si="40"/>
+        <v>0.17454194792671113</v>
+      </c>
+      <c r="AD18" s="7">
+        <f t="shared" si="40"/>
+        <v>-0.28449096098953325</v>
+      </c>
+      <c r="AE18" s="7">
+        <f t="shared" ref="AE18:AO18" si="41">AE16/AE17</f>
+        <v>-1.1823573433115062</v>
+      </c>
+      <c r="AF18" s="7">
         <f t="shared" si="41"/>
-        <v>-0.20284427767354599</v>
-      </c>
-      <c r="U18" s="7">
+        <v>-0.26111805191768034</v>
+      </c>
+      <c r="AG18" s="7">
         <f t="shared" si="41"/>
-        <v>-0.32063789868667919</v>
-      </c>
-      <c r="V18" s="7">
+        <v>-1.3343235196445152E-2</v>
+      </c>
+      <c r="AH18" s="7">
         <f t="shared" si="41"/>
-        <v>-3.3527204502814108E-2</v>
-      </c>
-      <c r="X18" s="7">
-        <f t="shared" ref="X18:AD18" si="42">X16/X17</f>
-        <v>-0.13693346190935357</v>
-      </c>
-      <c r="Y18" s="7">
-        <f t="shared" si="42"/>
-        <v>-9.2574734811957424E-2</v>
-      </c>
-      <c r="Z18" s="7">
-        <f t="shared" si="42"/>
-        <v>-5.9787849566056352E-2</v>
-      </c>
-      <c r="AA18" s="7">
-        <f t="shared" si="42"/>
-        <v>-1.2536162005786767E-2</v>
-      </c>
-      <c r="AB18" s="7">
-        <f t="shared" si="42"/>
-        <v>2.5718418514946957</v>
-      </c>
-      <c r="AC18" s="7">
-        <f t="shared" si="42"/>
-        <v>0.17454194792671113</v>
-      </c>
-      <c r="AD18" s="7">
-        <f t="shared" si="42"/>
-        <v>-0.28449096098953325</v>
-      </c>
-      <c r="AE18" s="7">
-        <f t="shared" ref="AE18:AO18" si="43">AE16/AE17</f>
-        <v>-0.7314671741198866</v>
-      </c>
-      <c r="AF18" s="7">
-        <f t="shared" si="43"/>
-        <v>-0.42236986869648019</v>
-      </c>
-      <c r="AG18" s="7">
-        <f t="shared" si="43"/>
-        <v>-0.17925537583254059</v>
-      </c>
-      <c r="AH18" s="7">
-        <f t="shared" si="43"/>
-        <v>-1.7211336341103327E-2</v>
+        <v>0.13841570597146852</v>
       </c>
       <c r="AI18" s="7">
-        <f t="shared" si="43"/>
-        <v>6.2457700504886492E-2</v>
+        <f t="shared" si="41"/>
+        <v>0.25896887189655543</v>
       </c>
       <c r="AJ18" s="7">
-        <f t="shared" si="43"/>
-        <v>0.12119794388874372</v>
+        <f t="shared" si="41"/>
+        <v>0.31752253949239118</v>
       </c>
       <c r="AK18" s="7">
-        <f t="shared" si="43"/>
-        <v>0.16862706342595118</v>
+        <f t="shared" si="41"/>
+        <v>0.38046702548603423</v>
       </c>
       <c r="AL18" s="7">
-        <f t="shared" si="43"/>
-        <v>0.21809989956875206</v>
+        <f t="shared" si="41"/>
+        <v>0.44583403415757539</v>
       </c>
       <c r="AM18" s="7">
-        <f t="shared" si="43"/>
-        <v>0.26968763046965533</v>
+        <f t="shared" si="41"/>
+        <v>0.51370158306833291</v>
       </c>
       <c r="AN18" s="7">
-        <f t="shared" si="43"/>
-        <v>0.32346374145676993</v>
+        <f t="shared" si="41"/>
+        <v>0.58415008372527333</v>
       </c>
       <c r="AO18" s="7">
-        <f t="shared" si="43"/>
-        <v>0.37950409743067487</v>
+        <f t="shared" si="41"/>
+        <v>0.65726241393357121</v>
       </c>
     </row>
     <row r="20" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3767,68 +3774,68 @@
       <c r="E20" s="10"/>
       <c r="F20" s="10"/>
       <c r="G20" s="10">
-        <f t="shared" ref="G20:P20" si="44">G3/C3-1</f>
+        <f t="shared" ref="G20:P20" si="42">G3/C3-1</f>
         <v>1.9153225806451513E-2</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-1.9143576826196496E-2</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-4.1884816753926746E-2</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-1.1084337349397622E-2</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-7.2205736894164207E-2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-6.0606060606060552E-2</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-4.1287188828172283E-2</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-8.3820662768031129E-2</v>
       </c>
       <c r="O20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-7.0362473347547971E-2</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>-0.10825587752870425</v>
       </c>
       <c r="Q20" s="10">
-        <f t="shared" ref="Q20" si="45">Q3/M3-1</f>
+        <f t="shared" ref="Q20" si="43">Q3/M3-1</f>
         <v>-0.13489550348321733</v>
       </c>
       <c r="R20" s="10">
-        <f t="shared" ref="R20" si="46">R3/N3-1</f>
+        <f t="shared" ref="R20" si="44">R3/N3-1</f>
         <v>-0.23670212765957444</v>
       </c>
       <c r="S20" s="10">
-        <f t="shared" ref="S20" si="47">S3/O3-1</f>
+        <f t="shared" ref="S20" si="45">S3/O3-1</f>
         <v>-0.30389908256880738</v>
       </c>
       <c r="T20" s="10">
-        <f t="shared" ref="T20" si="48">T3/P3-1</f>
-        <v>-0.20000000000000007</v>
+        <f t="shared" ref="T20" si="46">T3/P3-1</f>
+        <v>-0.35561005518087063</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" ref="U20" si="49">U3/Q3-1</f>
-        <v>-0.25</v>
+        <f t="shared" ref="U20" si="47">U3/Q3-1</f>
+        <v>-0.44363103953147875</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" ref="V20" si="50">V3/R3-1</f>
-        <v>-5.0000000000000044E-2</v>
+        <f t="shared" ref="V20" si="48">V3/R3-1</f>
+        <v>-0.35</v>
       </c>
       <c r="X20" s="10"/>
       <c r="Y20" s="10">
@@ -3836,67 +3843,67 @@
         <v>0.27966365618187461</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" ref="Z20:AO20" si="51">Z3/Y3-1</f>
+        <f t="shared" ref="Z20:AO20" si="49">Z3/Y3-1</f>
         <v>0.56802141640301773</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>0.20487350613068456</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-1.223753703465158E-2</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-6.5727699530516381E-2</v>
       </c>
       <c r="AD20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>-0.13791178112786151</v>
       </c>
       <c r="AE20" s="10">
-        <f t="shared" si="51"/>
-        <v>-0.20554566062176172</v>
+        <f t="shared" si="49"/>
+        <v>-0.35917260362694303</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="51"/>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" si="49"/>
+        <v>0.14999999999999991</v>
       </c>
       <c r="AG20" s="10">
-        <f t="shared" si="51"/>
-        <v>0.10000000000000031</v>
+        <f t="shared" si="49"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="AH20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AI20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AK20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AL20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AM20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AO20" s="10">
-        <f t="shared" si="51"/>
+        <f t="shared" si="49"/>
         <v>3.0000000000000027E-2</v>
       </c>
     </row>
@@ -3905,155 +3912,155 @@
         <v>43</v>
       </c>
       <c r="C21" s="9">
-        <f t="shared" ref="C21:J21" si="52">C5/C3</f>
+        <f t="shared" ref="C21:J21" si="50">C5/C3</f>
         <v>0.6401209677419355</v>
       </c>
       <c r="D21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.69420654911838797</v>
+      </c>
+      <c r="E21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.60965677719604427</v>
+      </c>
+      <c r="F21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.73156626506024103</v>
+      </c>
+      <c r="G21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.72749752720079131</v>
+      </c>
+      <c r="H21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.76527991782229077</v>
+      </c>
+      <c r="I21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.72556162720097139</v>
+      </c>
+      <c r="J21" s="9">
+        <f t="shared" si="50"/>
+        <v>0.74951267056530213</v>
+      </c>
+      <c r="K21" s="9">
+        <f t="shared" ref="K21:P21" si="51">K5/K3</f>
+        <v>0.73773987206823022</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="51"/>
+        <v>0.74084199015855656</v>
+      </c>
+      <c r="M21" s="9">
+        <f t="shared" si="51"/>
+        <v>0.4705509816339456</v>
+      </c>
+      <c r="N21" s="9">
+        <f t="shared" si="51"/>
+        <v>0.75638297872340421</v>
+      </c>
+      <c r="O21" s="9">
+        <f t="shared" si="51"/>
+        <v>0.73337155963302758</v>
+      </c>
+      <c r="P21" s="9">
+        <f t="shared" si="51"/>
+        <v>0.72164316370324955</v>
+      </c>
+      <c r="Q21" s="9">
+        <f t="shared" ref="Q21:R21" si="52">Q5/Q3</f>
+        <v>0.68228404099560758</v>
+      </c>
+      <c r="R21" s="9">
         <f t="shared" si="52"/>
-        <v>0.69420654911838797</v>
-      </c>
-      <c r="E21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.60965677719604427</v>
-      </c>
-      <c r="F21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.73156626506024103</v>
-      </c>
-      <c r="G21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.72749752720079131</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.76527991782229077</v>
-      </c>
-      <c r="I21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.72556162720097139</v>
-      </c>
-      <c r="J21" s="9">
-        <f t="shared" si="52"/>
-        <v>0.74951267056530213</v>
-      </c>
-      <c r="K21" s="9">
-        <f t="shared" ref="K21:P21" si="53">K5/K3</f>
-        <v>0.73773987206823022</v>
-      </c>
-      <c r="L21" s="9">
+        <v>0.68222996515679446</v>
+      </c>
+      <c r="S21" s="9">
+        <f t="shared" ref="S21:V21" si="53">S5/S3</f>
+        <v>0.55518945634266892</v>
+      </c>
+      <c r="T21" s="9">
         <f t="shared" si="53"/>
-        <v>0.74084199015855656</v>
-      </c>
-      <c r="M21" s="9">
+        <v>0.66222645099904853</v>
+      </c>
+      <c r="U21" s="9">
         <f t="shared" si="53"/>
-        <v>0.4705509816339456</v>
-      </c>
-      <c r="N21" s="9">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="V21" s="9">
         <f t="shared" si="53"/>
-        <v>0.75638297872340421</v>
-      </c>
-      <c r="O21" s="9">
-        <f t="shared" si="53"/>
-        <v>0.73337155963302758</v>
-      </c>
-      <c r="P21" s="9">
-        <f t="shared" si="53"/>
-        <v>0.72164316370324955</v>
-      </c>
-      <c r="Q21" s="9">
-        <f t="shared" ref="Q21:R21" si="54">Q5/Q3</f>
-        <v>0.68228404099560758</v>
-      </c>
-      <c r="R21" s="9">
+        <v>0.67</v>
+      </c>
+      <c r="X21" s="9">
+        <f t="shared" ref="X21:AO21" si="54">X5/X3</f>
+        <v>0.7508564310183744</v>
+      </c>
+      <c r="Y21" s="9">
         <f t="shared" si="54"/>
-        <v>0.68222996515679446</v>
-      </c>
-      <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="55">S5/S3</f>
-        <v>0.55518945634266892</v>
-      </c>
-      <c r="T21" s="9">
-        <f t="shared" si="55"/>
+        <v>0.77561450474568028</v>
+      </c>
+      <c r="Z21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.68120440788452585</v>
+      </c>
+      <c r="AA21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.67164755893340189</v>
+      </c>
+      <c r="AB21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.74256651017214403</v>
+      </c>
+      <c r="AC21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.68453378001116694</v>
+      </c>
+      <c r="AD21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.70709196891191717</v>
+      </c>
+      <c r="AE21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.61159560356263021</v>
+      </c>
+      <c r="AF21" s="9">
+        <f t="shared" si="54"/>
+        <v>0.65</v>
+      </c>
+      <c r="AG21" s="9">
+        <f t="shared" si="54"/>
         <v>0.68</v>
       </c>
-      <c r="U21" s="9">
-        <f t="shared" si="55"/>
-        <v>0.68</v>
-      </c>
-      <c r="V21" s="9">
-        <f t="shared" si="55"/>
-        <v>0.68</v>
-      </c>
-      <c r="X21" s="9">
-        <f t="shared" ref="X21:AO21" si="56">X5/X3</f>
-        <v>0.7508564310183744</v>
-      </c>
-      <c r="Y21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.77561450474568028</v>
-      </c>
-      <c r="Z21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.68120440788452585</v>
-      </c>
-      <c r="AA21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.67164755893340189</v>
-      </c>
-      <c r="AB21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.74256651017214403</v>
-      </c>
-      <c r="AC21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.68453378001116694</v>
-      </c>
-      <c r="AD21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.70709196891191717</v>
-      </c>
-      <c r="AE21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.64911883095046408</v>
-      </c>
-      <c r="AF21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AH21" s="9">
+        <f t="shared" si="54"/>
         <v>0.69</v>
       </c>
-      <c r="AG21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AI21" s="9">
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
-      <c r="AH21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AJ21" s="9">
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
-      <c r="AI21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AK21" s="9">
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
-      <c r="AJ21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AL21" s="9">
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
-      <c r="AK21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AM21" s="9">
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
-      <c r="AL21" s="9">
-        <f t="shared" si="56"/>
+      <c r="AN21" s="9">
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
-      <c r="AM21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
-      <c r="AN21" s="9">
-        <f t="shared" si="56"/>
-        <v>0.7</v>
-      </c>
       <c r="AO21" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="54"/>
         <v>0.7</v>
       </c>
       <c r="AR21" t="s">
@@ -4072,68 +4079,68 @@
       <c r="E22" s="9"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9">
-        <f t="shared" ref="G22" si="57">G6/C6-1</f>
+        <f t="shared" ref="G22" si="55">G6/C6-1</f>
         <v>0.1366594360086768</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22" si="58">H6/D6-1</f>
+        <f t="shared" ref="H22" si="56">H6/D6-1</f>
         <v>0.26201923076923062</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" ref="I22" si="59">I6/E6-1</f>
+        <f t="shared" ref="I22" si="57">I6/E6-1</f>
         <v>4.8498845265589008E-2</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" ref="J22" si="60">J6/F6-1</f>
+        <f t="shared" ref="J22" si="58">J6/F6-1</f>
         <v>-3.1380753138075312E-2</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" ref="K22:P22" si="61">K6/G6-1</f>
+        <f t="shared" ref="K22:P22" si="59">K6/G6-1</f>
         <v>-0.10496183206106868</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>7.6190476190476364E-3</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>1.7621145374449476E-2</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>-1.2958963282937219E-2</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>-5.3304904051172719E-2</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="61"/>
+        <f t="shared" si="59"/>
         <v>-0.17391304347826075</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" ref="Q22" si="62">Q6/M6-1</f>
+        <f t="shared" ref="Q22" si="60">Q6/M6-1</f>
         <v>-0.10606060606060619</v>
       </c>
       <c r="R22" s="9">
-        <f t="shared" ref="R22" si="63">R6/N6-1</f>
+        <f t="shared" ref="R22" si="61">R6/N6-1</f>
         <v>-0.10284463894967177</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22" si="64">S6/O6-1</f>
+        <f t="shared" ref="S22" si="62">S6/O6-1</f>
         <v>-0.33783783783783783</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" ref="T22" si="65">T6/P6-1</f>
-        <v>-9.9999999999999978E-2</v>
+        <f t="shared" ref="T22" si="63">T6/P6-1</f>
+        <v>-0.34324942791762014</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" ref="U22" si="66">U6/Q6-1</f>
-        <v>-9.9999999999999867E-2</v>
+        <f t="shared" ref="U22" si="64">U6/Q6-1</f>
+        <v>-0.19999999999999996</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" ref="V22" si="67">V6/R6-1</f>
-        <v>-0.10000000000000009</v>
+        <f t="shared" ref="V22" si="65">V6/R6-1</f>
+        <v>-0.14999999999999991</v>
       </c>
       <c r="X22" s="9"/>
       <c r="Y22" s="9">
@@ -4141,67 +4148,67 @@
         <v>0.22309711286089251</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AO22" si="68">Z6/Y6-1</f>
+        <f t="shared" ref="Z22:AO22" si="66">Z6/Y6-1</f>
         <v>0.22246065808297555</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>4.6225863077823393E-2</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>9.9552572706935072E-2</v>
       </c>
       <c r="AC22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>-2.4923702950152782E-2</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>-0.11111111111111116</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="68"/>
-        <v>-0.16197183098591528</v>
+        <f t="shared" si="66"/>
+        <v>-0.26062206572769953</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="68"/>
+      <c r="AH22" s="9">
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="68"/>
+      <c r="AI22" s="9">
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI22" s="9">
-        <f t="shared" si="68"/>
+      <c r="AJ22" s="9">
+        <f t="shared" si="66"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AJ22" s="9">
-        <f t="shared" si="68"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AK22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO22" s="9">
-        <f t="shared" si="68"/>
+        <f t="shared" si="66"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR22" t="s">
@@ -4216,155 +4223,155 @@
         <v>45</v>
       </c>
       <c r="C23" s="9">
-        <f t="shared" ref="C23:J23" si="69">C7/C3</f>
+        <f t="shared" ref="C23:J23" si="67">C7/C3</f>
         <v>0.13205645161290322</v>
       </c>
       <c r="D23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.1093198992443325</v>
+      </c>
+      <c r="E23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.15823152995927864</v>
+      </c>
+      <c r="F23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.14602409638554217</v>
+      </c>
+      <c r="G23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.21018793273986153</v>
+      </c>
+      <c r="H23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.18130457113507961</v>
+      </c>
+      <c r="I23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.19307832422586524</v>
+      </c>
+      <c r="J23" s="9">
+        <f t="shared" si="67"/>
+        <v>0.18567251461988304</v>
+      </c>
+      <c r="K23" s="9">
+        <f t="shared" ref="K23:P23" si="68">K7/K3</f>
+        <v>0.19722814498933902</v>
+      </c>
+      <c r="L23" s="9">
+        <f t="shared" si="68"/>
+        <v>0.16949152542372881</v>
+      </c>
+      <c r="M23" s="9">
+        <f t="shared" si="68"/>
+        <v>0.1830272324255858</v>
+      </c>
+      <c r="N23" s="9">
+        <f t="shared" si="68"/>
+        <v>0.15797872340425531</v>
+      </c>
+      <c r="O23" s="9">
+        <f t="shared" si="68"/>
+        <v>0.17431192660550457</v>
+      </c>
+      <c r="P23" s="9">
+        <f t="shared" si="68"/>
+        <v>0.14408338442673208</v>
+      </c>
+      <c r="Q23" s="9">
+        <f t="shared" ref="Q23:R23" si="69">Q7/Q3</f>
+        <v>0.19399707174231334</v>
+      </c>
+      <c r="R23" s="9">
         <f t="shared" si="69"/>
-        <v>0.1093198992443325</v>
-      </c>
-      <c r="E23" s="9">
-        <f t="shared" si="69"/>
-        <v>0.15823152995927864</v>
-      </c>
-      <c r="F23" s="9">
-        <f t="shared" si="69"/>
-        <v>0.14602409638554217</v>
-      </c>
-      <c r="G23" s="9">
-        <f t="shared" si="69"/>
-        <v>0.21018793273986153</v>
-      </c>
-      <c r="H23" s="9">
-        <f t="shared" si="69"/>
-        <v>0.18130457113507961</v>
-      </c>
-      <c r="I23" s="9">
-        <f t="shared" si="69"/>
-        <v>0.19307832422586524</v>
-      </c>
-      <c r="J23" s="9">
-        <f t="shared" si="69"/>
-        <v>0.18567251461988304</v>
-      </c>
-      <c r="K23" s="9">
-        <f t="shared" ref="K23:P23" si="70">K7/K3</f>
-        <v>0.19722814498933902</v>
-      </c>
-      <c r="L23" s="9">
+        <v>0.19442508710801393</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" ref="S23:V23" si="70">S7/S3</f>
+        <v>0.21087314662273476</v>
+      </c>
+      <c r="T23" s="9">
         <f t="shared" si="70"/>
-        <v>0.16949152542372881</v>
-      </c>
-      <c r="M23" s="9">
+        <v>0.16555661274976213</v>
+      </c>
+      <c r="U23" s="9">
         <f t="shared" si="70"/>
-        <v>0.1830272324255858</v>
-      </c>
-      <c r="N23" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="V23" s="9">
         <f t="shared" si="70"/>
-        <v>0.15797872340425531</v>
-      </c>
-      <c r="O23" s="9">
-        <f t="shared" si="70"/>
-        <v>0.17431192660550457</v>
-      </c>
-      <c r="P23" s="9">
-        <f t="shared" si="70"/>
-        <v>0.14408338442673208</v>
-      </c>
-      <c r="Q23" s="9">
-        <f t="shared" ref="Q23:R23" si="71">Q7/Q3</f>
-        <v>0.19399707174231334</v>
-      </c>
-      <c r="R23" s="9">
+        <v>0.19</v>
+      </c>
+      <c r="X23" s="9">
+        <f t="shared" ref="X23:AO23" si="71">X7/X3</f>
+        <v>0.17035191529118654</v>
+      </c>
+      <c r="Y23" s="9">
         <f t="shared" si="71"/>
-        <v>0.19442508710801393</v>
-      </c>
-      <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="72">S7/S3</f>
-        <v>0.21087314662273476</v>
-      </c>
-      <c r="T23" s="9">
-        <f t="shared" si="72"/>
-        <v>0.17</v>
-      </c>
-      <c r="U23" s="9">
-        <f t="shared" si="72"/>
-        <v>0.2</v>
-      </c>
-      <c r="V23" s="9">
-        <f t="shared" si="72"/>
-        <v>0.2</v>
-      </c>
-      <c r="X23" s="9">
-        <f t="shared" ref="X23:AO23" si="73">X7/X3</f>
-        <v>0.17035191529118654</v>
-      </c>
-      <c r="Y23" s="9">
-        <f t="shared" si="73"/>
         <v>0.15478218544658068</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.12711469812199289</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.13577225299497617</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.1926186750130412</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.17671691792294808</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.17535621761658032</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="73"/>
-        <v>0.19471237427520355</v>
+        <f t="shared" si="71"/>
+        <v>0.18991156591497696</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="73"/>
-        <v>0.17</v>
+        <f t="shared" si="71"/>
+        <v>0.15</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="73"/>
-        <v>0.16</v>
+        <f t="shared" si="71"/>
+        <v>0.15</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="73"/>
+        <f t="shared" si="71"/>
         <v>0.15</v>
       </c>
       <c r="AR23" t="s">
@@ -4372,7 +4379,7 @@
       </c>
       <c r="AS23" s="2">
         <f>NPV(AS22,AE16:EO16)</f>
-        <v>28.817784958557201</v>
+        <v>157.76171319069601</v>
       </c>
     </row>
     <row r="24" spans="2:45" x14ac:dyDescent="0.3">
@@ -4384,67 +4391,67 @@
       <c r="E24" s="9"/>
       <c r="F24" s="9"/>
       <c r="G24" s="9">
-        <f t="shared" ref="G24" si="74">G8/C8-1</f>
+        <f t="shared" ref="G24" si="72">G8/C8-1</f>
         <v>0.23746701846965701</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24" si="75">H8/D8-1</f>
+        <f t="shared" ref="H24" si="73">H8/D8-1</f>
         <v>0.35768261964735504</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" ref="I24" si="76">I8/E8-1</f>
+        <f t="shared" ref="I24" si="74">I8/E8-1</f>
         <v>0.57941176470588251</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" ref="J24" si="77">J8/F8-1</f>
+        <f t="shared" ref="J24" si="75">J8/F8-1</f>
         <v>0.29894736842105263</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" ref="K24:P24" si="78">K8/G8-1</f>
+        <f t="shared" ref="K24:P24" si="76">K8/G8-1</f>
         <v>0.25799573560767586</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.30426716141001853</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>6.3314711359404141E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-0.1345218800648299</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-5.9322033898305038E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>-0.2318634423897582</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" ref="Q24" si="79">Q8/M8-1</f>
+        <f t="shared" ref="Q24" si="77">Q8/M8-1</f>
         <v>-9.1068301225919468E-2</v>
       </c>
       <c r="R24" s="9">
-        <f t="shared" ref="R24" si="80">R8/N8-1</f>
+        <f t="shared" ref="R24" si="78">R8/N8-1</f>
         <v>5.4307116104868935E-2</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24" si="81">S8/O8-1</f>
+        <f t="shared" ref="S24" si="79">S8/O8-1</f>
         <v>-0.29009009009009012</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" ref="T24" si="82">T8/P8-1</f>
+        <f t="shared" ref="T24" si="80">T8/P8-1</f>
+        <v>0.11111111111111116</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" ref="U24" si="81">U8/Q8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="U24" s="9">
-        <f t="shared" ref="U24" si="83">U8/Q8-1</f>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="V24" s="9">
-        <f t="shared" ref="V24" si="84">V8/R8-1</f>
+        <f t="shared" ref="V24" si="82">V8/R8-1</f>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="X24" s="9"/>
@@ -4453,75 +4460,75 @@
         <v>0.25482625482625476</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AO24" si="85">Z8/Y8-1</f>
+        <f t="shared" ref="Z24:AO24" si="83">Z8/Y8-1</f>
         <v>0.32615384615384624</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.23047177107501926</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.35889377749842866</v>
       </c>
       <c r="AC24" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>0.10915818686401502</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
         <v>-9.2160133444537218E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="85"/>
-        <v>-5.9053743683968762E-2</v>
+        <f t="shared" si="83"/>
+        <v>-3.6453835553513891E-2</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="83"/>
+        <v>-9.9999999999999867E-2</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="83"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="83"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="85"/>
+      <c r="AI24" s="9">
+        <f t="shared" si="83"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="85"/>
+      <c r="AJ24" s="9">
+        <f t="shared" si="83"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AI24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="AK24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="83"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="83"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="83"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="83"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AO24" s="9">
-        <f t="shared" si="85"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="83"/>
+        <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR24" t="s">
         <v>52</v>
       </c>
       <c r="AS24" s="2">
         <f>Main!D8</f>
-        <v>63.900000000000006</v>
+        <v>51.599999999999994</v>
       </c>
     </row>
     <row r="25" spans="2:45" x14ac:dyDescent="0.3">
@@ -4529,163 +4536,163 @@
         <v>47</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:J25" si="86">C11/C3</f>
+        <f t="shared" ref="C25:J25" si="84">C11/C3</f>
         <v>8.4677419354838759E-2</v>
       </c>
       <c r="D25" s="9">
+        <f t="shared" si="84"/>
+        <v>0.17531486146095723</v>
+      </c>
+      <c r="E25" s="9">
+        <f t="shared" si="84"/>
+        <v>1.7452006980803454E-3</v>
+      </c>
+      <c r="F25" s="9">
+        <f t="shared" si="84"/>
+        <v>0.12626506024096393</v>
+      </c>
+      <c r="G25" s="9">
+        <f t="shared" si="84"/>
+        <v>2.6211671612265001E-2</v>
+      </c>
+      <c r="H25" s="9">
+        <f t="shared" si="84"/>
+        <v>3.7493579866461284E-2</v>
+      </c>
+      <c r="I25" s="9">
+        <f t="shared" si="84"/>
+        <v>-6.9216757741348028E-2</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="84"/>
+        <v>3.7524366471734703E-2</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" ref="K25:P25" si="85">K11/K3</f>
+        <v>-2.3987206823027872E-2</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="85"/>
+        <v>-0.1022416621104428</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="85"/>
+        <v>-0.36668777707409739</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="85"/>
+        <v>7.1276595744680732E-2</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" si="85"/>
+        <v>-1.3761467889908289E-2</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="85"/>
+        <v>-2.1459227467811245E-2</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" ref="Q25:R25" si="86">Q11/Q3</f>
+        <v>-0.19399707174231334</v>
+      </c>
+      <c r="R25" s="9">
         <f t="shared" si="86"/>
-        <v>0.17531486146095723</v>
-      </c>
-      <c r="E25" s="9">
-        <f t="shared" si="86"/>
-        <v>1.7452006980803454E-3</v>
-      </c>
-      <c r="F25" s="9">
-        <f t="shared" si="86"/>
-        <v>0.12626506024096393</v>
-      </c>
-      <c r="G25" s="9">
-        <f t="shared" si="86"/>
-        <v>2.6211671612265001E-2</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="86"/>
-        <v>3.7493579866461284E-2</v>
-      </c>
-      <c r="I25" s="9">
-        <f t="shared" si="86"/>
-        <v>-6.9216757741348028E-2</v>
-      </c>
-      <c r="J25" s="9">
-        <f t="shared" si="86"/>
-        <v>3.7524366471734703E-2</v>
-      </c>
-      <c r="K25" s="9">
-        <f t="shared" ref="K25:P25" si="87">K11/K3</f>
-        <v>-2.3987206823027872E-2</v>
-      </c>
-      <c r="L25" s="9">
+        <v>-0.19024390243902436</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:V25" si="87">S11/S3</f>
+        <v>-0.23887973640856672</v>
+      </c>
+      <c r="T25" s="9">
         <f t="shared" si="87"/>
-        <v>-0.1022416621104428</v>
-      </c>
-      <c r="M25" s="9">
+        <v>-0.34728829686013324</v>
+      </c>
+      <c r="U25" s="9">
         <f t="shared" si="87"/>
-        <v>-0.36668777707409739</v>
-      </c>
-      <c r="N25" s="9">
+        <v>-0.76128947368421063</v>
+      </c>
+      <c r="V25" s="9">
         <f t="shared" si="87"/>
-        <v>7.1276595744680732E-2</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" si="87"/>
-        <v>-1.3761467889908289E-2</v>
-      </c>
-      <c r="P25" s="9">
-        <f t="shared" si="87"/>
-        <v>-2.1459227467811245E-2</v>
-      </c>
-      <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="88">Q11/Q3</f>
-        <v>-0.19399707174231334</v>
-      </c>
-      <c r="R25" s="9">
+        <v>-0.50928973465558813</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" ref="X25:AO25" si="88">X11/X3</f>
+        <v>-1.7440049828713691E-2</v>
+      </c>
+      <c r="Y25" s="9">
         <f t="shared" si="88"/>
-        <v>-0.19024390243902436</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="89">S11/S3</f>
-        <v>-0.23887973640856672</v>
-      </c>
-      <c r="T25" s="9">
-        <f t="shared" si="89"/>
-        <v>-0.2135591661557327</v>
-      </c>
-      <c r="U25" s="9">
-        <f t="shared" si="89"/>
-        <v>-0.39953147877013184</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="89"/>
-        <v>-0.21192004401247011</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" ref="X25:AO25" si="90">X11/X3</f>
-        <v>-1.7440049828713691E-2</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="90"/>
         <v>4.3319542467753741E-2</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>8.8157690516839915E-2</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>0.10060543604276687</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>1.1606677099634817E-2</v>
       </c>
       <c r="AC25" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>-9.4500279173646076E-2</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" si="90"/>
+        <f t="shared" si="88"/>
         <v>-9.6664507772020611E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.2582001610092633</v>
+        <f t="shared" si="88"/>
+        <v>-0.4317149895774115</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.21745004335104759</v>
+        <f t="shared" si="88"/>
+        <v>-0.17776344156896356</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.14381731292551669</v>
+        <f t="shared" si="88"/>
+        <v>-0.10224236432096628</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="90"/>
-        <v>-0.10186323288226813</v>
+        <f t="shared" si="88"/>
+        <v>-6.269832860503334E-2</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="90"/>
-        <v>-8.3238569085631861E-2</v>
+        <f t="shared" si="88"/>
+        <v>-3.5478376359175161E-2</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="90"/>
-        <v>-7.1060904295523503E-2</v>
+        <f t="shared" si="88"/>
+        <v>-2.4219176813806503E-2</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="90"/>
-        <v>-6.2554389648011799E-2</v>
+        <f t="shared" si="88"/>
+        <v>-1.3069289885383133E-2</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="90"/>
-        <v>-5.4178555669506689E-2</v>
+        <f t="shared" si="88"/>
+        <v>-2.1359056157640921E-3</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="90"/>
-        <v>-4.5931199768111698E-2</v>
+        <f t="shared" si="88"/>
+        <v>8.5851799301731539E-3</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="90"/>
-        <v>-3.7810158869279832E-2</v>
+        <f t="shared" si="88"/>
+        <v>1.9098089057742684E-2</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="90"/>
-        <v>-2.9813308680053319E-2</v>
+        <f t="shared" si="88"/>
+        <v>2.9406864027495341E-2</v>
       </c>
       <c r="AR25" t="s">
         <v>53</v>
       </c>
       <c r="AS25" s="2">
         <f>AS23+AS24</f>
-        <v>92.717784958557203</v>
+        <v>209.36171319069601</v>
       </c>
     </row>
     <row r="26" spans="2:45" x14ac:dyDescent="0.3">
@@ -4693,155 +4700,155 @@
         <v>38</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:J26" si="91">C15/C14</f>
+        <f t="shared" ref="C26:J26" si="89">C15/C14</f>
         <v>-4.4943820224719107E-2</v>
       </c>
       <c r="D26" s="9">
+        <f t="shared" si="89"/>
+        <v>6.2857142857142848E-2</v>
+      </c>
+      <c r="E26" s="9">
+        <f t="shared" si="89"/>
+        <v>9.4594594594594447E-2</v>
+      </c>
+      <c r="F26" s="9">
+        <f t="shared" si="89"/>
+        <v>5.4474708171206185E-2</v>
+      </c>
+      <c r="G26" s="9">
+        <f t="shared" si="89"/>
+        <v>0.42424242424242503</v>
+      </c>
+      <c r="H26" s="9">
+        <f t="shared" si="89"/>
+        <v>1.3333333333333313E-2</v>
+      </c>
+      <c r="I26" s="9">
+        <f t="shared" si="89"/>
+        <v>-1.9822274881516595</v>
+      </c>
+      <c r="J26" s="9">
+        <f t="shared" si="89"/>
+        <v>0.13636363636363882</v>
+      </c>
+      <c r="K26" s="9">
+        <f t="shared" ref="K26:P26" si="90">K15/K14</f>
+        <v>0.66666666666666974</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="90"/>
+        <v>0.44469525959367939</v>
+      </c>
+      <c r="M26" s="9">
+        <f t="shared" si="90"/>
+        <v>-1.1049723756906091E-2</v>
+      </c>
+      <c r="N26" s="9">
+        <f t="shared" si="90"/>
+        <v>0.45505617977528151</v>
+      </c>
+      <c r="O26" s="9">
+        <f t="shared" si="90"/>
+        <v>1.1818181818181825</v>
+      </c>
+      <c r="P26" s="9">
+        <f t="shared" si="90"/>
+        <v>2.8965517241379479</v>
+      </c>
+      <c r="Q26" s="9">
+        <f t="shared" ref="Q26:R26" si="91">Q15/Q14</f>
+        <v>0.13775510204081631</v>
+      </c>
+      <c r="R26" s="9">
         <f t="shared" si="91"/>
-        <v>6.2857142857142848E-2</v>
-      </c>
-      <c r="E26" s="9">
-        <f t="shared" si="91"/>
-        <v>9.4594594594594447E-2</v>
-      </c>
-      <c r="F26" s="9">
-        <f t="shared" si="91"/>
-        <v>5.4474708171206185E-2</v>
-      </c>
-      <c r="G26" s="9">
-        <f t="shared" si="91"/>
-        <v>0.42424242424242503</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="91"/>
-        <v>1.3333333333333313E-2</v>
-      </c>
-      <c r="I26" s="9">
-        <f t="shared" si="91"/>
-        <v>-1.9822274881516595</v>
-      </c>
-      <c r="J26" s="9">
-        <f t="shared" si="91"/>
-        <v>0.13636363636363882</v>
-      </c>
-      <c r="K26" s="9">
-        <f t="shared" ref="K26:P26" si="92">K15/K14</f>
-        <v>0.66666666666666974</v>
-      </c>
-      <c r="L26" s="9">
+        <v>-1.9047619047619067</v>
+      </c>
+      <c r="S26" s="9">
+        <f t="shared" ref="S26:V26" si="92">S15/S14</f>
+        <v>-6.0606060606060608E-2</v>
+      </c>
+      <c r="T26" s="9">
         <f t="shared" si="92"/>
-        <v>0.44469525959367939</v>
-      </c>
-      <c r="M26" s="9">
+        <v>-3.4883720930232558E-2</v>
+      </c>
+      <c r="U26" s="9">
         <f t="shared" si="92"/>
-        <v>-1.1049723756906091E-2</v>
-      </c>
-      <c r="N26" s="9">
+        <v>0</v>
+      </c>
+      <c r="V26" s="9">
         <f t="shared" si="92"/>
-        <v>0.45505617977528151</v>
-      </c>
-      <c r="O26" s="9">
-        <f t="shared" si="92"/>
-        <v>1.1818181818181825</v>
-      </c>
-      <c r="P26" s="9">
-        <f t="shared" si="92"/>
-        <v>2.8965517241379479</v>
-      </c>
-      <c r="Q26" s="9">
-        <f t="shared" ref="Q26:R26" si="93">Q15/Q14</f>
-        <v>0.13775510204081631</v>
-      </c>
-      <c r="R26" s="9">
+        <v>0</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" ref="X26:AO26" si="93">X15/X14</f>
+        <v>-0.10937500000000029</v>
+      </c>
+      <c r="Y26" s="9">
         <f t="shared" si="93"/>
-        <v>-1.9047619047619067</v>
-      </c>
-      <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="94">S15/S14</f>
-        <v>-6.0606060606060608E-2</v>
-      </c>
-      <c r="T26" s="9">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="U26" s="9">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="94"/>
-        <v>0</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" ref="X26:AO26" si="95">X15/X14</f>
-        <v>-0.10937500000000029</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="95"/>
         <v>-0.37142857142857222</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>-6.749999999999635</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>1.2241379310345013</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>-1.5644230769230771</v>
       </c>
       <c r="AC26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.64015904572564675</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>-1.6936936936937039</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="95"/>
-        <v>-1.3179189532560493E-2</v>
+        <f t="shared" si="93"/>
+        <v>-1.7714221298935535E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AO26" s="9">
-        <f t="shared" si="95"/>
+        <f t="shared" si="93"/>
         <v>0.15</v>
       </c>
       <c r="AR26" t="s">
@@ -4849,7 +4856,7 @@
       </c>
       <c r="AS26" s="3">
         <f>AS25/AO17</f>
-        <v>0.88218634594250434</v>
+        <v>1.9584818820457999</v>
       </c>
     </row>
     <row r="27" spans="2:45" x14ac:dyDescent="0.3">
@@ -4857,163 +4864,163 @@
         <v>48</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:J27" si="96">C16/C3</f>
+        <f t="shared" ref="C27:J27" si="94">C16/C3</f>
         <v>-0.32812499999999994</v>
       </c>
       <c r="D27" s="9">
+        <f t="shared" si="94"/>
+        <v>0.16523929471032747</v>
+      </c>
+      <c r="E27" s="9">
+        <f t="shared" si="94"/>
+        <v>3.8976148923792968E-2</v>
+      </c>
+      <c r="F27" s="9">
+        <f t="shared" si="94"/>
+        <v>0.11710843373493984</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="94"/>
+        <v>2.8189910979228402E-2</v>
+      </c>
+      <c r="H27" s="9">
+        <f t="shared" si="94"/>
+        <v>3.8007190549563495E-2</v>
+      </c>
+      <c r="I27" s="9">
+        <f t="shared" si="94"/>
+        <v>1.5282331511839709</v>
+      </c>
+      <c r="J27" s="9">
+        <f t="shared" si="94"/>
+        <v>9.2592592592590662E-3</v>
+      </c>
+      <c r="K27" s="9">
+        <f t="shared" ref="K27:P27" si="95">K16/K3</f>
+        <v>1.1194029850746115E-2</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="95"/>
+        <v>0.13449972662657192</v>
+      </c>
+      <c r="M27" s="9">
+        <f t="shared" si="95"/>
+        <v>-0.11589613679544002</v>
+      </c>
+      <c r="N27" s="9">
+        <f t="shared" si="95"/>
+        <v>5.1595744680850937E-2</v>
+      </c>
+      <c r="O27" s="9">
+        <f t="shared" si="95"/>
+        <v>-8.027522935779843E-3</v>
+      </c>
+      <c r="P27" s="9">
+        <f t="shared" si="95"/>
+        <v>-3.3721643163703373E-2</v>
+      </c>
+      <c r="Q27" s="9">
+        <f t="shared" ref="Q27:R27" si="96">Q16/Q3</f>
+        <v>-0.12371888726207908</v>
+      </c>
+      <c r="R27" s="9">
         <f t="shared" si="96"/>
-        <v>0.16523929471032747</v>
-      </c>
-      <c r="E27" s="9">
-        <f t="shared" si="96"/>
-        <v>3.8976148923792968E-2</v>
-      </c>
-      <c r="F27" s="9">
-        <f t="shared" si="96"/>
-        <v>0.11710843373493984</v>
-      </c>
-      <c r="G27" s="9">
-        <f t="shared" si="96"/>
-        <v>2.8189910979228402E-2</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" si="96"/>
-        <v>3.8007190549563495E-2</v>
-      </c>
-      <c r="I27" s="9">
-        <f t="shared" si="96"/>
-        <v>1.5282331511839709</v>
-      </c>
-      <c r="J27" s="9">
-        <f t="shared" si="96"/>
-        <v>9.2592592592590662E-3</v>
-      </c>
-      <c r="K27" s="9">
-        <f t="shared" ref="K27:P27" si="97">K16/K3</f>
-        <v>1.1194029850746115E-2</v>
-      </c>
-      <c r="L27" s="9">
+        <v>-4.2508710801393713E-2</v>
+      </c>
+      <c r="S27" s="9">
+        <f t="shared" ref="S27:V27" si="97">S16/S3</f>
+        <v>-0.1441515650741351</v>
+      </c>
+      <c r="T27" s="9">
         <f t="shared" si="97"/>
-        <v>0.13449972662657192</v>
-      </c>
-      <c r="M27" s="9">
+        <v>-0.33872502378686969</v>
+      </c>
+      <c r="U27" s="9">
         <f t="shared" si="97"/>
-        <v>-0.11589613679544002</v>
-      </c>
-      <c r="N27" s="9">
+        <v>-0.67244736842105268</v>
+      </c>
+      <c r="V27" s="9">
         <f t="shared" si="97"/>
-        <v>5.1595744680850937E-2</v>
-      </c>
-      <c r="O27" s="9">
-        <f t="shared" si="97"/>
-        <v>-8.027522935779843E-3</v>
-      </c>
-      <c r="P27" s="9">
-        <f t="shared" si="97"/>
-        <v>-3.3721643163703373E-2</v>
-      </c>
-      <c r="Q27" s="9">
-        <f t="shared" ref="Q27:R27" si="98">Q16/Q3</f>
-        <v>-0.12371888726207908</v>
-      </c>
-      <c r="R27" s="9">
+        <v>-0.23787724470651286</v>
+      </c>
+      <c r="X27" s="9">
+        <f t="shared" ref="X27:AO27" si="98">X16/X3</f>
+        <v>-4.4222983494238442E-2</v>
+      </c>
+      <c r="Y27" s="9">
         <f t="shared" si="98"/>
-        <v>-4.2508710801393713E-2</v>
-      </c>
-      <c r="S27" s="9">
-        <f t="shared" ref="S27:V27" si="99">S16/S3</f>
-        <v>-0.1441515650741351</v>
-      </c>
-      <c r="T27" s="9">
-        <f t="shared" si="99"/>
-        <v>-0.16572041692213368</v>
-      </c>
-      <c r="U27" s="9">
-        <f t="shared" si="99"/>
-        <v>-0.333626159102001</v>
-      </c>
-      <c r="V27" s="9">
-        <f t="shared" si="99"/>
-        <v>-2.6216761415734341E-2</v>
-      </c>
-      <c r="X27" s="9">
-        <f t="shared" ref="X27:AO27" si="100">X16/X3</f>
-        <v>-4.4222983494238442E-2</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="100"/>
         <v>-2.3363348746653651E-2</v>
       </c>
       <c r="Z27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>-9.6228465000776729E-3</v>
       </c>
       <c r="AA27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>-1.674610331057694E-3</v>
       </c>
       <c r="AB27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>0.34780907668231603</v>
       </c>
       <c r="AC27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>2.5265214963707351E-2</v>
       </c>
       <c r="AD27" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>-4.8413212435233069E-2</v>
       </c>
       <c r="AE27" s="9">
-        <f t="shared" si="100"/>
-        <v>-0.15668280156117859</v>
+        <f t="shared" si="98"/>
+        <v>-0.31935822121154706</v>
       </c>
       <c r="AF27" s="9">
-        <f t="shared" si="100"/>
-        <v>-9.231947798226417E-2</v>
+        <f t="shared" si="98"/>
+        <v>-6.1329355996627484E-2</v>
       </c>
       <c r="AG27" s="9">
-        <f t="shared" si="100"/>
-        <v>-3.5618851775680062E-2</v>
+        <f t="shared" si="98"/>
+        <v>-2.8490492936383374E-3</v>
       </c>
       <c r="AH27" s="9">
-        <f t="shared" si="100"/>
-        <v>-3.1962338028817486E-3</v>
+        <f t="shared" si="98"/>
+        <v>2.7621064789047352E-2</v>
       </c>
       <c r="AI27" s="9">
-        <f t="shared" si="100"/>
-        <v>1.1046396821458214E-2</v>
+        <f t="shared" si="98"/>
+        <v>4.9216792881772983E-2</v>
       </c>
       <c r="AJ27" s="9">
-        <f t="shared" si="100"/>
-        <v>2.0610881310894103E-2</v>
+        <f t="shared" si="98"/>
+        <v>5.8023906603152965E-2</v>
       </c>
       <c r="AK27" s="9">
-        <f t="shared" si="100"/>
-        <v>2.7841418761279057E-2</v>
+        <f t="shared" si="98"/>
+        <v>6.7501310492312838E-2</v>
       </c>
       <c r="AL27" s="9">
-        <f t="shared" si="100"/>
-        <v>3.4960877643008405E-2</v>
+        <f t="shared" si="98"/>
+        <v>7.6794687121489041E-2</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" si="100"/>
-        <v>4.197113015919416E-2</v>
+        <f t="shared" si="98"/>
+        <v>8.5907609835535692E-2</v>
       </c>
       <c r="AN27" s="9">
-        <f t="shared" si="100"/>
-        <v>4.8874014923201245E-2</v>
+        <f t="shared" si="98"/>
+        <v>9.4843582593969758E-2</v>
       </c>
       <c r="AO27" s="9">
-        <f t="shared" si="100"/>
-        <v>5.5671337584043773E-2</v>
+        <f t="shared" si="98"/>
+        <v>0.10360604131825954</v>
       </c>
       <c r="AR27" t="s">
         <v>55</v>
       </c>
       <c r="AS27" s="3">
         <f>Main!D3</f>
-        <v>0.98009999999999997</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="28" spans="2:45" x14ac:dyDescent="0.3">
@@ -5022,7 +5029,7 @@
       </c>
       <c r="AS28" s="10">
         <f>AS26/AS27-1</f>
-        <v>-9.9901697844603232E-2</v>
+        <v>0.16576302502726192</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.3">
@@ -5030,7 +5037,7 @@
         <v>57</v>
       </c>
       <c r="AS29" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="2:45" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5050,47 +5057,47 @@
       </c>
       <c r="AE30" s="8">
         <f>AE16</f>
-        <v>-76.877200000000073</v>
+        <v>-126.39400000000002</v>
       </c>
       <c r="AF30" s="8">
-        <f t="shared" ref="AF30:AO30" si="101">AF16</f>
-        <v>-44.391073200000065</v>
+        <f t="shared" ref="AF30:AO30" si="99">AF16</f>
+        <v>-27.913519750000027</v>
       </c>
       <c r="AG30" s="8">
-        <f t="shared" si="101"/>
-        <v>-18.839740000000013</v>
+        <f t="shared" si="99"/>
+        <v>-1.4263918424999869</v>
       </c>
       <c r="AH30" s="8">
-        <f t="shared" si="101"/>
-        <v>-1.8089114494499596</v>
+        <f t="shared" si="99"/>
+        <v>14.796638968349985</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" si="101"/>
-        <v>6.5643043230635696</v>
+        <f t="shared" si="99"/>
+        <v>27.683772405741777</v>
       </c>
       <c r="AJ30" s="8">
-        <f t="shared" si="101"/>
-        <v>12.737903902706964</v>
+        <f t="shared" si="99"/>
+        <v>33.943159471736621</v>
       </c>
       <c r="AK30" s="8">
-        <f t="shared" si="101"/>
-        <v>17.722704366067468</v>
+        <f t="shared" si="99"/>
+        <v>40.67192502445706</v>
       </c>
       <c r="AL30" s="8">
-        <f t="shared" si="101"/>
-        <v>22.92229944467584</v>
+        <f t="shared" si="99"/>
+        <v>47.65965825144481</v>
       </c>
       <c r="AM30" s="8">
-        <f t="shared" si="101"/>
-        <v>28.344169962360773</v>
+        <f t="shared" si="99"/>
+        <v>54.914699230004793</v>
       </c>
       <c r="AN30" s="8">
-        <f t="shared" si="101"/>
-        <v>33.996039227106515</v>
+        <f t="shared" si="99"/>
+        <v>62.445643950231727</v>
       </c>
       <c r="AO30" s="8">
-        <f t="shared" si="101"/>
-        <v>39.885880639963929</v>
+        <f t="shared" si="99"/>
+        <v>70.261352049498768</v>
       </c>
     </row>
     <row r="31" spans="2:45" x14ac:dyDescent="0.3">
@@ -5114,39 +5121,39 @@
         <v>48</v>
       </c>
       <c r="AG31" s="2">
-        <f t="shared" ref="AG31:AO31" si="102">AF31*0.8</f>
+        <f t="shared" ref="AG31:AO31" si="100">AF31*0.8</f>
         <v>38.400000000000006</v>
       </c>
       <c r="AH31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>30.720000000000006</v>
       </c>
       <c r="AI31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>24.576000000000008</v>
       </c>
       <c r="AJ31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>19.660800000000009</v>
       </c>
       <c r="AK31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>15.728640000000008</v>
       </c>
       <c r="AL31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>12.582912000000007</v>
       </c>
       <c r="AM31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>10.066329600000007</v>
       </c>
       <c r="AN31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>8.0530636800000064</v>
       </c>
       <c r="AO31" s="2">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>6.4424509440000053</v>
       </c>
     </row>
@@ -5171,39 +5178,39 @@
         <v>58.199999999999996</v>
       </c>
       <c r="AG32" s="2">
-        <f t="shared" ref="AG32:AO32" si="103">AF32*0.97</f>
+        <f t="shared" ref="AG32:AO32" si="101">AF32*0.97</f>
         <v>56.453999999999994</v>
       </c>
       <c r="AH32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>54.760379999999991</v>
       </c>
       <c r="AI32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>53.117568599999991</v>
       </c>
       <c r="AJ32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>51.524041541999992</v>
       </c>
       <c r="AK32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>49.978320295739991</v>
       </c>
       <c r="AL32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>48.47897068686779</v>
       </c>
       <c r="AM32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>47.024601566261758</v>
       </c>
       <c r="AN32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>45.613863519273906</v>
       </c>
       <c r="AO32" s="2">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>44.245447613695688</v>
       </c>
     </row>
@@ -6165,47 +6172,47 @@
       </c>
       <c r="AE53" s="8">
         <f>AE30+SUM(AE31:AE52)</f>
-        <v>56.92279999999991</v>
+        <v>7.4059999999999633</v>
       </c>
       <c r="AF53" s="8">
-        <f t="shared" ref="AF53:AO53" si="104">AF30+SUM(AF31:AF52)</f>
-        <v>75.608926799999921</v>
+        <f t="shared" ref="AF53:AO53" si="102">AF30+SUM(AF31:AF52)</f>
+        <v>92.086480249999966</v>
       </c>
       <c r="AG53" s="8">
-        <f t="shared" si="104"/>
-        <v>89.81425999999999</v>
+        <f t="shared" si="102"/>
+        <v>107.22760815750001</v>
       </c>
       <c r="AH53" s="8">
-        <f t="shared" si="104"/>
-        <v>97.471468550550028</v>
+        <f t="shared" si="102"/>
+        <v>114.07701896834998</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="104"/>
-        <v>98.057872923063556</v>
+        <f t="shared" si="102"/>
+        <v>119.17734100574177</v>
       </c>
       <c r="AJ53" s="8">
-        <f t="shared" si="104"/>
-        <v>97.722745444706959</v>
+        <f t="shared" si="102"/>
+        <v>118.92800101373662</v>
       </c>
       <c r="AK53" s="8">
-        <f t="shared" si="104"/>
-        <v>97.229664661807476</v>
+        <f t="shared" si="102"/>
+        <v>120.17888532019705</v>
       </c>
       <c r="AL53" s="8">
-        <f t="shared" si="104"/>
-        <v>97.784182131543645</v>
+        <f t="shared" si="102"/>
+        <v>122.52154093831261</v>
       </c>
       <c r="AM53" s="8">
-        <f t="shared" si="104"/>
-        <v>99.235101128622546</v>
+        <f t="shared" si="102"/>
+        <v>125.80563039626657</v>
       </c>
       <c r="AN53" s="8">
-        <f t="shared" si="104"/>
-        <v>101.46296642638043</v>
+        <f t="shared" si="102"/>
+        <v>129.91257114950565</v>
       </c>
       <c r="AO53" s="8">
-        <f t="shared" si="104"/>
-        <v>104.37377919765963</v>
+        <f t="shared" si="102"/>
+        <v>134.74925060719448</v>
       </c>
     </row>
     <row r="54" spans="2:150" x14ac:dyDescent="0.3">
@@ -6229,39 +6236,39 @@
         <v>64.349999999999994</v>
       </c>
       <c r="AG54" s="2">
-        <f t="shared" ref="AG54:AO54" si="105">AF54*0.99</f>
+        <f t="shared" ref="AG54:AO54" si="103">AF54*0.99</f>
         <v>63.706499999999991</v>
       </c>
       <c r="AH54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>63.069434999999991</v>
       </c>
       <c r="AI54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>62.438740649999993</v>
       </c>
       <c r="AJ54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>61.814353243499994</v>
       </c>
       <c r="AK54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>61.196209711064995</v>
       </c>
       <c r="AL54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>60.584247613954346</v>
       </c>
       <c r="AM54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>59.978405137814804</v>
       </c>
       <c r="AN54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>59.378621086436652</v>
       </c>
       <c r="AO54" s="2">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>58.784834875572287</v>
       </c>
     </row>
@@ -6283,483 +6290,483 @@
       </c>
       <c r="AE55" s="8">
         <f>AE53-AE54</f>
-        <v>-8.0772000000000901</v>
+        <v>-57.594000000000037</v>
       </c>
       <c r="AF55" s="8">
-        <f t="shared" ref="AF55:AO55" si="106">AF53-AF54</f>
-        <v>11.258926799999927</v>
+        <f t="shared" ref="AF55:AO55" si="104">AF53-AF54</f>
+        <v>27.736480249999971</v>
       </c>
       <c r="AG55" s="8">
-        <f t="shared" si="106"/>
-        <v>26.107759999999999</v>
+        <f t="shared" si="104"/>
+        <v>43.521108157500024</v>
       </c>
       <c r="AH55" s="8">
-        <f t="shared" si="106"/>
-        <v>34.402033550550037</v>
+        <f t="shared" si="104"/>
+        <v>51.007583968349984</v>
       </c>
       <c r="AI55" s="8">
-        <f t="shared" si="106"/>
-        <v>35.619132273063563</v>
+        <f t="shared" si="104"/>
+        <v>56.738600355741774</v>
       </c>
       <c r="AJ55" s="8">
-        <f t="shared" si="106"/>
-        <v>35.908392201206965</v>
+        <f t="shared" si="104"/>
+        <v>57.113647770236625</v>
       </c>
       <c r="AK55" s="8">
-        <f t="shared" si="106"/>
-        <v>36.033454950742481</v>
+        <f t="shared" si="104"/>
+        <v>58.982675609132059</v>
       </c>
       <c r="AL55" s="8">
-        <f t="shared" si="106"/>
-        <v>37.199934517589298</v>
+        <f t="shared" si="104"/>
+        <v>61.937293324358265</v>
       </c>
       <c r="AM55" s="8">
-        <f t="shared" si="106"/>
-        <v>39.256695990807742</v>
+        <f t="shared" si="104"/>
+        <v>65.827225258451762</v>
       </c>
       <c r="AN55" s="8">
-        <f t="shared" si="106"/>
-        <v>42.084345339943781</v>
+        <f t="shared" si="104"/>
+        <v>70.533950063069</v>
       </c>
       <c r="AO55" s="8">
-        <f t="shared" si="106"/>
-        <v>45.588944322087343</v>
+        <f t="shared" si="104"/>
+        <v>75.964415731622196</v>
       </c>
       <c r="AP55" s="1">
         <f>AO55*(1+$AS$21)</f>
-        <v>45.133054878866467</v>
+        <v>75.20477157430598</v>
       </c>
       <c r="AQ55" s="1">
-        <f t="shared" ref="AQ55:DB55" si="107">AP55*(1+$AS$21)</f>
-        <v>44.681724330077799</v>
+        <f t="shared" ref="AQ55:DB55" si="105">AP55*(1+$AS$21)</f>
+        <v>74.452723858562919</v>
       </c>
       <c r="AR55" s="1">
-        <f t="shared" si="107"/>
-        <v>44.234907086777021</v>
+        <f t="shared" si="105"/>
+        <v>73.708196619977286</v>
       </c>
       <c r="AS55" s="1">
-        <f t="shared" si="107"/>
-        <v>43.79255801590925</v>
+        <f t="shared" si="105"/>
+        <v>72.971114653777519</v>
       </c>
       <c r="AT55" s="1">
-        <f t="shared" si="107"/>
-        <v>43.354632435750155</v>
+        <f t="shared" si="105"/>
+        <v>72.241403507239738</v>
       </c>
       <c r="AU55" s="1">
-        <f t="shared" si="107"/>
-        <v>42.921086111392654</v>
+        <f t="shared" si="105"/>
+        <v>71.518989472167334</v>
       </c>
       <c r="AV55" s="1">
-        <f t="shared" si="107"/>
-        <v>42.491875250278724</v>
+        <f t="shared" si="105"/>
+        <v>70.803799577445659</v>
       </c>
       <c r="AW55" s="1">
-        <f t="shared" si="107"/>
-        <v>42.066956497775934</v>
+        <f t="shared" si="105"/>
+        <v>70.095761581671198</v>
       </c>
       <c r="AX55" s="1">
-        <f t="shared" si="107"/>
-        <v>41.646286932798176</v>
+        <f t="shared" si="105"/>
+        <v>69.394803965854479</v>
       </c>
       <c r="AY55" s="1">
-        <f t="shared" si="107"/>
-        <v>41.229824063470197</v>
+        <f t="shared" si="105"/>
+        <v>68.700855926195928</v>
       </c>
       <c r="AZ55" s="1">
-        <f t="shared" si="107"/>
-        <v>40.817525822835492</v>
+        <f t="shared" si="105"/>
+        <v>68.013847366933973</v>
       </c>
       <c r="BA55" s="1">
-        <f t="shared" si="107"/>
-        <v>40.409350564607138</v>
+        <f t="shared" si="105"/>
+        <v>67.333708893264628</v>
       </c>
       <c r="BB55" s="1">
-        <f t="shared" si="107"/>
-        <v>40.005257058961064</v>
+        <f t="shared" si="105"/>
+        <v>66.660371804331987</v>
       </c>
       <c r="BC55" s="1">
-        <f t="shared" si="107"/>
-        <v>39.605204488371456</v>
+        <f t="shared" si="105"/>
+        <v>65.993768086288668</v>
       </c>
       <c r="BD55" s="1">
-        <f t="shared" si="107"/>
-        <v>39.209152443487739</v>
+        <f t="shared" si="105"/>
+        <v>65.333830405425786</v>
       </c>
       <c r="BE55" s="1">
-        <f t="shared" si="107"/>
-        <v>38.817060919052864</v>
+        <f t="shared" si="105"/>
+        <v>64.680492101371527</v>
       </c>
       <c r="BF55" s="1">
-        <f t="shared" si="107"/>
-        <v>38.428890309862332</v>
+        <f t="shared" si="105"/>
+        <v>64.033687180357816</v>
       </c>
       <c r="BG55" s="1">
-        <f t="shared" si="107"/>
-        <v>38.044601406763711</v>
+        <f t="shared" si="105"/>
+        <v>63.39335030855424</v>
       </c>
       <c r="BH55" s="1">
-        <f t="shared" si="107"/>
-        <v>37.664155392696074</v>
+        <f t="shared" si="105"/>
+        <v>62.759416805468696</v>
       </c>
       <c r="BI55" s="1">
-        <f t="shared" si="107"/>
-        <v>37.287513838769115</v>
+        <f t="shared" si="105"/>
+        <v>62.131822637414011</v>
       </c>
       <c r="BJ55" s="1">
-        <f t="shared" si="107"/>
-        <v>36.914638700381424</v>
+        <f t="shared" si="105"/>
+        <v>61.510504411039868</v>
       </c>
       <c r="BK55" s="1">
-        <f t="shared" si="107"/>
-        <v>36.545492313377608</v>
+        <f t="shared" si="105"/>
+        <v>60.895399366929468</v>
       </c>
       <c r="BL55" s="1">
-        <f t="shared" si="107"/>
-        <v>36.180037390243832</v>
+        <f t="shared" si="105"/>
+        <v>60.286445373260172</v>
       </c>
       <c r="BM55" s="1">
-        <f t="shared" si="107"/>
-        <v>35.818237016341392</v>
+        <f t="shared" si="105"/>
+        <v>59.683580919527571</v>
       </c>
       <c r="BN55" s="1">
-        <f t="shared" si="107"/>
-        <v>35.46005464617798</v>
+        <f t="shared" si="105"/>
+        <v>59.086745110332295</v>
       </c>
       <c r="BO55" s="1">
-        <f t="shared" si="107"/>
-        <v>35.105454099716198</v>
+        <f t="shared" si="105"/>
+        <v>58.495877659228974</v>
       </c>
       <c r="BP55" s="1">
-        <f t="shared" si="107"/>
-        <v>34.754399558719037</v>
+        <f t="shared" si="105"/>
+        <v>57.910918882636686</v>
       </c>
       <c r="BQ55" s="1">
-        <f t="shared" si="107"/>
-        <v>34.406855563131849</v>
+        <f t="shared" si="105"/>
+        <v>57.331809693810321</v>
       </c>
       <c r="BR55" s="1">
-        <f t="shared" si="107"/>
-        <v>34.062787007500532</v>
+        <f t="shared" si="105"/>
+        <v>56.758491596872219</v>
       </c>
       <c r="BS55" s="1">
-        <f t="shared" si="107"/>
-        <v>33.722159137425528</v>
+        <f t="shared" si="105"/>
+        <v>56.190906680903495</v>
       </c>
       <c r="BT55" s="1">
-        <f t="shared" si="107"/>
-        <v>33.384937546051276</v>
+        <f t="shared" si="105"/>
+        <v>55.628997614094459</v>
       </c>
       <c r="BU55" s="1">
-        <f t="shared" si="107"/>
-        <v>33.051088170590766</v>
+        <f t="shared" si="105"/>
+        <v>55.072707637953513</v>
       </c>
       <c r="BV55" s="1">
-        <f t="shared" si="107"/>
-        <v>32.720577288884861</v>
+        <f t="shared" si="105"/>
+        <v>54.521980561573976</v>
       </c>
       <c r="BW55" s="1">
-        <f t="shared" si="107"/>
-        <v>32.393371515996016</v>
+        <f t="shared" si="105"/>
+        <v>53.976760755958239</v>
       </c>
       <c r="BX55" s="1">
-        <f t="shared" si="107"/>
-        <v>32.069437800836056</v>
+        <f t="shared" si="105"/>
+        <v>53.436993148398656</v>
       </c>
       <c r="BY55" s="1">
-        <f t="shared" si="107"/>
-        <v>31.748743422827694</v>
+        <f t="shared" si="105"/>
+        <v>52.90262321691467</v>
       </c>
       <c r="BZ55" s="1">
-        <f t="shared" si="107"/>
-        <v>31.431255988599418</v>
+        <f t="shared" si="105"/>
+        <v>52.373596984745525</v>
       </c>
       <c r="CA55" s="1">
-        <f t="shared" si="107"/>
-        <v>31.116943428713423</v>
+        <f t="shared" si="105"/>
+        <v>51.849861014898067</v>
       </c>
       <c r="CB55" s="1">
-        <f t="shared" si="107"/>
-        <v>30.805773994426289</v>
+        <f t="shared" si="105"/>
+        <v>51.331362404749086</v>
       </c>
       <c r="CC55" s="1">
-        <f t="shared" si="107"/>
-        <v>30.497716254482025</v>
+        <f t="shared" si="105"/>
+        <v>50.818048780701595</v>
       </c>
       <c r="CD55" s="1">
-        <f t="shared" si="107"/>
-        <v>30.192739091937206</v>
+        <f t="shared" si="105"/>
+        <v>50.309868292894578</v>
       </c>
       <c r="CE55" s="1">
-        <f t="shared" si="107"/>
-        <v>29.890811701017835</v>
+        <f t="shared" si="105"/>
+        <v>49.806769609965635</v>
       </c>
       <c r="CF55" s="1">
-        <f t="shared" si="107"/>
-        <v>29.591903584007657</v>
+        <f t="shared" si="105"/>
+        <v>49.308701913865981</v>
       </c>
       <c r="CG55" s="1">
-        <f t="shared" si="107"/>
-        <v>29.295984548167581</v>
+        <f t="shared" si="105"/>
+        <v>48.815614894727318</v>
       </c>
       <c r="CH55" s="1">
-        <f t="shared" si="107"/>
-        <v>29.003024702685906</v>
+        <f t="shared" si="105"/>
+        <v>48.327458745780042</v>
       </c>
       <c r="CI55" s="1">
-        <f t="shared" si="107"/>
-        <v>28.712994455659047</v>
+        <f t="shared" si="105"/>
+        <v>47.844184158322243</v>
       </c>
       <c r="CJ55" s="1">
-        <f t="shared" si="107"/>
-        <v>28.425864511102457</v>
+        <f t="shared" si="105"/>
+        <v>47.365742316739016</v>
       </c>
       <c r="CK55" s="1">
-        <f t="shared" si="107"/>
-        <v>28.141605865991433</v>
+        <f t="shared" si="105"/>
+        <v>46.892084893571628</v>
       </c>
       <c r="CL55" s="1">
-        <f t="shared" si="107"/>
-        <v>27.860189807331519</v>
+        <f t="shared" si="105"/>
+        <v>46.423164044635911</v>
       </c>
       <c r="CM55" s="1">
-        <f t="shared" si="107"/>
-        <v>27.581587909258204</v>
+        <f t="shared" si="105"/>
+        <v>45.958932404189554</v>
       </c>
       <c r="CN55" s="1">
-        <f t="shared" si="107"/>
-        <v>27.30577203016562</v>
+        <f t="shared" si="105"/>
+        <v>45.499343080147661</v>
       </c>
       <c r="CO55" s="1">
-        <f t="shared" si="107"/>
-        <v>27.032714309863962</v>
+        <f t="shared" si="105"/>
+        <v>45.044349649346181</v>
       </c>
       <c r="CP55" s="1">
-        <f t="shared" si="107"/>
-        <v>26.762387166765322</v>
+        <f t="shared" si="105"/>
+        <v>44.593906152852718</v>
       </c>
       <c r="CQ55" s="1">
-        <f t="shared" si="107"/>
-        <v>26.49476329509767</v>
+        <f t="shared" si="105"/>
+        <v>44.14796709132419</v>
       </c>
       <c r="CR55" s="1">
-        <f t="shared" si="107"/>
-        <v>26.229815662146692</v>
+        <f t="shared" si="105"/>
+        <v>43.706487420410951</v>
       </c>
       <c r="CS55" s="1">
-        <f t="shared" si="107"/>
-        <v>25.967517505525226</v>
+        <f t="shared" si="105"/>
+        <v>43.26942254620684</v>
       </c>
       <c r="CT55" s="1">
-        <f t="shared" si="107"/>
-        <v>25.707842330469973</v>
+        <f t="shared" si="105"/>
+        <v>42.836728320744768</v>
       </c>
       <c r="CU55" s="1">
-        <f t="shared" si="107"/>
-        <v>25.450763907165271</v>
+        <f t="shared" si="105"/>
+        <v>42.408361037537318</v>
       </c>
       <c r="CV55" s="1">
-        <f t="shared" si="107"/>
-        <v>25.196256268093617</v>
+        <f t="shared" si="105"/>
+        <v>41.984277427161942</v>
       </c>
       <c r="CW55" s="1">
-        <f t="shared" si="107"/>
-        <v>24.944293705412679</v>
+        <f t="shared" si="105"/>
+        <v>41.56443465289032</v>
       </c>
       <c r="CX55" s="1">
-        <f t="shared" si="107"/>
-        <v>24.694850768358553</v>
+        <f t="shared" si="105"/>
+        <v>41.14879030636142</v>
       </c>
       <c r="CY55" s="1">
-        <f t="shared" si="107"/>
-        <v>24.447902260674965</v>
+        <f t="shared" si="105"/>
+        <v>40.737302403297804</v>
       </c>
       <c r="CZ55" s="1">
-        <f t="shared" si="107"/>
-        <v>24.203423238068215</v>
+        <f t="shared" si="105"/>
+        <v>40.329929379264826</v>
       </c>
       <c r="DA55" s="1">
-        <f t="shared" si="107"/>
-        <v>23.961389005687533</v>
+        <f t="shared" si="105"/>
+        <v>39.926630085472176</v>
       </c>
       <c r="DB55" s="1">
-        <f t="shared" si="107"/>
-        <v>23.721775115630656</v>
+        <f t="shared" si="105"/>
+        <v>39.527363784617457</v>
       </c>
       <c r="DC55" s="1">
-        <f t="shared" ref="DC55:ET55" si="108">DB55*(1+$AS$21)</f>
-        <v>23.484557364474348</v>
+        <f t="shared" ref="DC55:ET55" si="106">DB55*(1+$AS$21)</f>
+        <v>39.132090146771283</v>
       </c>
       <c r="DD55" s="1">
-        <f t="shared" si="108"/>
-        <v>23.249711790829604</v>
+        <f t="shared" si="106"/>
+        <v>38.740769245303568</v>
       </c>
       <c r="DE55" s="1">
-        <f t="shared" si="108"/>
-        <v>23.017214672921309</v>
+        <f t="shared" si="106"/>
+        <v>38.353361552850529</v>
       </c>
       <c r="DF55" s="1">
-        <f t="shared" si="108"/>
-        <v>22.787042526192096</v>
+        <f t="shared" si="106"/>
+        <v>37.969827937322023</v>
       </c>
       <c r="DG55" s="1">
-        <f t="shared" si="108"/>
-        <v>22.559172100930173</v>
+        <f t="shared" si="106"/>
+        <v>37.5901296579488</v>
       </c>
       <c r="DH55" s="1">
-        <f t="shared" si="108"/>
-        <v>22.333580379920871</v>
+        <f t="shared" si="106"/>
+        <v>37.214228361369315</v>
       </c>
       <c r="DI55" s="1">
-        <f t="shared" si="108"/>
-        <v>22.110244576121662</v>
+        <f t="shared" si="106"/>
+        <v>36.842086077755624</v>
       </c>
       <c r="DJ55" s="1">
-        <f t="shared" si="108"/>
-        <v>21.889142130360444</v>
+        <f t="shared" si="106"/>
+        <v>36.47366521697807</v>
       </c>
       <c r="DK55" s="1">
-        <f t="shared" si="108"/>
-        <v>21.670250709056837</v>
+        <f t="shared" si="106"/>
+        <v>36.108928564808288</v>
       </c>
       <c r="DL55" s="1">
-        <f t="shared" si="108"/>
-        <v>21.453548201966267</v>
+        <f t="shared" si="106"/>
+        <v>35.747839279160203</v>
       </c>
       <c r="DM55" s="1">
-        <f t="shared" si="108"/>
-        <v>21.239012719946604</v>
+        <f t="shared" si="106"/>
+        <v>35.390360886368597</v>
       </c>
       <c r="DN55" s="1">
-        <f t="shared" si="108"/>
-        <v>21.026622592747138</v>
+        <f t="shared" si="106"/>
+        <v>35.036457277504908</v>
       </c>
       <c r="DO55" s="1">
-        <f t="shared" si="108"/>
-        <v>20.816356366819665</v>
+        <f t="shared" si="106"/>
+        <v>34.686092704729859</v>
       </c>
       <c r="DP55" s="1">
-        <f t="shared" si="108"/>
-        <v>20.608192803151468</v>
+        <f t="shared" si="106"/>
+        <v>34.339231777682556</v>
       </c>
       <c r="DQ55" s="1">
-        <f t="shared" si="108"/>
-        <v>20.402110875119952</v>
+        <f t="shared" si="106"/>
+        <v>33.995839459905731</v>
       </c>
       <c r="DR55" s="1">
-        <f t="shared" si="108"/>
-        <v>20.198089766368753</v>
+        <f t="shared" si="106"/>
+        <v>33.655881065306673</v>
       </c>
       <c r="DS55" s="1">
-        <f t="shared" si="108"/>
-        <v>19.996108868705065</v>
+        <f t="shared" si="106"/>
+        <v>33.319322254653606</v>
       </c>
       <c r="DT55" s="1">
-        <f t="shared" si="108"/>
-        <v>19.796147780018014</v>
+        <f t="shared" si="106"/>
+        <v>32.986129032107073</v>
       </c>
       <c r="DU55" s="1">
-        <f t="shared" si="108"/>
-        <v>19.598186302217833</v>
+        <f t="shared" si="106"/>
+        <v>32.656267741786003</v>
       </c>
       <c r="DV55" s="1">
-        <f t="shared" si="108"/>
-        <v>19.402204439195653</v>
+        <f t="shared" si="106"/>
+        <v>32.329705064368142</v>
       </c>
       <c r="DW55" s="1">
-        <f t="shared" si="108"/>
-        <v>19.208182394803696</v>
+        <f t="shared" si="106"/>
+        <v>32.00640801372446</v>
       </c>
       <c r="DX55" s="1">
-        <f t="shared" si="108"/>
-        <v>19.016100570855659</v>
+        <f t="shared" si="106"/>
+        <v>31.686343933587214</v>
       </c>
       <c r="DY55" s="1">
-        <f t="shared" si="108"/>
-        <v>18.825939565147102</v>
+        <f t="shared" si="106"/>
+        <v>31.369480494251341</v>
       </c>
       <c r="DZ55" s="1">
-        <f t="shared" si="108"/>
-        <v>18.637680169495631</v>
+        <f t="shared" si="106"/>
+        <v>31.055785689308827</v>
       </c>
       <c r="EA55" s="1">
-        <f t="shared" si="108"/>
-        <v>18.451303367800676</v>
+        <f t="shared" si="106"/>
+        <v>30.74522783241574</v>
       </c>
       <c r="EB55" s="1">
-        <f t="shared" si="108"/>
-        <v>18.266790334122671</v>
+        <f t="shared" si="106"/>
+        <v>30.437775554091584</v>
       </c>
       <c r="EC55" s="1">
-        <f t="shared" si="108"/>
-        <v>18.084122430781445</v>
+        <f t="shared" si="106"/>
+        <v>30.133397798550668</v>
       </c>
       <c r="ED55" s="1">
-        <f t="shared" si="108"/>
-        <v>17.903281206473629</v>
+        <f t="shared" si="106"/>
+        <v>29.83206382056516</v>
       </c>
       <c r="EE55" s="1">
-        <f t="shared" si="108"/>
-        <v>17.724248394408892</v>
+        <f t="shared" si="106"/>
+        <v>29.533743182359508</v>
       </c>
       <c r="EF55" s="1">
-        <f t="shared" si="108"/>
-        <v>17.547005910464804</v>
+        <f t="shared" si="106"/>
+        <v>29.238405750535915</v>
       </c>
       <c r="EG55" s="1">
-        <f t="shared" si="108"/>
-        <v>17.371535851360157</v>
+        <f t="shared" si="106"/>
+        <v>28.946021693030556</v>
       </c>
       <c r="EH55" s="1">
-        <f t="shared" si="108"/>
-        <v>17.197820492846557</v>
+        <f t="shared" si="106"/>
+        <v>28.656561476100251</v>
       </c>
       <c r="EI55" s="1">
-        <f t="shared" si="108"/>
-        <v>17.025842287918092</v>
+        <f t="shared" si="106"/>
+        <v>28.369995861339248</v>
       </c>
       <c r="EJ55" s="1">
-        <f t="shared" si="108"/>
-        <v>16.855583865038909</v>
+        <f t="shared" si="106"/>
+        <v>28.086295902725855</v>
       </c>
       <c r="EK55" s="1">
-        <f t="shared" si="108"/>
-        <v>16.687028026388521</v>
+        <f t="shared" si="106"/>
+        <v>27.805432943698595</v>
       </c>
       <c r="EL55" s="1">
-        <f t="shared" si="108"/>
-        <v>16.520157746124635</v>
+        <f t="shared" si="106"/>
+        <v>27.527378614261607</v>
       </c>
       <c r="EM55" s="1">
-        <f t="shared" si="108"/>
-        <v>16.354956168663389</v>
+        <f t="shared" si="106"/>
+        <v>27.252104828118991</v>
       </c>
       <c r="EN55" s="1">
-        <f t="shared" si="108"/>
-        <v>16.191406606976756</v>
+        <f t="shared" si="106"/>
+        <v>26.9795837798378</v>
       </c>
       <c r="EO55" s="1">
-        <f t="shared" si="108"/>
-        <v>16.02949254090699</v>
+        <f t="shared" si="106"/>
+        <v>26.709787942039423</v>
       </c>
       <c r="EP55" s="1">
-        <f t="shared" si="108"/>
-        <v>15.869197615497919</v>
+        <f t="shared" si="106"/>
+        <v>26.442690062619029</v>
       </c>
       <c r="EQ55" s="1">
-        <f t="shared" si="108"/>
-        <v>15.710505639342939</v>
+        <f t="shared" si="106"/>
+        <v>26.178263161992838</v>
       </c>
       <c r="ER55" s="1">
-        <f t="shared" si="108"/>
-        <v>15.553400582949509</v>
+        <f t="shared" si="106"/>
+        <v>25.916480530372908</v>
       </c>
       <c r="ES55" s="1">
-        <f t="shared" si="108"/>
-        <v>15.397866577120014</v>
+        <f t="shared" si="106"/>
+        <v>25.657315725069179</v>
       </c>
       <c r="ET55" s="1">
-        <f t="shared" si="108"/>
-        <v>15.243887911348814</v>
+        <f t="shared" si="106"/>
+        <v>25.400742567818487</v>
       </c>
     </row>
     <row r="59" spans="2:150" x14ac:dyDescent="0.3">
@@ -6768,7 +6775,7 @@
       </c>
       <c r="AS59" s="2">
         <f>NPV(AS22,AE55:ET55)</f>
-        <v>252.55472952584131</v>
+        <v>381.49873966507113</v>
       </c>
     </row>
     <row r="60" spans="2:150" x14ac:dyDescent="0.3">
@@ -6777,7 +6784,7 @@
       </c>
       <c r="AS60" s="2">
         <f>Main!D8</f>
-        <v>63.900000000000006</v>
+        <v>51.599999999999994</v>
       </c>
     </row>
     <row r="61" spans="2:150" x14ac:dyDescent="0.3">
@@ -6786,7 +6793,7 @@
       </c>
       <c r="AS61" s="2">
         <f>AS59+AS60</f>
-        <v>316.45472952584134</v>
+        <v>433.09873966507109</v>
       </c>
     </row>
     <row r="62" spans="2:150" x14ac:dyDescent="0.3">
@@ -6795,7 +6802,7 @@
       </c>
       <c r="AS62" s="3">
         <f>AS61/Model!AO17</f>
-        <v>3.0109869602839332</v>
+        <v>4.0514381633776528</v>
       </c>
     </row>
     <row r="63" spans="2:150" x14ac:dyDescent="0.3">
@@ -6804,7 +6811,7 @@
       </c>
       <c r="AS63" s="3">
         <f>Main!D3</f>
-        <v>0.98009999999999997</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="64" spans="2:150" x14ac:dyDescent="0.3">
@@ -6813,7 +6820,7 @@
       </c>
       <c r="AS64" s="10">
         <f>AS62/AS63-1</f>
-        <v>2.0721221919027988</v>
+        <v>1.4115703353438409</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CHGG.xlsx
+++ b/Financial Analysis/CHGG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A011C9D0-079E-42B2-997D-21BC4FD798F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BB471E-06CF-429E-BEE2-0FF0D5CF873C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -925,14 +925,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
       <c r="E3" s="5">
-        <v>45905</v>
+        <v>45937</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45905</v>
+        <v>45937</v>
       </c>
       <c r="G3" s="5">
         <v>45964</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>179.59200000000001</v>
+        <v>161.41900000000001</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>127.99200000000002</v>
+        <v>109.81900000000002</v>
       </c>
       <c r="J9" t="s">
         <v>89</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AS27" s="3">
         <f>Main!D3</f>
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="28" spans="2:45" x14ac:dyDescent="0.3">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AS28" s="10">
         <f>AS26/AS27-1</f>
-        <v>0.16576302502726192</v>
+        <v>0.29700786890450326</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.3">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="AS63" s="3">
         <f>Main!D3</f>
-        <v>1.68</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="64" spans="2:150" x14ac:dyDescent="0.3">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AS64" s="10">
         <f>AS62/AS63-1</f>
-        <v>1.4115703353438409</v>
+        <v>1.6830716313759289</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CHGG.xlsx
+++ b/Financial Analysis/CHGG.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18BB471E-06CF-429E-BEE2-0FF0D5CF873C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1FE7075-36EB-473B-BD0C-BDAAFFC6EE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -925,14 +925,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="E3" s="5">
-        <v>45937</v>
+        <v>45960</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45937</v>
+        <v>45960</v>
       </c>
       <c r="G3" s="5">
         <v>45964</v>
@@ -955,7 +955,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>161.41900000000001</v>
+        <v>115.45200000000001</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>109.81900000000002</v>
+        <v>63.852000000000018</v>
       </c>
       <c r="J9" t="s">
         <v>89</v>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="AS27" s="3">
         <f>Main!D3</f>
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="28" spans="2:45" x14ac:dyDescent="0.3">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="AS28" s="10">
         <f>AS26/AS27-1</f>
-        <v>0.29700786890450326</v>
+        <v>0.81340915004240721</v>
       </c>
     </row>
     <row r="29" spans="2:45" x14ac:dyDescent="0.3">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="AS63" s="3">
         <f>Main!D3</f>
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="64" spans="2:150" x14ac:dyDescent="0.3">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="AS64" s="10">
         <f>AS62/AS63-1</f>
-        <v>1.6830716313759289</v>
+        <v>2.7513316327570858</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/CHGG.xlsx
+++ b/Financial Analysis/CHGG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD258BA-7DBC-473A-B163-5EB63D0300DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5703B83-F848-4175-B4F6-C9F74EC41224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EE075BA3-B62D-42AA-AD11-2E99A8FED7C3}"/>
   </bookViews>
@@ -99,7 +99,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-minus income tax effect of non-GAAP adjustments</t>
+minus 129.9 income tax effect of non-GAAP adjustments</t>
         </r>
       </text>
     </comment>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="102">
   <si>
     <t>CHGG</t>
   </si>
@@ -233,9 +233,6 @@
     <t>EPS</t>
   </si>
   <si>
-    <t>Non-GAAP</t>
-  </si>
-  <si>
     <t>Revenue y/y</t>
   </si>
   <si>
@@ -368,9 +365,6 @@
     <t>FCF</t>
   </si>
   <si>
-    <t>NPV (FCF)</t>
-  </si>
-  <si>
     <t>Chegg</t>
   </si>
   <si>
@@ -417,6 +411,9 @@
   </si>
   <si>
     <t>Services y/y</t>
+  </si>
+  <si>
+    <t>Cumulative</t>
   </si>
 </sst>
 </file>
@@ -490,7 +487,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -511,8 +508,6 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -542,8 +537,8 @@
     <xdr:to>
       <xdr:col>22</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>91440</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -559,7 +554,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14302740" y="0"/>
-          <a:ext cx="0" cy="6675120"/>
+          <a:ext cx="0" cy="12473940"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -592,7 +587,7 @@
     <xdr:to>
       <xdr:col>35</xdr:col>
       <xdr:colOff>30480</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
@@ -964,7 +959,7 @@
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>46063</v>
+        <v>46076</v>
       </c>
       <c r="G3" s="5">
         <v>46146</v>
@@ -979,7 +974,7 @@
         <v>109.4</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
@@ -1000,7 +995,7 @@
         <v>85.200000000000017</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
@@ -1012,13 +1007,13 @@
         <v>53.8</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
@@ -1039,15 +1034,15 @@
         <v>45.179999999999978</v>
       </c>
       <c r="J9" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="K10" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
@@ -1060,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB0C3E2D-253D-46B0-9AD3-C7A573AF3AFF}">
-  <dimension ref="B1:EX69"/>
+  <dimension ref="B2:EX87"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
@@ -1068,11 +1063,6 @@
     <col min="49" max="49" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:45" x14ac:dyDescent="0.3">
-      <c r="P1" t="s">
-        <v>41</v>
-      </c>
-    </row>
     <row r="2" spans="2:45" x14ac:dyDescent="0.3">
       <c r="C2" s="6" t="s">
         <v>15</v>
@@ -1123,28 +1113,28 @@
         <v>29</v>
       </c>
       <c r="S2" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="T2" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="T2" s="6" t="s">
+      <c r="U2" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="U2" s="6" t="s">
+      <c r="V2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="V2" s="6" t="s">
-        <v>61</v>
-      </c>
       <c r="W2" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="X2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>98</v>
       </c>
       <c r="AB2">
         <v>2018</v>
@@ -1203,7 +1193,7 @@
     </row>
     <row r="3" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C3" s="6"/>
       <c r="D3" s="6"/>
@@ -1249,7 +1239,7 @@
         <v>18.920000000000002</v>
       </c>
       <c r="Y3" s="11">
-        <f t="shared" ref="Y3:Z3" si="0">U3*1.1</f>
+        <f t="shared" ref="Y3" si="0">U3*1.1</f>
         <v>19.360000000000003</v>
       </c>
       <c r="Z3" s="11">
@@ -1260,11 +1250,11 @@
         <f>SUM(O3:R3)</f>
         <v>74.099999999999994</v>
       </c>
-      <c r="AI3" s="13">
+      <c r="AI3" s="2">
         <f>SUM(S3:V3)</f>
         <v>68.599999999999994</v>
       </c>
-      <c r="AJ3" s="13">
+      <c r="AJ3" s="2">
         <f>SUM(W3:Z3)</f>
         <v>76.384999999999991</v>
       </c>
@@ -1307,7 +1297,7 @@
     </row>
     <row r="4" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
@@ -1365,11 +1355,11 @@
         <f>SUM(O4:R4)</f>
         <v>543.6</v>
       </c>
-      <c r="AI4" s="13">
+      <c r="AI4" s="2">
         <f>SUM(S4:V4)</f>
         <v>308.29999999999995</v>
       </c>
-      <c r="AJ4" s="13">
+      <c r="AJ4" s="2">
         <f>SUM(W4:Z4)</f>
         <v>170.51499999999999</v>
       </c>
@@ -1673,7 +1663,7 @@
         <v>103.69800000000001</v>
       </c>
       <c r="AK6" s="2">
-        <f t="shared" ref="AJ6:AS6" si="6">AK5-AK7</f>
+        <f t="shared" ref="AK6:AS6" si="6">AK5-AK7</f>
         <v>99.932799999999986</v>
       </c>
       <c r="AL6" s="2">
@@ -2326,7 +2316,7 @@
     </row>
     <row r="11" spans="2:45" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -2341,8 +2331,12 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="P11" s="2">
+        <v>481.5</v>
+      </c>
+      <c r="Q11" s="2">
+        <v>195.7</v>
+      </c>
       <c r="R11" s="2"/>
       <c r="S11" s="2">
         <v>2</v>
@@ -2396,7 +2390,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="2">
-        <f t="shared" ref="C12:P12" si="17">SUM(C8:C10)</f>
+        <f t="shared" ref="C12:O12" si="17">SUM(C8:C10)</f>
         <v>110.19999999999999</v>
       </c>
       <c r="D12" s="2">
@@ -2448,15 +2442,15 @@
         <v>130.30000000000001</v>
       </c>
       <c r="P12" s="2">
-        <f t="shared" si="17"/>
-        <v>121.2</v>
+        <f>SUM(P8:P11)</f>
+        <v>602.70000000000005</v>
       </c>
       <c r="Q12" s="2">
-        <f t="shared" ref="Q12:R12" si="18">SUM(Q8:Q10)</f>
-        <v>119.69999999999999</v>
+        <f>SUM(Q8:Q11)</f>
+        <v>315.39999999999998</v>
       </c>
       <c r="R12" s="2">
-        <f t="shared" si="18"/>
+        <f t="shared" ref="R12" si="18">SUM(R8:R10)</f>
         <v>125.2</v>
       </c>
       <c r="S12" s="2">
@@ -2622,11 +2616,11 @@
       </c>
       <c r="P13" s="8">
         <f t="shared" si="22"/>
-        <v>-3.5000000000000142</v>
+        <v>-485.00000000000006</v>
       </c>
       <c r="Q13" s="8">
         <f t="shared" ref="Q13:R13" si="23">Q7-Q12</f>
-        <v>-26.5</v>
+        <v>-222.2</v>
       </c>
       <c r="R13" s="8">
         <f t="shared" si="23"/>
@@ -2847,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="2">
-        <f t="shared" ref="AJ14:AS14" si="28">AJ14*1.03</f>
+        <f t="shared" ref="AK14:AS14" si="28">AJ14*1.03</f>
         <v>0</v>
       </c>
       <c r="AL14" s="2">
@@ -2993,7 +2987,7 @@
         <v>-4</v>
       </c>
       <c r="AK15" s="2">
-        <f t="shared" ref="AJ15:AS15" si="29">AJ15*1.03</f>
+        <f t="shared" ref="AK15:AS15" si="29">AJ15*1.03</f>
         <v>-4.12</v>
       </c>
       <c r="AL15" s="2">
@@ -3087,11 +3081,11 @@
       </c>
       <c r="P16" s="8">
         <f t="shared" si="30"/>
-        <v>2.8999999999999853</v>
+        <v>-478.6</v>
       </c>
       <c r="Q16" s="8">
         <f t="shared" ref="Q16:Z16" si="31">Q13-Q14-Q15</f>
-        <v>-19.600000000000001</v>
+        <v>-215.29999999999998</v>
       </c>
       <c r="R16" s="8">
         <f t="shared" si="31"/>
@@ -3246,8 +3240,8 @@
         <v>9.1</v>
       </c>
       <c r="P17" s="2">
-        <f>138.3-129.9</f>
-        <v>8.4000000000000057</v>
+        <f>138.3</f>
+        <v>138.30000000000001</v>
       </c>
       <c r="Q17" s="2">
         <v>-2.7</v>
@@ -3306,7 +3300,7 @@
       </c>
       <c r="AH17" s="2">
         <f>SUM(O17:R17)</f>
-        <v>18.800000000000008</v>
+        <v>148.70000000000002</v>
       </c>
       <c r="AI17" s="2">
         <f>SUM(S17:V17)</f>
@@ -3411,11 +3405,11 @@
       </c>
       <c r="P18" s="8">
         <f t="shared" si="36"/>
-        <v>-5.5000000000000204</v>
+        <v>-616.90000000000009</v>
       </c>
       <c r="Q18" s="8">
         <f t="shared" ref="Q18:R18" si="37">Q16-Q17</f>
-        <v>-16.900000000000002</v>
+        <v>-212.6</v>
       </c>
       <c r="R18" s="8">
         <f t="shared" si="37"/>
@@ -3479,7 +3473,7 @@
       </c>
       <c r="AH18" s="8">
         <f t="shared" si="40"/>
-        <v>-29.899999999999945</v>
+        <v>-159.79999999999995</v>
       </c>
       <c r="AI18" s="8">
         <f t="shared" ref="AI18:AS18" si="41">AI16-AI17</f>
@@ -4046,47 +4040,47 @@
         <v>105.1</v>
       </c>
       <c r="AI19" s="2">
-        <f>109.4</f>
+        <f t="shared" ref="AI19:AS19" si="45">109.4</f>
         <v>109.4</v>
       </c>
       <c r="AJ19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AK19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AL19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AM19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AN19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AO19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AP19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AQ19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AR19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
       <c r="AS19" s="2">
-        <f>109.4</f>
+        <f t="shared" si="45"/>
         <v>109.4</v>
       </c>
     </row>
@@ -4095,422 +4089,422 @@
         <v>40</v>
       </c>
       <c r="C20" s="7">
-        <f t="shared" ref="C20:P20" si="45">C18/C19</f>
+        <f t="shared" ref="C20:P20" si="46">C18/C19</f>
         <v>-0.62777242044358716</v>
       </c>
       <c r="D20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.31629701060752174</v>
       </c>
       <c r="E20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>6.4609450337512156E-2</v>
       </c>
       <c r="F20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23432979749276778</v>
       </c>
       <c r="G20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>5.4966248794599638E-2</v>
       </c>
       <c r="H20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>7.1359691417550733E-2</v>
       </c>
       <c r="I20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.4271938283510122</v>
       </c>
       <c r="J20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>1.8322082931532886E-2</v>
       </c>
       <c r="K20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>2.025072324011544E-2</v>
       </c>
       <c r="L20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.23722275795564132</v>
       </c>
       <c r="M20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-0.17647058823529391</v>
       </c>
       <c r="N20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>9.3539054966248564E-2</v>
       </c>
       <c r="O20" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>-1.3500482160077192E-2</v>
       </c>
       <c r="P20" s="7">
-        <f t="shared" si="45"/>
-        <v>-5.3037608486017553E-2</v>
+        <f t="shared" si="46"/>
+        <v>-5.9488910318225656</v>
       </c>
       <c r="Q20" s="7">
-        <f t="shared" ref="Q20:R20" si="46">Q18/Q19</f>
-        <v>-0.16203259827420904</v>
+        <f t="shared" ref="Q20:R20" si="47">Q18/Q19</f>
+        <v>-2.0383509108341324</v>
       </c>
       <c r="R20" s="7">
-        <f t="shared" si="46"/>
+        <f t="shared" si="47"/>
         <v>-5.8039961941008543E-2</v>
       </c>
       <c r="S20" s="7">
-        <f t="shared" ref="S20:V20" si="47">S18/S19</f>
+        <f t="shared" ref="S20:V20" si="48">S18/S19</f>
         <v>-0.16416510318949346</v>
       </c>
       <c r="T20" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-0.33302151543498598</v>
       </c>
       <c r="U20" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-0.16129032258064518</v>
       </c>
       <c r="V20" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>-0.29890310786106034</v>
       </c>
       <c r="W20" s="7">
-        <f t="shared" ref="W20:Z20" si="48">W18/W19</f>
+        <f t="shared" ref="W20:Z20" si="49">W18/W19</f>
         <v>-0.17358775137111523</v>
       </c>
       <c r="X20" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-0.18975685557586838</v>
       </c>
       <c r="Y20" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-0.21722349177330902</v>
       </c>
       <c r="Z20" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>-0.2258056215722121</v>
       </c>
       <c r="AB20" s="7">
-        <f t="shared" ref="AB20:AH20" si="49">AB18/AB19</f>
+        <f t="shared" ref="AB20:AH20" si="50">AB18/AB19</f>
         <v>-0.13693346190935357</v>
       </c>
       <c r="AC20" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-9.2574734811957424E-2</v>
       </c>
       <c r="AD20" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-5.9787849566056352E-2</v>
       </c>
       <c r="AE20" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>-1.2536162005786767E-2</v>
       </c>
       <c r="AF20" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>2.5718418514946957</v>
       </c>
       <c r="AG20" s="7">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.17454194792671113</v>
       </c>
       <c r="AH20" s="7">
-        <f t="shared" si="49"/>
-        <v>-0.28449096098953325</v>
+        <f t="shared" si="50"/>
+        <v>-1.5204567078972404</v>
       </c>
       <c r="AI20" s="7">
-        <f t="shared" ref="AI20:AS20" si="50">AI18/AI19</f>
+        <f t="shared" ref="AI20:AS20" si="51">AI18/AI19</f>
         <v>-0.94424131627056695</v>
       </c>
       <c r="AJ20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.80637372029250465</v>
       </c>
       <c r="AK20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.48444219378427811</v>
       </c>
       <c r="AL20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.4539377760511884</v>
       </c>
       <c r="AM20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.41384804584095103</v>
       </c>
       <c r="AN20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.36204247085009189</v>
       </c>
       <c r="AO20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.30409849798644933</v>
       </c>
       <c r="AP20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.23120296790561043</v>
       </c>
       <c r="AQ20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-0.1658955657958571</v>
       </c>
       <c r="AR20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>-8.4037952581484346E-2</v>
       </c>
       <c r="AS20" s="7">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>1.6625108273940342E-2</v>
       </c>
     </row>
     <row r="22" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>101</v>
-      </c>
-      <c r="S22" s="12">
-        <f t="shared" ref="S22:S23" si="51">S3/O3-1</f>
+        <v>99</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" ref="S22:S23" si="52">S3/O3-1</f>
         <v>-0.21078431372549011</v>
       </c>
-      <c r="T22" s="12">
-        <f t="shared" ref="T22:T23" si="52">T3/P3-1</f>
+      <c r="T22" s="9">
+        <f t="shared" ref="T22:T23" si="53">T3/P3-1</f>
         <v>-8.9947089947089887E-2</v>
       </c>
-      <c r="U22" s="12">
-        <f t="shared" ref="U22:U23" si="53">U3/Q3-1</f>
+      <c r="U22" s="9">
+        <f t="shared" ref="U22:U23" si="54">U3/Q3-1</f>
         <v>-6.3829787234042534E-2</v>
       </c>
-      <c r="V22" s="12">
-        <f t="shared" ref="V22:V23" si="54">V3/R3-1</f>
+      <c r="V22" s="9">
+        <f t="shared" ref="V22:V23" si="55">V3/R3-1</f>
         <v>0.10624999999999996</v>
       </c>
-      <c r="W22" s="12">
-        <f t="shared" ref="W22:W24" si="55">W3/S3-1</f>
+      <c r="W22" s="9">
+        <f t="shared" ref="W22:W24" si="56">W3/S3-1</f>
         <v>0.10248447204968936</v>
       </c>
-      <c r="X22" s="12">
-        <f t="shared" ref="X22:X23" si="56">X3/T3-1</f>
+      <c r="X22" s="9">
+        <f t="shared" ref="X22:X23" si="57">X3/T3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="Y22" s="12">
-        <f t="shared" ref="Y22:Y23" si="57">Y3/U3-1</f>
+      <c r="Y22" s="9">
+        <f t="shared" ref="Y22:Y23" si="58">Y3/U3-1</f>
         <v>0.10000000000000009</v>
       </c>
-      <c r="Z22" s="12">
-        <f t="shared" ref="Z22:Z23" si="58">Z3/V3-1</f>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22:Z23" si="59">Z3/V3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AI22" s="12">
-        <f t="shared" ref="AD22:AS24" si="59">AI3/AH3-1</f>
+      <c r="AI22" s="9">
+        <f t="shared" ref="AD22:AS24" si="60">AI3/AH3-1</f>
         <v>-7.4224021592442679E-2</v>
       </c>
-      <c r="AJ22" s="12">
-        <f t="shared" si="59"/>
+      <c r="AJ22" s="9">
+        <f t="shared" si="60"/>
         <v>0.11348396501457714</v>
       </c>
-      <c r="AK22" s="12">
-        <f t="shared" ref="AK22:AK23" si="60">AK3/AJ3-1</f>
+      <c r="AK22" s="9">
+        <f t="shared" ref="AK22:AK23" si="61">AK3/AJ3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AL22" s="12">
-        <f t="shared" ref="AL22:AL23" si="61">AL3/AK3-1</f>
+      <c r="AL22" s="9">
+        <f t="shared" ref="AL22:AL23" si="62">AL3/AK3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AM22" s="12">
-        <f t="shared" ref="AM22:AM23" si="62">AM3/AL3-1</f>
+      <c r="AM22" s="9">
+        <f t="shared" ref="AM22:AM23" si="63">AM3/AL3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AN22" s="12">
-        <f t="shared" ref="AN22:AN23" si="63">AN3/AM3-1</f>
+      <c r="AN22" s="9">
+        <f t="shared" ref="AN22:AN23" si="64">AN3/AM3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AO22" s="12">
-        <f t="shared" ref="AO22:AO23" si="64">AO3/AN3-1</f>
+      <c r="AO22" s="9">
+        <f t="shared" ref="AO22:AO23" si="65">AO3/AN3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AP22" s="12">
-        <f t="shared" ref="AP22:AP23" si="65">AP3/AO3-1</f>
+      <c r="AP22" s="9">
+        <f t="shared" ref="AP22:AP23" si="66">AP3/AO3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AQ22" s="12">
-        <f t="shared" ref="AQ22:AQ23" si="66">AQ3/AP3-1</f>
+      <c r="AQ22" s="9">
+        <f t="shared" ref="AQ22:AQ23" si="67">AQ3/AP3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AR22" s="12">
-        <f t="shared" ref="AR22:AR23" si="67">AR3/AQ3-1</f>
+      <c r="AR22" s="9">
+        <f t="shared" ref="AR22:AR23" si="68">AR3/AQ3-1</f>
         <v>0.14999999999999991</v>
       </c>
-      <c r="AS22" s="12">
-        <f t="shared" ref="AS22:AS23" si="68">AS3/AR3-1</f>
+      <c r="AS22" s="9">
+        <f t="shared" ref="AS22:AS23" si="69">AS3/AR3-1</f>
         <v>0.14999999999999969</v>
       </c>
     </row>
     <row r="23" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
-        <v>102</v>
-      </c>
-      <c r="S23" s="12">
-        <f t="shared" si="51"/>
+        <v>100</v>
+      </c>
+      <c r="S23" s="9">
+        <f t="shared" si="52"/>
         <v>-0.3162337662337662</v>
       </c>
-      <c r="T23" s="12">
-        <f t="shared" si="52"/>
+      <c r="T23" s="9">
+        <f t="shared" si="53"/>
         <v>-0.39085239085239087</v>
       </c>
-      <c r="U23" s="12">
-        <f t="shared" si="53"/>
+      <c r="U23" s="9">
+        <f t="shared" si="54"/>
         <v>-0.48896434634974528</v>
       </c>
-      <c r="V23" s="12">
-        <f t="shared" si="54"/>
+      <c r="V23" s="9">
+        <f t="shared" si="55"/>
         <v>-0.56941176470588228</v>
       </c>
-      <c r="W23" s="12">
-        <f t="shared" si="55"/>
+      <c r="W23" s="9">
+        <f t="shared" si="56"/>
         <v>-0.58926875593542261</v>
       </c>
-      <c r="X23" s="12">
-        <f t="shared" si="56"/>
+      <c r="X23" s="9">
+        <f t="shared" si="57"/>
         <v>-0.5</v>
       </c>
-      <c r="Y23" s="12">
-        <f t="shared" si="57"/>
+      <c r="Y23" s="9">
+        <f t="shared" si="58"/>
         <v>-0.30000000000000004</v>
       </c>
-      <c r="Z23" s="12">
-        <f t="shared" si="58"/>
+      <c r="Z23" s="9">
+        <f t="shared" si="59"/>
         <v>-0.25</v>
       </c>
-      <c r="AI23" s="12">
-        <f t="shared" si="59"/>
+      <c r="AI23" s="9">
+        <f t="shared" si="60"/>
         <v>-0.43285504047093459</v>
       </c>
-      <c r="AJ23" s="12">
-        <f t="shared" si="59"/>
+      <c r="AJ23" s="9">
+        <f t="shared" si="60"/>
         <v>-0.44691858579305865</v>
       </c>
-      <c r="AK23" s="12">
-        <f t="shared" si="60"/>
-        <v>-5.0000000000000155E-2</v>
-      </c>
-      <c r="AL23" s="12">
+      <c r="AK23" s="9">
         <f t="shared" si="61"/>
         <v>-5.0000000000000155E-2</v>
       </c>
-      <c r="AM23" s="12">
+      <c r="AL23" s="9">
         <f t="shared" si="62"/>
         <v>-5.0000000000000155E-2</v>
       </c>
-      <c r="AN23" s="12">
+      <c r="AM23" s="9">
         <f t="shared" si="63"/>
-        <v>-5.0000000000000044E-2</v>
-      </c>
-      <c r="AO23" s="12">
+        <v>-5.0000000000000155E-2</v>
+      </c>
+      <c r="AN23" s="9">
         <f t="shared" si="64"/>
         <v>-5.0000000000000044E-2</v>
       </c>
-      <c r="AP23" s="12">
+      <c r="AO23" s="9">
         <f t="shared" si="65"/>
         <v>-5.0000000000000044E-2</v>
       </c>
-      <c r="AQ23" s="12">
+      <c r="AP23" s="9">
         <f t="shared" si="66"/>
         <v>-5.0000000000000044E-2</v>
       </c>
-      <c r="AR23" s="12">
+      <c r="AQ23" s="9">
         <f t="shared" si="67"/>
-        <v>-4.9999999999999933E-2</v>
-      </c>
-      <c r="AS23" s="12">
+        <v>-5.0000000000000044E-2</v>
+      </c>
+      <c r="AR23" s="9">
         <f t="shared" si="68"/>
         <v>-4.9999999999999933E-2</v>
       </c>
+      <c r="AS23" s="9">
+        <f t="shared" si="69"/>
+        <v>-4.9999999999999933E-2</v>
+      </c>
     </row>
     <row r="24" spans="2:149" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="10"/>
       <c r="D24" s="10"/>
       <c r="E24" s="10"/>
       <c r="F24" s="10"/>
       <c r="G24" s="10">
-        <f t="shared" ref="G24:P24" si="69">G5/C5-1</f>
+        <f t="shared" ref="G24:P24" si="70">G5/C5-1</f>
         <v>1.9153225806451513E-2</v>
       </c>
       <c r="H24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-1.9143576826196496E-2</v>
       </c>
       <c r="I24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-4.1884816753926746E-2</v>
       </c>
       <c r="J24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-1.1084337349397622E-2</v>
       </c>
       <c r="K24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-7.2205736894164207E-2</v>
       </c>
       <c r="L24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-6.0606060606060552E-2</v>
       </c>
       <c r="M24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-4.1287188828172283E-2</v>
       </c>
       <c r="N24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-8.3820662768031129E-2</v>
       </c>
       <c r="O24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-7.0362473347547971E-2</v>
       </c>
       <c r="P24" s="10">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-0.10825587752870425</v>
       </c>
       <c r="Q24" s="10">
-        <f t="shared" ref="Q24" si="70">Q5/M5-1</f>
+        <f t="shared" ref="Q24" si="71">Q5/M5-1</f>
         <v>-0.13489550348321733</v>
       </c>
       <c r="R24" s="10">
-        <f t="shared" ref="R24" si="71">R5/N5-1</f>
+        <f t="shared" ref="R24" si="72">R5/N5-1</f>
         <v>-0.23670212765957444</v>
       </c>
       <c r="S24" s="10">
-        <f t="shared" ref="S24" si="72">S5/O5-1</f>
+        <f t="shared" ref="S24" si="73">S5/O5-1</f>
         <v>-0.30389908256880738</v>
       </c>
       <c r="T24" s="10">
-        <f t="shared" ref="T24" si="73">T5/P5-1</f>
+        <f t="shared" ref="T24" si="74">T5/P5-1</f>
         <v>-0.35561005518087063</v>
       </c>
       <c r="U24" s="10">
-        <f t="shared" ref="U24" si="74">U5/Q5-1</f>
+        <f t="shared" ref="U24" si="75">U5/Q5-1</f>
         <v>-0.43118594436310387</v>
       </c>
       <c r="V24" s="10">
-        <f t="shared" ref="V24" si="75">V5/R5-1</f>
+        <f t="shared" ref="V24" si="76">V5/R5-1</f>
         <v>-0.49337979094076656</v>
       </c>
       <c r="W24" s="10">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>-0.49752883031301487</v>
       </c>
       <c r="X24" s="10">
-        <f t="shared" ref="X24" si="76">X5/T5-1</f>
+        <f t="shared" ref="X24" si="77">X5/T5-1</f>
         <v>-0.4018078020932444</v>
       </c>
       <c r="Y24" s="10">
-        <f t="shared" ref="Y24" si="77">Y5/U5-1</f>
+        <f t="shared" ref="Y24" si="78">Y5/U5-1</f>
         <v>-0.20849420849420852</v>
       </c>
       <c r="Z24" s="10">
-        <f t="shared" ref="Z24" si="78">Z5/V5-1</f>
+        <f t="shared" ref="Z24" si="79">Z5/V5-1</f>
         <v>-0.15364511691884464</v>
       </c>
       <c r="AB24" s="10"/>
@@ -4519,244 +4513,244 @@
         <v>0.27966365618187461</v>
       </c>
       <c r="AD24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.56802141640301773</v>
       </c>
       <c r="AE24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.20487350613068456</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-1.223753703465158E-2</v>
       </c>
       <c r="AG24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-6.5727699530516381E-2</v>
       </c>
       <c r="AH24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.13791178112786151</v>
       </c>
       <c r="AI24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.38973445595854928</v>
       </c>
       <c r="AJ24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-0.34491907667816402</v>
       </c>
       <c r="AK24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.187525313892257E-2</v>
       </c>
       <c r="AL24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>2.0321456018444373E-2</v>
       </c>
       <c r="AM24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>2.9259015817216349E-2</v>
       </c>
       <c r="AN24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.855678385039818E-2</v>
       </c>
       <c r="AO24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4.8059444617356117E-2</v>
       </c>
       <c r="AP24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.7597295066723397E-2</v>
       </c>
       <c r="AQ24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>6.6998114408873599E-2</v>
       </c>
       <c r="AR24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>7.6099408942952973E-2</v>
       </c>
       <c r="AS24" s="10">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>8.4759223059924338E-2</v>
       </c>
     </row>
     <row r="25" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:J25" si="79">C7/C5</f>
+        <f t="shared" ref="C25:J25" si="80">C7/C5</f>
         <v>0.6401209677419355</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.69420654911838797</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.60965677719604427</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.73156626506024103</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.72749752720079131</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.76527991782229077</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.72556162720097139</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>0.74951267056530213</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" ref="K25:P25" si="80">K7/K5</f>
+        <f t="shared" ref="K25:P25" si="81">K7/K5</f>
         <v>0.73773987206823022</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.74084199015855656</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.4705509816339456</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.75638297872340421</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.73337155963302758</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="80"/>
+        <f t="shared" si="81"/>
         <v>0.72164316370324955</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" ref="Q25:R25" si="81">Q7/Q5</f>
+        <f t="shared" ref="Q25:R25" si="82">Q7/Q5</f>
         <v>0.68228404099560758</v>
       </c>
       <c r="R25" s="9">
-        <f t="shared" si="81"/>
+        <f t="shared" si="82"/>
         <v>0.68222996515679446</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="82">S7/S5</f>
+        <f t="shared" ref="S25:V25" si="83">S7/S5</f>
         <v>0.55518945634266892</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.66222645099904853</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.59202059202059198</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.57359009628610735</v>
       </c>
       <c r="W25" s="9">
-        <f t="shared" ref="W25:Z25" si="83">W7/W5</f>
+        <f t="shared" ref="W25:Z25" si="84">W7/W5</f>
         <v>0.57999999999999996</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" si="83"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="83"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="83"/>
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" ref="AB25:AS25" si="84">AB7/AB5</f>
-        <v>0.7508564310183744</v>
-      </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.77561450474568028</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.68120440788452585</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.67164755893340189</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.74256651017214403</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.68453378001116694</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.70709196891191717</v>
-      </c>
-      <c r="AI25" s="9">
-        <f t="shared" si="84"/>
-        <v>0.59617935791987264</v>
-      </c>
-      <c r="AJ25" s="9">
         <f t="shared" si="84"/>
         <v>0.57999999999999996</v>
       </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="84"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="84"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" ref="AB25:AS25" si="85">AB7/AB5</f>
+        <v>0.7508564310183744</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.77561450474568028</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.68120440788452585</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.67164755893340189</v>
+      </c>
+      <c r="AF25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.74256651017214403</v>
+      </c>
+      <c r="AG25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.68453378001116694</v>
+      </c>
+      <c r="AH25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.70709196891191717</v>
+      </c>
+      <c r="AI25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.59617935791987264</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" si="85"/>
+        <v>0.57999999999999996</v>
+      </c>
       <c r="AK25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.6</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.62</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.64</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.66</v>
       </c>
       <c r="AO25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.67</v>
       </c>
       <c r="AP25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.68</v>
       </c>
       <c r="AQ25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.68</v>
       </c>
       <c r="AR25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.68</v>
       </c>
       <c r="AS25" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>0.68</v>
       </c>
       <c r="AV25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AW25" s="9">
         <v>-0.01</v>
@@ -4764,90 +4758,90 @@
     </row>
     <row r="26" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9"/>
       <c r="G26" s="9">
-        <f t="shared" ref="G26" si="85">G8/C8-1</f>
+        <f t="shared" ref="G26" si="86">G8/C8-1</f>
         <v>0.1366594360086768</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" ref="H26" si="86">H8/D8-1</f>
+        <f t="shared" ref="H26" si="87">H8/D8-1</f>
         <v>0.26201923076923062</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" ref="I26" si="87">I8/E8-1</f>
+        <f t="shared" ref="I26" si="88">I8/E8-1</f>
         <v>4.8498845265589008E-2</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" ref="J26" si="88">J8/F8-1</f>
+        <f t="shared" ref="J26" si="89">J8/F8-1</f>
         <v>-3.1380753138075312E-2</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" ref="K26:P26" si="89">K8/G8-1</f>
+        <f t="shared" ref="K26:P26" si="90">K8/G8-1</f>
         <v>-0.10496183206106868</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>7.6190476190476364E-3</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>1.7621145374449476E-2</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-1.2958963282937219E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-5.3304904051172719E-2</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>-0.17391304347826075</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" ref="Q26" si="90">Q8/M8-1</f>
+        <f t="shared" ref="Q26" si="91">Q8/M8-1</f>
         <v>-0.10606060606060619</v>
       </c>
       <c r="R26" s="9">
-        <f t="shared" ref="R26" si="91">R8/N8-1</f>
+        <f t="shared" ref="R26" si="92">R8/N8-1</f>
         <v>-0.10284463894967177</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26" si="92">S8/O8-1</f>
+        <f t="shared" ref="S26" si="93">S8/O8-1</f>
         <v>-0.33783783783783783</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" ref="T26" si="93">T8/P8-1</f>
+        <f t="shared" ref="T26" si="94">T8/P8-1</f>
         <v>-0.34324942791762014</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" ref="U26" si="94">U8/Q8-1</f>
+        <f t="shared" ref="U26" si="95">U8/Q8-1</f>
         <v>-0.55447941888619856</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" ref="V26" si="95">V8/R8-1</f>
+        <f t="shared" ref="V26" si="96">V8/R8-1</f>
         <v>-0.58536585365853666</v>
       </c>
       <c r="W26" s="9">
-        <f t="shared" ref="W26" si="96">W8/S8-1</f>
+        <f t="shared" ref="W26" si="97">W8/S8-1</f>
         <v>-0.45578231292517002</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" ref="X26" si="97">X8/T8-1</f>
+        <f t="shared" ref="X26" si="98">X8/T8-1</f>
         <v>-0.40766550522648082</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" ref="Y26" si="98">Y8/U8-1</f>
+        <f t="shared" ref="Y26" si="99">Y8/U8-1</f>
         <v>-2.1739130434782483E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26" si="99">Z8/V8-1</f>
+        <f t="shared" ref="Z26" si="100">Z8/V8-1</f>
         <v>0.11764705882352944</v>
       </c>
       <c r="AB26" s="9"/>
@@ -4856,71 +4850,71 @@
         <v>0.22309711286089251</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AS26" si="100">AD8/AC8-1</f>
+        <f t="shared" ref="AD26:AS26" si="101">AD8/AC8-1</f>
         <v>0.22246065808297555</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>4.6225863077823393E-2</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>9.9552572706935072E-2</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-2.4923702950152782E-2</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-0.11111111111111116</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-0.45129107981220651</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>-0.25133689839572193</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS26" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AW26" s="9">
         <v>0.12</v>
@@ -4928,178 +4922,178 @@
     </row>
     <row r="27" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C27" s="9">
-        <f t="shared" ref="C27:J27" si="101">C9/C5</f>
+        <f t="shared" ref="C27:J27" si="102">C9/C5</f>
         <v>0.13205645161290322</v>
       </c>
       <c r="D27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.1093198992443325</v>
       </c>
       <c r="E27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.15823152995927864</v>
       </c>
       <c r="F27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.14602409638554217</v>
       </c>
       <c r="G27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.21018793273986153</v>
       </c>
       <c r="H27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.18130457113507961</v>
       </c>
       <c r="I27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.19307832422586524</v>
       </c>
       <c r="J27" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.18567251461988304</v>
       </c>
       <c r="K27" s="9">
-        <f t="shared" ref="K27:P27" si="102">K9/K5</f>
+        <f t="shared" ref="K27:P27" si="103">K9/K5</f>
         <v>0.19722814498933902</v>
       </c>
       <c r="L27" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.16949152542372881</v>
       </c>
       <c r="M27" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.1830272324255858</v>
       </c>
       <c r="N27" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.15797872340425531</v>
       </c>
       <c r="O27" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.17431192660550457</v>
       </c>
       <c r="P27" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.14408338442673208</v>
       </c>
       <c r="Q27" s="9">
-        <f t="shared" ref="Q27:R27" si="103">Q9/Q5</f>
+        <f t="shared" ref="Q27:R27" si="104">Q9/Q5</f>
         <v>0.19399707174231334</v>
       </c>
       <c r="R27" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.19442508710801393</v>
       </c>
       <c r="S27" s="9">
-        <f t="shared" ref="S27:V27" si="104">S9/S5</f>
+        <f t="shared" ref="S27:V27" si="105">S9/S5</f>
         <v>0.21087314662273476</v>
       </c>
       <c r="T27" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.16555661274976213</v>
       </c>
       <c r="U27" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.14929214929214929</v>
       </c>
       <c r="V27" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.19394773039889956</v>
       </c>
       <c r="W27" s="9">
-        <f t="shared" ref="W27:Z27" si="105">W9/W5</f>
+        <f t="shared" ref="W27:Z27" si="106">W9/W5</f>
         <v>0.17</v>
       </c>
       <c r="X27" s="9">
-        <f t="shared" si="105"/>
-        <v>0.18</v>
-      </c>
-      <c r="Y27" s="9">
-        <f t="shared" si="105"/>
-        <v>0.19</v>
-      </c>
-      <c r="Z27" s="9">
-        <f t="shared" si="105"/>
-        <v>0.19</v>
-      </c>
-      <c r="AB27" s="9">
-        <f t="shared" ref="AB27:AS27" si="106">AB9/AB5</f>
-        <v>0.17035191529118654</v>
-      </c>
-      <c r="AC27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.15478218544658068</v>
-      </c>
-      <c r="AD27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.12711469812199289</v>
-      </c>
-      <c r="AE27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.13577225299497617</v>
-      </c>
-      <c r="AF27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.1926186750130412</v>
-      </c>
-      <c r="AG27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.17671691792294808</v>
-      </c>
-      <c r="AH27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.17535621761658032</v>
-      </c>
-      <c r="AI27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.18227646590607591</v>
-      </c>
-      <c r="AJ27" s="9">
-        <f t="shared" si="106"/>
-        <v>0.18251235317942488</v>
-      </c>
-      <c r="AK27" s="9">
         <f t="shared" si="106"/>
         <v>0.18</v>
       </c>
+      <c r="Y27" s="9">
+        <f t="shared" si="106"/>
+        <v>0.19</v>
+      </c>
+      <c r="Z27" s="9">
+        <f t="shared" si="106"/>
+        <v>0.19</v>
+      </c>
+      <c r="AB27" s="9">
+        <f t="shared" ref="AB27:AS27" si="107">AB9/AB5</f>
+        <v>0.17035191529118654</v>
+      </c>
+      <c r="AC27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.15478218544658068</v>
+      </c>
+      <c r="AD27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.12711469812199289</v>
+      </c>
+      <c r="AE27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.13577225299497617</v>
+      </c>
+      <c r="AF27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.1926186750130412</v>
+      </c>
+      <c r="AG27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.17671691792294808</v>
+      </c>
+      <c r="AH27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.17535621761658032</v>
+      </c>
+      <c r="AI27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.18227646590607591</v>
+      </c>
+      <c r="AJ27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.18251235317942488</v>
+      </c>
+      <c r="AK27" s="9">
+        <f t="shared" si="107"/>
+        <v>0.18</v>
+      </c>
       <c r="AL27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AM27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AN27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AO27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AP27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AQ27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AR27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18</v>
       </c>
       <c r="AS27" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.18000000000000002</v>
       </c>
       <c r="AV27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AW27" s="2">
         <f>NPV(AW26,AJ18:ES18)</f>
@@ -5108,90 +5102,90 @@
     </row>
     <row r="28" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9"/>
       <c r="G28" s="9">
-        <f t="shared" ref="G28" si="107">G10/C10-1</f>
+        <f t="shared" ref="G28" si="108">G10/C10-1</f>
         <v>0.23746701846965701</v>
       </c>
       <c r="H28" s="9">
-        <f t="shared" ref="H28" si="108">H10/D10-1</f>
+        <f t="shared" ref="H28" si="109">H10/D10-1</f>
         <v>0.35768261964735504</v>
       </c>
       <c r="I28" s="9">
-        <f t="shared" ref="I28" si="109">I10/E10-1</f>
+        <f t="shared" ref="I28" si="110">I10/E10-1</f>
         <v>0.57941176470588251</v>
       </c>
       <c r="J28" s="9">
-        <f t="shared" ref="J28" si="110">J10/F10-1</f>
+        <f t="shared" ref="J28" si="111">J10/F10-1</f>
         <v>0.29894736842105263</v>
       </c>
       <c r="K28" s="9">
-        <f t="shared" ref="K28:P28" si="111">K10/G10-1</f>
+        <f t="shared" ref="K28:P28" si="112">K10/G10-1</f>
         <v>0.25799573560767586</v>
       </c>
       <c r="L28" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.30426716141001853</v>
       </c>
       <c r="M28" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>6.3314711359404141E-2</v>
       </c>
       <c r="N28" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-0.1345218800648299</v>
       </c>
       <c r="O28" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-5.9322033898305038E-2</v>
       </c>
       <c r="P28" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>-0.2318634423897582</v>
       </c>
       <c r="Q28" s="9">
-        <f t="shared" ref="Q28" si="112">Q10/M10-1</f>
+        <f t="shared" ref="Q28" si="113">Q10/M10-1</f>
         <v>-9.1068301225919468E-2</v>
       </c>
       <c r="R28" s="9">
-        <f t="shared" ref="R28" si="113">R10/N10-1</f>
+        <f t="shared" ref="R28" si="114">R10/N10-1</f>
         <v>5.4307116104868935E-2</v>
       </c>
       <c r="S28" s="9">
-        <f t="shared" ref="S28" si="114">S10/O10-1</f>
+        <f t="shared" ref="S28" si="115">S10/O10-1</f>
         <v>-0.29009009009009012</v>
       </c>
       <c r="T28" s="9">
-        <f t="shared" ref="T28" si="115">T10/P10-1</f>
+        <f t="shared" ref="T28" si="116">T10/P10-1</f>
         <v>0.11111111111111116</v>
       </c>
       <c r="U28" s="9">
-        <f t="shared" ref="U28" si="116">U10/Q10-1</f>
+        <f t="shared" ref="U28" si="117">U10/Q10-1</f>
         <v>-0.36030828516377644</v>
       </c>
       <c r="V28" s="9">
-        <f t="shared" ref="V28" si="117">V10/R10-1</f>
+        <f t="shared" ref="V28" si="118">V10/R10-1</f>
         <v>-0.20426287744227356</v>
       </c>
       <c r="W28" s="9">
-        <f t="shared" ref="W28" si="118">W10/S10-1</f>
+        <f t="shared" ref="W28" si="119">W10/S10-1</f>
         <v>-0.23857868020304562</v>
       </c>
       <c r="X28" s="9">
-        <f t="shared" ref="X28" si="119">X10/T10-1</f>
+        <f t="shared" ref="X28" si="120">X10/T10-1</f>
         <v>-0.48333333333333328</v>
       </c>
       <c r="Y28" s="9">
-        <f t="shared" ref="Y28" si="120">Y10/U10-1</f>
+        <f t="shared" ref="Y28" si="121">Y10/U10-1</f>
         <v>-3.6144578313253128E-2</v>
       </c>
       <c r="Z28" s="9">
-        <f t="shared" ref="Z28" si="121">Z10/V10-1</f>
+        <f t="shared" ref="Z28" si="122">Z10/V10-1</f>
         <v>-0.2857142857142857</v>
       </c>
       <c r="AB28" s="9"/>
@@ -5200,71 +5194,71 @@
         <v>0.25482625482625476</v>
       </c>
       <c r="AD28" s="9">
-        <f t="shared" ref="AD28:AS28" si="122">AD10/AC10-1</f>
+        <f t="shared" ref="AD28:AS28" si="123">AD10/AC10-1</f>
         <v>0.32615384615384624</v>
       </c>
       <c r="AE28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.23047177107501926</v>
       </c>
       <c r="AF28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.35889377749842866</v>
       </c>
       <c r="AG28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.10915818686401502</v>
       </c>
       <c r="AH28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-9.2160133444537218E-2</v>
       </c>
       <c r="AI28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.18511713367018812</v>
       </c>
       <c r="AJ28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.29537767756482536</v>
       </c>
       <c r="AK28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.19999999999999996</v>
       </c>
       <c r="AL28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AO28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AP28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AR28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AS28" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AW28" s="2">
         <f>Main!D8</f>
@@ -5273,178 +5267,178 @@
     </row>
     <row r="29" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="9">
-        <f t="shared" ref="C29:J29" si="123">C13/C5</f>
+        <f t="shared" ref="C29:J29" si="124">C13/C5</f>
         <v>8.4677419354838759E-2</v>
       </c>
       <c r="D29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.17531486146095723</v>
       </c>
       <c r="E29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>1.7452006980803454E-3</v>
       </c>
       <c r="F29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.12626506024096393</v>
       </c>
       <c r="G29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>2.6211671612265001E-2</v>
       </c>
       <c r="H29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>3.7493579866461284E-2</v>
       </c>
       <c r="I29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>-6.9216757741348028E-2</v>
       </c>
       <c r="J29" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>3.7524366471734703E-2</v>
       </c>
       <c r="K29" s="9">
-        <f t="shared" ref="K29:P29" si="124">K13/K5</f>
+        <f t="shared" ref="K29:P29" si="125">K13/K5</f>
         <v>-2.3987206823027872E-2</v>
       </c>
       <c r="L29" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>-0.1022416621104428</v>
       </c>
       <c r="M29" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>-0.36668777707409739</v>
       </c>
       <c r="N29" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>7.1276595744680732E-2</v>
       </c>
       <c r="O29" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>-1.3761467889908289E-2</v>
       </c>
       <c r="P29" s="9">
-        <f t="shared" si="124"/>
-        <v>-2.1459227467811245E-2</v>
+        <f t="shared" si="125"/>
+        <v>-2.9736358062538324</v>
       </c>
       <c r="Q29" s="9">
-        <f t="shared" ref="Q29:R29" si="125">Q13/Q5</f>
-        <v>-0.19399707174231334</v>
+        <f t="shared" ref="Q29:R29" si="126">Q13/Q5</f>
+        <v>-1.6266471449487554</v>
       </c>
       <c r="R29" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-0.19024390243902436</v>
       </c>
       <c r="S29" s="9">
-        <f t="shared" ref="S29:V29" si="126">S13/S5</f>
+        <f t="shared" ref="S29:V29" si="127">S13/S5</f>
         <v>-0.23887973640856672</v>
       </c>
       <c r="T29" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>-0.34728829686013324</v>
       </c>
       <c r="U29" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>-0.2213642213642214</v>
       </c>
       <c r="V29" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>-0.47042640990371393</v>
       </c>
       <c r="W29" s="9">
-        <f t="shared" ref="W29:Z29" si="127">W13/W5</f>
+        <f t="shared" ref="W29:Z29" si="128">W13/W5</f>
         <v>-0.34409836065573784</v>
       </c>
       <c r="X29" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-0.36348019723238434</v>
       </c>
       <c r="Y29" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-0.42300813008130095</v>
       </c>
       <c r="Z29" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-0.43886396879570949</v>
       </c>
       <c r="AB29" s="9">
-        <f t="shared" ref="AB29:AS29" si="128">AB13/AB5</f>
+        <f t="shared" ref="AB29:AS29" si="129">AB13/AB5</f>
         <v>-1.7440049828713691E-2</v>
       </c>
       <c r="AC29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>4.3319542467753741E-2</v>
       </c>
       <c r="AD29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>8.8157690516839915E-2</v>
       </c>
       <c r="AE29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.10060543604276687</v>
       </c>
       <c r="AF29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>1.1606677099634817E-2</v>
       </c>
       <c r="AG29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-9.4500279173646076E-2</v>
       </c>
       <c r="AH29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-9.6664507772020611E-2</v>
       </c>
       <c r="AI29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.31016184664367219</v>
       </c>
       <c r="AJ29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.39230579181855013</v>
       </c>
       <c r="AK29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.26606103301418571</v>
       </c>
       <c r="AL29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.24584488696846479</v>
       </c>
       <c r="AM29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.21967515849486396</v>
       </c>
       <c r="AN29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.18753082011991856</v>
       </c>
       <c r="AO29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.15328996965173922</v>
       </c>
       <c r="AP29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-0.11433862622281565</v>
       </c>
       <c r="AQ29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-8.1521189312313239E-2</v>
       </c>
       <c r="AR29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-4.5801248773450959E-2</v>
       </c>
       <c r="AS29" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>-8.1858255200405131E-3</v>
       </c>
       <c r="AV29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AW29" s="2">
         <f>AW27+AW28</f>
@@ -5456,175 +5450,175 @@
         <v>38</v>
       </c>
       <c r="C30" s="9">
-        <f t="shared" ref="C30:J30" si="129">C17/C16</f>
+        <f t="shared" ref="C30:J30" si="130">C17/C16</f>
         <v>-4.4943820224719107E-2</v>
       </c>
       <c r="D30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>6.2857142857142848E-2</v>
       </c>
       <c r="E30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>9.4594594594594447E-2</v>
       </c>
       <c r="F30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>5.4474708171206185E-2</v>
       </c>
       <c r="G30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.42424242424242503</v>
       </c>
       <c r="H30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>1.3333333333333313E-2</v>
       </c>
       <c r="I30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>-1.9822274881516595</v>
       </c>
       <c r="J30" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>0.13636363636363882</v>
       </c>
       <c r="K30" s="9">
-        <f t="shared" ref="K30:P30" si="130">K17/K16</f>
+        <f t="shared" ref="K30:P30" si="131">K17/K16</f>
         <v>0.66666666666666974</v>
       </c>
       <c r="L30" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.44469525959367939</v>
       </c>
       <c r="M30" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>-1.1049723756906091E-2</v>
       </c>
       <c r="N30" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>0.45505617977528151</v>
       </c>
       <c r="O30" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>1.1818181818181825</v>
       </c>
       <c r="P30" s="9">
-        <f t="shared" si="130"/>
-        <v>2.8965517241379479</v>
+        <f t="shared" si="131"/>
+        <v>-0.28896782281654826</v>
       </c>
       <c r="Q30" s="9">
-        <f t="shared" ref="Q30:R30" si="131">Q17/Q16</f>
-        <v>0.13775510204081631</v>
+        <f t="shared" ref="Q30:R30" si="132">Q17/Q16</f>
+        <v>1.2540640966093825E-2</v>
       </c>
       <c r="R30" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>-1.9047619047619067</v>
       </c>
       <c r="S30" s="9">
-        <f t="shared" ref="S30:V30" si="132">S17/S16</f>
+        <f t="shared" ref="S30:V30" si="133">S17/S16</f>
         <v>-6.0606060606060608E-2</v>
       </c>
       <c r="T30" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-3.4883720930232558E-2</v>
       </c>
       <c r="U30" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.10759493670886074</v>
       </c>
       <c r="V30" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>1.8018018018018014E-2</v>
       </c>
       <c r="W30" s="9">
-        <f t="shared" ref="W30:Z30" si="133">W17/W16</f>
+        <f t="shared" ref="W30:Z30" si="134">W17/W16</f>
         <v>0.05</v>
       </c>
       <c r="X30" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.05</v>
       </c>
       <c r="Y30" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.05</v>
       </c>
       <c r="Z30" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.05</v>
       </c>
       <c r="AB30" s="9">
-        <f t="shared" ref="AB30:AS30" si="134">AB17/AB16</f>
+        <f t="shared" ref="AB30:AS30" si="135">AB17/AB16</f>
         <v>-0.10937500000000029</v>
       </c>
       <c r="AC30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>-0.37142857142857222</v>
       </c>
       <c r="AD30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>-6.749999999999635</v>
       </c>
       <c r="AE30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>1.2241379310345013</v>
       </c>
       <c r="AF30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>-1.5644230769230771</v>
       </c>
       <c r="AG30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.64015904572564675</v>
       </c>
       <c r="AH30" s="9">
-        <f t="shared" si="134"/>
-        <v>-1.6936936936937039</v>
+        <f t="shared" si="135"/>
+        <v>-13.396396396396474</v>
       </c>
       <c r="AI30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>-3.2999999999999995E-2</v>
       </c>
       <c r="AJ30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>5.000000000000001E-2</v>
       </c>
       <c r="AK30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AL30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AM30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AN30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AO30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AP30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AQ30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AR30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AS30" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>0.15</v>
       </c>
       <c r="AV30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AW30" s="3">
         <f>AW29/AS19</f>
@@ -5633,178 +5627,178 @@
     </row>
     <row r="31" spans="2:149" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C31" s="9">
-        <f t="shared" ref="C31:J31" si="135">C18/C5</f>
+        <f t="shared" ref="C31:J31" si="136">C18/C5</f>
         <v>-0.32812499999999994</v>
       </c>
       <c r="D31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.16523929471032747</v>
       </c>
       <c r="E31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>3.8976148923792968E-2</v>
       </c>
       <c r="F31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>0.11710843373493984</v>
       </c>
       <c r="G31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>2.8189910979228402E-2</v>
       </c>
       <c r="H31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>3.8007190549563495E-2</v>
       </c>
       <c r="I31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>1.5282331511839709</v>
       </c>
       <c r="J31" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>9.2592592592590662E-3</v>
       </c>
       <c r="K31" s="9">
-        <f t="shared" ref="K31:P31" si="136">K18/K5</f>
+        <f t="shared" ref="K31:P31" si="137">K18/K5</f>
         <v>1.1194029850746115E-2</v>
       </c>
       <c r="L31" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.13449972662657192</v>
       </c>
       <c r="M31" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>-0.11589613679544002</v>
       </c>
       <c r="N31" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>5.1595744680850937E-2</v>
       </c>
       <c r="O31" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>-8.027522935779843E-3</v>
       </c>
       <c r="P31" s="9">
-        <f t="shared" si="136"/>
-        <v>-3.3721643163703373E-2</v>
+        <f t="shared" si="137"/>
+        <v>-3.782342121397916</v>
       </c>
       <c r="Q31" s="9">
-        <f t="shared" ref="Q31:R31" si="137">Q18/Q5</f>
-        <v>-0.12371888726207908</v>
+        <f t="shared" ref="Q31:R31" si="138">Q18/Q5</f>
+        <v>-1.5563689604685214</v>
       </c>
       <c r="R31" s="9">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>-4.2508710801393713E-2</v>
       </c>
       <c r="S31" s="9">
-        <f t="shared" ref="S31:V31" si="138">S18/S5</f>
+        <f t="shared" ref="S31:V31" si="139">S18/S5</f>
         <v>-0.1441515650741351</v>
       </c>
       <c r="T31" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>-0.33872502378686969</v>
       </c>
       <c r="U31" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>-0.22522522522522526</v>
       </c>
       <c r="V31" s="9">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>-0.44979367262723524</v>
       </c>
       <c r="W31" s="9">
-        <f t="shared" ref="W31:Z31" si="139">W18/W5</f>
+        <f t="shared" ref="W31:Z31" si="140">W18/W5</f>
         <v>-0.3113196721311477</v>
       </c>
       <c r="X31" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>-0.33019564180054084</v>
       </c>
       <c r="Y31" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>-0.38641056910569116</v>
       </c>
       <c r="Z31" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>-0.40148114740776863</v>
       </c>
       <c r="AB31" s="9">
-        <f t="shared" ref="AB31:AS31" si="140">AB18/AB5</f>
+        <f t="shared" ref="AB31:AS31" si="141">AB18/AB5</f>
         <v>-4.4222983494238442E-2</v>
       </c>
       <c r="AC31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-2.3363348746653651E-2</v>
       </c>
       <c r="AD31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-9.6228465000776729E-3</v>
       </c>
       <c r="AE31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-1.674610331057694E-3</v>
       </c>
       <c r="AF31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>0.34780907668231603</v>
       </c>
       <c r="AG31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>2.5265214963707351E-2</v>
       </c>
       <c r="AH31" s="9">
-        <f t="shared" si="140"/>
-        <v>-4.8413212435233069E-2</v>
+        <f t="shared" si="141"/>
+        <v>-0.2587435233160621</v>
       </c>
       <c r="AI31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.27407800477580269</v>
       </c>
       <c r="AJ31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.35729965573106531</v>
       </c>
       <c r="AK31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.21213445835601541</v>
       </c>
       <c r="AL31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.19481776806973639</v>
       </c>
       <c r="AM31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.17256331172095055</v>
       </c>
       <c r="AN31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.14535729462449501</v>
       </c>
       <c r="AO31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-0.11649456666328527</v>
       </c>
       <c r="AP31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-8.3746076307957149E-2</v>
       </c>
       <c r="AQ31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-5.6317347253164937E-2</v>
       </c>
       <c r="AR31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>-2.6511266909549795E-2</v>
       </c>
       <c r="AS31" s="9">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>4.8348850152994125E-3</v>
       </c>
       <c r="AV31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AW31" s="3">
         <f>Main!D3</f>
@@ -5813,7 +5807,7 @@
     </row>
     <row r="32" spans="2:149" x14ac:dyDescent="0.3">
       <c r="AV32" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AW32" s="10">
         <f>AW30/AW31-1</f>
@@ -5822,15 +5816,51 @@
     </row>
     <row r="33" spans="2:49" x14ac:dyDescent="0.3">
       <c r="AV33" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AW33" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="2:49" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="O34" s="8">
+        <f>O18</f>
+        <v>-1.4000000000000048</v>
+      </c>
+      <c r="P34" s="8">
+        <f t="shared" ref="P34:W34" si="142">P18</f>
+        <v>-616.90000000000009</v>
+      </c>
+      <c r="Q34" s="8">
+        <f t="shared" si="142"/>
+        <v>-212.6</v>
+      </c>
+      <c r="R34" s="8">
+        <f t="shared" ref="R34" si="143">R18</f>
+        <v>-6.0999999999999979</v>
+      </c>
+      <c r="S34" s="8">
+        <f t="shared" si="142"/>
+        <v>-17.5</v>
+      </c>
+      <c r="T34" s="8">
+        <f t="shared" si="142"/>
+        <v>-35.6</v>
+      </c>
+      <c r="U34" s="8">
+        <f t="shared" si="142"/>
+        <v>-17.500000000000004</v>
+      </c>
+      <c r="V34" s="8">
+        <f t="shared" si="142"/>
+        <v>-32.700000000000003</v>
+      </c>
+      <c r="W34" s="8">
+        <f t="shared" si="142"/>
+        <v>-18.990500000000008</v>
       </c>
       <c r="AF34" s="8">
         <f>AF18</f>
@@ -5848,49 +5878,82 @@
         <v>-103.30000000000003</v>
       </c>
       <c r="AJ34" s="8">
-        <f t="shared" ref="AJ34:AS34" si="141">AJ18</f>
+        <f t="shared" ref="AJ34:AS34" si="144">AJ18</f>
         <v>-88.217285000000018</v>
       </c>
       <c r="AK34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-52.99797600000003</v>
       </c>
       <c r="AL34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-49.660792700000016</v>
       </c>
       <c r="AM34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-45.274976215000045</v>
       </c>
       <c r="AN34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-39.607446311000054</v>
       </c>
       <c r="AO34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-33.268375679717558</v>
       </c>
       <c r="AP34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-25.293604688873781</v>
       </c>
       <c r="AQ34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-18.148974898066768</v>
       </c>
       <c r="AR34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>-9.1937520124143877</v>
       </c>
       <c r="AS34" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="144"/>
         <v>1.8187868451690734</v>
       </c>
     </row>
     <row r="35" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="O35" s="2">
+        <v>29.3</v>
+      </c>
+      <c r="P35" s="2">
+        <f>P63-O35</f>
+        <v>17.999999999999996</v>
+      </c>
+      <c r="Q35" s="2">
+        <f>Q63-P63</f>
+        <v>22</v>
+      </c>
+      <c r="R35" s="2">
+        <f>AH35-Q63</f>
+        <v>15.299999999999997</v>
+      </c>
+      <c r="S35" s="2">
+        <v>11.3</v>
+      </c>
+      <c r="T35" s="2">
+        <f>T63-S35</f>
+        <v>7.8999999999999986</v>
+      </c>
+      <c r="U35" s="2">
+        <f t="shared" ref="U35:U56" si="145">U63-T63</f>
+        <v>5.9000000000000021</v>
+      </c>
+      <c r="V35" s="2">
+        <f>AI35-U63</f>
+        <v>6.7999999999999972</v>
+      </c>
+      <c r="W35">
+        <v>2.9</v>
       </c>
       <c r="AF35" s="2">
         <v>133.5</v>
@@ -5912,41 +5975,74 @@
         <v>20.2</v>
       </c>
       <c r="AL35" s="2">
-        <f t="shared" ref="AL35:AS35" si="142">AK35*1.01</f>
+        <f t="shared" ref="AL35:AS36" si="146">AK35*1.01</f>
         <v>20.402000000000001</v>
       </c>
       <c r="AM35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>20.606020000000001</v>
       </c>
       <c r="AN35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>20.8120802</v>
       </c>
       <c r="AO35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>21.020201002</v>
       </c>
       <c r="AP35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>21.230403012020002</v>
       </c>
       <c r="AQ35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>21.442707042140203</v>
       </c>
       <c r="AR35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>21.657134112561604</v>
       </c>
       <c r="AS35" s="2">
-        <f t="shared" si="142"/>
+        <f t="shared" si="146"/>
         <v>21.873705453687219</v>
       </c>
     </row>
     <row r="36" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="O36" s="2">
+        <v>19.7</v>
+      </c>
+      <c r="P36" s="2">
+        <f t="shared" ref="P36:P56" si="147">P64-O36</f>
+        <v>19.7</v>
+      </c>
+      <c r="Q36" s="2">
+        <f t="shared" ref="Q36:Q58" si="148">Q64-P64</f>
+        <v>19.600000000000001</v>
+      </c>
+      <c r="R36" s="2">
+        <f t="shared" ref="R36:R56" si="149">AH36-Q64</f>
+        <v>19.299999999999997</v>
+      </c>
+      <c r="S36" s="2">
+        <v>32.1</v>
+      </c>
+      <c r="T36" s="2">
+        <f t="shared" ref="T36:T56" si="150">T64-S36</f>
+        <v>16.199999999999996</v>
+      </c>
+      <c r="U36" s="2">
+        <f t="shared" si="145"/>
+        <v>15.300000000000004</v>
+      </c>
+      <c r="V36" s="2">
+        <f t="shared" ref="V36:V56" si="151">AI36-U64</f>
+        <v>14.999999999999993</v>
+      </c>
+      <c r="W36">
+        <v>14</v>
       </c>
       <c r="AF36" s="2">
         <v>90</v>
@@ -5961,48 +6057,78 @@
         <v>78.599999999999994</v>
       </c>
       <c r="AJ36" s="2">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AK36" s="2">
-        <f>AJ36*1.02</f>
-        <v>40.799999999999997</v>
+        <f>AJ36*1.01</f>
+        <v>60.6</v>
       </c>
       <c r="AL36" s="2">
-        <f t="shared" ref="AL36:AS36" si="143">AK36*1.02</f>
-        <v>41.616</v>
+        <f t="shared" si="146"/>
+        <v>61.206000000000003</v>
       </c>
       <c r="AM36" s="2">
-        <f t="shared" si="143"/>
-        <v>42.448320000000002</v>
+        <f t="shared" si="146"/>
+        <v>61.818060000000003</v>
       </c>
       <c r="AN36" s="2">
-        <f t="shared" si="143"/>
-        <v>43.297286400000004</v>
+        <f t="shared" si="146"/>
+        <v>62.436240600000005</v>
       </c>
       <c r="AO36" s="2">
-        <f t="shared" si="143"/>
-        <v>44.163232128000004</v>
+        <f t="shared" si="146"/>
+        <v>63.060603006000008</v>
       </c>
       <c r="AP36" s="2">
-        <f t="shared" si="143"/>
-        <v>45.046496770560005</v>
+        <f t="shared" si="146"/>
+        <v>63.691209036060009</v>
       </c>
       <c r="AQ36" s="2">
-        <f t="shared" si="143"/>
-        <v>45.947426705971203</v>
+        <f t="shared" si="146"/>
+        <v>64.328121126420612</v>
       </c>
       <c r="AR36" s="2">
-        <f t="shared" si="143"/>
-        <v>46.866375240090626</v>
+        <f t="shared" si="146"/>
+        <v>64.971402337684822</v>
       </c>
       <c r="AS36" s="2">
-        <f t="shared" si="143"/>
-        <v>47.803702744892441</v>
+        <f t="shared" si="146"/>
+        <v>65.621116361061667</v>
       </c>
     </row>
     <row r="37" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
-        <v>65</v>
+        <v>64</v>
+      </c>
+      <c r="O37" s="2">
+        <v>2.9</v>
+      </c>
+      <c r="P37" s="2">
+        <f t="shared" si="147"/>
+        <v>138.1</v>
+      </c>
+      <c r="Q37" s="2">
+        <f t="shared" si="148"/>
+        <v>9.9999999999994316E-2</v>
+      </c>
+      <c r="R37" s="2">
+        <f t="shared" si="149"/>
+        <v>2.2000000000000171</v>
+      </c>
+      <c r="S37" s="2">
+        <v>0</v>
+      </c>
+      <c r="T37" s="2">
+        <f t="shared" si="150"/>
+        <v>0.1</v>
+      </c>
+      <c r="U37" s="2">
+        <f t="shared" si="145"/>
+        <v>0.19999999999999998</v>
+      </c>
+      <c r="V37" s="2">
+        <f t="shared" si="151"/>
+        <v>0.7</v>
       </c>
       <c r="AF37" s="2">
         <v>-168.9</v>
@@ -6049,7 +6175,37 @@
     </row>
     <row r="38" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
-        <v>66</v>
+        <v>65</v>
+      </c>
+      <c r="O38" s="2">
+        <v>0</v>
+      </c>
+      <c r="P38" s="2">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="Q38" s="2">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="R38" s="2">
+        <f t="shared" si="149"/>
+        <v>-19.5</v>
+      </c>
+      <c r="S38" s="2">
+        <v>-7.4</v>
+      </c>
+      <c r="T38" s="2">
+        <f t="shared" si="150"/>
+        <v>0</v>
+      </c>
+      <c r="U38" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V38" s="2">
+        <f t="shared" si="151"/>
+        <v>-0.39999999999999947</v>
       </c>
       <c r="AF38" s="2">
         <v>-93.5</v>
@@ -6096,7 +6252,37 @@
     </row>
     <row r="39" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
-        <v>67</v>
+        <v>66</v>
+      </c>
+      <c r="O39" s="2">
+        <v>0</v>
+      </c>
+      <c r="P39" s="2">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="2">
+        <f t="shared" si="148"/>
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="R39" s="2">
+        <f t="shared" si="149"/>
+        <v>-5.0999999999999996</v>
+      </c>
+      <c r="S39" s="2">
+        <v>0</v>
+      </c>
+      <c r="T39" s="2">
+        <f t="shared" si="150"/>
+        <v>7.5</v>
+      </c>
+      <c r="U39" s="2">
+        <f t="shared" si="145"/>
+        <v>-7.5</v>
+      </c>
+      <c r="V39" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF39" s="2">
         <v>0</v>
@@ -6143,7 +6329,37 @@
     </row>
     <row r="40" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="O40" s="2">
+        <v>0</v>
+      </c>
+      <c r="P40" s="2">
+        <f t="shared" si="147"/>
+        <v>481.5</v>
+      </c>
+      <c r="Q40" s="2">
+        <f t="shared" si="148"/>
+        <v>195.70000000000005</v>
+      </c>
+      <c r="R40" s="2">
+        <f t="shared" si="149"/>
+        <v>0</v>
+      </c>
+      <c r="S40" s="2">
+        <v>0</v>
+      </c>
+      <c r="T40" s="2">
+        <f t="shared" si="150"/>
+        <v>2</v>
+      </c>
+      <c r="U40" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V40" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF40" s="2">
         <v>0</v>
@@ -6190,7 +6406,37 @@
     </row>
     <row r="41" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="O41" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P41" s="2">
+        <f t="shared" si="147"/>
+        <v>1.2</v>
+      </c>
+      <c r="Q41" s="2">
+        <f t="shared" si="148"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="R41" s="2">
+        <f t="shared" si="149"/>
+        <v>3.8</v>
+      </c>
+      <c r="S41" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="T41" s="2">
+        <f t="shared" si="150"/>
+        <v>-1.6999999999999997</v>
+      </c>
+      <c r="U41" s="2">
+        <f t="shared" si="145"/>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="V41" s="2">
+        <f t="shared" si="151"/>
+        <v>1.2</v>
       </c>
       <c r="AF41" s="2">
         <v>3.5</v>
@@ -6205,39 +6451,69 @@
         <v>2</v>
       </c>
       <c r="AJ41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AK41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AL41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AM41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AN41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AO41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AP41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AQ41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AR41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AS41" s="2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
-        <v>70</v>
+        <v>69</v>
+      </c>
+      <c r="O42" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="P42" s="2">
+        <f t="shared" si="147"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="Q42" s="2">
+        <f t="shared" si="148"/>
+        <v>0.5</v>
+      </c>
+      <c r="R42" s="2">
+        <f t="shared" si="149"/>
+        <v>0.5</v>
+      </c>
+      <c r="S42" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="T42" s="2">
+        <f t="shared" si="150"/>
+        <v>0</v>
+      </c>
+      <c r="U42" s="2">
+        <f t="shared" si="145"/>
+        <v>9.9999999999999978E-2</v>
+      </c>
+      <c r="V42" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF42" s="2">
         <v>5.2</v>
@@ -6252,39 +6528,69 @@
         <v>0.5</v>
       </c>
       <c r="AJ42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AM42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AN42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AP42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AQ42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AR42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS42" s="2">
-        <v>2.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
-        <v>71</v>
+        <v>70</v>
+      </c>
+      <c r="O43" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="P43" s="2">
+        <f t="shared" si="147"/>
+        <v>1.5</v>
+      </c>
+      <c r="Q43" s="2">
+        <f t="shared" si="148"/>
+        <v>1.4999999999999996</v>
+      </c>
+      <c r="R43" s="2">
+        <f t="shared" si="149"/>
+        <v>1.3000000000000007</v>
+      </c>
+      <c r="S43" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="T43" s="2">
+        <f t="shared" si="150"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="U43" s="2">
+        <f t="shared" si="145"/>
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="V43" s="2">
+        <f t="shared" si="151"/>
+        <v>0.70000000000000018</v>
       </c>
       <c r="AF43" s="2">
         <v>6.3</v>
@@ -6331,7 +6637,37 @@
     </row>
     <row r="44" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>72</v>
+        <v>71</v>
+      </c>
+      <c r="O44" s="2">
+        <v>0</v>
+      </c>
+      <c r="P44" s="2">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="Q44" s="2">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="R44" s="2">
+        <f t="shared" si="149"/>
+        <v>0</v>
+      </c>
+      <c r="S44" s="2">
+        <v>0</v>
+      </c>
+      <c r="T44" s="2">
+        <f t="shared" si="150"/>
+        <v>0</v>
+      </c>
+      <c r="U44" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V44" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF44" s="2">
         <v>9.6999999999999993</v>
@@ -6378,7 +6714,37 @@
     </row>
     <row r="45" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
-        <v>73</v>
+        <v>72</v>
+      </c>
+      <c r="O45" s="2">
+        <v>0</v>
+      </c>
+      <c r="P45" s="2">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="Q45" s="2">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="R45" s="2">
+        <f t="shared" si="149"/>
+        <v>0</v>
+      </c>
+      <c r="S45" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="T45" s="2">
+        <f t="shared" si="150"/>
+        <v>0</v>
+      </c>
+      <c r="U45" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V45" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF45" s="2">
         <v>-5</v>
@@ -6425,7 +6791,37 @@
     </row>
     <row r="46" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="O46" s="2">
+        <v>0</v>
+      </c>
+      <c r="P46" s="2">
+        <f t="shared" si="147"/>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q46" s="2">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="R46" s="2">
+        <f t="shared" si="149"/>
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="S46" s="2">
+        <v>0</v>
+      </c>
+      <c r="T46" s="2">
+        <f t="shared" si="150"/>
+        <v>3</v>
+      </c>
+      <c r="U46" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V46" s="2">
+        <f t="shared" si="151"/>
+        <v>4.3</v>
       </c>
       <c r="AF46" s="2">
         <v>1.6</v>
@@ -6472,7 +6868,37 @@
     </row>
     <row r="47" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="O47" s="2">
+        <v>0</v>
+      </c>
+      <c r="P47" s="2">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="Q47" s="2">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="R47" s="2">
+        <f t="shared" si="149"/>
+        <v>0</v>
+      </c>
+      <c r="S47" s="2">
+        <v>0</v>
+      </c>
+      <c r="T47" s="2">
+        <f t="shared" si="150"/>
+        <v>0</v>
+      </c>
+      <c r="U47" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V47" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF47" s="2">
         <v>-4.5999999999999996</v>
@@ -6519,7 +6945,37 @@
     </row>
     <row r="48" spans="2:49" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="O48" s="2">
+        <v>0</v>
+      </c>
+      <c r="P48" s="2">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="Q48" s="2">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="R48" s="2">
+        <f t="shared" si="149"/>
+        <v>5.6</v>
+      </c>
+      <c r="S48" s="2">
+        <v>0</v>
+      </c>
+      <c r="T48" s="2">
+        <f t="shared" si="150"/>
+        <v>6</v>
+      </c>
+      <c r="U48" s="2">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="V48" s="2">
+        <f t="shared" si="151"/>
+        <v>0</v>
       </c>
       <c r="AF48" s="2">
         <v>5.2</v>
@@ -6566,7 +7022,37 @@
     </row>
     <row r="49" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="O49" s="2">
+        <v>0</v>
+      </c>
+      <c r="P49" s="2">
+        <f t="shared" si="147"/>
+        <v>0.1</v>
+      </c>
+      <c r="Q49" s="2">
+        <f t="shared" si="148"/>
+        <v>0.1</v>
+      </c>
+      <c r="R49" s="2">
+        <f t="shared" si="149"/>
+        <v>0.49999999999999994</v>
+      </c>
+      <c r="S49" s="2">
+        <v>0</v>
+      </c>
+      <c r="T49" s="2">
+        <f t="shared" si="150"/>
+        <v>0.3</v>
+      </c>
+      <c r="U49" s="2">
+        <f t="shared" si="145"/>
+        <v>0.7</v>
+      </c>
+      <c r="V49" s="2">
+        <f t="shared" si="151"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="AF49" s="2">
         <v>0.4</v>
@@ -6613,7 +7099,37 @@
     </row>
     <row r="50" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="O50" s="2">
+        <v>6.7</v>
+      </c>
+      <c r="P50" s="2">
+        <f t="shared" si="147"/>
+        <v>3.8999999999999995</v>
+      </c>
+      <c r="Q50" s="2">
+        <f t="shared" si="148"/>
+        <v>-2.5999999999999996</v>
+      </c>
+      <c r="R50" s="2">
+        <f t="shared" si="149"/>
+        <v>-0.20000000000000018</v>
+      </c>
+      <c r="S50" s="2">
+        <v>-4.7</v>
+      </c>
+      <c r="T50" s="2">
+        <f t="shared" si="150"/>
+        <v>10.8</v>
+      </c>
+      <c r="U50" s="2">
+        <f t="shared" si="145"/>
+        <v>2.5</v>
+      </c>
+      <c r="V50" s="2">
+        <f t="shared" si="151"/>
+        <v>-0.19999999999999929</v>
       </c>
       <c r="AF50" s="2">
         <v>-3.8</v>
@@ -6660,7 +7176,37 @@
     </row>
     <row r="51" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="O51" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="P51" s="2">
+        <f t="shared" si="147"/>
+        <v>-15.799999999999999</v>
+      </c>
+      <c r="Q51" s="2">
+        <f t="shared" si="148"/>
+        <v>-43.5</v>
+      </c>
+      <c r="R51" s="2">
+        <f t="shared" si="149"/>
+        <v>14</v>
+      </c>
+      <c r="S51" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="T51" s="2">
+        <f t="shared" si="150"/>
+        <v>-6.8000000000000007</v>
+      </c>
+      <c r="U51" s="2">
+        <f t="shared" si="145"/>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="V51" s="2">
+        <f t="shared" si="151"/>
+        <v>59.8</v>
       </c>
       <c r="AF51" s="2">
         <v>17.2</v>
@@ -6707,7 +7253,37 @@
     </row>
     <row r="52" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
-        <v>79</v>
+        <v>78</v>
+      </c>
+      <c r="O52" s="2">
+        <v>-1.3</v>
+      </c>
+      <c r="P52" s="2">
+        <f t="shared" si="147"/>
+        <v>0.5</v>
+      </c>
+      <c r="Q52" s="2">
+        <f t="shared" si="148"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="R52" s="2">
+        <f t="shared" si="149"/>
+        <v>1.6</v>
+      </c>
+      <c r="S52" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="T52" s="2">
+        <f t="shared" si="150"/>
+        <v>0.4</v>
+      </c>
+      <c r="U52" s="2">
+        <f t="shared" si="145"/>
+        <v>0.4</v>
+      </c>
+      <c r="V52" s="2">
+        <f t="shared" si="151"/>
+        <v>-0.9</v>
       </c>
       <c r="AF52" s="2">
         <v>14.6</v>
@@ -6754,7 +7330,37 @@
     </row>
     <row r="53" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B53" t="s">
-        <v>80</v>
+        <v>79</v>
+      </c>
+      <c r="O53" s="2">
+        <v>-6.6</v>
+      </c>
+      <c r="P53" s="2">
+        <f t="shared" si="147"/>
+        <v>-5.4</v>
+      </c>
+      <c r="Q53" s="2">
+        <f t="shared" si="148"/>
+        <v>3.6999999999999993</v>
+      </c>
+      <c r="R53" s="2">
+        <f t="shared" si="149"/>
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="S53" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="T53" s="2">
+        <f t="shared" si="150"/>
+        <v>-7.5</v>
+      </c>
+      <c r="U53" s="2">
+        <f t="shared" si="145"/>
+        <v>1</v>
+      </c>
+      <c r="V53" s="2">
+        <f t="shared" si="151"/>
+        <v>-4.6999999999999993</v>
       </c>
       <c r="AF53" s="2">
         <v>-4.0999999999999996</v>
@@ -6801,7 +7407,37 @@
     </row>
     <row r="54" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B54" t="s">
-        <v>81</v>
+        <v>80</v>
+      </c>
+      <c r="O54" s="2">
+        <v>-1.2</v>
+      </c>
+      <c r="P54" s="2">
+        <f t="shared" si="147"/>
+        <v>-9</v>
+      </c>
+      <c r="Q54" s="2">
+        <f t="shared" si="148"/>
+        <v>-1.6000000000000014</v>
+      </c>
+      <c r="R54" s="2">
+        <f t="shared" si="149"/>
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="S54" s="2">
+        <v>5.4</v>
+      </c>
+      <c r="T54" s="2">
+        <f t="shared" si="150"/>
+        <v>-11.3</v>
+      </c>
+      <c r="U54" s="2">
+        <f t="shared" si="145"/>
+        <v>-2.2999999999999989</v>
+      </c>
+      <c r="V54" s="2">
+        <f t="shared" si="151"/>
+        <v>-2.5</v>
       </c>
       <c r="AF54" s="2">
         <v>7.5</v>
@@ -6848,7 +7484,37 @@
     </row>
     <row r="55" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B55" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="O55" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="P55" s="2">
+        <f t="shared" si="147"/>
+        <v>-4.6999999999999993</v>
+      </c>
+      <c r="Q55" s="2">
+        <f t="shared" si="148"/>
+        <v>50.9</v>
+      </c>
+      <c r="R55" s="2">
+        <f t="shared" si="149"/>
+        <v>0.30000000000000426</v>
+      </c>
+      <c r="S55" s="2">
+        <v>-4.9000000000000004</v>
+      </c>
+      <c r="T55" s="2">
+        <f t="shared" si="150"/>
+        <v>3.8000000000000003</v>
+      </c>
+      <c r="U55" s="2">
+        <f t="shared" si="145"/>
+        <v>-2.1999999999999997</v>
+      </c>
+      <c r="V55" s="2">
+        <f t="shared" si="151"/>
+        <v>-57.6</v>
       </c>
       <c r="AF55" s="2">
         <v>-20.100000000000001</v>
@@ -6895,7 +7561,37 @@
     </row>
     <row r="56" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B56" t="s">
-        <v>83</v>
+        <v>82</v>
+      </c>
+      <c r="O56" s="2">
+        <v>-1.6</v>
+      </c>
+      <c r="P56" s="2">
+        <f t="shared" si="147"/>
+        <v>-1.2999999999999998</v>
+      </c>
+      <c r="Q56" s="2">
+        <f t="shared" si="148"/>
+        <v>-0.10000000000000009</v>
+      </c>
+      <c r="R56" s="2">
+        <f t="shared" si="149"/>
+        <v>-4.8</v>
+      </c>
+      <c r="S56" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="T56" s="2">
+        <f t="shared" si="150"/>
+        <v>-0.7</v>
+      </c>
+      <c r="U56" s="2">
+        <f t="shared" si="145"/>
+        <v>-1.7999999999999998</v>
+      </c>
+      <c r="V56" s="2">
+        <f t="shared" si="151"/>
+        <v>1.2999999999999998</v>
       </c>
       <c r="AF56" s="2">
         <v>-5.8</v>
@@ -6942,7 +7638,39 @@
     </row>
     <row r="57" spans="2:154" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B57" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
+      </c>
+      <c r="O57" s="8">
+        <f t="shared" ref="O57:V57" si="152">O34+SUM(O35:O56)</f>
+        <v>53.29999999999999</v>
+      </c>
+      <c r="P57" s="8">
+        <f t="shared" si="152"/>
+        <v>14.200000000000045</v>
+      </c>
+      <c r="Q57" s="8">
+        <f t="shared" si="152"/>
+        <v>39.400000000000091</v>
+      </c>
+      <c r="R57" s="8">
+        <f t="shared" si="152"/>
+        <v>18.300000000000018</v>
+      </c>
+      <c r="S57" s="8">
+        <f t="shared" si="152"/>
+        <v>24.400000000000006</v>
+      </c>
+      <c r="T57" s="8">
+        <f t="shared" si="152"/>
+        <v>-4.6999999999999993</v>
+      </c>
+      <c r="U57" s="8">
+        <f t="shared" si="152"/>
+        <v>4.5999999999999979</v>
+      </c>
+      <c r="V57" s="8">
+        <f t="shared" si="152"/>
+        <v>-8.8000000000000291</v>
       </c>
       <c r="AF57" s="8">
         <f>AF34+SUM(AF35:AF56)</f>
@@ -6961,49 +7689,79 @@
         <v>15.499999999999986</v>
       </c>
       <c r="AJ57" s="8">
-        <f t="shared" ref="AJ57:AS57" si="144">AJ34+SUM(AJ35:AJ56)</f>
-        <v>-14.417285000000021</v>
+        <f t="shared" ref="AJ57:AS57" si="153">AJ34+SUM(AJ35:AJ56)</f>
+        <v>-2.3172850000000125</v>
       </c>
       <c r="AK57" s="8">
-        <f t="shared" si="144"/>
-        <v>21.802023999999967</v>
+        <f t="shared" si="153"/>
+        <v>33.702023999999973</v>
       </c>
       <c r="AL57" s="8">
-        <f t="shared" si="144"/>
-        <v>26.157207299999982</v>
+        <f t="shared" si="153"/>
+        <v>37.847207299999994</v>
       </c>
       <c r="AM57" s="8">
-        <f t="shared" si="144"/>
-        <v>31.579363784999963</v>
+        <f t="shared" si="153"/>
+        <v>43.049103784999964</v>
       </c>
       <c r="AN57" s="8">
-        <f t="shared" si="144"/>
-        <v>38.301920288999945</v>
+        <f t="shared" si="153"/>
+        <v>49.540874488999954</v>
       </c>
       <c r="AO57" s="8">
-        <f t="shared" si="144"/>
-        <v>45.715057450282437</v>
+        <f t="shared" si="153"/>
+        <v>56.712428328282449</v>
       </c>
       <c r="AP57" s="8">
-        <f t="shared" si="144"/>
-        <v>54.783295093706215</v>
+        <f t="shared" si="153"/>
+        <v>65.528007359206228</v>
       </c>
       <c r="AQ57" s="8">
-        <f t="shared" si="144"/>
-        <v>63.041158850044638</v>
+        <f t="shared" si="153"/>
+        <v>73.521853270494049</v>
       </c>
       <c r="AR57" s="8">
-        <f t="shared" si="144"/>
-        <v>73.12975734023783</v>
+        <f t="shared" si="153"/>
+        <v>83.334784437832042</v>
       </c>
       <c r="AS57" s="8">
-        <f t="shared" si="144"/>
-        <v>85.296195043748725</v>
+        <f t="shared" si="153"/>
+        <v>95.213608659917966</v>
       </c>
     </row>
     <row r="58" spans="2:154" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+      <c r="O58" s="2">
+        <v>28</v>
+      </c>
+      <c r="P58" s="2">
+        <f>P86-O58</f>
+        <v>17.799999999999997</v>
+      </c>
+      <c r="Q58" s="2">
+        <f t="shared" si="148"/>
+        <v>15.900000000000006</v>
+      </c>
+      <c r="R58" s="2">
+        <f>AH58-Q86</f>
+        <v>13.299999999999997</v>
+      </c>
+      <c r="S58" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="T58" s="2">
+        <f>T86-S58</f>
+        <v>7.2000000000000011</v>
+      </c>
+      <c r="U58" s="2">
+        <f t="shared" ref="U58" si="154">U86-T86</f>
+        <v>5.7999999999999989</v>
+      </c>
+      <c r="V58" s="2">
+        <f>AI58-U86</f>
+        <v>6.4000000000000021</v>
       </c>
       <c r="AF58" s="2">
         <v>103.1</v>
@@ -7026,11 +7784,11 @@
         <v>13.488000000000001</v>
       </c>
       <c r="AL58" s="2">
-        <f t="shared" ref="AL58:AM58" si="145">AK58*1.2</f>
+        <f t="shared" ref="AL58:AM58" si="155">AK58*1.2</f>
         <v>16.185600000000001</v>
       </c>
       <c r="AM58" s="2">
-        <f t="shared" si="145"/>
+        <f t="shared" si="155"/>
         <v>19.422720000000002</v>
       </c>
       <c r="AN58" s="2">
@@ -7042,25 +7800,57 @@
         <v>22.433241600000006</v>
       </c>
       <c r="AP58" s="2">
-        <f t="shared" ref="AP58:AS58" si="146">AO58*1.05</f>
+        <f t="shared" ref="AP58:AS58" si="156">AO58*1.05</f>
         <v>23.554903680000006</v>
       </c>
       <c r="AQ58" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>24.732648864000009</v>
       </c>
       <c r="AR58" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>25.96928130720001</v>
       </c>
       <c r="AS58" s="2">
-        <f t="shared" si="146"/>
+        <f t="shared" si="156"/>
         <v>27.267745372560011</v>
       </c>
     </row>
     <row r="59" spans="2:154" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="O59" s="8">
+        <f t="shared" ref="O59:V59" si="157">O57-O58</f>
+        <v>25.29999999999999</v>
+      </c>
+      <c r="P59" s="8">
+        <f t="shared" si="157"/>
+        <v>-3.5999999999999517</v>
+      </c>
+      <c r="Q59" s="8">
+        <f t="shared" si="157"/>
+        <v>23.500000000000085</v>
+      </c>
+      <c r="R59" s="8">
+        <f t="shared" si="157"/>
+        <v>5.0000000000000213</v>
+      </c>
+      <c r="S59" s="8">
+        <f t="shared" si="157"/>
+        <v>15.700000000000006</v>
+      </c>
+      <c r="T59" s="8">
+        <f t="shared" si="157"/>
+        <v>-11.9</v>
+      </c>
+      <c r="U59" s="8">
+        <f t="shared" si="157"/>
+        <v>-1.2000000000000011</v>
+      </c>
+      <c r="V59" s="8">
+        <f t="shared" si="157"/>
+        <v>-15.200000000000031</v>
       </c>
       <c r="AF59" s="8">
         <f>AF57-AF58</f>
@@ -7079,539 +7869,979 @@
         <v>-12.600000000000016</v>
       </c>
       <c r="AJ59" s="8">
-        <f t="shared" ref="AJ59:AS59" si="147">AJ57-AJ58</f>
-        <v>-25.657285000000023</v>
+        <f t="shared" ref="AJ59:AS59" si="158">AJ57-AJ58</f>
+        <v>-13.557285000000014</v>
       </c>
       <c r="AK59" s="8">
-        <f t="shared" si="147"/>
-        <v>8.3140239999999661</v>
+        <f t="shared" si="158"/>
+        <v>20.214023999999974</v>
       </c>
       <c r="AL59" s="8">
-        <f t="shared" si="147"/>
-        <v>9.971607299999981</v>
+        <f t="shared" si="158"/>
+        <v>21.661607299999993</v>
       </c>
       <c r="AM59" s="8">
-        <f t="shared" si="147"/>
-        <v>12.156643784999961</v>
+        <f t="shared" si="158"/>
+        <v>23.626383784999963</v>
       </c>
       <c r="AN59" s="8">
-        <f t="shared" si="147"/>
-        <v>16.93692828899994</v>
+        <f t="shared" si="158"/>
+        <v>28.17588248899995</v>
       </c>
       <c r="AO59" s="8">
-        <f t="shared" si="147"/>
-        <v>23.281815850282431</v>
+        <f t="shared" si="158"/>
+        <v>34.27918672828244</v>
       </c>
       <c r="AP59" s="8">
-        <f t="shared" si="147"/>
-        <v>31.228391413706209</v>
+        <f t="shared" si="158"/>
+        <v>41.973103679206218</v>
       </c>
       <c r="AQ59" s="8">
-        <f t="shared" si="147"/>
-        <v>38.308509986044626</v>
+        <f t="shared" si="158"/>
+        <v>48.789204406494036</v>
       </c>
       <c r="AR59" s="8">
-        <f t="shared" si="147"/>
-        <v>47.160476033037824</v>
+        <f t="shared" si="158"/>
+        <v>57.365503130632035</v>
       </c>
       <c r="AS59" s="8">
-        <f t="shared" si="147"/>
-        <v>58.02844967118871</v>
+        <f t="shared" si="158"/>
+        <v>67.945863287357952</v>
       </c>
       <c r="AT59" s="1">
         <f>AS59*(1+$AW$25)</f>
-        <v>57.44816517447682</v>
+        <v>67.266404654484376</v>
       </c>
       <c r="AU59" s="1">
-        <f t="shared" ref="AU59:DF59" si="148">AT59*(1+$AW$25)</f>
-        <v>56.873683522732051</v>
+        <f t="shared" ref="AU59:DF59" si="159">AT59*(1+$AW$25)</f>
+        <v>66.593740607939537</v>
       </c>
       <c r="AV59" s="1">
-        <f t="shared" si="148"/>
-        <v>56.304946687504732</v>
+        <f t="shared" si="159"/>
+        <v>65.927803201860144</v>
       </c>
       <c r="AW59" s="1">
-        <f t="shared" si="148"/>
-        <v>55.741897220629681</v>
+        <f t="shared" si="159"/>
+        <v>65.268525169841539</v>
       </c>
       <c r="AX59" s="1">
-        <f t="shared" si="148"/>
-        <v>55.184478248423382</v>
+        <f t="shared" si="159"/>
+        <v>64.615839918143124</v>
       </c>
       <c r="AY59" s="1">
-        <f t="shared" si="148"/>
-        <v>54.632633465939151</v>
+        <f t="shared" si="159"/>
+        <v>63.969681518961693</v>
       </c>
       <c r="AZ59" s="1">
-        <f t="shared" si="148"/>
-        <v>54.08630713127976</v>
+        <f t="shared" si="159"/>
+        <v>63.329984703772077</v>
       </c>
       <c r="BA59" s="1">
-        <f t="shared" si="148"/>
-        <v>53.545444059966961</v>
+        <f t="shared" si="159"/>
+        <v>62.696684856734358</v>
       </c>
       <c r="BB59" s="1">
-        <f t="shared" si="148"/>
-        <v>53.009989619367289</v>
+        <f t="shared" si="159"/>
+        <v>62.069718008167015</v>
       </c>
       <c r="BC59" s="1">
-        <f t="shared" si="148"/>
-        <v>52.479889723173613</v>
+        <f t="shared" si="159"/>
+        <v>61.449020828085345</v>
       </c>
       <c r="BD59" s="1">
-        <f t="shared" si="148"/>
-        <v>51.955090825941873</v>
+        <f t="shared" si="159"/>
+        <v>60.83453061980449</v>
       </c>
       <c r="BE59" s="1">
-        <f t="shared" si="148"/>
-        <v>51.435539917682455</v>
+        <f t="shared" si="159"/>
+        <v>60.226185313606443</v>
       </c>
       <c r="BF59" s="1">
-        <f t="shared" si="148"/>
-        <v>50.921184518505633</v>
+        <f t="shared" si="159"/>
+        <v>59.62392346047038</v>
       </c>
       <c r="BG59" s="1">
-        <f t="shared" si="148"/>
-        <v>50.411972673320577</v>
+        <f t="shared" si="159"/>
+        <v>59.027684225865677</v>
       </c>
       <c r="BH59" s="1">
-        <f t="shared" si="148"/>
-        <v>49.907852946587369</v>
+        <f t="shared" si="159"/>
+        <v>58.437407383607017</v>
       </c>
       <c r="BI59" s="1">
-        <f t="shared" si="148"/>
-        <v>49.408774417121492</v>
+        <f t="shared" si="159"/>
+        <v>57.853033309770943</v>
       </c>
       <c r="BJ59" s="1">
-        <f t="shared" si="148"/>
-        <v>48.914686672950275</v>
+        <f t="shared" si="159"/>
+        <v>57.274502976673233</v>
       </c>
       <c r="BK59" s="1">
-        <f t="shared" si="148"/>
-        <v>48.425539806220769</v>
+        <f t="shared" si="159"/>
+        <v>56.701757946906497</v>
       </c>
       <c r="BL59" s="1">
-        <f t="shared" si="148"/>
-        <v>47.941284408158559</v>
+        <f t="shared" si="159"/>
+        <v>56.134740367437431</v>
       </c>
       <c r="BM59" s="1">
-        <f t="shared" si="148"/>
-        <v>47.461871564076972</v>
+        <f t="shared" si="159"/>
+        <v>55.573392963763055</v>
       </c>
       <c r="BN59" s="1">
-        <f t="shared" si="148"/>
-        <v>46.987252848436199</v>
+        <f t="shared" si="159"/>
+        <v>55.017659034125423</v>
       </c>
       <c r="BO59" s="1">
-        <f t="shared" si="148"/>
-        <v>46.51738031995184</v>
+        <f t="shared" si="159"/>
+        <v>54.467482443784171</v>
       </c>
       <c r="BP59" s="1">
-        <f t="shared" si="148"/>
-        <v>46.052206516752321</v>
+        <f t="shared" si="159"/>
+        <v>53.922807619346329</v>
       </c>
       <c r="BQ59" s="1">
-        <f t="shared" si="148"/>
-        <v>45.591684451584797</v>
+        <f t="shared" si="159"/>
+        <v>53.383579543152862</v>
       </c>
       <c r="BR59" s="1">
-        <f t="shared" si="148"/>
-        <v>45.135767607068949</v>
+        <f t="shared" si="159"/>
+        <v>52.849743747721334</v>
       </c>
       <c r="BS59" s="1">
-        <f t="shared" si="148"/>
-        <v>44.684409930998257</v>
+        <f t="shared" si="159"/>
+        <v>52.321246310244121</v>
       </c>
       <c r="BT59" s="1">
-        <f t="shared" si="148"/>
-        <v>44.237565831688272</v>
+        <f t="shared" si="159"/>
+        <v>51.798033847141681</v>
       </c>
       <c r="BU59" s="1">
-        <f t="shared" si="148"/>
-        <v>43.795190173371388</v>
+        <f t="shared" si="159"/>
+        <v>51.280053508670264</v>
       </c>
       <c r="BV59" s="1">
-        <f t="shared" si="148"/>
-        <v>43.357238271637677</v>
+        <f t="shared" si="159"/>
+        <v>50.76725297358356</v>
       </c>
       <c r="BW59" s="1">
-        <f t="shared" si="148"/>
-        <v>42.923665888921299</v>
+        <f t="shared" si="159"/>
+        <v>50.259580443847724</v>
       </c>
       <c r="BX59" s="1">
-        <f t="shared" si="148"/>
-        <v>42.494429230032083</v>
+        <f t="shared" si="159"/>
+        <v>49.756984639409247</v>
       </c>
       <c r="BY59" s="1">
-        <f t="shared" si="148"/>
-        <v>42.069484937731758</v>
+        <f t="shared" si="159"/>
+        <v>49.259414793015154</v>
       </c>
       <c r="BZ59" s="1">
-        <f t="shared" si="148"/>
-        <v>41.648790088354438</v>
+        <f t="shared" si="159"/>
+        <v>48.766820645085005</v>
       </c>
       <c r="CA59" s="1">
-        <f t="shared" si="148"/>
-        <v>41.232302187470893</v>
+        <f t="shared" si="159"/>
+        <v>48.279152438634156</v>
       </c>
       <c r="CB59" s="1">
-        <f t="shared" si="148"/>
-        <v>40.81997916559618</v>
+        <f t="shared" si="159"/>
+        <v>47.796360914247813</v>
       </c>
       <c r="CC59" s="1">
-        <f t="shared" si="148"/>
-        <v>40.41177937394022</v>
+        <f t="shared" si="159"/>
+        <v>47.318397305105336</v>
       </c>
       <c r="CD59" s="1">
-        <f t="shared" si="148"/>
-        <v>40.007661580200818</v>
+        <f t="shared" si="159"/>
+        <v>46.845213332054279</v>
       </c>
       <c r="CE59" s="1">
-        <f t="shared" si="148"/>
-        <v>39.607584964398811</v>
+        <f t="shared" si="159"/>
+        <v>46.376761198733732</v>
       </c>
       <c r="CF59" s="1">
-        <f t="shared" si="148"/>
-        <v>39.211509114754826</v>
+        <f t="shared" si="159"/>
+        <v>45.912993586746396</v>
       </c>
       <c r="CG59" s="1">
-        <f t="shared" si="148"/>
-        <v>38.819394023607281</v>
+        <f t="shared" si="159"/>
+        <v>45.45386365087893</v>
       </c>
       <c r="CH59" s="1">
-        <f t="shared" si="148"/>
-        <v>38.431200083371209</v>
+        <f t="shared" si="159"/>
+        <v>44.999325014370143</v>
       </c>
       <c r="CI59" s="1">
-        <f t="shared" si="148"/>
-        <v>38.0468880825375</v>
+        <f t="shared" si="159"/>
+        <v>44.549331764226444</v>
       </c>
       <c r="CJ59" s="1">
-        <f t="shared" si="148"/>
-        <v>37.666419201712124</v>
+        <f t="shared" si="159"/>
+        <v>44.103838446584177</v>
       </c>
       <c r="CK59" s="1">
-        <f t="shared" si="148"/>
-        <v>37.289755009695</v>
+        <f t="shared" si="159"/>
+        <v>43.662800062118336</v>
       </c>
       <c r="CL59" s="1">
-        <f t="shared" si="148"/>
-        <v>36.916857459598049</v>
+        <f t="shared" si="159"/>
+        <v>43.226172061497152</v>
       </c>
       <c r="CM59" s="1">
-        <f t="shared" si="148"/>
-        <v>36.547688885002067</v>
+        <f t="shared" si="159"/>
+        <v>42.793910340882178</v>
       </c>
       <c r="CN59" s="1">
-        <f t="shared" si="148"/>
-        <v>36.182211996152049</v>
+        <f t="shared" si="159"/>
+        <v>42.365971237473353</v>
       </c>
       <c r="CO59" s="1">
-        <f t="shared" si="148"/>
-        <v>35.820389876190525</v>
+        <f t="shared" si="159"/>
+        <v>41.942311525098617</v>
       </c>
       <c r="CP59" s="1">
-        <f t="shared" si="148"/>
-        <v>35.462185977428618</v>
+        <f t="shared" si="159"/>
+        <v>41.522888409847631</v>
       </c>
       <c r="CQ59" s="1">
-        <f t="shared" si="148"/>
-        <v>35.107564117654334</v>
+        <f t="shared" si="159"/>
+        <v>41.107659525749156</v>
       </c>
       <c r="CR59" s="1">
-        <f t="shared" si="148"/>
-        <v>34.756488476477791</v>
+        <f t="shared" si="159"/>
+        <v>40.696582930491665</v>
       </c>
       <c r="CS59" s="1">
-        <f t="shared" si="148"/>
-        <v>34.408923591713013</v>
+        <f t="shared" si="159"/>
+        <v>40.289617101186749</v>
       </c>
       <c r="CT59" s="1">
-        <f t="shared" si="148"/>
-        <v>34.064834355795881</v>
+        <f t="shared" si="159"/>
+        <v>39.886720930174882</v>
       </c>
       <c r="CU59" s="1">
-        <f t="shared" si="148"/>
-        <v>33.724186012237922</v>
+        <f t="shared" si="159"/>
+        <v>39.487853720873133</v>
       </c>
       <c r="CV59" s="1">
-        <f t="shared" si="148"/>
-        <v>33.386944152115539</v>
+        <f t="shared" si="159"/>
+        <v>39.0929751836644</v>
       </c>
       <c r="CW59" s="1">
-        <f t="shared" si="148"/>
-        <v>33.05307471059438</v>
+        <f t="shared" si="159"/>
+        <v>38.702045431827756</v>
       </c>
       <c r="CX59" s="1">
-        <f t="shared" si="148"/>
-        <v>32.722543963488434</v>
+        <f t="shared" si="159"/>
+        <v>38.315024977509481</v>
       </c>
       <c r="CY59" s="1">
-        <f t="shared" si="148"/>
-        <v>32.395318523853547</v>
+        <f t="shared" si="159"/>
+        <v>37.931874727734389</v>
       </c>
       <c r="CZ59" s="1">
-        <f t="shared" si="148"/>
-        <v>32.07136533861501</v>
+        <f t="shared" si="159"/>
+        <v>37.552555980457043</v>
       </c>
       <c r="DA59" s="1">
-        <f t="shared" si="148"/>
-        <v>31.75065168522886</v>
+        <f t="shared" si="159"/>
+        <v>37.177030420652471</v>
       </c>
       <c r="DB59" s="1">
-        <f t="shared" si="148"/>
-        <v>31.433145168376569</v>
+        <f t="shared" si="159"/>
+        <v>36.805260116445943</v>
       </c>
       <c r="DC59" s="1">
-        <f t="shared" si="148"/>
-        <v>31.118813716692802</v>
+        <f t="shared" si="159"/>
+        <v>36.437207515281486</v>
       </c>
       <c r="DD59" s="1">
-        <f t="shared" si="148"/>
-        <v>30.807625579525872</v>
+        <f t="shared" si="159"/>
+        <v>36.072835440128671</v>
       </c>
       <c r="DE59" s="1">
-        <f t="shared" si="148"/>
-        <v>30.499549323730612</v>
+        <f t="shared" si="159"/>
+        <v>35.712107085727382</v>
       </c>
       <c r="DF59" s="1">
-        <f t="shared" si="148"/>
-        <v>30.194553830493305</v>
+        <f t="shared" si="159"/>
+        <v>35.354986014870107</v>
       </c>
       <c r="DG59" s="1">
-        <f t="shared" ref="DG59:EX59" si="149">DF59*(1+$AW$25)</f>
-        <v>29.89260829218837</v>
+        <f t="shared" ref="DG59:EX59" si="160">DF59*(1+$AW$25)</f>
+        <v>35.001436154721404</v>
       </c>
       <c r="DH59" s="1">
-        <f t="shared" si="149"/>
-        <v>29.593682209266486</v>
+        <f t="shared" si="160"/>
+        <v>34.651421793174187</v>
       </c>
       <c r="DI59" s="1">
-        <f t="shared" si="149"/>
-        <v>29.297745387173823</v>
+        <f t="shared" si="160"/>
+        <v>34.304907575242446</v>
       </c>
       <c r="DJ59" s="1">
-        <f t="shared" si="149"/>
-        <v>29.004767933302084</v>
+        <f t="shared" si="160"/>
+        <v>33.96185849949002</v>
       </c>
       <c r="DK59" s="1">
-        <f t="shared" si="149"/>
-        <v>28.714720253969062</v>
+        <f t="shared" si="160"/>
+        <v>33.622239914495118</v>
       </c>
       <c r="DL59" s="1">
-        <f t="shared" si="149"/>
-        <v>28.42757305142937</v>
+        <f t="shared" si="160"/>
+        <v>33.286017515350167</v>
       </c>
       <c r="DM59" s="1">
-        <f t="shared" si="149"/>
-        <v>28.143297320915075</v>
+        <f t="shared" si="160"/>
+        <v>32.953157340196668</v>
       </c>
       <c r="DN59" s="1">
-        <f t="shared" si="149"/>
-        <v>27.861864347705925</v>
+        <f t="shared" si="160"/>
+        <v>32.623625766794703</v>
       </c>
       <c r="DO59" s="1">
-        <f t="shared" si="149"/>
-        <v>27.583245704228865</v>
+        <f t="shared" si="160"/>
+        <v>32.297389509126752</v>
       </c>
       <c r="DP59" s="1">
-        <f t="shared" si="149"/>
-        <v>27.307413247186577</v>
+        <f t="shared" si="160"/>
+        <v>31.974415614035486</v>
       </c>
       <c r="DQ59" s="1">
-        <f t="shared" si="149"/>
-        <v>27.034339114714712</v>
+        <f t="shared" si="160"/>
+        <v>31.65467145789513</v>
       </c>
       <c r="DR59" s="1">
-        <f t="shared" si="149"/>
-        <v>26.763995723567565</v>
+        <f t="shared" si="160"/>
+        <v>31.338124743316179</v>
       </c>
       <c r="DS59" s="1">
-        <f t="shared" si="149"/>
-        <v>26.496355766331888</v>
+        <f t="shared" si="160"/>
+        <v>31.024743495883015</v>
       </c>
       <c r="DT59" s="1">
-        <f t="shared" si="149"/>
-        <v>26.23139220866857</v>
+        <f t="shared" si="160"/>
+        <v>30.714496060924183</v>
       </c>
       <c r="DU59" s="1">
-        <f t="shared" si="149"/>
-        <v>25.969078286581883</v>
+        <f t="shared" si="160"/>
+        <v>30.407351100314941</v>
       </c>
       <c r="DV59" s="1">
-        <f t="shared" si="149"/>
-        <v>25.709387503716066</v>
+        <f t="shared" si="160"/>
+        <v>30.103277589311791</v>
       </c>
       <c r="DW59" s="1">
-        <f t="shared" si="149"/>
-        <v>25.452293628678905</v>
+        <f t="shared" si="160"/>
+        <v>29.802244813418671</v>
       </c>
       <c r="DX59" s="1">
-        <f t="shared" si="149"/>
-        <v>25.197770692392115</v>
+        <f t="shared" si="160"/>
+        <v>29.504222365284484</v>
       </c>
       <c r="DY59" s="1">
-        <f t="shared" si="149"/>
-        <v>24.945792985468195</v>
+        <f t="shared" si="160"/>
+        <v>29.209180141631638</v>
       </c>
       <c r="DZ59" s="1">
-        <f t="shared" si="149"/>
-        <v>24.696335055613513</v>
+        <f t="shared" si="160"/>
+        <v>28.917088340215322</v>
       </c>
       <c r="EA59" s="1">
-        <f t="shared" si="149"/>
-        <v>24.449371705057377</v>
+        <f t="shared" si="160"/>
+        <v>28.627917456813169</v>
       </c>
       <c r="EB59" s="1">
-        <f t="shared" si="149"/>
-        <v>24.204877988006803</v>
+        <f t="shared" si="160"/>
+        <v>28.341638282245036</v>
       </c>
       <c r="EC59" s="1">
-        <f t="shared" si="149"/>
-        <v>23.962829208126735</v>
+        <f t="shared" si="160"/>
+        <v>28.058221899422584</v>
       </c>
       <c r="ED59" s="1">
-        <f t="shared" si="149"/>
-        <v>23.723200916045467</v>
+        <f t="shared" si="160"/>
+        <v>27.777639680428358</v>
       </c>
       <c r="EE59" s="1">
-        <f t="shared" si="149"/>
-        <v>23.485968906885013</v>
+        <f t="shared" si="160"/>
+        <v>27.499863283624073</v>
       </c>
       <c r="EF59" s="1">
-        <f t="shared" si="149"/>
-        <v>23.251109217816161</v>
+        <f t="shared" si="160"/>
+        <v>27.224864650787833</v>
       </c>
       <c r="EG59" s="1">
-        <f t="shared" si="149"/>
-        <v>23.018598125638</v>
+        <f t="shared" si="160"/>
+        <v>26.952616004279953</v>
       </c>
       <c r="EH59" s="1">
-        <f t="shared" si="149"/>
-        <v>22.788412144381621</v>
+        <f t="shared" si="160"/>
+        <v>26.683089844237152</v>
       </c>
       <c r="EI59" s="1">
-        <f t="shared" si="149"/>
-        <v>22.560528022937802</v>
+        <f t="shared" si="160"/>
+        <v>26.41625894579478</v>
       </c>
       <c r="EJ59" s="1">
-        <f t="shared" si="149"/>
-        <v>22.334922742708425</v>
+        <f t="shared" si="160"/>
+        <v>26.15209635633683</v>
       </c>
       <c r="EK59" s="1">
-        <f t="shared" si="149"/>
-        <v>22.111573515281339</v>
+        <f t="shared" si="160"/>
+        <v>25.890575392773464</v>
       </c>
       <c r="EL59" s="1">
-        <f t="shared" si="149"/>
-        <v>21.890457780128525</v>
+        <f t="shared" si="160"/>
+        <v>25.631669638845729</v>
       </c>
       <c r="EM59" s="1">
-        <f t="shared" si="149"/>
-        <v>21.671553202327239</v>
+        <f t="shared" si="160"/>
+        <v>25.375352942457273</v>
       </c>
       <c r="EN59" s="1">
-        <f t="shared" si="149"/>
-        <v>21.454837670303966</v>
+        <f t="shared" si="160"/>
+        <v>25.121599413032701</v>
       </c>
       <c r="EO59" s="1">
-        <f t="shared" si="149"/>
-        <v>21.240289293600927</v>
+        <f t="shared" si="160"/>
+        <v>24.870383418902374</v>
       </c>
       <c r="EP59" s="1">
-        <f t="shared" si="149"/>
-        <v>21.027886400664919</v>
+        <f t="shared" si="160"/>
+        <v>24.621679584713352</v>
       </c>
       <c r="EQ59" s="1">
-        <f t="shared" si="149"/>
-        <v>20.817607536658269</v>
+        <f t="shared" si="160"/>
+        <v>24.375462788866219</v>
       </c>
       <c r="ER59" s="1">
-        <f t="shared" si="149"/>
-        <v>20.609431461291685</v>
+        <f t="shared" si="160"/>
+        <v>24.131708160977556</v>
       </c>
       <c r="ES59" s="1">
-        <f t="shared" si="149"/>
-        <v>20.403337146678769</v>
+        <f t="shared" si="160"/>
+        <v>23.890391079367781</v>
       </c>
       <c r="ET59" s="1">
-        <f t="shared" si="149"/>
-        <v>20.19930377521198</v>
+        <f t="shared" si="160"/>
+        <v>23.651487168574103</v>
       </c>
       <c r="EU59" s="1">
-        <f t="shared" si="149"/>
-        <v>19.997310737459859</v>
+        <f t="shared" si="160"/>
+        <v>23.414972296888362</v>
       </c>
       <c r="EV59" s="1">
-        <f t="shared" si="149"/>
-        <v>19.797337630085259</v>
+        <f t="shared" si="160"/>
+        <v>23.180822573919478</v>
       </c>
       <c r="EW59" s="1">
-        <f t="shared" si="149"/>
-        <v>19.599364253784408</v>
+        <f t="shared" si="160"/>
+        <v>22.949014348180285</v>
       </c>
       <c r="EX59" s="1">
-        <f t="shared" si="149"/>
-        <v>19.403370611246565</v>
+        <f t="shared" si="160"/>
+        <v>22.71952420469848</v>
+      </c>
+    </row>
+    <row r="62" spans="2:154" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>101</v>
+      </c>
+      <c r="P62" s="8">
+        <f>O18+P18</f>
+        <v>-618.30000000000007</v>
+      </c>
+      <c r="Q62" s="8">
+        <f>Q18+P18+O18</f>
+        <v>-830.90000000000009</v>
+      </c>
+      <c r="T62" s="8">
+        <f>S18+T18</f>
+        <v>-53.1</v>
+      </c>
+      <c r="U62" s="8">
+        <f>U18+T18+S18</f>
+        <v>-70.600000000000009</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>50</v>
+      </c>
+      <c r="AW62" s="2">
+        <f>NPV(AW26,AJ59:EX59)</f>
+        <v>315.65231896284138</v>
       </c>
     </row>
     <row r="63" spans="2:154" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>62</v>
+      </c>
+      <c r="P63" s="2">
+        <v>47.3</v>
+      </c>
+      <c r="Q63" s="2">
+        <v>69.3</v>
+      </c>
+      <c r="T63" s="2">
+        <v>19.2</v>
+      </c>
+      <c r="U63" s="2">
+        <v>25.1</v>
+      </c>
       <c r="AV63" t="s">
-        <v>86</v>
+        <v>51</v>
       </c>
       <c r="AW63" s="2">
-        <f>NPV(AW26,AI59:EX59)</f>
-        <v>191.89270014528663</v>
+        <f>Main!D8</f>
+        <v>31.40000000000002</v>
       </c>
     </row>
     <row r="64" spans="2:154" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>63</v>
+      </c>
+      <c r="P64" s="2">
+        <v>39.4</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>59</v>
+      </c>
+      <c r="T64" s="2">
+        <v>48.3</v>
+      </c>
+      <c r="U64" s="2">
+        <v>63.6</v>
+      </c>
       <c r="AV64" t="s">
         <v>52</v>
       </c>
       <c r="AW64" s="2">
-        <f>Main!D8</f>
-        <v>31.40000000000002</v>
-      </c>
-    </row>
-    <row r="65" spans="48:49" x14ac:dyDescent="0.3">
+        <f>AW62+AW63</f>
+        <v>347.05231896284141</v>
+      </c>
+    </row>
+    <row r="65" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>64</v>
+      </c>
+      <c r="P65" s="2">
+        <v>141</v>
+      </c>
+      <c r="Q65" s="2">
+        <v>141.1</v>
+      </c>
+      <c r="T65" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="U65" s="2">
+        <v>0.3</v>
+      </c>
       <c r="AV65" t="s">
         <v>53</v>
       </c>
-      <c r="AW65" s="2">
-        <f>AW63+AW64</f>
-        <v>223.29270014528663</v>
-      </c>
-    </row>
-    <row r="66" spans="48:49" x14ac:dyDescent="0.3">
+      <c r="AW65" s="3">
+        <f>AW62/Model!AS19</f>
+        <v>2.885304560903486</v>
+      </c>
+    </row>
+    <row r="66" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>65</v>
+      </c>
+      <c r="P66" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="2">
+        <v>0</v>
+      </c>
+      <c r="T66" s="2">
+        <v>-7.4</v>
+      </c>
+      <c r="U66" s="2">
+        <v>-7.4</v>
+      </c>
       <c r="AV66" t="s">
         <v>54</v>
       </c>
       <c r="AW66" s="3">
-        <f>AW65/Model!AS19</f>
-        <v>2.0410667289331501</v>
-      </c>
-    </row>
-    <row r="67" spans="48:49" x14ac:dyDescent="0.3">
-      <c r="AV67" t="s">
-        <v>55</v>
-      </c>
-      <c r="AW67" s="3">
         <f>Main!D3</f>
         <v>0.7</v>
       </c>
     </row>
-    <row r="68" spans="48:49" x14ac:dyDescent="0.3">
-      <c r="AV68" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AW68" s="10">
-        <f>AW66/AW67-1</f>
-        <v>1.9158096127616431</v>
-      </c>
-    </row>
-    <row r="69" spans="48:49" x14ac:dyDescent="0.3">
-      <c r="AW69" s="6" t="s">
-        <v>94</v>
+    <row r="67" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>66</v>
+      </c>
+      <c r="P67" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="T67" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="U67" s="2">
+        <v>0</v>
+      </c>
+      <c r="AV67" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AW67" s="10">
+        <f>AW65/AW66-1</f>
+        <v>3.1218636584335515</v>
+      </c>
+    </row>
+    <row r="68" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>67</v>
+      </c>
+      <c r="P68" s="2">
+        <v>481.5</v>
+      </c>
+      <c r="Q68" s="2">
+        <v>677.2</v>
+      </c>
+      <c r="T68" s="2">
+        <v>2</v>
+      </c>
+      <c r="U68" s="2">
+        <v>2</v>
+      </c>
+      <c r="AW68" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>68</v>
+      </c>
+      <c r="P69" s="2">
+        <v>1.7</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>2</v>
+      </c>
+      <c r="T69" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="U69" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="70" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>69</v>
+      </c>
+      <c r="P70" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="Q70" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="T70" s="2">
+        <v>0.4</v>
+      </c>
+      <c r="U70" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>70</v>
+      </c>
+      <c r="P71" s="2">
+        <v>3.1</v>
+      </c>
+      <c r="Q71" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="T71" s="2">
+        <v>2</v>
+      </c>
+      <c r="U71" s="2">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="72" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>71</v>
+      </c>
+      <c r="P72" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>0</v>
+      </c>
+      <c r="T72" s="2">
+        <v>0</v>
+      </c>
+      <c r="U72" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>72</v>
+      </c>
+      <c r="P73" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="2">
+        <v>0</v>
+      </c>
+      <c r="T73" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="U73" s="2">
+        <v>-0.8</v>
+      </c>
+    </row>
+    <row r="74" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>73</v>
+      </c>
+      <c r="P74" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="Q74" s="2">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="T74" s="2">
+        <v>3</v>
+      </c>
+      <c r="U74" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B75" t="s">
+        <v>74</v>
+      </c>
+      <c r="P75" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="2">
+        <v>0</v>
+      </c>
+      <c r="T75" s="2">
+        <v>0</v>
+      </c>
+      <c r="U75" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B76" t="s">
+        <v>67</v>
+      </c>
+      <c r="P76" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>0</v>
+      </c>
+      <c r="T76" s="2">
+        <v>6</v>
+      </c>
+      <c r="U76" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>75</v>
+      </c>
+      <c r="P77" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="Q77" s="2">
+        <v>0.2</v>
+      </c>
+      <c r="T77" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="U77" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>76</v>
+      </c>
+      <c r="P78" s="2">
+        <v>10.6</v>
+      </c>
+      <c r="Q78" s="2">
+        <v>8</v>
+      </c>
+      <c r="T78" s="2">
+        <v>6.1</v>
+      </c>
+      <c r="U78" s="2">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="79" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>77</v>
+      </c>
+      <c r="P79" s="2">
+        <v>-12.2</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>-55.7</v>
+      </c>
+      <c r="T79" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="U79" s="2">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="80" spans="2:49" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>78</v>
+      </c>
+      <c r="P80" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="Q80" s="2">
+        <v>-0.5</v>
+      </c>
+      <c r="T80" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="U80" s="2">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="81" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>79</v>
+      </c>
+      <c r="P81" s="2">
+        <v>-12</v>
+      </c>
+      <c r="Q81" s="2">
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="T81" s="2">
+        <v>-6</v>
+      </c>
+      <c r="U81" s="2">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="82" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>80</v>
+      </c>
+      <c r="P82" s="2">
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>-11.8</v>
+      </c>
+      <c r="T82" s="2">
+        <v>-5.9</v>
+      </c>
+      <c r="U82" s="2">
+        <v>-8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="83" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>81</v>
+      </c>
+      <c r="P83" s="2">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="Q83" s="2">
+        <v>46.8</v>
+      </c>
+      <c r="T83" s="2">
+        <v>-1.1000000000000001</v>
+      </c>
+      <c r="U83" s="2">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="84" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>82</v>
+      </c>
+      <c r="P84" s="2">
+        <v>-2.9</v>
+      </c>
+      <c r="Q84" s="2">
+        <v>-3</v>
+      </c>
+      <c r="T84" s="2">
+        <v>-1.5</v>
+      </c>
+      <c r="U84" s="2">
+        <v>-3.3</v>
+      </c>
+    </row>
+    <row r="85" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B85" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="P85" s="8">
+        <f>P62+SUM(P63:P84)</f>
+        <v>67.500000000000114</v>
+      </c>
+      <c r="Q85" s="8">
+        <f>Q62+SUM(Q63:Q84)</f>
+        <v>106.90000000000009</v>
+      </c>
+      <c r="T85" s="8">
+        <f>T62+SUM(T63:T84)</f>
+        <v>19.699999999999982</v>
+      </c>
+      <c r="U85" s="8">
+        <f>U62+SUM(U63:U84)</f>
+        <v>24.299999999999983</v>
+      </c>
+    </row>
+    <row r="86" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>68</v>
+      </c>
+      <c r="P86" s="2">
+        <v>45.8</v>
+      </c>
+      <c r="Q86" s="2">
+        <v>61.7</v>
+      </c>
+      <c r="T86" s="2">
+        <v>15.9</v>
+      </c>
+      <c r="U86" s="2">
+        <v>21.7</v>
+      </c>
+    </row>
+    <row r="87" spans="2:21" x14ac:dyDescent="0.3">
+      <c r="B87" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P87" s="8">
+        <f>P85-P86</f>
+        <v>21.700000000000117</v>
+      </c>
+      <c r="Q87" s="8">
+        <f>Q85-Q86</f>
+        <v>45.200000000000088</v>
+      </c>
+      <c r="T87" s="8">
+        <f>T85-T86</f>
+        <v>3.7999999999999812</v>
+      </c>
+      <c r="U87" s="8">
+        <f>U85-U86</f>
+        <v>2.5999999999999837</v>
       </c>
     </row>
   </sheetData>
